--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -22,9 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch</t>
+          <t>Nazarova Munisa</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -13722,80 +13722,64 @@
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Hikmatullo qizi</t>
+          <t>Erkin qizi</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
-        </is>
-      </c>
-      <c r="J120" s="5" t="inlineStr"/>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>AE7082532</t>
+          <t>AE7685867</t>
         </is>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>60212085680048</t>
+          <t>41205925680015</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="N120" s="5" t="inlineStr">
         <is>
-          <t>02.12.2008</t>
+          <t>12.05.1992</t>
         </is>
       </c>
       <c r="O120" s="4" t="inlineStr"/>
-      <c r="P120" s="2" t="inlineStr">
-        <is>
-          <t>UM 03727760</t>
-        </is>
-      </c>
+      <c r="P120" s="2" t="inlineStr"/>
       <c r="Q120" s="4" t="inlineStr"/>
-      <c r="R120" s="4" t="inlineStr">
-        <is>
-          <t>1-maktab</t>
-        </is>
-      </c>
-      <c r="S120" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T120" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U120" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V120" s="4" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W120" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="R120" s="4" t="inlineStr"/>
+      <c r="S120" s="5" t="inlineStr"/>
+      <c r="T120" s="5" t="inlineStr"/>
+      <c r="U120" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V120" s="4" t="inlineStr"/>
+      <c r="W120" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X120" s="7" t="inlineStr">
@@ -13815,74 +13799,66 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam</t>
+          <t>Ne'matova Sevinch</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
+          <t>Hamshiralik ishi</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr"/>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Elyor qizi</t>
+          <t>Hikmatullo qizi</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
-      <c r="J121" s="12" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+        </is>
+      </c>
+      <c r="J121" s="12" t="inlineStr"/>
       <c r="K121" s="9" t="inlineStr">
         <is>
-          <t>AE4817469</t>
+          <t>AE7082532</t>
         </is>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>61809085680096</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
-          <t>18.09.2008</t>
-        </is>
-      </c>
-      <c r="O121" s="11" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+          <t>02.12.2008</t>
+        </is>
+      </c>
+      <c r="O121" s="11" t="inlineStr"/>
       <c r="P121" s="9" t="inlineStr">
         <is>
-          <t>UM 03728575</t>
+          <t>UM 03727760</t>
         </is>
       </c>
       <c r="Q121" s="11" t="inlineStr"/>
       <c r="R121" s="11" t="inlineStr">
         <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>1-maktab</t>
         </is>
       </c>
       <c r="S121" s="12" t="inlineStr">
@@ -13895,15 +13871,19 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U121" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V121" s="11" t="inlineStr"/>
-      <c r="W121" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="U121" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V121" s="11" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W121" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X121" s="7" t="inlineStr">
@@ -13923,7 +13903,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Omonova Charos</t>
+          <t>Normurodova Gulsanam</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -13934,7 +13914,7 @@
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -13944,63 +13924,63 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Elyor qizi</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>AE1338424</t>
+          <t>AE4817469</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>40306985590014</t>
+          <t>61809085680096</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="N122" s="5" t="inlineStr">
         <is>
-          <t>03.06.1998</t>
+          <t>18.09.2008</t>
         </is>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>K 5023908</t>
+          <t>UM 03728575</t>
         </is>
       </c>
       <c r="Q122" s="4" t="inlineStr"/>
       <c r="R122" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S122" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T122" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U122" s="7" t="inlineStr">
@@ -14031,83 +14011,95 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Oripova Sevinch</t>
+          <t>Omonova Charos</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi</t>
+          <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr"/>
-      <c r="F123" s="12" t="inlineStr"/>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>G'olib qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>Oripova Sevinch G'olib qizi</t>
-        </is>
-      </c>
-      <c r="J123" s="12" t="inlineStr"/>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="K123" s="9" t="inlineStr">
         <is>
-          <t>AE3333890</t>
+          <t>AE1338424</t>
         </is>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>62007085680095</t>
+          <t>40306985590014</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>09.07.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="N123" s="12" t="inlineStr">
         <is>
-          <t>20.07.2008</t>
-        </is>
-      </c>
-      <c r="O123" s="11" t="inlineStr"/>
+          <t>03.06.1998</t>
+        </is>
+      </c>
+      <c r="O123" s="11" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="P123" s="9" t="inlineStr">
         <is>
-          <t>UM 03729323</t>
+          <t>K 5023908</t>
         </is>
       </c>
       <c r="Q123" s="11" t="inlineStr"/>
       <c r="R123" s="11" t="inlineStr">
         <is>
-          <t>45-maktab</t>
+          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S123" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T123" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U123" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="U123" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V123" s="11" t="inlineStr"/>
-      <c r="W123" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W123" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X123" s="7" t="inlineStr">
@@ -14127,72 +14119,62 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Ozodova Klara</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="inlineStr"/>
+          <t>Oripova Sevinch</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="inlineStr"/>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="n">
-        <v>46272</v>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Fayzullayevna</t>
+          <t>G'olib qizi</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
-      <c r="J124" s="5" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>Oripova Sevinch G'olib qizi</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>AD6663341</t>
+          <t>AE3333890</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>60803075590140</t>
+          <t>62007085680095</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>01.04.2024</t>
+          <t>09.07.2025</t>
         </is>
       </c>
       <c r="N124" s="5" t="inlineStr">
         <is>
-          <t>08.03.2007</t>
-        </is>
-      </c>
-      <c r="O124" s="4" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>20.07.2008</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr"/>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>UM 03298601</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03729323</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr"/>
       <c r="R124" s="4" t="inlineStr">
         <is>
-          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>45-maktab</t>
         </is>
       </c>
       <c r="S124" s="5" t="inlineStr">
@@ -14202,18 +14184,18 @@
       </c>
       <c r="T124" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U124" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U124" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V124" s="4" t="inlineStr"/>
-      <c r="W124" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W124" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X124" s="7" t="inlineStr">
@@ -14233,78 +14215,72 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z</t>
-        </is>
-      </c>
-      <c r="D125" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Ozodova Klara</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr"/>
       <c r="E125" s="12" t="inlineStr"/>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G125" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="G125" s="18" t="n">
+        <v>46272</v>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Ilyos qizi</t>
+          <t>Fayzullayevna</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="K125" s="9" t="inlineStr">
         <is>
-          <t>AE6043288</t>
+          <t>AD6663341</t>
         </is>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>60511085680024</t>
+          <t>60803075590140</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>01.04.2024</t>
         </is>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
-          <t>05.11.2008</t>
+          <t>08.03.2007</t>
         </is>
       </c>
       <c r="O125" s="11" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="P125" s="9" t="inlineStr">
         <is>
-          <t>UM 03730668</t>
+          <t>UM 03298601</t>
         </is>
       </c>
       <c r="Q125" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
         </is>
       </c>
       <c r="R125" s="11" t="inlineStr">
         <is>
-          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S125" s="12" t="inlineStr">
@@ -14314,7 +14290,7 @@
       </c>
       <c r="T125" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U125" s="7" t="inlineStr">
@@ -14345,7 +14321,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Sharipova Diyora</t>
+          <t>Saidova Dilso'z</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -14356,7 +14332,7 @@
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -14366,57 +14342,57 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Ilyos qizi</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AE6043288</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>60511085680024</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="N126" s="5" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>05.11.2008</t>
         </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>UM 03751494</t>
+          <t>UM 03730668</t>
         </is>
       </c>
       <c r="Q126" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
         </is>
       </c>
       <c r="R126" s="4" t="inlineStr">
         <is>
-          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S126" s="5" t="inlineStr">
@@ -14457,7 +14433,7 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara</t>
+          <t>Sharipova Diyora</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
@@ -14468,7 +14444,7 @@
       <c r="E127" s="12" t="inlineStr"/>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -14478,53 +14454,57 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Ilxom qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="K127" s="9" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
+          <t>23.07.2009</t>
         </is>
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="P127" s="9" t="inlineStr">
         <is>
-          <t>UM 1319051</t>
-        </is>
-      </c>
-      <c r="Q127" s="11" t="inlineStr"/>
+          <t>UM 03751494</t>
+        </is>
+      </c>
+      <c r="Q127" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+        </is>
+      </c>
       <c r="R127" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
+          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S127" s="12" t="inlineStr">
@@ -14534,7 +14514,7 @@
       </c>
       <c r="T127" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U127" s="7" t="inlineStr">
@@ -14545,7 +14525,7 @@
       <c r="V127" s="11" t="inlineStr"/>
       <c r="W127" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X127" s="7" t="inlineStr">
@@ -14565,74 +14545,74 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr"/>
+          <t>Toshmurodova Sarvara</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>388</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Anvarovna</t>
+          <t>Ilxom qizi</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="N128" s="5" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>28.03.2005</t>
         </is>
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>UM 02172465</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1319051</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="inlineStr"/>
       <c r="R128" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
       <c r="S128" s="5" t="inlineStr">
@@ -14642,7 +14622,7 @@
       </c>
       <c r="T128" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U128" s="7" t="inlineStr">
@@ -14673,78 +14653,74 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima</t>
-        </is>
-      </c>
-      <c r="D129" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Tursunova Aziza</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr"/>
       <c r="E129" s="12" t="inlineStr"/>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Qosim qizi</t>
+          <t>Anvarovna</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="K129" s="9" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="N129" s="12" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="P129" s="9" t="inlineStr">
         <is>
-          <t>UM 03730083</t>
+          <t>UM 02172465</t>
         </is>
       </c>
       <c r="Q129" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
         </is>
       </c>
       <c r="R129" s="11" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S129" s="12" t="inlineStr">
@@ -14754,7 +14730,7 @@
       </c>
       <c r="T129" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
@@ -14765,7 +14741,7 @@
       <c r="V129" s="11" t="inlineStr"/>
       <c r="W129" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X129" s="7" t="inlineStr">
@@ -14785,7 +14761,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra</t>
+          <t>Tursunova Fotima</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -14796,7 +14772,7 @@
       <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -14811,22 +14787,22 @@
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
@@ -14841,17 +14817,17 @@
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>UM 03730084</t>
+          <t>UM 03730083</t>
         </is>
       </c>
       <c r="Q130" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
         </is>
       </c>
       <c r="R130" s="4" t="inlineStr">
@@ -14897,7 +14873,7 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina</t>
+          <t>Tursunova Zuhra</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
@@ -14908,7 +14884,7 @@
       <c r="E131" s="12" t="inlineStr"/>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
@@ -14918,57 +14894,57 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Qosim qizi</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="N131" s="12" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>27.10.2008</t>
         </is>
       </c>
       <c r="O131" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="P131" s="9" t="inlineStr">
         <is>
-          <t>UM 03754097</t>
+          <t>UM 03730084</t>
         </is>
       </c>
       <c r="Q131" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
         </is>
       </c>
       <c r="R131" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S131" s="12" t="inlineStr">
@@ -15009,7 +14985,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Usmonova Sabrina</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -15020,7 +14996,7 @@
       <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>188</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -15030,63 +15006,67 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="inlineStr"/>
+          <t>UM 03754097</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+        </is>
+      </c>
       <c r="R132" s="4" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S132" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T132" s="5" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U132" s="7" t="inlineStr">
@@ -15094,14 +15074,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V132" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W132" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V132" s="4" t="inlineStr"/>
+      <c r="W132" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X132" s="7" t="inlineStr">
@@ -15121,7 +15097,7 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
@@ -15132,7 +15108,7 @@
       <c r="E133" s="12" t="inlineStr"/>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -15142,53 +15118,53 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="K133" s="9" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="N133" s="12" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="O133" s="11" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P133" s="9" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
+          <t>K 3418837</t>
         </is>
       </c>
       <c r="Q133" s="11" t="inlineStr"/>
       <c r="R133" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son texnikumi</t>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S133" s="12" t="inlineStr">
@@ -15198,7 +15174,7 @@
       </c>
       <c r="T133" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="U133" s="7" t="inlineStr">
@@ -15208,12 +15184,12 @@
       </c>
       <c r="V133" s="11" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
-        </is>
-      </c>
-      <c r="W133" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W133" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
         </is>
       </c>
       <c r="X133" s="7" t="inlineStr">
@@ -15228,84 +15204,84 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="inlineStr"/>
+          <t>Yuldosheva Ruhshona</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Farxod qizi</t>
+          <t>Xabibullo qizi</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>AE4512271</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>62501095720012</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr">
         <is>
-          <t>25.01.2009</t>
+          <t>13.09.2008</t>
         </is>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>UM 03718322</t>
-        </is>
-      </c>
-      <c r="Q134" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160259/3907782/88616609-4fee-4140-8c92-b0e3d21c7944?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="inlineStr"/>
       <c r="R134" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
       <c r="S134" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T134" s="5" t="inlineStr">
@@ -15320,12 +15296,12 @@
       </c>
       <c r="V134" s="4" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'ABDIXOLIQOVA ELMIRA' | bazada: 'Abduxoliqova Elmira'; imlo farqi — Shahodatnoma PDF: 'Abdixoliqova Elmira Farxod qizi' | bazada: 'Abduxoliqova Elmira'</t>
-        </is>
-      </c>
-      <c r="W134" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
+        </is>
+      </c>
+      <c r="W134" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X134" s="7" t="inlineStr">
@@ -15345,78 +15321,74 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Bahodirova Asila</t>
-        </is>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Abdixoliqova Elmira</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr"/>
       <c r="E135" s="12" t="inlineStr"/>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-07 00:00:00</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Olmos qizi</t>
+          <t>Farxod qizi</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr">
         <is>
-          <t>AE1222596</t>
+          <t>AE4512271</t>
         </is>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>61711085590032</t>
+          <t>62501095720012</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>16.01.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
-          <t>17.11.2008</t>
+          <t>25.01.2009</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="P135" s="9" t="inlineStr">
         <is>
-          <t>UM 03753386</t>
+          <t>UM 03718322</t>
         </is>
       </c>
       <c r="Q135" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3364811/3243239/86966b2b-ec7a-4817-bfa2-68cd1aceff78?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160259/3907782/88616609-4fee-4140-8c92-b0e3d21c7944?preview=true</t>
         </is>
       </c>
       <c r="R135" s="11" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S135" s="12" t="inlineStr">
@@ -15434,10 +15406,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V135" s="11" t="inlineStr"/>
-      <c r="W135" s="8" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
+      <c r="V135" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'ABDIXOLIQOVA ELMIRA' | bazada: 'Abduxoliqova Elmira'; imlo farqi — Shahodatnoma PDF: 'Abdixoliqova Elmira Farxod qizi' | bazada: 'Abduxoliqova Elmira'</t>
+        </is>
+      </c>
+      <c r="W135" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X135" s="7" t="inlineStr">
@@ -15457,91 +15433,99 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr"/>
+          <t>Bahodirova Asila</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="n">
-        <v>46281</v>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Husan qizi</t>
+          <t>Olmos qizi</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>AD8208717</t>
+          <t>AE1222596</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>41508955590021</t>
+          <t>61711085590032</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>12.08.2024</t>
+          <t>16.01.2025</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr">
         <is>
-          <t>15.08.1995</t>
+          <t>17.11.2008</t>
         </is>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>K 0216332</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr"/>
+          <t>UM 03753386</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3364811/3243239/86966b2b-ec7a-4817-bfa2-68cd1aceff78?preview=true</t>
+        </is>
+      </c>
       <c r="R136" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz Yengil sanoat kasb-hunar kolleji</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S136" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T136" s="5" t="n">
-        <v>2014</v>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T136" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U136" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V136" s="4" t="inlineStr">
-        <is>
-          <t>KARANTIN: ❌ Bir xil PINFL (41508955590021) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06]; ❌ Bir xil Pasport (AD8208717) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06] || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
-        </is>
-      </c>
+      <c r="V136" s="4" t="inlineStr"/>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X136" s="7" t="inlineStr">
@@ -15561,91 +15545,91 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Eshimova Zilola</t>
-        </is>
-      </c>
-      <c r="D137" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Davlatova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr"/>
       <c r="E137" s="12" t="inlineStr"/>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="G137" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="G137" s="18" t="n">
+        <v>46281</v>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Bekzod qizi</t>
+          <t>Husan qizi</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
         <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
+          <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
+          <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
       <c r="K137" s="9" t="inlineStr">
         <is>
-          <t>AE2935693</t>
+          <t>AD8208717</t>
         </is>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>61506085730076</t>
+          <t>41508955590021</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>09.06.2025</t>
+          <t>12.08.2024</t>
         </is>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
-          <t>15.06.2008</t>
-        </is>
-      </c>
-      <c r="O137" s="11" t="inlineStr"/>
+          <t>15.08.1995</t>
+        </is>
+      </c>
+      <c r="O137" s="11" t="inlineStr">
+        <is>
+          <t>Davlatova Gulnoza Husan qizi</t>
+        </is>
+      </c>
       <c r="P137" s="9" t="inlineStr">
         <is>
-          <t>UM 03756027</t>
+          <t>K 0216332</t>
         </is>
       </c>
       <c r="Q137" s="11" t="inlineStr"/>
       <c r="R137" s="11" t="inlineStr">
         <is>
-          <t>4-maktab</t>
+          <t>Shahrisabz Yengil sanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S137" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T137" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U137" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V137" s="11" t="inlineStr"/>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T137" s="12" t="n">
+        <v>2014</v>
+      </c>
+      <c r="U137" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V137" s="11" t="inlineStr">
+        <is>
+          <t>KARANTIN: ❌ Bir xil PINFL (41508955590021) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06]; ❌ Bir xil Pasport (AD8208717) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06] || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
+        </is>
+      </c>
       <c r="W137" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X137" s="7" t="inlineStr">
@@ -15665,7 +15649,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam</t>
+          <t>Eshimova Zilola</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -15676,7 +15660,7 @@
       <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -15686,57 +15670,49 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Ozodjon qizi</t>
+          <t>Bekzod qizi</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
+          <t>Eshimova Zilola Bekzod qizi</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
+          <t>Eshimova Zilola Bekzod qizi</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>AD9937321</t>
+          <t>AE2935693</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>60603085590037</t>
+          <t>61506085730076</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>24.12.2024</t>
+          <t>09.06.2025</t>
         </is>
       </c>
       <c r="N138" s="5" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
-        </is>
-      </c>
-      <c r="O138" s="4" t="inlineStr">
-        <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
+          <t>15.06.2008</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr"/>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>UM 03752997</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03756027</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr"/>
       <c r="R138" s="4" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>4-maktab</t>
         </is>
       </c>
       <c r="S138" s="5" t="inlineStr">
@@ -15749,15 +15725,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U138" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U138" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V138" s="4" t="inlineStr"/>
       <c r="W138" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X138" s="7" t="inlineStr">
@@ -15777,7 +15753,7 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida</t>
+          <t>Jalilova Shabnam</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
@@ -15788,7 +15764,7 @@
       <c r="E139" s="12" t="inlineStr"/>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -15798,52 +15774,52 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Shovkat qizi</t>
+          <t>Ozodjon qizi</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>AE6299685</t>
+          <t>AD9937321</t>
         </is>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>60907085590063</t>
+          <t>60603085590037</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>24.12.2024</t>
         </is>
       </c>
       <c r="N139" s="12" t="inlineStr">
         <is>
-          <t>09.07.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
       <c r="O139" s="11" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="P139" s="9" t="inlineStr">
         <is>
-          <t>UM 03752998</t>
+          <t>UM 03752997</t>
         </is>
       </c>
       <c r="Q139" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
         </is>
       </c>
       <c r="R139" s="11" t="inlineStr">
@@ -15867,9 +15843,9 @@
         </is>
       </c>
       <c r="V139" s="11" t="inlineStr"/>
-      <c r="W139" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+      <c r="W139" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X139" s="7" t="inlineStr">
@@ -15889,74 +15865,78 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Karimova Nozliya</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr"/>
+          <t>Jumayeva Husnida</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="inlineStr"/>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Rustamovna</t>
+          <t>Shovkat qizi</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>AE4674508</t>
+          <t>AE6299685</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>61502085680047</t>
+          <t>60907085590063</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="N140" s="5" t="inlineStr">
         <is>
-          <t>15.02.2008</t>
+          <t>09.07.2008</t>
         </is>
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>UM 03729342</t>
+          <t>UM 03752998</t>
         </is>
       </c>
       <c r="Q140" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
         </is>
       </c>
       <c r="R140" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S140" s="5" t="inlineStr">
@@ -15975,9 +15955,9 @@
         </is>
       </c>
       <c r="V140" s="4" t="inlineStr"/>
-      <c r="W140" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W140" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
       </c>
       <c r="X140" s="7" t="inlineStr">
@@ -15997,84 +15977,84 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara</t>
-        </is>
-      </c>
-      <c r="D141" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Karimova Nozliya</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr"/>
       <c r="E141" s="12" t="inlineStr"/>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Safarali qizi</t>
+          <t>Rustamovna</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="K141" s="9" t="inlineStr">
         <is>
-          <t>AE2103843</t>
+          <t>AE4674508</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>60705005680087</t>
+          <t>61502085680047</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>27.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
-          <t>07.05.2000</t>
+          <t>15.02.2008</t>
         </is>
       </c>
       <c r="O141" s="11" t="inlineStr">
         <is>
-          <t>Mahmamurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="P141" s="9" t="inlineStr">
         <is>
-          <t>K 5493345</t>
-        </is>
-      </c>
-      <c r="Q141" s="11" t="inlineStr"/>
+          <t>UM 03729342</t>
+        </is>
+      </c>
+      <c r="Q141" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+        </is>
+      </c>
       <c r="R141" s="11" t="inlineStr">
         <is>
-          <t>Kitob agrobiznes kasb-hunar kolleji</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S141" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T141" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
@@ -16082,14 +16062,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V141" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
-        </is>
-      </c>
-      <c r="W141" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: BOSHQA ODAM</t>
+      <c r="V141" s="11" t="inlineStr"/>
+      <c r="W141" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X141" s="7" t="inlineStr">
@@ -16109,7 +16085,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna</t>
+          <t>Mahmadmurodova Sevara</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -16120,7 +16096,7 @@
       <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>390</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -16130,67 +16106,63 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>To'ra qizi</t>
+          <t>Safarali qizi</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE2103843</t>
         </is>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60705005680087</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>07.05.2000</t>
         </is>
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mahmamurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>UM 03730531</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
-        </is>
-      </c>
+          <t>K 5493345</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr"/>
       <c r="R142" s="4" t="inlineStr">
         <is>
-          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S142" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T142" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U142" s="7" t="inlineStr">
@@ -16198,10 +16170,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V142" s="4" t="inlineStr"/>
-      <c r="W142" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V142" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
+        </is>
+      </c>
+      <c r="W142" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: BOSHQA ODAM</t>
         </is>
       </c>
       <c r="X142" s="7" t="inlineStr">
@@ -16221,7 +16197,7 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda</t>
+          <t>Mahmudova Maftuna</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
@@ -16232,7 +16208,7 @@
       <c r="E143" s="12" t="inlineStr"/>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -16242,27 +16218,27 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Nosir qizi</t>
+          <t>To'ra qizi</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
@@ -16272,27 +16248,27 @@
       </c>
       <c r="N143" s="12" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
       <c r="O143" s="11" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="P143" s="9" t="inlineStr">
         <is>
-          <t>UM 03728995</t>
+          <t>UM 03730531</t>
         </is>
       </c>
       <c r="Q143" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
         </is>
       </c>
       <c r="R143" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S143" s="12" t="inlineStr">
@@ -16333,74 +16309,78 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr"/>
+          <t>Mannonova Shahrizoda</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Hasan qizi</t>
+          <t>Nosir qizi</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>07.10.2008</t>
         </is>
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>UM 03718284</t>
+          <t>UM 03728995</t>
         </is>
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
         </is>
       </c>
       <c r="R144" s="4" t="inlineStr">
         <is>
-          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S144" s="5" t="inlineStr">
@@ -16441,56 +16421,100 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Muminova Durdona</t>
+          <t>Maxmarajabova Zerda</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr"/>
       <c r="E145" s="12" t="inlineStr"/>
-      <c r="F145" s="12" t="inlineStr"/>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Anvar qizi</t>
+          <t>Hasan qizi</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Muminova Durdona Anvar qizi</t>
-        </is>
-      </c>
-      <c r="J145" s="12" t="inlineStr"/>
-      <c r="K145" s="9" t="inlineStr"/>
-      <c r="L145" s="12" t="inlineStr"/>
-      <c r="M145" s="12" t="inlineStr"/>
-      <c r="N145" s="12" t="inlineStr"/>
-      <c r="O145" s="11" t="inlineStr"/>
-      <c r="P145" s="9" t="inlineStr"/>
-      <c r="Q145" s="11" t="inlineStr"/>
-      <c r="R145" s="11" t="inlineStr"/>
-      <c r="S145" s="12" t="inlineStr"/>
-      <c r="T145" s="12" t="inlineStr"/>
-      <c r="U145" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V145" s="11" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W145" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X145" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>AE5221552</t>
+        </is>
+      </c>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>60106075720246</t>
+        </is>
+      </c>
+      <c r="M145" s="12" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="N145" s="12" t="inlineStr">
+        <is>
+          <t>01.06.2007</t>
+        </is>
+      </c>
+      <c r="O145" s="11" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="P145" s="9" t="inlineStr">
+        <is>
+          <t>UM 03718284</t>
+        </is>
+      </c>
+      <c r="Q145" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+        </is>
+      </c>
+      <c r="R145" s="11" t="inlineStr">
+        <is>
+          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S145" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T145" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U145" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V145" s="11" t="inlineStr"/>
+      <c r="W145" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X145" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -16505,104 +16529,56 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Muminova Sevinch</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Muminova Durdona</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr"/>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+      <c r="F146" s="5" t="inlineStr"/>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Anvar qizi</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="J146" s="5" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>AE2259069</t>
-        </is>
-      </c>
-      <c r="L146" s="5" t="inlineStr">
-        <is>
-          <t>63001085590111</t>
-        </is>
-      </c>
-      <c r="M146" s="5" t="inlineStr">
-        <is>
-          <t>09.04.2025</t>
-        </is>
-      </c>
-      <c r="N146" s="5" t="inlineStr">
-        <is>
-          <t>30.01.2008</t>
-        </is>
-      </c>
-      <c r="O146" s="4" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="P146" s="2" t="inlineStr">
-        <is>
-          <t>UM 03752895</t>
-        </is>
-      </c>
-      <c r="Q146" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
-        </is>
-      </c>
-      <c r="R146" s="4" t="inlineStr">
-        <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S146" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T146" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U146" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V146" s="4" t="inlineStr"/>
-      <c r="W146" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X146" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Muminova Durdona Anvar qizi</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="5" t="inlineStr"/>
+      <c r="M146" s="5" t="inlineStr"/>
+      <c r="N146" s="5" t="inlineStr"/>
+      <c r="O146" s="4" t="inlineStr"/>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="4" t="inlineStr"/>
+      <c r="R146" s="4" t="inlineStr"/>
+      <c r="S146" s="5" t="inlineStr"/>
+      <c r="T146" s="5" t="inlineStr"/>
+      <c r="U146" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V146" s="4" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W146" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X146" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16593,7 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha</t>
+          <t>Muminova Sevinch</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
@@ -16628,7 +16604,7 @@
       <c r="E147" s="12" t="inlineStr"/>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>163</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
@@ -16638,57 +16614,57 @@
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Zaxriddin qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>30.01.2008</t>
         </is>
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="P147" s="9" t="inlineStr">
         <is>
-          <t>UM 03751925</t>
+          <t>UM 03752895</t>
         </is>
       </c>
       <c r="Q147" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
         </is>
       </c>
       <c r="R147" s="11" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S147" s="12" t="inlineStr">
@@ -16729,56 +16705,104 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr"/>
+          <t>Muxtorova Xadicha</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E148" s="5" t="inlineStr"/>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr"/>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>Zaxriddin qizi</t>
+        </is>
+      </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="J148" s="5" t="inlineStr"/>
-      <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="5" t="inlineStr"/>
-      <c r="M148" s="5" t="inlineStr"/>
-      <c r="N148" s="5" t="inlineStr"/>
-      <c r="O148" s="4" t="inlineStr"/>
-      <c r="P148" s="2" t="inlineStr"/>
-      <c r="Q148" s="4" t="inlineStr"/>
-      <c r="R148" s="4" t="inlineStr"/>
-      <c r="S148" s="5" t="inlineStr"/>
-      <c r="T148" s="5" t="inlineStr"/>
-      <c r="U148" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V148" s="4" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W148" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X148" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>AE2428256</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>60506085590066</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>22.04.2025</t>
+        </is>
+      </c>
+      <c r="N148" s="5" t="inlineStr">
+        <is>
+          <t>05.06.2008</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>UM 03751925</t>
+        </is>
+      </c>
+      <c r="Q148" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+        </is>
+      </c>
+      <c r="R148" s="4" t="inlineStr">
+        <is>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S148" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T148" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U148" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V148" s="4" t="inlineStr"/>
+      <c r="W148" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X148" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -16793,104 +16817,56 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch</t>
-        </is>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr"/>
       <c r="E149" s="12" t="inlineStr"/>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>304</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="H149" s="11" t="inlineStr">
-        <is>
-          <t>Mirsharaf qizi</t>
-        </is>
-      </c>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="H149" s="11" t="inlineStr"/>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="J149" s="12" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="K149" s="9" t="inlineStr">
-        <is>
-          <t>AD9494409</t>
-        </is>
-      </c>
-      <c r="L149" s="12" t="inlineStr">
-        <is>
-          <t>60504085680019</t>
-        </is>
-      </c>
-      <c r="M149" s="12" t="inlineStr">
-        <is>
-          <t>20.11.2024</t>
-        </is>
-      </c>
-      <c r="N149" s="12" t="inlineStr">
-        <is>
-          <t>05.04.2008</t>
-        </is>
-      </c>
-      <c r="O149" s="11" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="P149" s="9" t="inlineStr">
-        <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q149" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
-      <c r="R149" s="11" t="inlineStr">
-        <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S149" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T149" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U149" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V149" s="11" t="inlineStr"/>
-      <c r="W149" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X149" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="J149" s="12" t="inlineStr"/>
+      <c r="K149" s="9" t="inlineStr"/>
+      <c r="L149" s="12" t="inlineStr"/>
+      <c r="M149" s="12" t="inlineStr"/>
+      <c r="N149" s="12" t="inlineStr"/>
+      <c r="O149" s="11" t="inlineStr"/>
+      <c r="P149" s="9" t="inlineStr"/>
+      <c r="Q149" s="11" t="inlineStr"/>
+      <c r="R149" s="11" t="inlineStr"/>
+      <c r="S149" s="12" t="inlineStr"/>
+      <c r="T149" s="12" t="inlineStr"/>
+      <c r="U149" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V149" s="11" t="inlineStr">
+        <is>
+          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W149" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X149" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -16905,7 +16881,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza</t>
+          <t>Nuraliyeva Sevinch</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -16916,7 +16892,7 @@
       <c r="E150" s="5" t="inlineStr"/>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -16926,53 +16902,57 @@
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Zokir qizi</t>
+          <t>Mirsharaf qizi</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="M150" s="5" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>20.11.2024</t>
         </is>
       </c>
       <c r="N150" s="5" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>UM 1313018</t>
-        </is>
-      </c>
-      <c r="Q150" s="4" t="inlineStr"/>
+          <t>UM 03729348</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
+        </is>
+      </c>
       <c r="R150" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S150" s="5" t="inlineStr">
@@ -16982,7 +16962,7 @@
       </c>
       <c r="T150" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U150" s="7" t="inlineStr">
@@ -16993,7 +16973,7 @@
       <c r="V150" s="4" t="inlineStr"/>
       <c r="W150" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X150" s="7" t="inlineStr">
@@ -17013,7 +16993,7 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo</t>
+          <t>Ortiqova Dilnoza</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
@@ -17024,7 +17004,7 @@
       <c r="E151" s="12" t="inlineStr"/>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -17034,57 +17014,53 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Talantjon qizi</t>
+          <t>Zokir qizi</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="N151" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="P151" s="9" t="inlineStr">
         <is>
-          <t>UM 03753960</t>
-        </is>
-      </c>
-      <c r="Q151" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1313018</t>
+        </is>
+      </c>
+      <c r="Q151" s="11" t="inlineStr"/>
       <c r="R151" s="11" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S151" s="12" t="inlineStr">
@@ -17094,7 +17070,7 @@
       </c>
       <c r="T151" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
@@ -17105,7 +17081,7 @@
       <c r="V151" s="11" t="inlineStr"/>
       <c r="W151" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X151" s="7" t="inlineStr">
@@ -17125,7 +17101,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso</t>
+          <t>Qarshiyeva Shahlo</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -17136,7 +17112,7 @@
       <c r="E152" s="5" t="inlineStr"/>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -17146,49 +17122,57 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Talantjon qizi</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="N152" s="5" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
-        </is>
-      </c>
-      <c r="O152" s="4" t="inlineStr"/>
+          <t>22.01.2008</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+        </is>
+      </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>UM 03742130</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr"/>
+          <t>UM 03753960</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
+        </is>
+      </c>
       <c r="R152" s="4" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S152" s="5" t="inlineStr">
@@ -17201,19 +17185,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U152" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V152" s="4" t="inlineStr">
-        <is>
-          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
-        </is>
-      </c>
+      <c r="U152" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V152" s="4" t="inlineStr"/>
       <c r="W152" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X152" s="7" t="inlineStr">
@@ -17233,78 +17213,70 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
+          <t>Quchqarova Zebiniso</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi</t>
+          <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr"/>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="N153" s="12" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
-        </is>
-      </c>
-      <c r="O153" s="11" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>29.11.2008</t>
+        </is>
+      </c>
+      <c r="O153" s="11" t="inlineStr"/>
       <c r="P153" s="9" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q153" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03742130</t>
+        </is>
+      </c>
+      <c r="Q153" s="11" t="inlineStr"/>
       <c r="R153" s="11" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S153" s="12" t="inlineStr">
@@ -17322,10 +17294,14 @@
           <t>CHALA</t>
         </is>
       </c>
-      <c r="V153" s="11" t="inlineStr"/>
+      <c r="V153" s="11" t="inlineStr">
+        <is>
+          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
+        </is>
+      </c>
       <c r="W153" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X153" s="7" t="inlineStr">
@@ -17345,7 +17321,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
+          <t>Samiyeva Sevinchbonu</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -17356,67 +17332,67 @@
       <c r="E154" s="5" t="inlineStr"/>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="N154" s="5" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q154" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R154" s="4" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S154" s="5" t="inlineStr">
@@ -17435,9 +17411,9 @@
         </is>
       </c>
       <c r="V154" s="4" t="inlineStr"/>
-      <c r="W154" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W154" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X154" s="7" t="inlineStr">
@@ -17457,89 +17433,93 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
+          <t>Sanaqulova Muxtarama</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
+          <t>Hamshiralik ishi</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr"/>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="O155" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P155" s="9" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q155" s="11" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q155" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R155" s="11" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S155" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T155" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U155" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U155" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V155" s="11" t="inlineStr"/>
@@ -17565,84 +17545,84 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr"/>
+          <t>Sanaqulova Nozliya</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="inlineStr"/>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="N156" s="5" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q156" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 5509185</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="inlineStr"/>
       <c r="R156" s="4" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S156" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T156" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U156" s="7" t="inlineStr">
@@ -17650,14 +17630,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V156" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W156" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+      <c r="V156" s="4" t="inlineStr"/>
+      <c r="W156" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X156" s="7" t="inlineStr">
@@ -17677,78 +17653,74 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 2 yillik</t>
-        </is>
-      </c>
+          <t>Sayfillayeva Shodiyona</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr"/>
       <c r="E157" s="12" t="inlineStr"/>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P157" s="9" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q157" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R157" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S157" s="12" t="inlineStr">
@@ -17758,7 +17730,7 @@
       </c>
       <c r="T157" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
@@ -17766,10 +17738,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V157" s="11" t="inlineStr"/>
-      <c r="W157" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V157" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W157" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X157" s="7" t="inlineStr">
@@ -17789,18 +17765,18 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
+          <t>Hamshiralik ishi - 2 yillik</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr"/>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -17810,53 +17786,57 @@
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q158" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S158" s="5" t="inlineStr">
@@ -17866,7 +17846,7 @@
       </c>
       <c r="T158" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U158" s="7" t="inlineStr">
@@ -17877,7 +17857,7 @@
       <c r="V158" s="4" t="inlineStr"/>
       <c r="W158" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X158" s="7" t="inlineStr">
@@ -17897,7 +17877,7 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
@@ -17908,7 +17888,7 @@
       <c r="E159" s="12" t="inlineStr"/>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
@@ -17918,57 +17898,53 @@
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="N159" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P159" s="9" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q159" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02172469</t>
+        </is>
+      </c>
+      <c r="Q159" s="11" t="inlineStr"/>
       <c r="R159" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S159" s="12" t="inlineStr">
@@ -17978,7 +17954,7 @@
       </c>
       <c r="T159" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U159" s="7" t="inlineStr">
@@ -17989,7 +17965,7 @@
       <c r="V159" s="11" t="inlineStr"/>
       <c r="W159" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X159" s="7" t="inlineStr">
@@ -18009,7 +17985,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yahyomurodova Gulsanam</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -18020,7 +17996,7 @@
       <c r="E160" s="5" t="inlineStr"/>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -18030,57 +18006,57 @@
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="N160" s="5" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q160" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R160" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S160" s="5" t="inlineStr">
@@ -18116,12 +18092,12 @@
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
@@ -18132,71 +18108,77 @@
       <c r="E161" s="12" t="inlineStr"/>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="G161" s="18" t="n">
-        <v>46161</v>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>G‘ani qizi</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila G‘ani qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila G‘ani qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
         <is>
-          <t>AE5575300</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>41011925590038</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="N161" s="12" t="inlineStr">
         <is>
-          <t>10.11.1992</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila G‘ani qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P161" s="9" t="inlineStr">
         <is>
-          <t>L 125287</t>
-        </is>
-      </c>
-      <c r="Q161" s="11" t="inlineStr"/>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q161" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
       <c r="R161" s="11" t="inlineStr">
         <is>
-          <t>Toshkent irrigatsiya va melioratsiya instituti qoshidagi akademik litsey</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S161" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T161" s="12" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U161" s="7" t="inlineStr">
@@ -18227,7 +18209,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor</t>
+          <t>G‘aniyeva Asila</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -18238,61 +18220,61 @@
       <c r="E162" s="5" t="inlineStr"/>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>381</t>
         </is>
       </c>
       <c r="G162" s="6" t="n">
-        <v>46224</v>
+        <v>46161</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>G‘ani qizi</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>G‘aniyeva Asila G‘ani qizi</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>G‘aniyeva Asila G‘ani qizi</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>AD7829399</t>
+          <t>AE5575300</t>
         </is>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>41902975680049</t>
+          <t>41011925590038</t>
         </is>
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>11.07.2024</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="N162" s="5" t="inlineStr">
         <is>
-          <t>19.02.1997</t>
+          <t>10.11.1992</t>
         </is>
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>G‘aniyeva Asila G‘ani qizi</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>K 0236649</t>
+          <t>L 125287</t>
         </is>
       </c>
       <c r="Q162" s="4" t="inlineStr"/>
       <c r="R162" s="4" t="inlineStr">
         <is>
-          <t>Kitob agrosanoat kasb-hunar kolleji</t>
+          <t>Toshkent irrigatsiya va melioratsiya instituti qoshidagi akademik litsey</t>
         </is>
       </c>
       <c r="S162" s="5" t="inlineStr">
@@ -18302,7 +18284,7 @@
       </c>
       <c r="T162" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="U162" s="7" t="inlineStr">
@@ -18333,7 +18315,7 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola</t>
+          <t>Muhammadiyeva Gulbahor</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
@@ -18341,94 +18323,90 @@
           <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
-      <c r="E163" s="12" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+      <c r="E163" s="12" t="inlineStr"/>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G163" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-29 00:00:00</t>
-        </is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G163" s="18" t="n">
+        <v>46224</v>
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="J163" s="12" t="inlineStr"/>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+        </is>
+      </c>
+      <c r="J163" s="12" t="inlineStr">
+        <is>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+        </is>
+      </c>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>AC1458884</t>
+          <t>AD7829399</t>
         </is>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>42708915590028</t>
+          <t>41902975680049</t>
         </is>
       </c>
       <c r="M163" s="12" t="inlineStr">
         <is>
-          <t>04.11.2018</t>
+          <t>11.07.2024</t>
         </is>
       </c>
       <c r="N163" s="12" t="inlineStr">
         <is>
-          <t>27.08.1991</t>
+          <t>19.02.1997</t>
         </is>
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="P163" s="9" t="inlineStr">
         <is>
-          <t>O'r-Sh 0987579</t>
+          <t>K 0236649</t>
         </is>
       </c>
       <c r="Q163" s="11" t="inlineStr"/>
       <c r="R163" s="11" t="inlineStr">
         <is>
-          <t>Ixtisoslashgan maktab</t>
+          <t>Kitob agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S163" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T163" s="12" t="n">
-        <v>2009</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T163" s="12" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V163" s="11" t="inlineStr">
-        <is>
-          <t>Murtazayeva Kamola 25.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
+      <c r="V163" s="11" t="inlineStr"/>
       <c r="W163" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X163" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X163" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -18443,7 +18421,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza</t>
+          <t>Murtazayeva Kamola</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -18451,73 +18429,75 @@
           <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
-      <c r="E164" s="5" t="inlineStr"/>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="G164" s="6" t="n">
-        <v>46255</v>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Ulug‘bek qizi</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
-        </is>
-      </c>
-      <c r="J164" s="5" t="inlineStr">
-        <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
-        </is>
-      </c>
+          <t>Murtazayeva Kamola Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>AB8521319</t>
+          <t>AC1458884</t>
         </is>
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>62906005590060</t>
+          <t>42708915590028</t>
         </is>
       </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>02.01.2018</t>
+          <t>04.11.2018</t>
         </is>
       </c>
       <c r="N164" s="5" t="inlineStr">
         <is>
-          <t>29.06.2000</t>
+          <t>27.08.1991</t>
         </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>K 5487472</t>
+          <t>O'r-Sh 0987579</t>
         </is>
       </c>
       <c r="Q164" s="4" t="inlineStr"/>
       <c r="R164" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
+          <t>Ixtisoslashgan maktab</t>
         </is>
       </c>
       <c r="S164" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T164" s="5" t="n">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="U164" s="7" t="inlineStr">
         <is>
@@ -18526,7 +18506,7 @@
       </c>
       <c r="V164" s="4" t="inlineStr">
         <is>
-          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
+          <t>Murtazayeva Kamola 25.docx faylidan to'liq kiritildi</t>
         </is>
       </c>
       <c r="W164" s="8" t="inlineStr">
@@ -18534,9 +18514,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X164" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X164" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -18551,7 +18531,7 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor</t>
+          <t>Mustafayeva Nargiza</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
@@ -18562,74 +18542,70 @@
       <c r="E165" s="12" t="inlineStr"/>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="G165" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="G165" s="18" t="n">
+        <v>46255</v>
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="K165" s="9" t="inlineStr">
         <is>
-          <t>AB5359926</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>40211995680023</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
-          <t>12.12.2016</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="N165" s="12" t="inlineStr">
         <is>
-          <t>02.11.1999</t>
+          <t>29.06.2000</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="P165" s="9" t="inlineStr">
         <is>
-          <t>K 5047841</t>
+          <t>K 5487472</t>
         </is>
       </c>
       <c r="Q165" s="11" t="inlineStr"/>
       <c r="R165" s="11" t="inlineStr">
         <is>
-          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S165" s="12" t="inlineStr">
         <is>
-          <t>Kasb-hunar kolleji diplomi</t>
-        </is>
-      </c>
-      <c r="T165" s="12" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T165" s="12" t="n">
+        <v>2019</v>
       </c>
       <c r="U165" s="7" t="inlineStr">
         <is>
@@ -18638,12 +18614,12 @@
       </c>
       <c r="V165" s="11" t="inlineStr">
         <is>
-          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
         </is>
       </c>
       <c r="W165" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X165" s="7" t="inlineStr">
@@ -18663,14 +18639,18 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Nazarova Munisa</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr"/>
+          <t>Narziyeva Intizor</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E166" s="5" t="inlineStr"/>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>212</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -18680,54 +18660,78 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Erkin qizi</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>AE7685867</t>
+          <t>AB5359926</t>
         </is>
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>41205925680015</t>
+          <t>40211995680023</t>
         </is>
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>17.06.2026</t>
+          <t>12.12.2016</t>
         </is>
       </c>
       <c r="N166" s="5" t="inlineStr">
         <is>
-          <t>12.05.1992</t>
-        </is>
-      </c>
-      <c r="O166" s="4" t="inlineStr"/>
-      <c r="P166" s="2" t="inlineStr"/>
+          <t>02.11.1999</t>
+        </is>
+      </c>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>K 5047841</t>
+        </is>
+      </c>
       <c r="Q166" s="4" t="inlineStr"/>
-      <c r="R166" s="4" t="inlineStr"/>
-      <c r="S166" s="5" t="inlineStr"/>
-      <c r="T166" s="5" t="inlineStr"/>
-      <c r="U166" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V166" s="4" t="inlineStr"/>
+      <c r="R166" s="4" t="inlineStr">
+        <is>
+          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S166" s="5" t="inlineStr">
+        <is>
+          <t>Kasb-hunar kolleji diplomi</t>
+        </is>
+      </c>
+      <c r="T166" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U166" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V166" s="4" t="inlineStr">
+        <is>
+          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+        </is>
+      </c>
       <c r="W166" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X166" s="7" t="inlineStr">
@@ -30923,7 +30927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -32867,7 +32871,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch</t>
+          <t>Nazarova Munisa</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -32878,80 +32882,64 @@
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Hikmatullo qizi</t>
+          <t>Erkin qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>AE7082532</t>
+          <t>AE7685867</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>60212085680048</t>
+          <t>41205925680015</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>02.12.2008</t>
+          <t>12.05.1992</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>UM 03727760</t>
-        </is>
-      </c>
+      <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>1-maktab</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U18" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W18" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X18" s="7" t="inlineStr">
@@ -32971,74 +32959,66 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam</t>
+          <t>Ne'matova Sevinch</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
+          <t>Hamshiralik ishi</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Elyor qizi</t>
+          <t>Hikmatullo qizi</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr"/>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>AE4817469</t>
+          <t>AE7082532</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>61809085680096</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>18.09.2008</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+          <t>02.12.2008</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr"/>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM 03728575</t>
+          <t>UM 03727760</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>1-maktab</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
@@ -33051,15 +33031,19 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="U19" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W19" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -33079,7 +33063,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Omonova Charos</t>
+          <t>Normurodova Gulsanam</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -33090,7 +33074,7 @@
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -33100,63 +33084,63 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Elyor qizi</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>AE1338424</t>
+          <t>AE4817469</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>40306985590014</t>
+          <t>61809085680096</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>03.06.1998</t>
+          <t>18.09.2008</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>K 5023908</t>
+          <t>UM 03728575</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
@@ -33187,83 +33171,95 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Oripova Sevinch</t>
+          <t>Omonova Charos</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi</t>
+          <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
-      <c r="F21" s="12" t="inlineStr"/>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>G'olib qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Oripova Sevinch G'olib qizi</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr"/>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>AE3333890</t>
+          <t>AE1338424</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>62007085680095</t>
+          <t>40306985590014</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>09.07.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>20.07.2008</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr"/>
+          <t>03.06.1998</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>UM 03729323</t>
+          <t>K 5023908</t>
         </is>
       </c>
       <c r="Q21" s="11" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>45-maktab</t>
+          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U21" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V21" s="11" t="inlineStr"/>
-      <c r="W21" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X21" s="7" t="inlineStr">
@@ -33283,72 +33279,62 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Ozodova Klara</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
+          <t>Oripova Sevinch</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>46272</v>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Fayzullayevna</t>
+          <t>G'olib qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>Oripova Sevinch G'olib qizi</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>AD6663341</t>
+          <t>AE3333890</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>60803075590140</t>
+          <t>62007085680095</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>01.04.2024</t>
+          <t>09.07.2025</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>08.03.2007</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>20.07.2008</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 03298601</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03729323</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>45-maktab</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
@@ -33358,18 +33344,18 @@
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U22" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U22" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W22" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
@@ -33389,78 +33375,72 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Ozodova Klara</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr"/>
       <c r="E23" s="12" t="inlineStr"/>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>46272</v>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Ilyos qizi</t>
+          <t>Fayzullayevna</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>AE6043288</t>
+          <t>AD6663341</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>60511085680024</t>
+          <t>60803075590140</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>01.04.2024</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>05.11.2008</t>
+          <t>08.03.2007</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03730668</t>
+          <t>UM 03298601</t>
         </is>
       </c>
       <c r="Q23" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
         </is>
       </c>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
@@ -33470,7 +33450,7 @@
       </c>
       <c r="T23" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">
@@ -33501,7 +33481,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Sharipova Diyora</t>
+          <t>Saidova Dilso'z</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -33512,7 +33492,7 @@
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -33522,57 +33502,57 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Ilyos qizi</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AE6043288</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>60511085680024</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>05.11.2008</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03751494</t>
+          <t>UM 03730668</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
         </is>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
@@ -33613,7 +33593,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara</t>
+          <t>Sharipova Diyora</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -33624,7 +33604,7 @@
       <c r="E25" s="12" t="inlineStr"/>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -33634,53 +33614,57 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Ilxom qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
+          <t>23.07.2009</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 1319051</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr"/>
+          <t>UM 03751494</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+        </is>
+      </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
+          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
@@ -33690,7 +33674,7 @@
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -33701,7 +33685,7 @@
       <c r="V25" s="11" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -33721,74 +33705,74 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>Toshmurodova Sarvara</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>388</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Anvarovna</t>
+          <t>Ilxom qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>28.03.2005</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 02172465</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1319051</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -33798,7 +33782,7 @@
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -33829,78 +33813,74 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Tursunova Aziza</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr"/>
       <c r="E27" s="12" t="inlineStr"/>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Qosim qizi</t>
+          <t>Anvarovna</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 03730083</t>
+          <t>UM 02172465</t>
         </is>
       </c>
       <c r="Q27" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
         </is>
       </c>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
@@ -33910,7 +33890,7 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -33921,7 +33901,7 @@
       <c r="V27" s="11" t="inlineStr"/>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -33941,7 +33921,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra</t>
+          <t>Tursunova Fotima</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -33952,7 +33932,7 @@
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -33967,22 +33947,22 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
@@ -33997,17 +33977,17 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03730084</t>
+          <t>UM 03730083</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
         </is>
       </c>
       <c r="R28" s="4" t="inlineStr">
@@ -34053,7 +34033,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina</t>
+          <t>Tursunova Zuhra</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -34064,7 +34044,7 @@
       <c r="E29" s="12" t="inlineStr"/>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -34074,57 +34054,57 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Qosim qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>27.10.2008</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03754097</t>
+          <t>UM 03730084</t>
         </is>
       </c>
       <c r="Q29" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
         </is>
       </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -34165,7 +34145,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Usmonova Sabrina</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -34176,7 +34156,7 @@
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>188</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -34186,63 +34166,67 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr"/>
+          <t>UM 03754097</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+        </is>
+      </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T30" s="5" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U30" s="7" t="inlineStr">
@@ -34250,14 +34234,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W30" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X30" s="7" t="inlineStr">
@@ -34277,7 +34257,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -34288,7 +34268,7 @@
       <c r="E31" s="12" t="inlineStr"/>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -34298,88 +34278,200 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
+          <t>K 3418837</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr"/>
       <c r="R31" s="11" t="inlineStr">
         <is>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S31" s="12" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T31" s="12" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W31" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
+        </is>
+      </c>
+      <c r="X31" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Yuldosheva Ruhshona</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Xabibullo qizi</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>AE1419035</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>61309085590066</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>29.01.2025</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>13.09.2008</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
           <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
-      <c r="S31" s="12" t="inlineStr">
+      <c r="S32" s="5" t="inlineStr">
         <is>
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T31" s="12" t="inlineStr">
+      <c r="T32" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="U31" s="7" t="inlineStr">
+      <c r="U32" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="11" t="inlineStr">
+      <c r="V32" s="4" t="inlineStr">
         <is>
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
         </is>
       </c>
-      <c r="W31" s="13" t="inlineStr">
+      <c r="W32" s="13" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
       </c>
-      <c r="X31" s="7" t="inlineStr">
+      <c r="X32" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X31"/>
+  <autoFilter ref="A1:X32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37441,7 +37533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38145,14 +38237,18 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Nazarova Munisa</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr"/>
+          <t>Salayeva Dilroz</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E7" s="12" t="inlineStr"/>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>205</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -38160,61 +38256,37 @@
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>Erkin qizi</t>
-        </is>
-      </c>
+      <c r="H7" s="11" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>Nazarova Munisa Erkin qizi</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>AE7685867</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>41205925680015</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr">
-        <is>
-          <t>17.06.2026</t>
-        </is>
-      </c>
-      <c r="N7" s="12" t="inlineStr">
-        <is>
-          <t>12.05.1992</t>
-        </is>
-      </c>
+          <t>Salayeva Dilroz</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr"/>
+      <c r="M7" s="12" t="inlineStr"/>
+      <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="11" t="inlineStr"/>
       <c r="P7" s="9" t="inlineStr"/>
       <c r="Q7" s="11" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="12" t="inlineStr"/>
-      <c r="U7" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="U7" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X7" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W7" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X7" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -38229,165 +38301,101 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Usmonova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>46272</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Xamdam qizi</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>AB5702170</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>42601925680010</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>19.01.2017</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>26.01.1992</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>K 1994177</t>
+        </is>
+      </c>
       <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X8" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>26-07</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>46272</v>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>AB5702170</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>42601925680010</t>
-        </is>
-      </c>
-      <c r="M9" s="12" t="inlineStr">
-        <is>
-          <t>19.01.2017</t>
-        </is>
-      </c>
-      <c r="N9" s="12" t="inlineStr">
-        <is>
-          <t>26.01.1992</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>K 1994177</t>
-        </is>
-      </c>
-      <c r="Q9" s="11" t="inlineStr"/>
-      <c r="R9" s="11" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="S9" s="12" t="inlineStr">
+      <c r="S8" s="5" t="inlineStr">
         <is>
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T9" s="12" t="n">
+      <c r="T8" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="U9" s="7" t="inlineStr">
+      <c r="U8" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V9" s="11" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
         </is>
       </c>
-      <c r="W9" s="8" t="inlineStr">
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X9" s="7" t="inlineStr">
+      <c r="X8" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X9"/>
+  <autoFilter ref="A1:X8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -22,9 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13497,7 +13497,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Murodova Munisa</t>
+          <t>Muhammadiyeva Gulbahor</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -13508,73 +13508,71 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="n">
+        <v>46224</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Muxtor qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>AE2895049</t>
+          <t>AD7829399</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>62112085680050</t>
+          <t>41902975680049</t>
         </is>
       </c>
       <c r="M118" s="5" t="inlineStr">
         <is>
-          <t>03.06.2025</t>
+          <t>11.07.2024</t>
         </is>
       </c>
       <c r="N118" s="5" t="inlineStr">
         <is>
-          <t>21.12.2008</t>
+          <t>19.02.1997</t>
         </is>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>UM 03753455</t>
+          <t>K 0236649</t>
         </is>
       </c>
       <c r="Q118" s="4" t="inlineStr"/>
       <c r="R118" s="4" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>Kitob agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S118" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T118" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="U118" s="7" t="inlineStr">
@@ -13583,9 +13581,9 @@
         </is>
       </c>
       <c r="V118" s="4" t="inlineStr"/>
-      <c r="W118" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W118" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X118" s="7" t="inlineStr">
@@ -13605,7 +13603,7 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona</t>
+          <t>Murodova Munisa</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
@@ -13616,71 +13614,73 @@
       <c r="E119" s="12" t="inlineStr"/>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="G119" s="18" t="n">
-        <v>46221</v>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Asrorxon qizi</t>
+          <t>Muxtor qizi</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="K119" s="9" t="inlineStr">
         <is>
-          <t>AD9123240</t>
+          <t>AE2895049</t>
         </is>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>62710075590066</t>
+          <t>62112085680050</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>03.06.2025</t>
         </is>
       </c>
       <c r="N119" s="12" t="inlineStr">
         <is>
-          <t>27.10.2007</t>
+          <t>21.12.2008</t>
         </is>
       </c>
       <c r="O119" s="11" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="P119" s="9" t="inlineStr">
         <is>
-          <t>PT 0257899</t>
+          <t>UM 03753455</t>
         </is>
       </c>
       <c r="Q119" s="11" t="inlineStr"/>
       <c r="R119" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 1-son politexnikumi</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S119" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T119" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U119" s="7" t="inlineStr">
@@ -13689,9 +13689,9 @@
         </is>
       </c>
       <c r="V119" s="11" t="inlineStr"/>
-      <c r="W119" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W119" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X119" s="7" t="inlineStr">
@@ -13711,75 +13711,93 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Nazarova Munisa</t>
+          <t>Muzrapova Ruhshona</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi</t>
+          <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="n">
+        <v>46221</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Erkin qizi</t>
+          <t>Asrorxon qizi</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>AE7685867</t>
+          <t>AD9123240</t>
         </is>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>41205925680015</t>
+          <t>62710075590066</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>17.06.2026</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="N120" s="5" t="inlineStr">
         <is>
-          <t>12.05.1992</t>
-        </is>
-      </c>
-      <c r="O120" s="4" t="inlineStr"/>
-      <c r="P120" s="2" t="inlineStr"/>
+          <t>27.10.2007</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>PT 0257899</t>
+        </is>
+      </c>
       <c r="Q120" s="4" t="inlineStr"/>
-      <c r="R120" s="4" t="inlineStr"/>
-      <c r="S120" s="5" t="inlineStr"/>
-      <c r="T120" s="5" t="inlineStr"/>
-      <c r="U120" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="R120" s="4" t="inlineStr">
+        <is>
+          <t>Shahrisabz shahar 1-son politexnikumi</t>
+        </is>
+      </c>
+      <c r="S120" s="5" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T120" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U120" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V120" s="4" t="inlineStr"/>
       <c r="W120" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X120" s="7" t="inlineStr">
@@ -13799,7 +13817,7 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch</t>
+          <t>Nazarova Munisa</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
@@ -13810,80 +13828,64 @@
       <c r="E121" s="12" t="inlineStr"/>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Hikmatullo qizi</t>
+          <t>Erkin qizi</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
-        </is>
-      </c>
-      <c r="J121" s="12" t="inlineStr"/>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
       <c r="K121" s="9" t="inlineStr">
         <is>
-          <t>AE7082532</t>
+          <t>AE7685867</t>
         </is>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>60212085680048</t>
+          <t>41205925680015</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
-          <t>02.12.2008</t>
+          <t>12.05.1992</t>
         </is>
       </c>
       <c r="O121" s="11" t="inlineStr"/>
-      <c r="P121" s="9" t="inlineStr">
-        <is>
-          <t>UM 03727760</t>
-        </is>
-      </c>
+      <c r="P121" s="9" t="inlineStr"/>
       <c r="Q121" s="11" t="inlineStr"/>
-      <c r="R121" s="11" t="inlineStr">
-        <is>
-          <t>1-maktab</t>
-        </is>
-      </c>
-      <c r="S121" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T121" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U121" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V121" s="11" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W121" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="R121" s="11" t="inlineStr"/>
+      <c r="S121" s="12" t="inlineStr"/>
+      <c r="T121" s="12" t="inlineStr"/>
+      <c r="U121" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V121" s="11" t="inlineStr"/>
+      <c r="W121" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X121" s="7" t="inlineStr">
@@ -13903,74 +13905,66 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam</t>
+          <t>Ne'matova Sevinch</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
+          <t>Hamshiralik ishi</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Elyor qizi</t>
+          <t>Hikmatullo qizi</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
-      <c r="J122" s="5" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>AE4817469</t>
+          <t>AE7082532</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>61809085680096</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="N122" s="5" t="inlineStr">
         <is>
-          <t>18.09.2008</t>
-        </is>
-      </c>
-      <c r="O122" s="4" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+          <t>02.12.2008</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr"/>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>UM 03728575</t>
+          <t>UM 03727760</t>
         </is>
       </c>
       <c r="Q122" s="4" t="inlineStr"/>
       <c r="R122" s="4" t="inlineStr">
         <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>1-maktab</t>
         </is>
       </c>
       <c r="S122" s="5" t="inlineStr">
@@ -13983,15 +13977,19 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U122" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V122" s="4" t="inlineStr"/>
-      <c r="W122" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="U122" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V122" s="4" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W122" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X122" s="7" t="inlineStr">
@@ -14011,7 +14009,7 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Omonova Charos</t>
+          <t>Normurodova Gulsanam</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
@@ -14022,7 +14020,7 @@
       <c r="E123" s="12" t="inlineStr"/>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
@@ -14032,63 +14030,63 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Elyor qizi</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="K123" s="9" t="inlineStr">
         <is>
-          <t>AE1338424</t>
+          <t>AE4817469</t>
         </is>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>40306985590014</t>
+          <t>61809085680096</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="N123" s="12" t="inlineStr">
         <is>
-          <t>03.06.1998</t>
+          <t>18.09.2008</t>
         </is>
       </c>
       <c r="O123" s="11" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="P123" s="9" t="inlineStr">
         <is>
-          <t>K 5023908</t>
+          <t>UM 03728575</t>
         </is>
       </c>
       <c r="Q123" s="11" t="inlineStr"/>
       <c r="R123" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S123" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T123" s="12" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
@@ -14119,83 +14117,95 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Oripova Sevinch</t>
+          <t>Omonova Charos</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi</t>
+          <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr"/>
-      <c r="F124" s="5" t="inlineStr"/>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>G'olib qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>Oripova Sevinch G'olib qizi</t>
-        </is>
-      </c>
-      <c r="J124" s="5" t="inlineStr"/>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>AE3333890</t>
+          <t>AE1338424</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>62007085680095</t>
+          <t>40306985590014</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>09.07.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="N124" s="5" t="inlineStr">
         <is>
-          <t>20.07.2008</t>
-        </is>
-      </c>
-      <c r="O124" s="4" t="inlineStr"/>
+          <t>03.06.1998</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>UM 03729323</t>
+          <t>K 5023908</t>
         </is>
       </c>
       <c r="Q124" s="4" t="inlineStr"/>
       <c r="R124" s="4" t="inlineStr">
         <is>
-          <t>45-maktab</t>
+          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S124" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T124" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U124" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="U124" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V124" s="4" t="inlineStr"/>
-      <c r="W124" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W124" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X124" s="7" t="inlineStr">
@@ -14215,72 +14225,62 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Ozodova Klara</t>
-        </is>
-      </c>
-      <c r="D125" s="11" t="inlineStr"/>
+          <t>Oripova Sevinch</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
       <c r="E125" s="12" t="inlineStr"/>
-      <c r="F125" s="12" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="G125" s="18" t="n">
-        <v>46272</v>
+      <c r="F125" s="12" t="inlineStr"/>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Fayzullayevna</t>
+          <t>G'olib qizi</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
         <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
-      <c r="J125" s="12" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>Oripova Sevinch G'olib qizi</t>
+        </is>
+      </c>
+      <c r="J125" s="12" t="inlineStr"/>
       <c r="K125" s="9" t="inlineStr">
         <is>
-          <t>AD6663341</t>
+          <t>AE3333890</t>
         </is>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>60803075590140</t>
+          <t>62007085680095</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>01.04.2024</t>
+          <t>09.07.2025</t>
         </is>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
-          <t>08.03.2007</t>
-        </is>
-      </c>
-      <c r="O125" s="11" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>20.07.2008</t>
+        </is>
+      </c>
+      <c r="O125" s="11" t="inlineStr"/>
       <c r="P125" s="9" t="inlineStr">
         <is>
-          <t>UM 03298601</t>
-        </is>
-      </c>
-      <c r="Q125" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03729323</t>
+        </is>
+      </c>
+      <c r="Q125" s="11" t="inlineStr"/>
       <c r="R125" s="11" t="inlineStr">
         <is>
-          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>45-maktab</t>
         </is>
       </c>
       <c r="S125" s="12" t="inlineStr">
@@ -14290,18 +14290,18 @@
       </c>
       <c r="T125" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U125" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V125" s="11" t="inlineStr"/>
-      <c r="W125" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W125" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X125" s="7" t="inlineStr">
@@ -14321,78 +14321,72 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Ozodova Klara</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Ilyos qizi</t>
+          <t>Fayzullayevna</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>AE6043288</t>
+          <t>AD6663341</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>60511085680024</t>
+          <t>60803075590140</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>01.04.2024</t>
         </is>
       </c>
       <c r="N126" s="5" t="inlineStr">
         <is>
-          <t>05.11.2008</t>
+          <t>08.03.2007</t>
         </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>UM 03730668</t>
+          <t>UM 03298601</t>
         </is>
       </c>
       <c r="Q126" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
         </is>
       </c>
       <c r="R126" s="4" t="inlineStr">
         <is>
-          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S126" s="5" t="inlineStr">
@@ -14402,7 +14396,7 @@
       </c>
       <c r="T126" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U126" s="7" t="inlineStr">
@@ -14433,7 +14427,7 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Sharipova Diyora</t>
+          <t>Saidova Dilso'z</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
@@ -14444,7 +14438,7 @@
       <c r="E127" s="12" t="inlineStr"/>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -14454,57 +14448,57 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Ilyos qizi</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="K127" s="9" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AE6043288</t>
         </is>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>60511085680024</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>05.11.2008</t>
         </is>
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="P127" s="9" t="inlineStr">
         <is>
-          <t>UM 03751494</t>
+          <t>UM 03730668</t>
         </is>
       </c>
       <c r="Q127" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
         </is>
       </c>
       <c r="R127" s="11" t="inlineStr">
         <is>
-          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S127" s="12" t="inlineStr">
@@ -14545,7 +14539,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara</t>
+          <t>Sharipova Diyora</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -14556,7 +14550,7 @@
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -14566,53 +14560,57 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Ilxom qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="N128" s="5" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
+          <t>23.07.2009</t>
         </is>
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>UM 1319051</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="inlineStr"/>
+          <t>UM 03751494</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+        </is>
+      </c>
       <c r="R128" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
+          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S128" s="5" t="inlineStr">
@@ -14622,7 +14620,7 @@
       </c>
       <c r="T128" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U128" s="7" t="inlineStr">
@@ -14633,7 +14631,7 @@
       <c r="V128" s="4" t="inlineStr"/>
       <c r="W128" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X128" s="7" t="inlineStr">
@@ -14653,74 +14651,74 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Aziza</t>
-        </is>
-      </c>
-      <c r="D129" s="11" t="inlineStr"/>
+          <t>Toshmurodova Sarvara</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E129" s="12" t="inlineStr"/>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>388</t>
         </is>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Anvarovna</t>
+          <t>Ilxom qizi</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="K129" s="9" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="N129" s="12" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>28.03.2005</t>
         </is>
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="P129" s="9" t="inlineStr">
         <is>
-          <t>UM 02172465</t>
-        </is>
-      </c>
-      <c r="Q129" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1319051</t>
+        </is>
+      </c>
+      <c r="Q129" s="11" t="inlineStr"/>
       <c r="R129" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
       <c r="S129" s="12" t="inlineStr">
@@ -14730,7 +14728,7 @@
       </c>
       <c r="T129" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
@@ -14761,78 +14759,74 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Fotima</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Tursunova Aziza</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Qosim qizi</t>
+          <t>Anvarovna</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="N130" s="5" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>UM 03730083</t>
+          <t>UM 02172465</t>
         </is>
       </c>
       <c r="Q130" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
         </is>
       </c>
       <c r="R130" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S130" s="5" t="inlineStr">
@@ -14842,7 +14836,7 @@
       </c>
       <c r="T130" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U130" s="7" t="inlineStr">
@@ -14853,7 +14847,7 @@
       <c r="V130" s="4" t="inlineStr"/>
       <c r="W130" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X130" s="7" t="inlineStr">
@@ -14873,7 +14867,7 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra</t>
+          <t>Tursunova Fotima</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
@@ -14884,7 +14878,7 @@
       <c r="E131" s="12" t="inlineStr"/>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
@@ -14899,22 +14893,22 @@
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
@@ -14929,17 +14923,17 @@
       </c>
       <c r="O131" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="P131" s="9" t="inlineStr">
         <is>
-          <t>UM 03730084</t>
+          <t>UM 03730083</t>
         </is>
       </c>
       <c r="Q131" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
         </is>
       </c>
       <c r="R131" s="11" t="inlineStr">
@@ -14985,7 +14979,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina</t>
+          <t>Tursunova Zuhra</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -14996,7 +14990,7 @@
       <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -15006,57 +15000,57 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Qosim qizi</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>27.10.2008</t>
         </is>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>UM 03754097</t>
+          <t>UM 03730084</t>
         </is>
       </c>
       <c r="Q132" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
         </is>
       </c>
       <c r="R132" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S132" s="5" t="inlineStr">
@@ -15097,7 +15091,7 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Usmonova Sabrina</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
@@ -15108,7 +15102,7 @@
       <c r="E133" s="12" t="inlineStr"/>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>188</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -15118,63 +15112,67 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="K133" s="9" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="N133" s="12" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="O133" s="11" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P133" s="9" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q133" s="11" t="inlineStr"/>
+          <t>UM 03754097</t>
+        </is>
+      </c>
+      <c r="Q133" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+        </is>
+      </c>
       <c r="R133" s="11" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S133" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T133" s="12" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U133" s="7" t="inlineStr">
@@ -15182,14 +15180,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V133" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W133" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V133" s="11" t="inlineStr"/>
+      <c r="W133" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X133" s="7" t="inlineStr">
@@ -15209,7 +15203,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -15220,7 +15214,7 @@
       <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -15230,53 +15224,53 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
+          <t>K 3418837</t>
         </is>
       </c>
       <c r="Q134" s="4" t="inlineStr"/>
       <c r="R134" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son texnikumi</t>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S134" s="5" t="inlineStr">
@@ -15286,7 +15280,7 @@
       </c>
       <c r="T134" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="U134" s="7" t="inlineStr">
@@ -15296,12 +15290,12 @@
       </c>
       <c r="V134" s="4" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
-        </is>
-      </c>
-      <c r="W134" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W134" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
         </is>
       </c>
       <c r="X134" s="7" t="inlineStr">
@@ -15316,84 +15310,84 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira</t>
-        </is>
-      </c>
-      <c r="D135" s="11" t="inlineStr"/>
+          <t>Yuldosheva Ruhshona</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E135" s="12" t="inlineStr"/>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Farxod qizi</t>
+          <t>Xabibullo qizi</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr">
         <is>
-          <t>AE4512271</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>62501095720012</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
-          <t>25.01.2009</t>
+          <t>13.09.2008</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="P135" s="9" t="inlineStr">
         <is>
-          <t>UM 03718322</t>
-        </is>
-      </c>
-      <c r="Q135" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160259/3907782/88616609-4fee-4140-8c92-b0e3d21c7944?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q135" s="11" t="inlineStr"/>
       <c r="R135" s="11" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
       <c r="S135" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T135" s="12" t="inlineStr">
@@ -15408,12 +15402,12 @@
       </c>
       <c r="V135" s="11" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'ABDIXOLIQOVA ELMIRA' | bazada: 'Abduxoliqova Elmira'; imlo farqi — Shahodatnoma PDF: 'Abdixoliqova Elmira Farxod qizi' | bazada: 'Abduxoliqova Elmira'</t>
-        </is>
-      </c>
-      <c r="W135" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
+        </is>
+      </c>
+      <c r="W135" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X135" s="7" t="inlineStr">
@@ -15433,78 +15427,74 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Bahodirova Asila</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Abdixoliqova Elmira</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-07 00:00:00</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Olmos qizi</t>
+          <t>Farxod qizi</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>AE1222596</t>
+          <t>AE4512271</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>61711085590032</t>
+          <t>62501095720012</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>16.01.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr">
         <is>
-          <t>17.11.2008</t>
+          <t>25.01.2009</t>
         </is>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>UM 03753386</t>
+          <t>UM 03718322</t>
         </is>
       </c>
       <c r="Q136" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3364811/3243239/86966b2b-ec7a-4817-bfa2-68cd1aceff78?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160259/3907782/88616609-4fee-4140-8c92-b0e3d21c7944?preview=true</t>
         </is>
       </c>
       <c r="R136" s="4" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S136" s="5" t="inlineStr">
@@ -15522,10 +15512,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V136" s="4" t="inlineStr"/>
-      <c r="W136" s="8" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
+      <c r="V136" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'ABDIXOLIQOVA ELMIRA' | bazada: 'Abduxoliqova Elmira'; imlo farqi — Shahodatnoma PDF: 'Abdixoliqova Elmira Farxod qizi' | bazada: 'Abduxoliqova Elmira'</t>
+        </is>
+      </c>
+      <c r="W136" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X136" s="7" t="inlineStr">
@@ -15545,91 +15539,99 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D137" s="11" t="inlineStr"/>
+          <t>Bahodirova Asila</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E137" s="12" t="inlineStr"/>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="G137" s="18" t="n">
-        <v>46281</v>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Husan qizi</t>
+          <t>Olmos qizi</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="K137" s="9" t="inlineStr">
         <is>
-          <t>AD8208717</t>
+          <t>AE1222596</t>
         </is>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>41508955590021</t>
+          <t>61711085590032</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>12.08.2024</t>
+          <t>16.01.2025</t>
         </is>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
-          <t>15.08.1995</t>
+          <t>17.11.2008</t>
         </is>
       </c>
       <c r="O137" s="11" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="P137" s="9" t="inlineStr">
         <is>
-          <t>K 0216332</t>
-        </is>
-      </c>
-      <c r="Q137" s="11" t="inlineStr"/>
+          <t>UM 03753386</t>
+        </is>
+      </c>
+      <c r="Q137" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3364811/3243239/86966b2b-ec7a-4817-bfa2-68cd1aceff78?preview=true</t>
+        </is>
+      </c>
       <c r="R137" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz Yengil sanoat kasb-hunar kolleji</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S137" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T137" s="12" t="n">
-        <v>2014</v>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T137" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U137" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V137" s="11" t="inlineStr">
-        <is>
-          <t>KARANTIN: ❌ Bir xil PINFL (41508955590021) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06]; ❌ Bir xil Pasport (AD8208717) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06] || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
-        </is>
-      </c>
+      <c r="V137" s="11" t="inlineStr"/>
       <c r="W137" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X137" s="7" t="inlineStr">
@@ -15649,91 +15651,91 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Eshimova Zilola</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Davlatova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="G138" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="n">
+        <v>46281</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Bekzod qizi</t>
+          <t>Husan qizi</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
+          <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
+          <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>AE2935693</t>
+          <t>AD8208717</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>61506085730076</t>
+          <t>41508955590021</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>09.06.2025</t>
+          <t>12.08.2024</t>
         </is>
       </c>
       <c r="N138" s="5" t="inlineStr">
         <is>
-          <t>15.06.2008</t>
-        </is>
-      </c>
-      <c r="O138" s="4" t="inlineStr"/>
+          <t>15.08.1995</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>Davlatova Gulnoza Husan qizi</t>
+        </is>
+      </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>UM 03756027</t>
+          <t>K 0216332</t>
         </is>
       </c>
       <c r="Q138" s="4" t="inlineStr"/>
       <c r="R138" s="4" t="inlineStr">
         <is>
-          <t>4-maktab</t>
+          <t>Shahrisabz Yengil sanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S138" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T138" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U138" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V138" s="4" t="inlineStr"/>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T138" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="U138" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V138" s="4" t="inlineStr">
+        <is>
+          <t>KARANTIN: ❌ Bir xil PINFL (41508955590021) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06]; ❌ Bir xil Pasport (AD8208717) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06] || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
+        </is>
+      </c>
       <c r="W138" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X138" s="7" t="inlineStr">
@@ -15753,7 +15755,7 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam</t>
+          <t>Eshimova Zilola</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
@@ -15764,7 +15766,7 @@
       <c r="E139" s="12" t="inlineStr"/>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -15774,57 +15776,49 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Ozodjon qizi</t>
+          <t>Bekzod qizi</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
+          <t>Eshimova Zilola Bekzod qizi</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
+          <t>Eshimova Zilola Bekzod qizi</t>
         </is>
       </c>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>AD9937321</t>
+          <t>AE2935693</t>
         </is>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>60603085590037</t>
+          <t>61506085730076</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>24.12.2024</t>
+          <t>09.06.2025</t>
         </is>
       </c>
       <c r="N139" s="12" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
-        </is>
-      </c>
-      <c r="O139" s="11" t="inlineStr">
-        <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
+          <t>15.06.2008</t>
+        </is>
+      </c>
+      <c r="O139" s="11" t="inlineStr"/>
       <c r="P139" s="9" t="inlineStr">
         <is>
-          <t>UM 03752997</t>
-        </is>
-      </c>
-      <c r="Q139" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03756027</t>
+        </is>
+      </c>
+      <c r="Q139" s="11" t="inlineStr"/>
       <c r="R139" s="11" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>4-maktab</t>
         </is>
       </c>
       <c r="S139" s="12" t="inlineStr">
@@ -15837,15 +15831,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U139" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U139" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V139" s="11" t="inlineStr"/>
       <c r="W139" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X139" s="7" t="inlineStr">
@@ -15865,7 +15859,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida</t>
+          <t>Jalilova Shabnam</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -15876,7 +15870,7 @@
       <c r="E140" s="5" t="inlineStr"/>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -15886,52 +15880,52 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Shovkat qizi</t>
+          <t>Ozodjon qizi</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>AE6299685</t>
+          <t>AD9937321</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>60907085590063</t>
+          <t>60603085590037</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>24.12.2024</t>
         </is>
       </c>
       <c r="N140" s="5" t="inlineStr">
         <is>
-          <t>09.07.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>UM 03752998</t>
+          <t>UM 03752997</t>
         </is>
       </c>
       <c r="Q140" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
         </is>
       </c>
       <c r="R140" s="4" t="inlineStr">
@@ -15955,9 +15949,9 @@
         </is>
       </c>
       <c r="V140" s="4" t="inlineStr"/>
-      <c r="W140" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+      <c r="W140" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X140" s="7" t="inlineStr">
@@ -15977,74 +15971,78 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Karimova Nozliya</t>
-        </is>
-      </c>
-      <c r="D141" s="11" t="inlineStr"/>
+          <t>Jumayeva Husnida</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E141" s="12" t="inlineStr"/>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Rustamovna</t>
+          <t>Shovkat qizi</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="K141" s="9" t="inlineStr">
         <is>
-          <t>AE4674508</t>
+          <t>AE6299685</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>61502085680047</t>
+          <t>60907085590063</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
-          <t>15.02.2008</t>
+          <t>09.07.2008</t>
         </is>
       </c>
       <c r="O141" s="11" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="P141" s="9" t="inlineStr">
         <is>
-          <t>UM 03729342</t>
+          <t>UM 03752998</t>
         </is>
       </c>
       <c r="Q141" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
         </is>
       </c>
       <c r="R141" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S141" s="12" t="inlineStr">
@@ -16063,9 +16061,9 @@
         </is>
       </c>
       <c r="V141" s="11" t="inlineStr"/>
-      <c r="W141" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W141" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
       </c>
       <c r="X141" s="7" t="inlineStr">
@@ -16085,84 +16083,84 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Karimova Nozliya</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr"/>
       <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Safarali qizi</t>
+          <t>Rustamovna</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>AE2103843</t>
+          <t>AE4674508</t>
         </is>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>60705005680087</t>
+          <t>61502085680047</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>27.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr">
         <is>
-          <t>07.05.2000</t>
+          <t>15.02.2008</t>
         </is>
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>Mahmamurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>K 5493345</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr"/>
+          <t>UM 03729342</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+        </is>
+      </c>
       <c r="R142" s="4" t="inlineStr">
         <is>
-          <t>Kitob agrobiznes kasb-hunar kolleji</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S142" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T142" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U142" s="7" t="inlineStr">
@@ -16170,14 +16168,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V142" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
-        </is>
-      </c>
-      <c r="W142" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: BOSHQA ODAM</t>
+      <c r="V142" s="4" t="inlineStr"/>
+      <c r="W142" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X142" s="7" t="inlineStr">
@@ -16197,7 +16191,7 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna</t>
+          <t>Mahmadmurodova Sevara</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
@@ -16208,7 +16202,7 @@
       <c r="E143" s="12" t="inlineStr"/>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>390</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -16218,67 +16212,63 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>To'ra qizi</t>
+          <t>Safarali qizi</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE2103843</t>
         </is>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60705005680087</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="N143" s="12" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>07.05.2000</t>
         </is>
       </c>
       <c r="O143" s="11" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mahmamurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="P143" s="9" t="inlineStr">
         <is>
-          <t>UM 03730531</t>
-        </is>
-      </c>
-      <c r="Q143" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
-        </is>
-      </c>
+          <t>K 5493345</t>
+        </is>
+      </c>
+      <c r="Q143" s="11" t="inlineStr"/>
       <c r="R143" s="11" t="inlineStr">
         <is>
-          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S143" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T143" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U143" s="7" t="inlineStr">
@@ -16286,10 +16276,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V143" s="11" t="inlineStr"/>
-      <c r="W143" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V143" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
+        </is>
+      </c>
+      <c r="W143" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: BOSHQA ODAM</t>
         </is>
       </c>
       <c r="X143" s="7" t="inlineStr">
@@ -16309,7 +16303,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda</t>
+          <t>Mahmudova Maftuna</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -16320,7 +16314,7 @@
       <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -16330,27 +16324,27 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Nosir qizi</t>
+          <t>To'ra qizi</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
@@ -16360,27 +16354,27 @@
       </c>
       <c r="N144" s="5" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>UM 03728995</t>
+          <t>UM 03730531</t>
         </is>
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
         </is>
       </c>
       <c r="R144" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S144" s="5" t="inlineStr">
@@ -16421,74 +16415,78 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda</t>
-        </is>
-      </c>
-      <c r="D145" s="11" t="inlineStr"/>
+          <t>Mannonova Shahrizoda</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E145" s="12" t="inlineStr"/>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Hasan qizi</t>
+          <t>Nosir qizi</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="N145" s="12" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>07.10.2008</t>
         </is>
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="P145" s="9" t="inlineStr">
         <is>
-          <t>UM 03718284</t>
+          <t>UM 03728995</t>
         </is>
       </c>
       <c r="Q145" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
         </is>
       </c>
       <c r="R145" s="11" t="inlineStr">
         <is>
-          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S145" s="12" t="inlineStr">
@@ -16529,56 +16527,100 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Muminova Durdona</t>
+          <t>Maxmarajabova Zerda</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr"/>
-      <c r="F146" s="5" t="inlineStr"/>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Anvar qizi</t>
+          <t>Hasan qizi</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Muminova Durdona Anvar qizi</t>
-        </is>
-      </c>
-      <c r="J146" s="5" t="inlineStr"/>
-      <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="5" t="inlineStr"/>
-      <c r="M146" s="5" t="inlineStr"/>
-      <c r="N146" s="5" t="inlineStr"/>
-      <c r="O146" s="4" t="inlineStr"/>
-      <c r="P146" s="2" t="inlineStr"/>
-      <c r="Q146" s="4" t="inlineStr"/>
-      <c r="R146" s="4" t="inlineStr"/>
-      <c r="S146" s="5" t="inlineStr"/>
-      <c r="T146" s="5" t="inlineStr"/>
-      <c r="U146" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V146" s="4" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W146" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X146" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>AE5221552</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>60106075720246</t>
+        </is>
+      </c>
+      <c r="M146" s="5" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="N146" s="5" t="inlineStr">
+        <is>
+          <t>01.06.2007</t>
+        </is>
+      </c>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>UM 03718284</t>
+        </is>
+      </c>
+      <c r="Q146" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+        </is>
+      </c>
+      <c r="R146" s="4" t="inlineStr">
+        <is>
+          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S146" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T146" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U146" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V146" s="4" t="inlineStr"/>
+      <c r="W146" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X146" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -16593,104 +16635,56 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Muminova Sevinch</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Muminova Durdona</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr"/>
       <c r="E147" s="12" t="inlineStr"/>
-      <c r="F147" s="12" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+      <c r="F147" s="12" t="inlineStr"/>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Anvar qizi</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="J147" s="12" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="K147" s="9" t="inlineStr">
-        <is>
-          <t>AE2259069</t>
-        </is>
-      </c>
-      <c r="L147" s="12" t="inlineStr">
-        <is>
-          <t>63001085590111</t>
-        </is>
-      </c>
-      <c r="M147" s="12" t="inlineStr">
-        <is>
-          <t>09.04.2025</t>
-        </is>
-      </c>
-      <c r="N147" s="12" t="inlineStr">
-        <is>
-          <t>30.01.2008</t>
-        </is>
-      </c>
-      <c r="O147" s="11" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="P147" s="9" t="inlineStr">
-        <is>
-          <t>UM 03752895</t>
-        </is>
-      </c>
-      <c r="Q147" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
-        </is>
-      </c>
-      <c r="R147" s="11" t="inlineStr">
-        <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S147" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T147" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U147" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V147" s="11" t="inlineStr"/>
-      <c r="W147" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X147" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Muminova Durdona Anvar qizi</t>
+        </is>
+      </c>
+      <c r="J147" s="12" t="inlineStr"/>
+      <c r="K147" s="9" t="inlineStr"/>
+      <c r="L147" s="12" t="inlineStr"/>
+      <c r="M147" s="12" t="inlineStr"/>
+      <c r="N147" s="12" t="inlineStr"/>
+      <c r="O147" s="11" t="inlineStr"/>
+      <c r="P147" s="9" t="inlineStr"/>
+      <c r="Q147" s="11" t="inlineStr"/>
+      <c r="R147" s="11" t="inlineStr"/>
+      <c r="S147" s="12" t="inlineStr"/>
+      <c r="T147" s="12" t="inlineStr"/>
+      <c r="U147" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V147" s="11" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W147" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X147" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -16705,7 +16699,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha</t>
+          <t>Muminova Sevinch</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -16716,7 +16710,7 @@
       <c r="E148" s="5" t="inlineStr"/>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>163</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -16726,57 +16720,57 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Zaxriddin qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="N148" s="5" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>30.01.2008</t>
         </is>
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>UM 03751925</t>
+          <t>UM 03752895</t>
         </is>
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
         </is>
       </c>
       <c r="R148" s="4" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S148" s="5" t="inlineStr">
@@ -16817,56 +16811,104 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="D149" s="11" t="inlineStr"/>
+          <t>Muxtorova Xadicha</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E149" s="12" t="inlineStr"/>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="H149" s="11" t="inlineStr"/>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H149" s="11" t="inlineStr">
+        <is>
+          <t>Zaxriddin qizi</t>
+        </is>
+      </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="J149" s="12" t="inlineStr"/>
-      <c r="K149" s="9" t="inlineStr"/>
-      <c r="L149" s="12" t="inlineStr"/>
-      <c r="M149" s="12" t="inlineStr"/>
-      <c r="N149" s="12" t="inlineStr"/>
-      <c r="O149" s="11" t="inlineStr"/>
-      <c r="P149" s="9" t="inlineStr"/>
-      <c r="Q149" s="11" t="inlineStr"/>
-      <c r="R149" s="11" t="inlineStr"/>
-      <c r="S149" s="12" t="inlineStr"/>
-      <c r="T149" s="12" t="inlineStr"/>
-      <c r="U149" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V149" s="11" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W149" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X149" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="J149" s="12" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="K149" s="9" t="inlineStr">
+        <is>
+          <t>AE2428256</t>
+        </is>
+      </c>
+      <c r="L149" s="12" t="inlineStr">
+        <is>
+          <t>60506085590066</t>
+        </is>
+      </c>
+      <c r="M149" s="12" t="inlineStr">
+        <is>
+          <t>22.04.2025</t>
+        </is>
+      </c>
+      <c r="N149" s="12" t="inlineStr">
+        <is>
+          <t>05.06.2008</t>
+        </is>
+      </c>
+      <c r="O149" s="11" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="P149" s="9" t="inlineStr">
+        <is>
+          <t>UM 03751925</t>
+        </is>
+      </c>
+      <c r="Q149" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+        </is>
+      </c>
+      <c r="R149" s="11" t="inlineStr">
+        <is>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S149" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T149" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U149" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V149" s="11" t="inlineStr"/>
+      <c r="W149" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X149" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -16881,104 +16923,56 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr"/>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>304</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>Mirsharaf qizi</t>
-        </is>
-      </c>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr"/>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="J150" s="5" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>AD9494409</t>
-        </is>
-      </c>
-      <c r="L150" s="5" t="inlineStr">
-        <is>
-          <t>60504085680019</t>
-        </is>
-      </c>
-      <c r="M150" s="5" t="inlineStr">
-        <is>
-          <t>20.11.2024</t>
-        </is>
-      </c>
-      <c r="N150" s="5" t="inlineStr">
-        <is>
-          <t>05.04.2008</t>
-        </is>
-      </c>
-      <c r="O150" s="4" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="P150" s="2" t="inlineStr">
-        <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q150" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
-      <c r="R150" s="4" t="inlineStr">
-        <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S150" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T150" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U150" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V150" s="4" t="inlineStr"/>
-      <c r="W150" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X150" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="5" t="inlineStr"/>
+      <c r="M150" s="5" t="inlineStr"/>
+      <c r="N150" s="5" t="inlineStr"/>
+      <c r="O150" s="4" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="4" t="inlineStr"/>
+      <c r="R150" s="4" t="inlineStr"/>
+      <c r="S150" s="5" t="inlineStr"/>
+      <c r="T150" s="5" t="inlineStr"/>
+      <c r="U150" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V150" s="4" t="inlineStr">
+        <is>
+          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W150" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X150" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -16993,7 +16987,7 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza</t>
+          <t>Nuraliyeva Sevinch</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
@@ -17004,7 +16998,7 @@
       <c r="E151" s="12" t="inlineStr"/>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -17014,53 +17008,57 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Zokir qizi</t>
+          <t>Mirsharaf qizi</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>20.11.2024</t>
         </is>
       </c>
       <c r="N151" s="12" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="P151" s="9" t="inlineStr">
         <is>
-          <t>UM 1313018</t>
-        </is>
-      </c>
-      <c r="Q151" s="11" t="inlineStr"/>
+          <t>UM 03729348</t>
+        </is>
+      </c>
+      <c r="Q151" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
+        </is>
+      </c>
       <c r="R151" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S151" s="12" t="inlineStr">
@@ -17070,7 +17068,7 @@
       </c>
       <c r="T151" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
@@ -17081,7 +17079,7 @@
       <c r="V151" s="11" t="inlineStr"/>
       <c r="W151" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X151" s="7" t="inlineStr">
@@ -17101,7 +17099,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo</t>
+          <t>Ortiqova Dilnoza</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -17112,7 +17110,7 @@
       <c r="E152" s="5" t="inlineStr"/>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -17122,57 +17120,53 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Talantjon qizi</t>
+          <t>Zokir qizi</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="N152" s="5" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>UM 03753960</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1313018</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="inlineStr"/>
       <c r="R152" s="4" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S152" s="5" t="inlineStr">
@@ -17182,7 +17176,7 @@
       </c>
       <c r="T152" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U152" s="7" t="inlineStr">
@@ -17193,7 +17187,7 @@
       <c r="V152" s="4" t="inlineStr"/>
       <c r="W152" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X152" s="7" t="inlineStr">
@@ -17213,7 +17207,7 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso</t>
+          <t>Qarshiyeva Shahlo</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
@@ -17224,7 +17218,7 @@
       <c r="E153" s="12" t="inlineStr"/>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -17234,49 +17228,57 @@
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Talantjon qizi</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="N153" s="12" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
-        </is>
-      </c>
-      <c r="O153" s="11" t="inlineStr"/>
+          <t>22.01.2008</t>
+        </is>
+      </c>
+      <c r="O153" s="11" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+        </is>
+      </c>
       <c r="P153" s="9" t="inlineStr">
         <is>
-          <t>UM 03742130</t>
-        </is>
-      </c>
-      <c r="Q153" s="11" t="inlineStr"/>
+          <t>UM 03753960</t>
+        </is>
+      </c>
+      <c r="Q153" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
+        </is>
+      </c>
       <c r="R153" s="11" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S153" s="12" t="inlineStr">
@@ -17289,19 +17291,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U153" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V153" s="11" t="inlineStr">
-        <is>
-          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
-        </is>
-      </c>
+      <c r="U153" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V153" s="11" t="inlineStr"/>
       <c r="W153" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X153" s="7" t="inlineStr">
@@ -17321,78 +17319,70 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
+          <t>Quchqarova Zebiniso</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi</t>
+          <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr"/>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="N154" s="5" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
-        </is>
-      </c>
-      <c r="O154" s="4" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>29.11.2008</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr"/>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03742130</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="inlineStr"/>
       <c r="R154" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S154" s="5" t="inlineStr">
@@ -17410,10 +17400,14 @@
           <t>CHALA</t>
         </is>
       </c>
-      <c r="V154" s="4" t="inlineStr"/>
+      <c r="V154" s="4" t="inlineStr">
+        <is>
+          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
+        </is>
+      </c>
       <c r="W154" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X154" s="7" t="inlineStr">
@@ -17433,7 +17427,7 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
+          <t>Samiyeva Sevinchbonu</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
@@ -17444,67 +17438,67 @@
       <c r="E155" s="12" t="inlineStr"/>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="O155" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P155" s="9" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q155" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R155" s="11" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S155" s="12" t="inlineStr">
@@ -17523,9 +17517,9 @@
         </is>
       </c>
       <c r="V155" s="11" t="inlineStr"/>
-      <c r="W155" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W155" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X155" s="7" t="inlineStr">
@@ -17545,89 +17539,93 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
+          <t>Sanaqulova Muxtarama</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
+          <t>Hamshiralik ishi</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr"/>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="N156" s="5" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q156" s="4" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R156" s="4" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S156" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T156" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U156" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U156" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V156" s="4" t="inlineStr"/>
@@ -17653,84 +17651,84 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr"/>
+          <t>Sanaqulova Nozliya</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E157" s="12" t="inlineStr"/>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P157" s="9" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q157" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 5509185</t>
+        </is>
+      </c>
+      <c r="Q157" s="11" t="inlineStr"/>
       <c r="R157" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S157" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T157" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
@@ -17738,14 +17736,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V157" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W157" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+      <c r="V157" s="11" t="inlineStr"/>
+      <c r="W157" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X157" s="7" t="inlineStr">
@@ -17765,78 +17759,74 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 2 yillik</t>
-        </is>
-      </c>
+          <t>Sayfillayeva Shodiyona</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr"/>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q158" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S158" s="5" t="inlineStr">
@@ -17846,7 +17836,7 @@
       </c>
       <c r="T158" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U158" s="7" t="inlineStr">
@@ -17854,10 +17844,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V158" s="4" t="inlineStr"/>
-      <c r="W158" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V158" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W158" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X158" s="7" t="inlineStr">
@@ -17877,18 +17871,18 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
+          <t>Hamshiralik ishi - 2 yillik</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr"/>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
@@ -17898,53 +17892,57 @@
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="N159" s="12" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P159" s="9" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q159" s="11" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q159" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R159" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S159" s="12" t="inlineStr">
@@ -17954,7 +17952,7 @@
       </c>
       <c r="T159" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U159" s="7" t="inlineStr">
@@ -17965,7 +17963,7 @@
       <c r="V159" s="11" t="inlineStr"/>
       <c r="W159" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X159" s="7" t="inlineStr">
@@ -17985,7 +17983,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -17996,7 +17994,7 @@
       <c r="E160" s="5" t="inlineStr"/>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -18006,57 +18004,53 @@
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="N160" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q160" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02172469</t>
+        </is>
+      </c>
+      <c r="Q160" s="4" t="inlineStr"/>
       <c r="R160" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S160" s="5" t="inlineStr">
@@ -18066,7 +18060,7 @@
       </c>
       <c r="T160" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U160" s="7" t="inlineStr">
@@ -18077,7 +18071,7 @@
       <c r="V160" s="4" t="inlineStr"/>
       <c r="W160" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X160" s="7" t="inlineStr">
@@ -18097,7 +18091,7 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yahyomurodova Gulsanam</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
@@ -18108,7 +18102,7 @@
       <c r="E161" s="12" t="inlineStr"/>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G161" s="12" t="inlineStr">
@@ -18118,57 +18112,57 @@
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="N161" s="12" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P161" s="9" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q161" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R161" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S161" s="12" t="inlineStr">
@@ -18204,12 +18198,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -18220,71 +18214,77 @@
       <c r="E162" s="5" t="inlineStr"/>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="n">
-        <v>46161</v>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>G‘ani qizi</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila G‘ani qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila G‘ani qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>AE5575300</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>41011925590038</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="N162" s="5" t="inlineStr">
         <is>
-          <t>10.11.1992</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila G‘ani qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>L 125287</t>
-        </is>
-      </c>
-      <c r="Q162" s="4" t="inlineStr"/>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
       <c r="R162" s="4" t="inlineStr">
         <is>
-          <t>Toshkent irrigatsiya va melioratsiya instituti qoshidagi akademik litsey</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S162" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T162" s="5" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U162" s="7" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor</t>
+          <t>G‘aniyeva Asila</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
@@ -18326,61 +18326,61 @@
       <c r="E163" s="12" t="inlineStr"/>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>381</t>
         </is>
       </c>
       <c r="G163" s="18" t="n">
-        <v>46224</v>
+        <v>46161</v>
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>G‘ani qizi</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>G‘aniyeva Asila G‘ani qizi</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>G‘aniyeva Asila G‘ani qizi</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>AD7829399</t>
+          <t>AE5575300</t>
         </is>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>41902975680049</t>
+          <t>41011925590038</t>
         </is>
       </c>
       <c r="M163" s="12" t="inlineStr">
         <is>
-          <t>11.07.2024</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="N163" s="12" t="inlineStr">
         <is>
-          <t>19.02.1997</t>
+          <t>10.11.1992</t>
         </is>
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>G‘aniyeva Asila G‘ani qizi</t>
         </is>
       </c>
       <c r="P163" s="9" t="inlineStr">
         <is>
-          <t>K 0236649</t>
+          <t>L 125287</t>
         </is>
       </c>
       <c r="Q163" s="11" t="inlineStr"/>
       <c r="R163" s="11" t="inlineStr">
         <is>
-          <t>Kitob agrosanoat kasb-hunar kolleji</t>
+          <t>Toshkent irrigatsiya va melioratsiya instituti qoshidagi akademik litsey</t>
         </is>
       </c>
       <c r="S163" s="12" t="inlineStr">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="T163" s="12" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
@@ -30927,7 +30927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Murodova Munisa</t>
+          <t>Muhammadiyeva Gulbahor</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -32668,73 +32668,71 @@
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>46224</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Muxtor qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>AE2895049</t>
+          <t>AD7829399</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>62112085680050</t>
+          <t>41902975680049</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>03.06.2025</t>
+          <t>11.07.2024</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>21.12.2008</t>
+          <t>19.02.1997</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>UM 03753455</t>
+          <t>K 0236649</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr"/>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>Kitob agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="U16" s="7" t="inlineStr">
@@ -32743,9 +32741,9 @@
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X16" s="7" t="inlineStr">
@@ -32765,7 +32763,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona</t>
+          <t>Murodova Munisa</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -32776,71 +32774,73 @@
       <c r="E17" s="12" t="inlineStr"/>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="n">
-        <v>46221</v>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Asrorxon qizi</t>
+          <t>Muxtor qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>AD9123240</t>
+          <t>AE2895049</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>62710075590066</t>
+          <t>62112085680050</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>03.06.2025</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>27.10.2007</t>
+          <t>21.12.2008</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>PT 0257899</t>
+          <t>UM 03753455</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 1-son politexnikumi</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T17" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
@@ -32849,9 +32849,9 @@
         </is>
       </c>
       <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W17" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X17" s="7" t="inlineStr">
@@ -32871,75 +32871,93 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Nazarova Munisa</t>
+          <t>Muzrapova Ruhshona</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi</t>
+          <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>46221</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Erkin qizi</t>
+          <t>Asrorxon qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>AE7685867</t>
+          <t>AD9123240</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>41205925680015</t>
+          <t>62710075590066</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>17.06.2026</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>12.05.1992</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
+          <t>27.10.2007</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>PT 0257899</t>
+        </is>
+      </c>
       <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="5" t="inlineStr"/>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>Shahrisabz shahar 1-son politexnikumi</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X18" s="7" t="inlineStr">
@@ -32959,7 +32977,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch</t>
+          <t>Nazarova Munisa</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -32970,80 +32988,64 @@
       <c r="E19" s="12" t="inlineStr"/>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Hikmatullo qizi</t>
+          <t>Erkin qizi</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr"/>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>AE7082532</t>
+          <t>AE7685867</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>60212085680048</t>
+          <t>41205925680015</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>02.12.2008</t>
+          <t>12.05.1992</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="9" t="inlineStr">
-        <is>
-          <t>UM 03727760</t>
-        </is>
-      </c>
+      <c r="P19" s="9" t="inlineStr"/>
       <c r="Q19" s="11" t="inlineStr"/>
-      <c r="R19" s="11" t="inlineStr">
-        <is>
-          <t>1-maktab</t>
-        </is>
-      </c>
-      <c r="S19" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T19" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U19" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V19" s="11" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W19" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="R19" s="11" t="inlineStr"/>
+      <c r="S19" s="12" t="inlineStr"/>
+      <c r="T19" s="12" t="inlineStr"/>
+      <c r="U19" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr"/>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -33063,74 +33065,66 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam</t>
+          <t>Ne'matova Sevinch</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
+          <t>Hamshiralik ishi</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Elyor qizi</t>
+          <t>Hikmatullo qizi</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>AE4817469</t>
+          <t>AE7082532</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>61809085680096</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>18.09.2008</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+          <t>02.12.2008</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>UM 03728575</t>
+          <t>UM 03727760</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>1-maktab</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -33143,15 +33137,19 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr"/>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="U20" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W20" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -33171,7 +33169,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Omonova Charos</t>
+          <t>Normurodova Gulsanam</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -33182,7 +33180,7 @@
       <c r="E21" s="12" t="inlineStr"/>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -33192,63 +33190,63 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Elyor qizi</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>AE1338424</t>
+          <t>AE4817469</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>40306985590014</t>
+          <t>61809085680096</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>03.06.1998</t>
+          <t>18.09.2008</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>K 5023908</t>
+          <t>UM 03728575</t>
         </is>
       </c>
       <c r="Q21" s="11" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -33279,83 +33277,95 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Oripova Sevinch</t>
+          <t>Omonova Charos</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Hamshiralik ishi</t>
+          <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>G'olib qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Oripova Sevinch G'olib qizi</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr"/>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>AE3333890</t>
+          <t>AE1338424</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>62007085680095</t>
+          <t>40306985590014</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>09.07.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>20.07.2008</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr"/>
+          <t>03.06.1998</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 03729323</t>
+          <t>K 5023908</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>45-maktab</t>
+          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U22" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
-      <c r="W22" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
@@ -33375,72 +33385,62 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Ozodova Klara</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr"/>
+          <t>Oripova Sevinch</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
       <c r="E23" s="12" t="inlineStr"/>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>46272</v>
+      <c r="F23" s="12" t="inlineStr"/>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Fayzullayevna</t>
+          <t>G'olib qizi</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>Oripova Sevinch G'olib qizi</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr"/>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>AD6663341</t>
+          <t>AE3333890</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>60803075590140</t>
+          <t>62007085680095</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>01.04.2024</t>
+          <t>09.07.2025</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>08.03.2007</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>20.07.2008</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr"/>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03298601</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03729323</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>45-maktab</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
@@ -33450,18 +33450,18 @@
       </c>
       <c r="T23" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U23" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W23" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X23" s="7" t="inlineStr">
@@ -33481,78 +33481,72 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Ozodova Klara</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Ilyos qizi</t>
+          <t>Fayzullayevna</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>AE6043288</t>
+          <t>AD6663341</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>60511085680024</t>
+          <t>60803075590140</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>01.04.2024</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>05.11.2008</t>
+          <t>08.03.2007</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03730668</t>
+          <t>UM 03298601</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
         </is>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
@@ -33562,7 +33556,7 @@
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U24" s="7" t="inlineStr">
@@ -33593,7 +33587,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Sharipova Diyora</t>
+          <t>Saidova Dilso'z</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -33604,7 +33598,7 @@
       <c r="E25" s="12" t="inlineStr"/>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -33614,57 +33608,57 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Ilyos qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AE6043288</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>60511085680024</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>05.11.2008</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03751494</t>
+          <t>UM 03730668</t>
         </is>
       </c>
       <c r="Q25" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
         </is>
       </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
@@ -33705,7 +33699,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara</t>
+          <t>Sharipova Diyora</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -33716,7 +33710,7 @@
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -33726,53 +33720,57 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Ilxom qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
+          <t>23.07.2009</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 1319051</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+          <t>UM 03751494</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
+          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -33782,7 +33780,7 @@
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -33793,7 +33791,7 @@
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -33813,74 +33811,74 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Aziza</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr"/>
+          <t>Toshmurodova Sarvara</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
       <c r="E27" s="12" t="inlineStr"/>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>388</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Anvarovna</t>
+          <t>Ilxom qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>28.03.2005</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 02172465</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1319051</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
@@ -33890,7 +33888,7 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -33921,78 +33919,74 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Fotima</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Tursunova Aziza</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Qosim qizi</t>
+          <t>Anvarovna</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03730083</t>
+          <t>UM 02172465</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
         </is>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -34002,7 +33996,7 @@
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U28" s="7" t="inlineStr">
@@ -34013,7 +34007,7 @@
       <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X28" s="7" t="inlineStr">
@@ -34033,7 +34027,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra</t>
+          <t>Tursunova Fotima</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -34044,7 +34038,7 @@
       <c r="E29" s="12" t="inlineStr"/>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -34059,22 +34053,22 @@
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
@@ -34089,17 +34083,17 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03730084</t>
+          <t>UM 03730083</t>
         </is>
       </c>
       <c r="Q29" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
         </is>
       </c>
       <c r="R29" s="11" t="inlineStr">
@@ -34145,7 +34139,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina</t>
+          <t>Tursunova Zuhra</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -34156,7 +34150,7 @@
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -34166,57 +34160,57 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Qosim qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>27.10.2008</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03754097</t>
+          <t>UM 03730084</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -34257,7 +34251,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Usmonova Sabrina</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -34268,7 +34262,7 @@
       <c r="E31" s="12" t="inlineStr"/>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>188</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -34278,63 +34272,67 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q31" s="11" t="inlineStr"/>
+          <t>UM 03754097</t>
+        </is>
+      </c>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+        </is>
+      </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T31" s="12" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -34342,14 +34340,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W31" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V31" s="11" t="inlineStr"/>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X31" s="7" t="inlineStr">
@@ -34369,7 +34363,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -34380,7 +34374,7 @@
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -34390,88 +34384,200 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
+          <t>K 3418837</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W32" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
+        </is>
+      </c>
+      <c r="X32" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Yuldosheva Ruhshona</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr"/>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Xabibullo qizi</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>AE1419035</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>61309085590066</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>29.01.2025</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="inlineStr">
+        <is>
+          <t>13.09.2008</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q33" s="11" t="inlineStr"/>
+      <c r="R33" s="11" t="inlineStr">
+        <is>
           <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
-      <c r="S32" s="5" t="inlineStr">
+      <c r="S33" s="12" t="inlineStr">
         <is>
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T32" s="5" t="inlineStr">
+      <c r="T33" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="U32" s="7" t="inlineStr">
+      <c r="U33" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V32" s="4" t="inlineStr">
+      <c r="V33" s="11" t="inlineStr">
         <is>
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
         </is>
       </c>
-      <c r="W32" s="13" t="inlineStr">
+      <c r="W33" s="13" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
       </c>
-      <c r="X32" s="7" t="inlineStr">
+      <c r="X33" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X32"/>
+  <autoFilter ref="A1:X33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37533,7 +37639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37801,7 +37907,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor</t>
+          <t>Murtazayeva Kamola</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
@@ -37809,90 +37915,94 @@
           <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr"/>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="G3" s="18" t="n">
-        <v>46224</v>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
-        </is>
-      </c>
+          <t>Murtazayeva Kamola Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr"/>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>AD7829399</t>
+          <t>AC1458884</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>41902975680049</t>
+          <t>42708915590028</t>
         </is>
       </c>
       <c r="M3" s="12" t="inlineStr">
         <is>
-          <t>11.07.2024</t>
+          <t>04.11.2018</t>
         </is>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
-          <t>19.02.1997</t>
+          <t>27.08.1991</t>
         </is>
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>K 0236649</t>
+          <t>O'r-Sh 0987579</t>
         </is>
       </c>
       <c r="Q3" s="11" t="inlineStr"/>
       <c r="R3" s="11" t="inlineStr">
         <is>
-          <t>Kitob agrosanoat kasb-hunar kolleji</t>
+          <t>Ixtisoslashgan maktab</t>
         </is>
       </c>
       <c r="S3" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T3" s="12" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="n">
+        <v>2009</v>
       </c>
       <c r="U3" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V3" s="11" t="inlineStr"/>
+      <c r="V3" s="11" t="inlineStr">
+        <is>
+          <t>Murtazayeva Kamola 25.docx faylidan to'liq kiritildi</t>
+        </is>
+      </c>
       <c r="W3" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X3" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X3" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -37907,7 +38017,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola</t>
+          <t>Mustafayeva Nargiza</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -37915,75 +38025,73 @@
           <t>Hamshiralik ishi - 3 yillik</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+      <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-29 00:00:00</t>
-        </is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>46255</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr"/>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>AC1458884</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>42708915590028</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>04.11.2018</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>27.08.1991</t>
+          <t>29.06.2000</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>O'r-Sh 0987579</t>
+          <t>K 5487472</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr"/>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>Ixtisoslashgan maktab</t>
+          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T4" s="5" t="n">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="U4" s="7" t="inlineStr">
         <is>
@@ -37992,7 +38100,7 @@
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola 25.docx faylidan to'liq kiritildi</t>
+          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
         </is>
       </c>
       <c r="W4" s="8" t="inlineStr">
@@ -38000,9 +38108,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X4" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X4" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38017,7 +38125,7 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza</t>
+          <t>Narziyeva Intizor</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -38028,70 +38136,74 @@
       <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>46255</v>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Ulug‘bek qizi</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>AB8521319</t>
+          <t>AB5359926</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>62906005590060</t>
+          <t>40211995680023</t>
         </is>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>02.01.2018</t>
+          <t>12.12.2016</t>
         </is>
       </c>
       <c r="N5" s="12" t="inlineStr">
         <is>
-          <t>29.06.2000</t>
+          <t>02.11.1999</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>K 5487472</t>
+          <t>K 5047841</t>
         </is>
       </c>
       <c r="Q5" s="11" t="inlineStr"/>
       <c r="R5" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
+          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S5" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T5" s="12" t="n">
-        <v>2019</v>
+          <t>Kasb-hunar kolleji diplomi</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
       </c>
       <c r="U5" s="7" t="inlineStr">
         <is>
@@ -38100,12 +38212,12 @@
       </c>
       <c r="V5" s="11" t="inlineStr">
         <is>
-          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
+          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
         </is>
       </c>
       <c r="W5" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X5" s="7" t="inlineStr">
@@ -38125,7 +38237,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor</t>
+          <t>Salayeva Dilroz</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -38136,7 +38248,7 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>205</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -38144,85 +38256,37 @@
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Iskandar qizi</t>
-        </is>
-      </c>
+      <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>AB5359926</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>40211995680023</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>12.12.2016</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>02.11.1999</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>K 5047841</t>
-        </is>
-      </c>
+          <t>Salayeva Dilroz</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>Kasb-hunar kolleji diplomi</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
-        </is>
-      </c>
-      <c r="X6" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X6" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -38237,165 +38301,101 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Usmonova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr"/>
       <c r="E7" s="12" t="inlineStr"/>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>46272</v>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Xamdam qizi</t>
+        </is>
+      </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr"/>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="12" t="inlineStr"/>
-      <c r="O7" s="11" t="inlineStr"/>
-      <c r="P7" s="9" t="inlineStr"/>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>AB5702170</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>42601925680010</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>19.01.2017</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr">
+        <is>
+          <t>26.01.1992</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>K 1994177</t>
+        </is>
+      </c>
       <c r="Q7" s="11" t="inlineStr"/>
-      <c r="R7" s="11" t="inlineStr"/>
-      <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="12" t="inlineStr"/>
-      <c r="U7" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X7" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>26-07</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>46272</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>AB5702170</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>42601925680010</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>19.01.2017</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>26.01.1992</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>K 1994177</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="R7" s="11" t="inlineStr">
         <is>
           <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="S8" s="5" t="inlineStr">
+      <c r="S7" s="12" t="inlineStr">
         <is>
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T8" s="5" t="n">
+      <c r="T7" s="12" t="n">
         <v>2011</v>
       </c>
-      <c r="U8" s="7" t="inlineStr">
+      <c r="U7" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="V7" s="11" t="inlineStr">
         <is>
           <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
         </is>
       </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="X7" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X8"/>
+  <autoFilter ref="A1:X7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -17013,14 +17013,14 @@
       </c>
       <c r="I151" s="10" t="inlineStr">
         <is>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
+        </is>
+      </c>
+      <c r="J151" s="12" t="inlineStr">
+        <is>
           <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
-      <c r="J151" s="12" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
           <t>AD9494409</t>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P151" s="9" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="R151" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S151" s="12" t="inlineStr">
@@ -36336,14 +36336,14 @@
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
           <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
           <t>AD9494409</t>
@@ -36366,7 +36366,7 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
@@ -36381,7 +36381,7 @@
       </c>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -16987,7 +16987,7 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch</t>
+          <t>Nurillayeva Sevinch</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Mirsharaf qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
@@ -36310,7 +36310,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch</t>
+          <t>Nurillayeva Sevinch</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -36331,7 +36331,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Mirsharaf qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -16987,7 +16987,7 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
+          <t>Nuraliyeva Sevinch</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
@@ -17008,12 +17008,12 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Mashrab qizi</t>
+          <t>Mirsharaf qizi</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="J151" s="12" t="inlineStr">
@@ -17023,32 +17023,32 @@
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>AD9494409</t>
+          <t>AE4360739</t>
         </is>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>60504085680019</t>
+          <t>63006085730022</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="N151" s="12" t="inlineStr">
         <is>
-          <t>05.04.2008</t>
+          <t>30.06.2008</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="P151" s="9" t="inlineStr">
         <is>
-          <t>UM 03729348</t>
+          <t>UM 03756167</t>
         </is>
       </c>
       <c r="Q151" s="11" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="R151" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S151" s="12" t="inlineStr">
@@ -17066,10 +17066,8 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T151" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="T151" s="12" t="n">
+        <v>2026</v>
       </c>
       <c r="U151" s="7" t="inlineStr">
         <is>
@@ -36310,7 +36308,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
+          <t>Nuraliyeva Sevinch</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -36331,12 +36329,12 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Mashrab qizi</t>
+          <t>Mirsharaf qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -36346,32 +36344,32 @@
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>AD9494409</t>
+          <t>AE4360739</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>60504085680019</t>
+          <t>63006085730022</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>05.04.2008</t>
+          <t>30.06.2008</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>UM 03729348</t>
+          <t>UM 03756167</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr">
@@ -36381,7 +36379,7 @@
       </c>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
@@ -36389,10 +36387,8 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T17" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="T17" s="12" t="n">
+        <v>2026</v>
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -16987,7 +16987,7 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch</t>
+          <t>Nurillayeva Sevinch</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
@@ -17008,27 +17008,27 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Mirsharaf qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
         <is>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
+        </is>
+      </c>
+      <c r="J151" s="12" t="inlineStr">
+        <is>
           <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
-      <c r="J151" s="12" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>AE4360739</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>63006085730022</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
@@ -17038,17 +17038,17 @@
       </c>
       <c r="N151" s="12" t="inlineStr">
         <is>
-          <t>30.06.2008</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P151" s="9" t="inlineStr">
         <is>
-          <t>UM 03756167</t>
+          <t>UM 03729348</t>
         </is>
       </c>
       <c r="Q151" s="11" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="R151" s="11" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S151" s="12" t="inlineStr">
@@ -36308,7 +36308,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch</t>
+          <t>Nurillayeva Sevinch</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -36329,27 +36329,27 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Mirsharaf qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
           <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>AE4360739</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>63006085730022</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
@@ -36359,17 +36359,17 @@
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>30.06.2008</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>UM 03756167</t>
+          <t>UM 03729348</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr">
@@ -36379,7 +36379,7 @@
       </c>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -17066,8 +17066,10 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T151" s="12" t="n">
-        <v>2026</v>
+      <c r="T151" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
         <is>
@@ -36387,8 +36389,10 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T17" s="12" t="n">
-        <v>2026</v>
+      <c r="T17" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26-05 (Rayimova.X)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26-06 (Yuldashev.O)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26-07 (Asraliyev.A)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$170</definedName>
@@ -25,6 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -99,7 +101,7 @@
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +156,12 @@
         <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00991B1B"/>
+        <bgColor rgb="00991B1B"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -195,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -249,6 +257,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -18914,7 +18925,7 @@
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
@@ -19018,7 +19029,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -38398,4 +38409,371 @@
   <autoFilter ref="A1:X7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="35" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Guruh</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>I.F.O</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>Yo'nalishi</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>To'lov statusi</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami</t>
+        </is>
+      </c>
+      <c r="G1" s="19" t="inlineStr">
+        <is>
+          <t>Sanasi</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t>Otasining ismi (Sharifi)</t>
+        </is>
+      </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
+          <t>To'liq F.I.SH</t>
+        </is>
+      </c>
+      <c r="J1" s="19" t="inlineStr">
+        <is>
+          <t>Passport bo'yicha F.I.SH</t>
+        </is>
+      </c>
+      <c r="K1" s="19" t="inlineStr">
+        <is>
+          <t>Passport / ID-karta (Seriya va raqam)</t>
+        </is>
+      </c>
+      <c r="L1" s="19" t="inlineStr">
+        <is>
+          <t>JSHSHIR (PINFL)</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t>Berilgan sanasi</t>
+        </is>
+      </c>
+      <c r="N1" s="19" t="inlineStr">
+        <is>
+          <t>Tug'ilgan sanasi</t>
+        </is>
+      </c>
+      <c r="O1" s="19" t="inlineStr">
+        <is>
+          <t>Shahodatnoma bo'yicha F.I.SH</t>
+        </is>
+      </c>
+      <c r="P1" s="19" t="inlineStr">
+        <is>
+          <t>Shahodatnoma / Diplom Seriyasi</t>
+        </is>
+      </c>
+      <c r="Q1" s="19" t="inlineStr">
+        <is>
+          <t>Shahodatnoma QR Havolasi (e-shahodatnoma.uz)</t>
+        </is>
+      </c>
+      <c r="R1" s="19" t="inlineStr">
+        <is>
+          <t>Tugatgan o'qish joyi</t>
+        </is>
+      </c>
+      <c r="S1" s="19" t="inlineStr">
+        <is>
+          <t>Ta'lim muassasasi turi</t>
+        </is>
+      </c>
+      <c r="T1" s="19" t="inlineStr">
+        <is>
+          <t>Bitirgan yili</t>
+        </is>
+      </c>
+      <c r="U1" s="19" t="inlineStr">
+        <is>
+          <t>Qidiruv holati (Status)</t>
+        </is>
+      </c>
+      <c r="V1" s="19" t="inlineStr">
+        <is>
+          <t>Izoh va Eslatmalar (Notes)</t>
+        </is>
+      </c>
+      <c r="W1" s="19" t="inlineStr">
+        <is>
+          <t>Ism mosligi (Pasport / Shahodatnoma)</t>
+        </is>
+      </c>
+      <c r="X1" s="19" t="inlineStr">
+        <is>
+          <t>Operator Tasdig'i</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Axmedova Saodat</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Hamro qizi</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Axmedova Saodat Hamro qizi</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Axmedova Saodat Hamro qizi</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>AD8221813</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>42504932740019</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>13.08.2024</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>25.04.1993</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>K 1630107</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>Koson maishiy xizmat kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="U2" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr"/>
+      <c r="W2" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X2" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>G'iyosova Shodiyona</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Abduqahhor qizi</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>G'iyosova Shodiyona Abduqahhor qizi</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>AE 4764561</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>60202085590030</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>24.10.2025</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>02.02.2008</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr"/>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t>UM 03752499</t>
+        </is>
+      </c>
+      <c r="Q3" s="11" t="inlineStr"/>
+      <c r="R3" s="11" t="inlineStr">
+        <is>
+          <t>14-maktab</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U3" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V3" s="11" t="inlineStr"/>
+      <c r="W3" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X3" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10529,14 +10529,10 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Qodirova Shabnam</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Qodirova Sabina</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr"/>
       <c r="E91" s="12" t="inlineStr"/>
       <c r="F91" s="12" t="inlineStr">
         <is>
@@ -10550,7 +10546,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>O'tkir qizi</t>
+          <t>Suxrob qizi</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -10563,54 +10559,28 @@
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="K91" s="9" t="inlineStr">
-        <is>
-          <t>AE5242435</t>
-        </is>
-      </c>
-      <c r="L91" s="12" t="inlineStr">
-        <is>
-          <t>61807085680045</t>
-        </is>
-      </c>
-      <c r="M91" s="12" t="inlineStr">
-        <is>
-          <t>01.12.2025</t>
-        </is>
-      </c>
-      <c r="N91" s="12" t="inlineStr">
-        <is>
-          <t>18.07.2008</t>
-        </is>
-      </c>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="12" t="inlineStr"/>
+      <c r="M91" s="12" t="inlineStr"/>
+      <c r="N91" s="12" t="inlineStr"/>
       <c r="O91" s="11" t="inlineStr">
         <is>
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="P91" s="9" t="inlineStr">
-        <is>
-          <t>UM 03729278</t>
-        </is>
-      </c>
+      <c r="P91" s="9" t="inlineStr"/>
       <c r="Q91" s="11" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R91" s="11" t="inlineStr">
-        <is>
-          <t>44-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
+      <c r="R91" s="11" t="inlineStr"/>
       <c r="S91" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T91" s="12" t="n">
-        <v>2026</v>
-      </c>
+      <c r="T91" s="12" t="inlineStr"/>
       <c r="U91" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -29526,14 +29496,10 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Qodirova Shabnam</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
+          <t>Qodirova Sabina</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -29547,7 +29513,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>O'tkir qizi</t>
+          <t>Suxrob qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -29560,54 +29526,28 @@
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>AE5242435</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>61807085680045</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>01.12.2025</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>18.07.2008</t>
-        </is>
-      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
       <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>UM 03729278</t>
-        </is>
-      </c>
+      <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>44-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
+      <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T18" s="5" t="n">
-        <v>2026</v>
-      </c>
+      <c r="T18" s="5" t="inlineStr"/>
       <c r="U18" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10532,7 +10532,11 @@
           <t>Qodirova Sabina</t>
         </is>
       </c>
-      <c r="D91" s="11" t="inlineStr"/>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
       <c r="E91" s="12" t="inlineStr"/>
       <c r="F91" s="12" t="inlineStr">
         <is>
@@ -10551,7 +10555,7 @@
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>Qodirova Shabnam O'tkir qizi</t>
+          <t>Qodirova Sabina Suxrob qizi</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
@@ -29499,7 +29503,11 @@
           <t>Qodirova Sabina</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -29518,7 +29526,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Qodirova Shabnam O'tkir qizi</t>
+          <t>Qodirova Sabina Suxrob qizi</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10578,7 +10578,11 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R91" s="11" t="inlineStr"/>
+      <c r="R91" s="11" t="inlineStr">
+        <is>
+          <t>TEST-SINOV-123</t>
+        </is>
+      </c>
       <c r="S91" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -29549,7 +29553,11 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>TEST-SINOV-123</t>
+        </is>
+      </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10578,11 +10578,7 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R91" s="11" t="inlineStr">
-        <is>
-          <t>TEST-SINOV-123</t>
-        </is>
-      </c>
+      <c r="R91" s="11" t="inlineStr"/>
       <c r="S91" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -29553,11 +29549,7 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>TEST-SINOV-123</t>
-        </is>
-      </c>
+      <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10578,7 +10578,11 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R91" s="11" t="inlineStr"/>
+      <c r="R91" s="11" t="inlineStr">
+        <is>
+          <t>OLCHOV-1</t>
+        </is>
+      </c>
       <c r="S91" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -29549,7 +29553,11 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>OLCHOV-1</t>
+        </is>
+      </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10580,7 +10580,7 @@
       </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>OLCHOV-1</t>
+          <t>BATCH-C</t>
         </is>
       </c>
       <c r="S91" s="12" t="inlineStr">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>OLCHOV-1</t>
+          <t>BATCH-C</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10578,11 +10578,7 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R91" s="11" t="inlineStr">
-        <is>
-          <t>BATCH-C</t>
-        </is>
-      </c>
+      <c r="R91" s="11" t="inlineStr"/>
       <c r="S91" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -29553,11 +29549,7 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>BATCH-C</t>
-        </is>
-      </c>
+      <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10578,7 +10578,11 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R91" s="11" t="inlineStr"/>
+      <c r="R91" s="11" t="inlineStr">
+        <is>
+          <t>OLCHOV-2</t>
+        </is>
+      </c>
       <c r="S91" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -29549,7 +29553,11 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>OLCHOV-2</t>
+        </is>
+      </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10578,11 +10578,7 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R91" s="11" t="inlineStr">
-        <is>
-          <t>OLCHOV-2</t>
-        </is>
-      </c>
+      <c r="R91" s="11" t="inlineStr"/>
       <c r="S91" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -29553,11 +29549,7 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>OLCHOV-2</t>
-        </is>
-      </c>
+      <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10529,7 +10529,7 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Qodirova Sabina</t>
+          <t>Qodirova Sabinaa</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>Qodirova Sabina Suxrob qizi</t>
+          <t>Qodirova Sabinaa Suxrob qizi</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
@@ -10563,7 +10563,11 @@
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="K91" s="9" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
       <c r="L91" s="12" t="inlineStr"/>
       <c r="M91" s="12" t="inlineStr"/>
       <c r="N91" s="12" t="inlineStr"/>
@@ -29500,7 +29504,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Qodirova Sabina</t>
+          <t>Qodirova Sabinaa</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -29526,7 +29530,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Qodirova Sabina Suxrob qizi</t>
+          <t>Qodirova Sabinaa Suxrob qizi</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -29534,7 +29538,11 @@
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr"/>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10582,7 +10582,11 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R91" s="11" t="inlineStr"/>
+      <c r="R91" s="11" t="inlineStr">
+        <is>
+          <t>TUGMA-SINOV</t>
+        </is>
+      </c>
       <c r="S91" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -29557,7 +29561,11 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>TUGMA-SINOV</t>
+        </is>
+      </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10582,11 +10582,7 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R91" s="11" t="inlineStr">
-        <is>
-          <t>TUGMA-SINOV</t>
-        </is>
-      </c>
+      <c r="R91" s="11" t="inlineStr"/>
       <c r="S91" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -29561,11 +29557,7 @@
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>TUGMA-SINOV</t>
-        </is>
-      </c>
+      <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10529,7 +10529,7 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Qodirova Sabinaa</t>
+          <t>Qodirova Sabina</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>Qodirova Sabinaa Suxrob qizi</t>
+          <t>Qodirova Sabina Suxrob qizi</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
@@ -10563,11 +10563,7 @@
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="K91" s="9" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
+      <c r="K91" s="9" t="inlineStr"/>
       <c r="L91" s="12" t="inlineStr"/>
       <c r="M91" s="12" t="inlineStr"/>
       <c r="N91" s="12" t="inlineStr"/>
@@ -29504,7 +29500,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Qodirova Sabinaa</t>
+          <t>Qodirova Sabina</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -29530,7 +29526,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Qodirova Sabinaa Suxrob qizi</t>
+          <t>Qodirova Sabina Suxrob qizi</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -29538,11 +29534,7 @@
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr"/>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -18,13 +18,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$171</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$3</definedName>
   </definedNames>
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X170"/>
+  <dimension ref="A1:X171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -16340,78 +16340,70 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr"/>
+          <t>Mahmatqulova Nilufar</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr"/>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>To'ra qizi</t>
+          <t>Qayum qizi</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
+          <t>Mahmatqulova Nilufar Qayum qizi</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr"/>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE6047826</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60806085590115</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>08.06.2008</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>UM 03730531</t>
-        </is>
-      </c>
-      <c r="Q144" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03754788</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="inlineStr"/>
       <c r="R144" s="4" t="inlineStr">
         <is>
-          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>43-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S144" s="5" t="inlineStr">
@@ -16421,23 +16413,15 @@
       </c>
       <c r="T144" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U144" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U144" s="5" t="inlineStr"/>
       <c r="V144" s="4" t="inlineStr"/>
-      <c r="W144" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X144" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W144" s="15" t="inlineStr"/>
+      <c r="X144" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -16452,13 +16436,13 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda</t>
+          <t>Mahmudova Maftuna</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr"/>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
@@ -16468,27 +16452,27 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Nosir qizi</t>
+          <t>To'ra qizi</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="L145" s="12" t="inlineStr">
@@ -16498,7 +16482,7 @@
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
       <c r="N145" s="12" t="inlineStr">
@@ -16508,22 +16492,22 @@
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="P145" s="9" t="inlineStr">
         <is>
-          <t>UM 03728995</t>
+          <t>UM 03730531</t>
         </is>
       </c>
       <c r="Q145" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
         </is>
       </c>
       <c r="R145" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S145" s="12" t="inlineStr">
@@ -16564,78 +16548,78 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda</t>
+          <t>Mannonova Shahrizoda</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Hasan qizi</t>
+          <t>Nosir qizi</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>07.10.2008</t>
         </is>
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>UM 03718284</t>
+          <t>UM 03728995</t>
         </is>
       </c>
       <c r="Q146" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
         </is>
       </c>
       <c r="R146" s="4" t="inlineStr">
         <is>
-          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S146" s="5" t="inlineStr">
@@ -16676,56 +16660,104 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Muminova Durdona</t>
+          <t>Maxmarajabova Zerda</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr"/>
-      <c r="E147" s="12" t="inlineStr"/>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Anvar qizi</t>
+          <t>Hasan qizi</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Muminova Durdona Anvar qizi</t>
-        </is>
-      </c>
-      <c r="I147" s="10" t="inlineStr"/>
-      <c r="J147" s="12" t="inlineStr"/>
-      <c r="K147" s="9" t="inlineStr"/>
-      <c r="L147" s="12" t="inlineStr"/>
-      <c r="M147" s="12" t="inlineStr"/>
-      <c r="N147" s="12" t="inlineStr"/>
-      <c r="O147" s="11" t="inlineStr"/>
-      <c r="P147" s="9" t="inlineStr"/>
-      <c r="Q147" s="11" t="inlineStr"/>
-      <c r="R147" s="11" t="inlineStr"/>
-      <c r="S147" s="12" t="inlineStr"/>
-      <c r="T147" s="12" t="inlineStr"/>
-      <c r="U147" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V147" s="11" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W147" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X147" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="J147" s="12" t="inlineStr">
+        <is>
+          <t>AE5221552</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>60106075720246</t>
+        </is>
+      </c>
+      <c r="L147" s="12" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="M147" s="12" t="inlineStr">
+        <is>
+          <t>01.06.2007</t>
+        </is>
+      </c>
+      <c r="N147" s="12" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O147" s="11" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="P147" s="9" t="inlineStr">
+        <is>
+          <t>UM 03718284</t>
+        </is>
+      </c>
+      <c r="Q147" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+        </is>
+      </c>
+      <c r="R147" s="11" t="inlineStr">
+        <is>
+          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S147" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T147" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U147" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V147" s="11" t="inlineStr"/>
+      <c r="W147" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X147" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -16740,104 +16772,56 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Muminova Sevinch</t>
+          <t>Muminova Durdona</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+      <c r="E148" s="5" t="inlineStr"/>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Anvar qizi</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="J148" s="5" t="inlineStr">
-        <is>
-          <t>AE2259069</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>63001085590111</t>
-        </is>
-      </c>
-      <c r="L148" s="5" t="inlineStr">
-        <is>
-          <t>09.04.2025</t>
-        </is>
-      </c>
-      <c r="M148" s="5" t="inlineStr">
-        <is>
-          <t>30.01.2008</t>
-        </is>
-      </c>
-      <c r="N148" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O148" s="4" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="P148" s="2" t="inlineStr">
-        <is>
-          <t>UM 03752895</t>
-        </is>
-      </c>
-      <c r="Q148" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
-        </is>
-      </c>
-      <c r="R148" s="4" t="inlineStr">
-        <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S148" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T148" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U148" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V148" s="4" t="inlineStr"/>
-      <c r="W148" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X148" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Muminova Durdona Anvar qizi</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr"/>
+      <c r="J148" s="5" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="5" t="inlineStr"/>
+      <c r="M148" s="5" t="inlineStr"/>
+      <c r="N148" s="5" t="inlineStr"/>
+      <c r="O148" s="4" t="inlineStr"/>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="4" t="inlineStr"/>
+      <c r="R148" s="4" t="inlineStr"/>
+      <c r="S148" s="5" t="inlineStr"/>
+      <c r="T148" s="5" t="inlineStr"/>
+      <c r="U148" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V148" s="4" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W148" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X148" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -16852,13 +16836,13 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha</t>
+          <t>Muminova Sevinch</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr"/>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
@@ -16868,37 +16852,37 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Zaxriddin qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="K149" s="9" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>30.01.2008</t>
         </is>
       </c>
       <c r="N149" s="12" t="inlineStr">
@@ -16908,22 +16892,22 @@
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="P149" s="9" t="inlineStr">
         <is>
-          <t>UM 03751925</t>
+          <t>UM 03752895</t>
         </is>
       </c>
       <c r="Q149" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
         </is>
       </c>
       <c r="R149" s="11" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S149" s="12" t="inlineStr">
@@ -16964,56 +16948,104 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Muxtorova Xadicha</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr"/>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>Zaxriddin qizi</t>
+        </is>
+      </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr"/>
-      <c r="J150" s="5" t="inlineStr"/>
-      <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="5" t="inlineStr"/>
-      <c r="M150" s="5" t="inlineStr"/>
-      <c r="N150" s="5" t="inlineStr"/>
-      <c r="O150" s="4" t="inlineStr"/>
-      <c r="P150" s="2" t="inlineStr"/>
-      <c r="Q150" s="4" t="inlineStr"/>
-      <c r="R150" s="4" t="inlineStr"/>
-      <c r="S150" s="5" t="inlineStr"/>
-      <c r="T150" s="5" t="inlineStr"/>
-      <c r="U150" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V150" s="4" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W150" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X150" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>AE2428256</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>60506085590066</t>
+        </is>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>22.04.2025</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="inlineStr">
+        <is>
+          <t>05.06.2008</t>
+        </is>
+      </c>
+      <c r="N150" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>UM 03751925</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+        </is>
+      </c>
+      <c r="R150" s="4" t="inlineStr">
+        <is>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S150" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T150" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U150" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V150" s="4" t="inlineStr"/>
+      <c r="W150" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X150" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -17028,104 +17060,56 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
+          <t>Niyozova Sevara</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr"/>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G151" s="12" t="inlineStr">
-        <is>
-          <t>Mashrab qizi</t>
-        </is>
-      </c>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="G151" s="12" t="inlineStr"/>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="J151" s="12" t="inlineStr">
-        <is>
-          <t>AD9494409</t>
-        </is>
-      </c>
-      <c r="K151" s="9" t="inlineStr">
-        <is>
-          <t>60504085680019</t>
-        </is>
-      </c>
-      <c r="L151" s="12" t="inlineStr">
-        <is>
-          <t>26.09.2025</t>
-        </is>
-      </c>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>05.04.2008</t>
-        </is>
-      </c>
-      <c r="N151" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O151" s="11" t="inlineStr">
-        <is>
-          <t>Mavjud</t>
-        </is>
-      </c>
-      <c r="P151" s="9" t="inlineStr">
-        <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q151" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
-      <c r="R151" s="11" t="inlineStr">
-        <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
-        </is>
-      </c>
-      <c r="S151" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T151" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V151" s="11" t="inlineStr"/>
-      <c r="W151" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X151" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr"/>
+      <c r="J151" s="12" t="inlineStr"/>
+      <c r="K151" s="9" t="inlineStr"/>
+      <c r="L151" s="12" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr"/>
+      <c r="N151" s="12" t="inlineStr"/>
+      <c r="O151" s="11" t="inlineStr"/>
+      <c r="P151" s="9" t="inlineStr"/>
+      <c r="Q151" s="11" t="inlineStr"/>
+      <c r="R151" s="11" t="inlineStr"/>
+      <c r="S151" s="12" t="inlineStr"/>
+      <c r="T151" s="12" t="inlineStr"/>
+      <c r="U151" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V151" s="11" t="inlineStr">
+        <is>
+          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W151" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X151" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -17140,13 +17124,13 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza</t>
+          <t>Nurillayeva Sevinch</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -17156,58 +17140,62 @@
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>Zokir qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="N152" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>UM 1313018</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr"/>
+          <t>UM 03729348</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
+        </is>
+      </c>
       <c r="R152" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S152" s="5" t="inlineStr">
@@ -17217,7 +17205,7 @@
       </c>
       <c r="T152" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U152" s="7" t="inlineStr">
@@ -17228,7 +17216,7 @@
       <c r="V152" s="4" t="inlineStr"/>
       <c r="W152" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X152" s="7" t="inlineStr">
@@ -17248,13 +17236,13 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo</t>
+          <t>Ortiqova Dilnoza</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr"/>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
@@ -17264,37 +17252,37 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Talantjon qizi</t>
+          <t>Zokir qizi</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="N153" s="12" t="inlineStr">
@@ -17304,22 +17292,18 @@
       </c>
       <c r="O153" s="11" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="P153" s="9" t="inlineStr">
         <is>
-          <t>UM 03753960</t>
-        </is>
-      </c>
-      <c r="Q153" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1313018</t>
+        </is>
+      </c>
+      <c r="Q153" s="11" t="inlineStr"/>
       <c r="R153" s="11" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S153" s="12" t="inlineStr">
@@ -17329,7 +17313,7 @@
       </c>
       <c r="T153" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U153" s="7" t="inlineStr">
@@ -17340,7 +17324,7 @@
       <c r="V153" s="11" t="inlineStr"/>
       <c r="W153" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X153" s="7" t="inlineStr">
@@ -17360,13 +17344,13 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso</t>
+          <t>Qarshiyeva Shahlo</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -17376,54 +17360,62 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Talantjon qizi</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N154" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
-        </is>
-      </c>
-      <c r="O154" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+        </is>
+      </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>UM 03742130</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr"/>
+          <t>UM 03753960</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
+        </is>
+      </c>
       <c r="R154" s="4" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S154" s="5" t="inlineStr">
@@ -17436,19 +17428,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U154" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="inlineStr">
-        <is>
-          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
-        </is>
-      </c>
+      <c r="U154" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V154" s="4" t="inlineStr"/>
       <c r="W154" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X154" s="7" t="inlineStr">
@@ -17468,78 +17456,70 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
+          <t>Quchqarova Zebiniso</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr"/>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O155" s="11" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="O155" s="11" t="inlineStr"/>
       <c r="P155" s="9" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q155" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03742130</t>
+        </is>
+      </c>
+      <c r="Q155" s="11" t="inlineStr"/>
       <c r="R155" s="11" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S155" s="12" t="inlineStr">
@@ -17557,10 +17537,14 @@
           <t>CHALA</t>
         </is>
       </c>
-      <c r="V155" s="11" t="inlineStr"/>
+      <c r="V155" s="11" t="inlineStr">
+        <is>
+          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
+        </is>
+      </c>
       <c r="W155" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X155" s="7" t="inlineStr">
@@ -17580,78 +17564,78 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
+          <t>Samiyeva Sevinchbonu</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="N156" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q156" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R156" s="4" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S156" s="5" t="inlineStr">
@@ -17670,9 +17654,9 @@
         </is>
       </c>
       <c r="V156" s="4" t="inlineStr"/>
-      <c r="W156" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W156" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X156" s="7" t="inlineStr">
@@ -17692,53 +17676,53 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
+          <t>Sanaqulova Muxtarama</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr"/>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N157" s="12" t="inlineStr">
@@ -17748,33 +17732,37 @@
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P157" s="9" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q157" s="11" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q157" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R157" s="11" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S157" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T157" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U157" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U157" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V157" s="11" t="inlineStr"/>
@@ -17800,88 +17788,84 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
+          <t>Sanaqulova Nozliya</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 5509185</t>
+        </is>
+      </c>
+      <c r="Q158" s="4" t="inlineStr"/>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S158" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T158" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U158" s="7" t="inlineStr">
@@ -17889,14 +17873,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V158" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W158" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+      <c r="V158" s="4" t="inlineStr"/>
+      <c r="W158" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X158" s="7" t="inlineStr">
@@ -17916,78 +17896,78 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
+          <t>Sayfillayeva Shodiyona</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr"/>
       <c r="E159" s="12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N159" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P159" s="9" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q159" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R159" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S159" s="12" t="inlineStr">
@@ -17997,7 +17977,7 @@
       </c>
       <c r="T159" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U159" s="7" t="inlineStr">
@@ -18005,10 +17985,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V159" s="11" t="inlineStr"/>
-      <c r="W159" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V159" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W159" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X159" s="7" t="inlineStr">
@@ -18028,13 +18012,13 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -18044,37 +18028,37 @@
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N160" s="5" t="inlineStr">
@@ -18084,18 +18068,22 @@
       </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q160" s="4" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q160" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R160" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S160" s="5" t="inlineStr">
@@ -18105,7 +18093,7 @@
       </c>
       <c r="T160" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U160" s="7" t="inlineStr">
@@ -18116,7 +18104,7 @@
       <c r="V160" s="4" t="inlineStr"/>
       <c r="W160" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X160" s="7" t="inlineStr">
@@ -18136,13 +18124,13 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr"/>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
@@ -18152,62 +18140,58 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N161" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P161" s="9" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q161" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02172469</t>
+        </is>
+      </c>
+      <c r="Q161" s="11" t="inlineStr"/>
       <c r="R161" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S161" s="12" t="inlineStr">
@@ -18217,7 +18201,7 @@
       </c>
       <c r="T161" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U161" s="7" t="inlineStr">
@@ -18228,7 +18212,7 @@
       <c r="V161" s="11" t="inlineStr"/>
       <c r="W161" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X161" s="7" t="inlineStr">
@@ -18248,13 +18232,13 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yahyomurodova Gulsanam</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr"/>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
@@ -18264,37 +18248,37 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N162" s="5" t="inlineStr">
@@ -18304,22 +18288,22 @@
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q162" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R162" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S162" s="5" t="inlineStr">
@@ -18355,87 +18339,93 @@
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr"/>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="F163" s="18" t="n">
-        <v>46161</v>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F163" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>G‘ani qizi</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila G‘ani qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila G‘ani qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>AE5575300</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>41011925590038</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="M163" s="12" t="inlineStr">
         <is>
-          <t>10.11.1992</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="N163" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>G‘aniyeva Asila G‘ani qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P163" s="9" t="inlineStr">
         <is>
-          <t>L 125287</t>
-        </is>
-      </c>
-      <c r="Q163" s="11" t="inlineStr"/>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q163" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
       <c r="R163" s="11" t="inlineStr">
         <is>
-          <t>Toshkent irrigatsiya va melioratsiya instituti qoshidagi akademik litsey</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S163" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T163" s="12" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
@@ -18466,53 +18456,51 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>G‘aniyeva Asila</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr"/>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F164" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-29 00:00:00</t>
-        </is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="n">
+        <v>46161</v>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>G‘ani qizi</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr"/>
+          <t>G‘aniyeva Asila G‘ani qizi</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>G‘aniyeva Asila G‘ani qizi</t>
+        </is>
+      </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>AC1458884</t>
+          <t>AE5575300</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>42708915590028</t>
+          <t>41011925590038</t>
         </is>
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>04.11.2018</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>27.08.1991</t>
+          <t>10.11.1992</t>
         </is>
       </c>
       <c r="N164" s="5" t="inlineStr">
@@ -18522,46 +18510,44 @@
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>G‘aniyeva Asila G‘ani qizi</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>O'r-Sh 0987579</t>
+          <t>L 125287</t>
         </is>
       </c>
       <c r="Q164" s="4" t="inlineStr"/>
       <c r="R164" s="4" t="inlineStr">
         <is>
-          <t>Ixtisoslashgan maktab</t>
+          <t>Toshkent irrigatsiya va melioratsiya instituti qoshidagi akademik litsey</t>
         </is>
       </c>
       <c r="S164" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T164" s="5" t="n">
-        <v>2009</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T164" s="5" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
       </c>
       <c r="U164" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V164" s="4" t="inlineStr">
-        <is>
-          <t>Murtazayeva Kamola 25.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
+      <c r="V164" s="4" t="inlineStr"/>
       <c r="W164" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X164" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X164" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -18576,51 +18562,53 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza</t>
-        </is>
-      </c>
-      <c r="D165" s="11" t="inlineStr"/>
+          <t>Murtazayeva Kamola</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="F165" s="18" t="n">
-        <v>46255</v>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F165" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Ulug‘bek qizi</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
-        </is>
-      </c>
-      <c r="I165" s="10" t="inlineStr">
-        <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
-        </is>
-      </c>
+          <t>Murtazayeva Kamola Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="I165" s="10" t="inlineStr"/>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>AB8521319</t>
+          <t>AC1458884</t>
         </is>
       </c>
       <c r="K165" s="9" t="inlineStr">
         <is>
-          <t>62906005590060</t>
+          <t>42708915590028</t>
         </is>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>02.01.2018</t>
+          <t>04.11.2018</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
-          <t>29.06.2000</t>
+          <t>27.08.1991</t>
         </is>
       </c>
       <c r="N165" s="12" t="inlineStr">
@@ -18630,27 +18618,27 @@
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P165" s="9" t="inlineStr">
         <is>
-          <t>K 5487472</t>
+          <t>O'r-Sh 0987579</t>
         </is>
       </c>
       <c r="Q165" s="11" t="inlineStr"/>
       <c r="R165" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
+          <t>Ixtisoslashgan maktab</t>
         </is>
       </c>
       <c r="S165" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T165" s="12" t="n">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="U165" s="7" t="inlineStr">
         <is>
@@ -18659,7 +18647,7 @@
       </c>
       <c r="V165" s="11" t="inlineStr">
         <is>
-          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
+          <t>Murtazayeva Kamola 25.docx faylidan to'liq kiritildi</t>
         </is>
       </c>
       <c r="W165" s="8" t="inlineStr">
@@ -18667,9 +18655,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X165" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X165" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -18684,85 +18672,81 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor</t>
+          <t>Mustafayeva Nargiza</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr"/>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="F166" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="n">
+        <v>46255</v>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>AB5359926</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>40211995680023</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>12.12.2016</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>02.11.1999</t>
+          <t>29.06.2000</t>
         </is>
       </c>
       <c r="N166" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>K 5047841</t>
+          <t>K 5487472</t>
         </is>
       </c>
       <c r="Q166" s="4" t="inlineStr"/>
       <c r="R166" s="4" t="inlineStr">
         <is>
-          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S166" s="5" t="inlineStr">
         <is>
-          <t>Kasb-hunar kolleji diplomi</t>
-        </is>
-      </c>
-      <c r="T166" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T166" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="U166" s="7" t="inlineStr">
         <is>
@@ -18771,12 +18755,12 @@
       </c>
       <c r="V166" s="4" t="inlineStr">
         <is>
-          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
         </is>
       </c>
       <c r="W166" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X166" s="7" t="inlineStr">
@@ -18796,13 +18780,13 @@
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
+          <t>Narziyeva Intizor</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr"/>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
@@ -18810,38 +18794,90 @@
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G167" s="12" t="inlineStr"/>
+      <c r="G167" s="12" t="inlineStr">
+        <is>
+          <t>Iskandar qizi</t>
+        </is>
+      </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="I167" s="10" t="inlineStr"/>
-      <c r="J167" s="12" t="inlineStr"/>
-      <c r="K167" s="9" t="inlineStr"/>
-      <c r="L167" s="12" t="inlineStr"/>
-      <c r="M167" s="12" t="inlineStr"/>
-      <c r="N167" s="12" t="inlineStr"/>
-      <c r="O167" s="11" t="inlineStr"/>
-      <c r="P167" s="9" t="inlineStr"/>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="I167" s="10" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="J167" s="12" t="inlineStr">
+        <is>
+          <t>AB5359926</t>
+        </is>
+      </c>
+      <c r="K167" s="9" t="inlineStr">
+        <is>
+          <t>40211995680023</t>
+        </is>
+      </c>
+      <c r="L167" s="12" t="inlineStr">
+        <is>
+          <t>12.12.2016</t>
+        </is>
+      </c>
+      <c r="M167" s="12" t="inlineStr">
+        <is>
+          <t>02.11.1999</t>
+        </is>
+      </c>
+      <c r="N167" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O167" s="11" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="P167" s="9" t="inlineStr">
+        <is>
+          <t>K 5047841</t>
+        </is>
+      </c>
       <c r="Q167" s="11" t="inlineStr"/>
-      <c r="R167" s="11" t="inlineStr"/>
-      <c r="S167" s="12" t="inlineStr"/>
-      <c r="T167" s="12" t="inlineStr"/>
-      <c r="U167" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V167" s="11" t="inlineStr"/>
-      <c r="W167" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X167" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="R167" s="11" t="inlineStr">
+        <is>
+          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S167" s="12" t="inlineStr">
+        <is>
+          <t>Kasb-hunar kolleji diplomi</t>
+        </is>
+      </c>
+      <c r="T167" s="12" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U167" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V167" s="11" t="inlineStr">
+        <is>
+          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+        </is>
+      </c>
+      <c r="W167" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
+        </is>
+      </c>
+      <c r="X167" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -18856,100 +18892,52 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza</t>
+          <t>Salayeva Dilroz</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr"/>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F168" s="6" t="n">
-        <v>46272</v>
-      </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>Xamdam qizi</t>
-        </is>
-      </c>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr"/>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="I168" s="3" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="J168" s="5" t="inlineStr">
-        <is>
-          <t>AB5702170</t>
-        </is>
-      </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>42601925680010</t>
-        </is>
-      </c>
-      <c r="L168" s="5" t="inlineStr">
-        <is>
-          <t>19.01.2017</t>
-        </is>
-      </c>
-      <c r="M168" s="5" t="inlineStr">
-        <is>
-          <t>26.01.1992</t>
-        </is>
-      </c>
-      <c r="N168" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O168" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="P168" s="2" t="inlineStr">
-        <is>
-          <t>K 1994177</t>
-        </is>
-      </c>
+          <t>Salayeva Dilroz</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr"/>
+      <c r="J168" s="5" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="5" t="inlineStr"/>
+      <c r="M168" s="5" t="inlineStr"/>
+      <c r="N168" s="5" t="inlineStr"/>
+      <c r="O168" s="4" t="inlineStr"/>
+      <c r="P168" s="2" t="inlineStr"/>
       <c r="Q168" s="4" t="inlineStr"/>
-      <c r="R168" s="4" t="inlineStr">
-        <is>
-          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
-        </is>
-      </c>
-      <c r="S168" s="5" t="inlineStr">
-        <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T168" s="5" t="n">
-        <v>2011</v>
-      </c>
-      <c r="U168" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V168" s="4" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
-        </is>
-      </c>
-      <c r="W168" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X168" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="R168" s="4" t="inlineStr"/>
+      <c r="S168" s="5" t="inlineStr"/>
+      <c r="T168" s="5" t="inlineStr"/>
+      <c r="U168" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V168" s="4" t="inlineStr"/>
+      <c r="W168" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X168" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -18959,71 +18947,77 @@
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>Talabalar safidan chiqarilganlar</t>
+          <t>26-07</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Axmedova Saodat</t>
+          <t>Usmonova Gulnoza</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr"/>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="F169" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-18 00:00:00</t>
-        </is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F169" s="18" t="n">
+        <v>46272</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Hamro qizi</t>
+          <t>Xamdam qizi</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Axmedova Saodat Hamro qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
         <is>
-          <t>Axmedova Saodat Hamro qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="J169" s="12" t="inlineStr">
         <is>
-          <t>AD8221813</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>42504932740019</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="L169" s="12" t="inlineStr">
         <is>
-          <t>13.08.2024</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="M169" s="12" t="inlineStr">
         <is>
-          <t>25.04.1993</t>
-        </is>
-      </c>
-      <c r="N169" s="12" t="inlineStr"/>
-      <c r="O169" s="11" t="inlineStr"/>
+          <t>26.01.1992</t>
+        </is>
+      </c>
+      <c r="N169" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O169" s="11" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
       <c r="P169" s="9" t="inlineStr">
         <is>
-          <t>K 1630107</t>
+          <t>K 1994177</t>
         </is>
       </c>
       <c r="Q169" s="11" t="inlineStr"/>
       <c r="R169" s="11" t="inlineStr">
         <is>
-          <t>Koson maishiy xizmat kasb-hunar kolleji</t>
+          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S169" s="12" t="inlineStr">
@@ -19031,20 +19025,22 @@
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T169" s="12" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="U169" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V169" s="11" t="inlineStr"/>
+      <c r="T169" s="12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="U169" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V169" s="11" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
+        </is>
+      </c>
       <c r="W169" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X169" s="7" t="inlineStr">
@@ -19064,97 +19060,197 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>G'iyosova Shodiyona</t>
+          <t>Axmedova Saodat</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr"/>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>265</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Abduqahhor qizi</t>
+          <t>Hamro qizi</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>G'iyosova Shodiyona Abduqahhor qizi</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr"/>
+          <t>Axmedova Saodat Hamro qizi</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>Axmedova Saodat Hamro qizi</t>
+        </is>
+      </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>AE 4764561</t>
+          <t>AD8221813</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>60202085590030</t>
+          <t>42504932740019</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>13.08.2024</t>
         </is>
       </c>
       <c r="M170" s="5" t="inlineStr">
         <is>
-          <t>02.02.2008</t>
-        </is>
-      </c>
-      <c r="N170" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>25.04.1993</t>
+        </is>
+      </c>
+      <c r="N170" s="5" t="inlineStr"/>
       <c r="O170" s="4" t="inlineStr"/>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>UM 03752499</t>
+          <t>K 1630107</t>
         </is>
       </c>
       <c r="Q170" s="4" t="inlineStr"/>
       <c r="R170" s="4" t="inlineStr">
         <is>
+          <t>Koson maishiy xizmat kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S170" s="5" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T170" s="5" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="U170" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V170" s="4" t="inlineStr"/>
+      <c r="W170" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X170" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="22" customHeight="1">
+      <c r="A171" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>G'iyosova Shodiyona</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr"/>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>Abduqahhor qizi</t>
+        </is>
+      </c>
+      <c r="H171" s="11" t="inlineStr">
+        <is>
+          <t>G'iyosova Shodiyona Abduqahhor qizi</t>
+        </is>
+      </c>
+      <c r="I171" s="10" t="inlineStr"/>
+      <c r="J171" s="12" t="inlineStr">
+        <is>
+          <t>AE 4764561</t>
+        </is>
+      </c>
+      <c r="K171" s="9" t="inlineStr">
+        <is>
+          <t>60202085590030</t>
+        </is>
+      </c>
+      <c r="L171" s="12" t="inlineStr">
+        <is>
+          <t>24.10.2025</t>
+        </is>
+      </c>
+      <c r="M171" s="12" t="inlineStr">
+        <is>
+          <t>02.02.2008</t>
+        </is>
+      </c>
+      <c r="N171" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O171" s="11" t="inlineStr"/>
+      <c r="P171" s="9" t="inlineStr">
+        <is>
+          <t>UM 03752499</t>
+        </is>
+      </c>
+      <c r="Q171" s="11" t="inlineStr"/>
+      <c r="R171" s="11" t="inlineStr">
+        <is>
           <t>14-maktab</t>
         </is>
       </c>
-      <c r="S170" s="5" t="inlineStr">
+      <c r="S171" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T170" s="5" t="inlineStr">
+      <c r="T171" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="U170" s="14" t="inlineStr">
+      <c r="U171" s="14" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
         </is>
       </c>
-      <c r="V170" s="4" t="inlineStr"/>
-      <c r="W170" s="15" t="inlineStr">
+      <c r="V171" s="11" t="inlineStr"/>
+      <c r="W171" s="15" t="inlineStr">
         <is>
           <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
-      <c r="X170" s="7" t="inlineStr">
+      <c r="X171" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X170"/>
+  <autoFilter ref="A1:X171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34643,7 +34739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X28"/>
+  <dimension ref="A1:X29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -35693,78 +35789,70 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
+          <t>Mahmatqulova Nilufar</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>To'ra qizi</t>
+          <t>Qayum qizi</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
+          <t>Mahmatqulova Nilufar Qayum qizi</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE6047826</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60806085590115</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>08.06.2008</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>UM 03730531</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03754788</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr"/>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>43-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
@@ -35774,23 +35862,15 @@
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr"/>
       <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X10" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W10" s="15" t="inlineStr"/>
+      <c r="X10" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -35805,13 +35885,13 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda</t>
+          <t>Mahmudova Maftuna</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr"/>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -35821,27 +35901,27 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Nosir qizi</t>
+          <t>To'ra qizi</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
@@ -35851,7 +35931,7 @@
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
       <c r="N11" s="12" t="inlineStr">
@@ -35861,22 +35941,22 @@
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>UM 03728995</t>
+          <t>UM 03730531</t>
         </is>
       </c>
       <c r="Q11" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
         </is>
       </c>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
@@ -35917,78 +35997,78 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda</t>
+          <t>Mannonova Shahrizoda</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Hasan qizi</t>
+          <t>Nosir qizi</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>07.10.2008</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>UM 03718284</t>
+          <t>UM 03728995</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
@@ -36029,56 +36109,104 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Muminova Durdona</t>
+          <t>Maxmarajabova Zerda</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr"/>
-      <c r="E13" s="12" t="inlineStr"/>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Anvar qizi</t>
+          <t>Hasan qizi</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Muminova Durdona Anvar qizi</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="12" t="inlineStr"/>
-      <c r="K13" s="9" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr"/>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="12" t="inlineStr"/>
-      <c r="O13" s="11" t="inlineStr"/>
-      <c r="P13" s="9" t="inlineStr"/>
-      <c r="Q13" s="11" t="inlineStr"/>
-      <c r="R13" s="11" t="inlineStr"/>
-      <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="12" t="inlineStr"/>
-      <c r="U13" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V13" s="11" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W13" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X13" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>AE5221552</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>60106075720246</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>01.06.2007</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t>UM 03718284</t>
+        </is>
+      </c>
+      <c r="Q13" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+        </is>
+      </c>
+      <c r="R13" s="11" t="inlineStr">
+        <is>
+          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T13" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V13" s="11" t="inlineStr"/>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36093,104 +36221,56 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Muminova Sevinch</t>
+          <t>Muminova Durdona</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+      <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Anvar qizi</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>AE2259069</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>63001085590111</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>09.04.2025</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>30.01.2008</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>UM 03752895</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
-        </is>
-      </c>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U14" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Muminova Durdona Anvar qizi</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr"/>
+      <c r="U14" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W14" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X14" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -36205,13 +36285,13 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha</t>
+          <t>Muminova Sevinch</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr"/>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -36221,37 +36301,37 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Zaxriddin qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>30.01.2008</t>
         </is>
       </c>
       <c r="N15" s="12" t="inlineStr">
@@ -36261,22 +36341,22 @@
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>UM 03751925</t>
+          <t>UM 03752895</t>
         </is>
       </c>
       <c r="Q15" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
         </is>
       </c>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
@@ -36317,56 +36397,104 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Muxtorova Xadicha</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Zaxriddin qizi</t>
+        </is>
+      </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr"/>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W16" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X16" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>AE2428256</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>60506085590066</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>22.04.2025</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>05.06.2008</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>UM 03751925</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36381,104 +36509,56 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
+          <t>Niyozova Sevara</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr"/>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>Mashrab qizi</t>
-        </is>
-      </c>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr"/>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>AD9494409</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>60504085680019</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>26.09.2025</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="inlineStr">
-        <is>
-          <t>05.04.2008</t>
-        </is>
-      </c>
-      <c r="N17" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="inlineStr">
-        <is>
-          <t>Mavjud</t>
-        </is>
-      </c>
-      <c r="P17" s="9" t="inlineStr">
-        <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q17" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
-      <c r="R17" s="11" t="inlineStr">
-        <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
-        </is>
-      </c>
-      <c r="S17" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T17" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr"/>
+      <c r="K17" s="9" t="inlineStr"/>
+      <c r="L17" s="12" t="inlineStr"/>
+      <c r="M17" s="12" t="inlineStr"/>
+      <c r="N17" s="12" t="inlineStr"/>
+      <c r="O17" s="11" t="inlineStr"/>
+      <c r="P17" s="9" t="inlineStr"/>
+      <c r="Q17" s="11" t="inlineStr"/>
+      <c r="R17" s="11" t="inlineStr"/>
+      <c r="S17" s="12" t="inlineStr"/>
+      <c r="T17" s="12" t="inlineStr"/>
+      <c r="U17" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W17" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X17" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -36493,13 +36573,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza</t>
+          <t>Nurillayeva Sevinch</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -36509,58 +36589,62 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Zokir qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>UM 1313018</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr"/>
+          <t>UM 03729348</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
+        </is>
+      </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
@@ -36570,7 +36654,7 @@
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
@@ -36581,7 +36665,7 @@
       <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X18" s="7" t="inlineStr">
@@ -36601,13 +36685,13 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo</t>
+          <t>Ortiqova Dilnoza</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -36617,37 +36701,37 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Talantjon qizi</t>
+          <t>Zokir qizi</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
@@ -36657,22 +36741,18 @@
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM 03753960</t>
-        </is>
-      </c>
-      <c r="Q19" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1313018</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
@@ -36682,7 +36762,7 @@
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
@@ -36693,7 +36773,7 @@
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -36713,13 +36793,13 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso</t>
+          <t>Qarshiyeva Shahlo</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -36729,54 +36809,62 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Talantjon qizi</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>UM 03742130</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr"/>
+          <t>UM 03753960</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
+        </is>
+      </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -36789,19 +36877,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U20" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
-        </is>
-      </c>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -36821,78 +36905,70 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
+          <t>Quchqarova Zebiniso</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr"/>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr"/>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q21" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03742130</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
@@ -36910,10 +36986,14 @@
           <t>CHALA</t>
         </is>
       </c>
-      <c r="V21" s="11" t="inlineStr"/>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
+        </is>
+      </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X21" s="7" t="inlineStr">
@@ -36933,78 +37013,78 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
+          <t>Samiyeva Sevinchbonu</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
@@ -37023,9 +37103,9 @@
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
-      <c r="W22" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
@@ -37045,53 +37125,53 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
+          <t>Sanaqulova Muxtarama</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr"/>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
@@ -37101,33 +37181,37 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U23" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr"/>
@@ -37153,88 +37237,84 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
+          <t>Sanaqulova Nozliya</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 5509185</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U24" s="7" t="inlineStr">
@@ -37242,14 +37322,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W24" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -37269,78 +37345,78 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
+          <t>Sayfillayeva Shodiyona</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q25" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
@@ -37350,7 +37426,7 @@
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -37358,10 +37434,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W25" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -37381,13 +37461,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -37397,37 +37477,37 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -37437,18 +37517,22 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -37458,7 +37542,7 @@
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -37469,7 +37553,7 @@
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -37489,13 +37573,13 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr"/>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -37505,62 +37589,58 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02172469</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
@@ -37570,7 +37650,7 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -37581,7 +37661,7 @@
       <c r="V27" s="11" t="inlineStr"/>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -37601,13 +37681,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yahyomurodova Gulsanam</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -37617,37 +37697,37 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -37657,22 +37737,22 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -37702,8 +37782,120 @@
         </is>
       </c>
     </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr"/>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Samijon qizi</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>AE4688777</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>63007085680074</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>20.10.2025</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>30.07.2008</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="P29" s="9" t="inlineStr">
+        <is>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
+      <c r="R29" s="11" t="inlineStr">
+        <is>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S29" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T29" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V29" s="11" t="inlineStr"/>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X28"/>
+  <autoFilter ref="A1:X29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -16419,9 +16419,9 @@
       <c r="U144" s="5" t="inlineStr"/>
       <c r="V144" s="4" t="inlineStr"/>
       <c r="W144" s="15" t="inlineStr"/>
-      <c r="X144" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X144" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35868,9 +35868,9 @@
       <c r="U10" s="5" t="inlineStr"/>
       <c r="V10" s="4" t="inlineStr"/>
       <c r="W10" s="15" t="inlineStr"/>
-      <c r="X10" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X10" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -18,11 +18,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$173</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$6</definedName>
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X172"/>
+  <dimension ref="A1:X173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11702,98 +11702,88 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr"/>
+          <t>Xujamuratova Durdona</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F102" s="6" t="n">
-        <v>46204</v>
-      </c>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Shuhrat qizi</t>
+          <t>Bahrom qizi</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
+          <t>22.04.2008</t>
         </is>
       </c>
       <c r="N102" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>UM 0084478</t>
+          <t>UM 03717652</t>
         </is>
       </c>
       <c r="Q102" s="4" t="inlineStr"/>
       <c r="R102" s="4" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S102" s="5" t="inlineStr">
         <is>
-          <t>Attestat</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T102" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U102" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U102" s="5" t="inlineStr"/>
       <c r="V102" s="4" t="inlineStr"/>
-      <c r="W102" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X102" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W102" s="15" t="inlineStr"/>
+      <c r="X102" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -11808,19 +11798,17 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda</t>
+          <t>Xurramova Shahnoza</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr"/>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="F103" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F103" s="18" t="n">
+        <v>46204</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -11829,32 +11817,32 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="J103" s="12" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="K103" s="9" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
       <c r="N103" s="12" t="inlineStr">
@@ -11864,32 +11852,28 @@
       </c>
       <c r="O103" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="P103" s="9" t="inlineStr">
         <is>
-          <t>UM 02149677</t>
-        </is>
-      </c>
-      <c r="Q103" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0084478</t>
+        </is>
+      </c>
+      <c r="Q103" s="11" t="inlineStr"/>
       <c r="R103" s="11" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S103" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Attestat</t>
         </is>
       </c>
       <c r="T103" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U103" s="7" t="inlineStr">
@@ -11920,13 +11904,13 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza</t>
+          <t>Xurramova Shahrizoda</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr"/>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -11936,62 +11920,62 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>Fazliddin qizi</t>
+          <t>Shuhrat qizi</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>30.04.2007</t>
         </is>
       </c>
       <c r="N104" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>UM 03753649</t>
+          <t>UM 02149677</t>
         </is>
       </c>
       <c r="Q104" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
         </is>
       </c>
       <c r="R104" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S104" s="5" t="inlineStr">
@@ -12001,7 +11985,7 @@
       </c>
       <c r="T104" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U104" s="7" t="inlineStr">
@@ -12009,14 +11993,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V104" s="4" t="inlineStr">
-        <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
-        </is>
-      </c>
+      <c r="V104" s="4" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X104" s="7" t="inlineStr">
@@ -12036,13 +12016,13 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda</t>
+          <t>Xusanova Aziza</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr"/>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -12052,62 +12032,62 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>Sodiqovna</t>
+          <t>Fazliddin qizi</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="K105" s="9" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N105" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O105" s="11" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="P105" s="9" t="inlineStr">
         <is>
-          <t>UM 03729571</t>
+          <t>UM 03753649</t>
         </is>
       </c>
       <c r="Q105" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
         </is>
       </c>
       <c r="R105" s="11" t="inlineStr">
         <is>
-          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S105" s="12" t="inlineStr">
@@ -12125,10 +12105,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V105" s="11" t="inlineStr"/>
+      <c r="V105" s="11" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+        </is>
+      </c>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X105" s="7" t="inlineStr">
@@ -12143,18 +12127,18 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Abdishukurova Gulsevar</t>
+          <t>Zayidova Shaboda</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -12164,62 +12148,62 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>Xusniddin qizi</t>
+          <t>Sodiqovna</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>AE4148917</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>60609085720090</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>11.09.2025</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="M106" s="5" t="inlineStr">
         <is>
-          <t>06.09.2008</t>
+          <t>31.12.2008</t>
         </is>
       </c>
       <c r="N106" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
-          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>UM 03719993</t>
+          <t>UM 03729571</t>
         </is>
       </c>
       <c r="Q106" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4504005/3958383/15398298-8212-4586-9b09-3430b67a8ca2?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
         </is>
       </c>
       <c r="R106" s="4" t="inlineStr">
         <is>
-          <t>109-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S106" s="5" t="inlineStr">
@@ -12240,7 +12224,7 @@
       <c r="V106" s="4" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X106" s="7" t="inlineStr">
@@ -12260,13 +12244,13 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Ahmadova Munisa</t>
+          <t>Abdishukurova Gulsevar</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr"/>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -12276,62 +12260,62 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>Bekzod qizi</t>
+          <t>Xusniddin qizi</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Ahmadova Munisa Bekzod qizi</t>
+          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>Ahmadova Munisa Bekzod qizi</t>
+          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
         <is>
-          <t>AE4831229</t>
+          <t>AE4148917</t>
         </is>
       </c>
       <c r="K107" s="9" t="inlineStr">
         <is>
-          <t>60409085680037</t>
+          <t>60609085720090</t>
         </is>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>30.10.2025</t>
+          <t>11.09.2025</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>04.09.2008</t>
+          <t>06.09.2008</t>
         </is>
       </c>
       <c r="N107" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O107" s="11" t="inlineStr">
         <is>
-          <t>Ahmadova Munisa Bekzod qizi</t>
+          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
         </is>
       </c>
       <c r="P107" s="9" t="inlineStr">
         <is>
-          <t>UM 03729337</t>
+          <t>UM 03719993</t>
         </is>
       </c>
       <c r="Q107" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101957/3660101/b47be765-60bf-4b55-8a31-72708c1f6d97?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4504005/3958383/15398298-8212-4586-9b09-3430b67a8ca2?preview=true</t>
         </is>
       </c>
       <c r="R107" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>109-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S107" s="12" t="inlineStr">
@@ -12350,9 +12334,9 @@
         </is>
       </c>
       <c r="V107" s="11" t="inlineStr"/>
-      <c r="W107" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+      <c r="W107" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X107" s="7" t="inlineStr">
@@ -12372,13 +12356,13 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Ashirova Gulsanam</t>
+          <t>Ahmadova Munisa</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -12388,62 +12372,62 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>Abduvali qizi</t>
+          <t>Bekzod qizi</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>Ashirova Gulsanam Abduvali qizi</t>
+          <t>Ahmadova Munisa Bekzod qizi</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>Ashirova Gulsanam Abduvali qizi</t>
+          <t>Ahmadova Munisa Bekzod qizi</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>AD6820021</t>
+          <t>AE4831229</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>62311065590082</t>
+          <t>60409085680037</t>
         </is>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>15.04.2024</t>
+          <t>30.10.2025</t>
         </is>
       </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
-          <t>23.11.2006</t>
+          <t>04.09.2008</t>
         </is>
       </c>
       <c r="N108" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t>Ashirova Gulsanam Abduvali qizi</t>
+          <t>Ahmadova Munisa Bekzod qizi</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>UM 03297113</t>
+          <t>UM 03729337</t>
         </is>
       </c>
       <c r="Q108" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3099486/2737490/cba3dc9e-37cd-49af-bc76-de37d05dfa2a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101957/3660101/b47be765-60bf-4b55-8a31-72708c1f6d97?preview=true</t>
         </is>
       </c>
       <c r="R108" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S108" s="5" t="inlineStr">
@@ -12453,7 +12437,7 @@
       </c>
       <c r="T108" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U108" s="7" t="inlineStr">
@@ -12462,9 +12446,9 @@
         </is>
       </c>
       <c r="V108" s="4" t="inlineStr"/>
-      <c r="W108" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W108" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
       </c>
       <c r="X108" s="7" t="inlineStr">
@@ -12484,13 +12468,13 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Berdimurodova Nafosat</t>
+          <t>Ashirova Gulsanam</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr"/>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>224</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
@@ -12500,62 +12484,62 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>Javlon qizi</t>
+          <t>Abduvali qizi</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Berdimurodova Nafosat Javlon qizi</t>
+          <t>Ashirova Gulsanam Abduvali qizi</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>Berdimurodova Nafosat Javlon qizi</t>
+          <t>Ashirova Gulsanam Abduvali qizi</t>
         </is>
       </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
-          <t>AD9709558</t>
+          <t>AD6820021</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr">
         <is>
-          <t>60904075680023</t>
+          <t>62311065590082</t>
         </is>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>06.12.2024</t>
+          <t>15.04.2024</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>09.04.2007</t>
+          <t>23.11.2006</t>
         </is>
       </c>
       <c r="N109" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O109" s="11" t="inlineStr">
         <is>
-          <t>Berdimurodova Nafosat Javlon qizi</t>
+          <t>Ashirova Gulsanam Abduvali qizi</t>
         </is>
       </c>
       <c r="P109" s="9" t="inlineStr">
         <is>
-          <t>UM 03273940</t>
+          <t>UM 03297113</t>
         </is>
       </c>
       <c r="Q109" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2637941/2320526/141f302a-d1f7-4fb3-bd19-c2f47bdf4aee?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3099486/2737490/cba3dc9e-37cd-49af-bc76-de37d05dfa2a?preview=true</t>
         </is>
       </c>
       <c r="R109" s="11" t="inlineStr">
         <is>
-          <t>21-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S109" s="12" t="inlineStr">
@@ -12573,14 +12557,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V109" s="11" t="inlineStr">
-        <is>
-          <t>PINFL ID-karta QR dan tuzatildi (edi: 60904075590028).</t>
-        </is>
-      </c>
+      <c r="V109" s="11" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X109" s="7" t="inlineStr">
@@ -12600,13 +12580,13 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Choriyeva Zahro</t>
+          <t>Berdimurodova Nafosat</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr"/>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -12616,63 +12596,67 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Xayrullo qizi</t>
+          <t>Javlon qizi</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>Choriyeva Zahro Xayrullo qizi</t>
+          <t>Berdimurodova Nafosat Javlon qizi</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>Choriyeva Zahro Xayrullo qizi</t>
+          <t>Berdimurodova Nafosat Javlon qizi</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>AD9654318</t>
+          <t>AD9709558</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>62802085590063</t>
+          <t>60904075680023</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>06.12.2024</t>
         </is>
       </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>09.04.2007</t>
         </is>
       </c>
       <c r="N110" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>Choriyeva Zaxro Xayrullo qizi</t>
+          <t>Berdimurodova Nafosat Javlon qizi</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>PT 0017576</t>
-        </is>
-      </c>
-      <c r="Q110" s="4" t="inlineStr"/>
+          <t>UM 03273940</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2637941/2320526/141f302a-d1f7-4fb3-bd19-c2f47bdf4aee?preview=true</t>
+        </is>
+      </c>
       <c r="R110" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son politexnikumi</t>
+          <t>21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S110" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T110" s="5" t="inlineStr">
@@ -12685,10 +12669,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V110" s="4" t="inlineStr"/>
-      <c r="W110" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+      <c r="V110" s="4" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta QR dan tuzatildi (edi: 60904075590028).</t>
+        </is>
+      </c>
+      <c r="W110" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X110" s="7" t="inlineStr">
@@ -12708,13 +12696,13 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Ergasheva Shabbona</t>
+          <t>Choriyeva Zahro</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr"/>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -12724,58 +12712,58 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Shodmon qizi</t>
+          <t>Xayrullo qizi</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Ergasheva Shabbona Shodmon qizi</t>
+          <t>Choriyeva Zahro Xayrullo qizi</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
         <is>
-          <t>Ergasheva Shabbona Shodmon qizi</t>
+          <t>Choriyeva Zahro Xayrullo qizi</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
         <is>
-          <t>AE2374828</t>
+          <t>AD9654318</t>
         </is>
       </c>
       <c r="K111" s="9" t="inlineStr">
         <is>
-          <t>61803085680050</t>
+          <t>62802085590063</t>
         </is>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>18.03.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N111" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O111" s="11" t="inlineStr">
         <is>
-          <t>Ergashova Shabbona Shodmon qizi</t>
+          <t>Choriyeva Zaxro Xayrullo qizi</t>
         </is>
       </c>
       <c r="P111" s="9" t="inlineStr">
         <is>
-          <t>PT 0030461</t>
+          <t>PT 0017576</t>
         </is>
       </c>
       <c r="Q111" s="11" t="inlineStr"/>
       <c r="R111" s="11" t="inlineStr">
         <is>
-          <t>Kitob tuman 2-son texnikumi</t>
+          <t>Shahrisabz shahar 2-son politexnikumi</t>
         </is>
       </c>
       <c r="S111" s="12" t="inlineStr">
@@ -12785,7 +12773,7 @@
       </c>
       <c r="T111" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U111" s="7" t="inlineStr">
@@ -12793,14 +12781,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V111" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'ERGASHEVA SHABBONA' | bazada: 'Ergashova Shabbona'</t>
-        </is>
-      </c>
-      <c r="W111" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V111" s="11" t="inlineStr"/>
+      <c r="W111" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X111" s="7" t="inlineStr">
@@ -12820,13 +12804,13 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Eshboboyeva Fotima</t>
+          <t>Ergasheva Shabbona</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr"/>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -12836,68 +12820,68 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Shodmon qizi</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Eshboboyeva Fotima Nurali qizi</t>
+          <t>Ergasheva Shabbona Shodmon qizi</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>Eshboboyeva Fotima Nurali qizi</t>
+          <t>Ergasheva Shabbona Shodmon qizi</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>AD0697178</t>
+          <t>AE2374828</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>61306045630044</t>
+          <t>61803085680050</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>05.10.2021</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="M112" s="5" t="inlineStr">
         <is>
-          <t>13.06.2004</t>
+          <t>18.03.2008</t>
         </is>
       </c>
       <c r="N112" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>Eshboboyeva Fotima Nurali qizi</t>
+          <t>Ergashova Shabbona Shodmon qizi</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>UM 1283543</t>
+          <t>PT 0030461</t>
         </is>
       </c>
       <c r="Q112" s="4" t="inlineStr"/>
       <c r="R112" s="4" t="inlineStr">
         <is>
-          <t>Qamashi tumani 11-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tuman 2-son texnikumi</t>
         </is>
       </c>
       <c r="S112" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T112" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U112" s="7" t="inlineStr">
@@ -12905,10 +12889,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V112" s="4" t="inlineStr"/>
-      <c r="W112" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="V112" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'ERGASHEVA SHABBONA' | bazada: 'Ergashova Shabbona'</t>
+        </is>
+      </c>
+      <c r="W112" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
         </is>
       </c>
       <c r="X112" s="7" t="inlineStr">
@@ -12928,13 +12916,13 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>G'ayratova Jasmina</t>
+          <t>Eshboboyeva Fotima</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr"/>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
@@ -12944,58 +12932,58 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>Sherali qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>G'ayratova Jasmina Sherali qizi</t>
+          <t>Eshboboyeva Fotima Nurali qizi</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>G'ayratova Jasmina Sherali qizi</t>
+          <t>Eshboboyeva Fotima Nurali qizi</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
         <is>
-          <t>AE3497923</t>
+          <t>AD0697178</t>
         </is>
       </c>
       <c r="K113" s="9" t="inlineStr">
         <is>
-          <t>60208085590146</t>
+          <t>61306045630044</t>
         </is>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>23.07.2025</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>02.08.2008</t>
+          <t>13.06.2004</t>
         </is>
       </c>
       <c r="N113" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Qamashi tumani</t>
         </is>
       </c>
       <c r="O113" s="11" t="inlineStr">
         <is>
-          <t>G'ayratova Jasmina Sherali qizi</t>
+          <t>Eshboboyeva Fotima Nurali qizi</t>
         </is>
       </c>
       <c r="P113" s="9" t="inlineStr">
         <is>
-          <t>UM 03754785</t>
+          <t>UM 1283543</t>
         </is>
       </c>
       <c r="Q113" s="11" t="inlineStr"/>
       <c r="R113" s="11" t="inlineStr">
         <is>
-          <t>43-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qamashi tumani 11-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S113" s="12" t="inlineStr">
@@ -13005,7 +12993,7 @@
       </c>
       <c r="T113" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U113" s="7" t="inlineStr">
@@ -13013,14 +13001,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V113" s="11" t="inlineStr">
-        <is>
-          <t>KARANTIN: ❌ Bir xil PINFL (60208085590146) 2 ta talabada: Isomiddinova Ruxshona [26-04], G'ayratova Jasmina [26-05]; ❌ Bir xil Pasport (AE3497923) 2 ta talabada: Isomiddinova Ruxshona [26-04], G'ayratova Jasmina [26-05]; ❌ Bir xil Shahodatnoma (UM 03754785) 2</t>
-        </is>
-      </c>
+      <c r="V113" s="11" t="inlineStr"/>
       <c r="W113" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X113" s="7" t="inlineStr">
@@ -13040,13 +13024,13 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Jabborova Bahoroy</t>
+          <t>G'ayratova Jasmina</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr"/>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -13056,62 +13040,58 @@
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>Shukurullo qizi</t>
+          <t>Sherali qizi</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>Jabborova Bahoroy Shukurullo qizi</t>
+          <t>G'ayratova Jasmina Sherali qizi</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>Jabborova Bahoroy Shukurullo qizi</t>
+          <t>G'ayratova Jasmina Sherali qizi</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>AE4255446</t>
+          <t>AE3497923</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>61510085680048</t>
+          <t>60208085590146</t>
         </is>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>15.10.2008</t>
+          <t>02.08.2008</t>
         </is>
       </c>
       <c r="N114" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>Jabborova Bahoroy Shukurullo qizi</t>
+          <t>G'ayratova Jasmina Sherali qizi</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>UM 03728624</t>
-        </is>
-      </c>
-      <c r="Q114" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4009746/3577240/7218a259-0bea-42da-9d2e-a5b64311a32f?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03754785</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="inlineStr"/>
       <c r="R114" s="4" t="inlineStr">
         <is>
-          <t>21-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>43-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S114" s="5" t="inlineStr">
@@ -13129,7 +13109,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V114" s="4" t="inlineStr"/>
+      <c r="V114" s="4" t="inlineStr">
+        <is>
+          <t>KARANTIN: ❌ Bir xil PINFL (60208085590146) 2 ta talabada: Isomiddinova Ruxshona [26-04], G'ayratova Jasmina [26-05]; ❌ Bir xil Pasport (AE3497923) 2 ta talabada: Isomiddinova Ruxshona [26-04], G'ayratova Jasmina [26-05]; ❌ Bir xil Shahodatnoma (UM 03754785) 2</t>
+        </is>
+      </c>
       <c r="W114" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -13152,13 +13136,13 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Jalilova Jasmina</t>
+          <t>Jabborova Bahoroy</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr"/>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
@@ -13168,37 +13152,37 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>Jamshid qizi</t>
+          <t>Shukurullo qizi</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Jalilova Jasmina Jamshid qizi</t>
+          <t>Jabborova Bahoroy Shukurullo qizi</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>Jalilova Jasmina Jamshid qizi</t>
+          <t>Jabborova Bahoroy Shukurullo qizi</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
         <is>
-          <t>AE4319796</t>
+          <t>AE4255446</t>
         </is>
       </c>
       <c r="K115" s="9" t="inlineStr">
         <is>
-          <t>60211085680014</t>
+          <t>61510085680048</t>
         </is>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>23.09.2025</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>02.11.2008</t>
+          <t>15.10.2008</t>
         </is>
       </c>
       <c r="N115" s="12" t="inlineStr">
@@ -13208,22 +13192,22 @@
       </c>
       <c r="O115" s="11" t="inlineStr">
         <is>
-          <t>Jalilova Jasmina Jamshid qizi</t>
+          <t>Jabborova Bahoroy Shukurullo qizi</t>
         </is>
       </c>
       <c r="P115" s="9" t="inlineStr">
         <is>
-          <t>UM 03728207</t>
+          <t>UM 03728624</t>
         </is>
       </c>
       <c r="Q115" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4125986/3657183/3c8296b5-4bba-41ed-ad34-54afaff3af9f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4009746/3577240/7218a259-0bea-42da-9d2e-a5b64311a32f?preview=true</t>
         </is>
       </c>
       <c r="R115" s="11" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S115" s="12" t="inlineStr">
@@ -13264,53 +13248,53 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Jumayeva Muxlisa</t>
+          <t>Jalilova Jasmina</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr"/>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>Komiljon qizi</t>
+          <t>Jamshid qizi</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Jumayeva Muxlisa Komiljon qizi</t>
+          <t>Jalilova Jasmina Jamshid qizi</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>Jumayeva Muxlisa Komiljon qizi</t>
+          <t>Jalilova Jasmina Jamshid qizi</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>AB6258375</t>
+          <t>AE4319796</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>61701005680057</t>
+          <t>60211085680014</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>29.03.2017</t>
+          <t>23.09.2025</t>
         </is>
       </c>
       <c r="M116" s="5" t="inlineStr">
         <is>
-          <t>17.01.2000</t>
+          <t>02.11.2008</t>
         </is>
       </c>
       <c r="N116" s="5" t="inlineStr">
@@ -13320,28 +13304,32 @@
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
-          <t>Jumayeva Muxlisa Komiljon qizi</t>
+          <t>Jalilova Jasmina Jamshid qizi</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>K 0349228</t>
-        </is>
-      </c>
-      <c r="Q116" s="4" t="inlineStr"/>
+          <t>UM 03728207</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4125986/3657183/3c8296b5-4bba-41ed-ad34-54afaff3af9f?preview=true</t>
+        </is>
+      </c>
       <c r="R116" s="4" t="inlineStr">
         <is>
-          <t>Qarshi pedagogika kolleji</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S116" s="5" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T116" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U116" s="7" t="inlineStr">
@@ -13349,14 +13337,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V116" s="4" t="inlineStr">
-        <is>
-          <t>Haqiqiy shartnoma (#60), Pasport AB6258375 va Kollej diplomi K 0349228 bilan tasdiqlandi.</t>
-        </is>
-      </c>
+      <c r="V116" s="4" t="inlineStr"/>
       <c r="W116" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X116" s="7" t="inlineStr">
@@ -13376,88 +13360,84 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Jurayeva Madina</t>
+          <t>Jumayeva Muxlisa</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr"/>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>Odil qizi</t>
+          <t>Komiljon qizi</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Jurayeva Madina Odil qizi</t>
+          <t>Jumayeva Muxlisa Komiljon qizi</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>Jurayeva Madina Odil qizi</t>
+          <t>Jumayeva Muxlisa Komiljon qizi</t>
         </is>
       </c>
       <c r="J117" s="12" t="inlineStr">
         <is>
-          <t>AD9394305</t>
+          <t>AB6258375</t>
         </is>
       </c>
       <c r="K117" s="9" t="inlineStr">
         <is>
-          <t>62512075730060</t>
+          <t>61701005680057</t>
         </is>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>13.11.2024</t>
+          <t>29.03.2017</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>25.12.2007</t>
+          <t>17.01.2000</t>
         </is>
       </c>
       <c r="N117" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O117" s="11" t="inlineStr">
         <is>
-          <t>Jurayeva Madina Odil qizi</t>
+          <t>Jumayeva Muxlisa Komiljon qizi</t>
         </is>
       </c>
       <c r="P117" s="9" t="inlineStr">
         <is>
-          <t>UM 03301327</t>
-        </is>
-      </c>
-      <c r="Q117" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2481788/2532775/a2612fc4-9c26-4161-a04f-f292dcd614e0?preview=true</t>
-        </is>
-      </c>
+          <t>K 0349228</t>
+        </is>
+      </c>
+      <c r="Q117" s="11" t="inlineStr"/>
       <c r="R117" s="11" t="inlineStr">
         <is>
-          <t>75-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qarshi pedagogika kolleji</t>
         </is>
       </c>
       <c r="S117" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T117" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U117" s="7" t="inlineStr">
@@ -13467,12 +13447,12 @@
       </c>
       <c r="V117" s="11" t="inlineStr">
         <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 62512075590018).</t>
+          <t>Haqiqiy shartnoma (#60), Pasport AB6258375 va Kollej diplomi K 0349228 bilan tasdiqlandi.</t>
         </is>
       </c>
       <c r="W117" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X117" s="7" t="inlineStr">
@@ -13492,13 +13472,13 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Karim Dinora</t>
+          <t>Jurayeva Madina</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -13508,62 +13488,62 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>Raxmonovna</t>
+          <t>Odil qizi</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Karim Dinora Raxmonovna</t>
+          <t>Jurayeva Madina Odil qizi</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>Karim Dinora Raxmonovna</t>
+          <t>Jurayeva Madina Odil qizi</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>AD9335686</t>
+          <t>AD9394305</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>60710085680054</t>
+          <t>62512075730060</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>13.11.2024</t>
         </is>
       </c>
       <c r="M118" s="5" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>25.12.2007</t>
         </is>
       </c>
       <c r="N118" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>Ixtiyorova Niginabonu Xolovna</t>
+          <t>Jurayeva Madina Odil qizi</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>UM 03729467</t>
+          <t>UM 03301327</t>
         </is>
       </c>
       <c r="Q118" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3978146/3485297/e19a9f73-3a29-4c71-8f04-8f35526bd2b6?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2481788/2532775/a2612fc4-9c26-4161-a04f-f292dcd614e0?preview=true</t>
         </is>
       </c>
       <c r="R118" s="4" t="inlineStr">
         <is>
-          <t>51-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>75-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S118" s="5" t="inlineStr">
@@ -13573,7 +13553,7 @@
       </c>
       <c r="T118" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U118" s="7" t="inlineStr">
@@ -13581,10 +13561,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V118" s="4" t="inlineStr"/>
+      <c r="V118" s="4" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 62512075590018).</t>
+        </is>
+      </c>
       <c r="W118" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X118" s="7" t="inlineStr">
@@ -13604,13 +13588,13 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Luxmonova Nozima</t>
+          <t>Karim Dinora</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr"/>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
@@ -13620,37 +13604,37 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>Ilhom qizi</t>
+          <t>Raxmonovna</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Luxmonova Nozima Ilhom qizi</t>
+          <t>Karim Dinora Raxmonovna</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>Luxmonova Nozima Ilhom qizi</t>
+          <t>Karim Dinora Raxmonovna</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
         <is>
-          <t>AE4290181</t>
+          <t>AD9335686</t>
         </is>
       </c>
       <c r="K119" s="9" t="inlineStr">
         <is>
-          <t>61611085680042</t>
+          <t>60710085680054</t>
         </is>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>22.09.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>16.11.2008</t>
+          <t>07.10.2008</t>
         </is>
       </c>
       <c r="N119" s="12" t="inlineStr">
@@ -13660,22 +13644,22 @@
       </c>
       <c r="O119" s="11" t="inlineStr">
         <is>
-          <t>Luxmonova Nozima Ilhom qizi</t>
+          <t>Ixtiyorova Niginabonu Xolovna</t>
         </is>
       </c>
       <c r="P119" s="9" t="inlineStr">
         <is>
-          <t>UM 03729343</t>
+          <t>UM 03729467</t>
         </is>
       </c>
       <c r="Q119" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101961/3662113/4246c17f-f0d6-4a6a-88e4-372c4123ed11?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3978146/3485297/e19a9f73-3a29-4c71-8f04-8f35526bd2b6?preview=true</t>
         </is>
       </c>
       <c r="R119" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>51-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S119" s="12" t="inlineStr">
@@ -13696,7 +13680,7 @@
       <c r="V119" s="11" t="inlineStr"/>
       <c r="W119" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X119" s="7" t="inlineStr">
@@ -13716,51 +13700,53 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor</t>
+          <t>Luxmonova Nozima</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="n">
-        <v>46224</v>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Ilhom qizi</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>Luxmonova Nozima Ilhom qizi</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>Luxmonova Nozima Ilhom qizi</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>AD7829399</t>
+          <t>AE4290181</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>41902975680049</t>
+          <t>61611085680042</t>
         </is>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>11.07.2024</t>
+          <t>22.09.2025</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>19.02.1997</t>
+          <t>16.11.2008</t>
         </is>
       </c>
       <c r="N120" s="5" t="inlineStr">
@@ -13770,28 +13756,32 @@
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>Luxmonova Nozima Ilhom qizi</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>K 0236649</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="inlineStr"/>
+          <t>UM 03729343</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101961/3662113/4246c17f-f0d6-4a6a-88e4-372c4123ed11?preview=true</t>
+        </is>
+      </c>
       <c r="R120" s="4" t="inlineStr">
         <is>
-          <t>Kitob agrosanoat kasb-hunar kolleji</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S120" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T120" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U120" s="7" t="inlineStr">
@@ -13822,53 +13812,51 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Murodova Munisa</t>
+          <t>Muhammadiyeva Gulbahor</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr"/>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="F121" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F121" s="18" t="n">
+        <v>46224</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Muxtor qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
         <is>
-          <t>AE2895049</t>
+          <t>AD7829399</t>
         </is>
       </c>
       <c r="K121" s="9" t="inlineStr">
         <is>
-          <t>62112085680050</t>
+          <t>41902975680049</t>
         </is>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>03.06.2025</t>
+          <t>11.07.2024</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>21.12.2008</t>
+          <t>19.02.1997</t>
         </is>
       </c>
       <c r="N121" s="12" t="inlineStr">
@@ -13878,28 +13866,28 @@
       </c>
       <c r="O121" s="11" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="P121" s="9" t="inlineStr">
         <is>
-          <t>UM 03753455</t>
+          <t>K 0236649</t>
         </is>
       </c>
       <c r="Q121" s="11" t="inlineStr"/>
       <c r="R121" s="11" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>Kitob agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S121" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T121" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="U121" s="7" t="inlineStr">
@@ -13908,9 +13896,9 @@
         </is>
       </c>
       <c r="V121" s="11" t="inlineStr"/>
-      <c r="W121" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W121" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X121" s="7" t="inlineStr">
@@ -13930,82 +13918,84 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona</t>
+          <t>Murodova Munisa</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="n">
-        <v>46221</v>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>Asrorxon qizi</t>
+          <t>Muxtor qizi</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>AD9123240</t>
+          <t>AE2895049</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>62710075590066</t>
+          <t>62112085680050</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>03.06.2025</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>27.10.2007</t>
+          <t>21.12.2008</t>
         </is>
       </c>
       <c r="N122" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>PT 0257899</t>
+          <t>UM 03753455</t>
         </is>
       </c>
       <c r="Q122" s="4" t="inlineStr"/>
       <c r="R122" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 1-son politexnikumi</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S122" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T122" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U122" s="7" t="inlineStr">
@@ -14014,9 +14004,9 @@
         </is>
       </c>
       <c r="V122" s="4" t="inlineStr"/>
-      <c r="W122" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W122" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X122" s="7" t="inlineStr">
@@ -14036,75 +14026,93 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Nazarova Munisa</t>
+          <t>Muzrapova Ruhshona</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr"/>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F123" s="18" t="n">
+        <v>46221</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Erkin qizi</t>
+          <t>Asrorxon qizi</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>AE7685867</t>
+          <t>AD9123240</t>
         </is>
       </c>
       <c r="K123" s="9" t="inlineStr">
         <is>
-          <t>41205925680015</t>
+          <t>62710075590066</t>
         </is>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>17.06.2026</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>12.05.1992</t>
+          <t>27.10.2007</t>
         </is>
       </c>
       <c r="N123" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O123" s="11" t="inlineStr"/>
-      <c r="P123" s="9" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O123" s="11" t="inlineStr">
+        <is>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+        </is>
+      </c>
+      <c r="P123" s="9" t="inlineStr">
+        <is>
+          <t>PT 0257899</t>
+        </is>
+      </c>
       <c r="Q123" s="11" t="inlineStr"/>
-      <c r="R123" s="11" t="inlineStr"/>
-      <c r="S123" s="12" t="inlineStr"/>
-      <c r="T123" s="12" t="inlineStr"/>
-      <c r="U123" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="R123" s="11" t="inlineStr">
+        <is>
+          <t>Shahrisabz shahar 1-son politexnikumi</t>
+        </is>
+      </c>
+      <c r="S123" s="12" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T123" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U123" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V123" s="11" t="inlineStr"/>
       <c r="W123" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X123" s="7" t="inlineStr">
@@ -14124,49 +14132,53 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch</t>
+          <t>Nazarova Munisa</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr"/>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>258</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>Hikmatullo qizi</t>
+          <t>Erkin qizi</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr"/>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>AE7082532</t>
+          <t>AE7685867</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>60212085680048</t>
+          <t>41205925680015</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>02.12.2008</t>
+          <t>12.05.1992</t>
         </is>
       </c>
       <c r="N124" s="5" t="inlineStr">
@@ -14175,40 +14187,20 @@
         </is>
       </c>
       <c r="O124" s="4" t="inlineStr"/>
-      <c r="P124" s="2" t="inlineStr">
-        <is>
-          <t>UM 03727760</t>
-        </is>
-      </c>
+      <c r="P124" s="2" t="inlineStr"/>
       <c r="Q124" s="4" t="inlineStr"/>
-      <c r="R124" s="4" t="inlineStr">
-        <is>
-          <t>1-maktab</t>
-        </is>
-      </c>
-      <c r="S124" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T124" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U124" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W124" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="R124" s="4" t="inlineStr"/>
+      <c r="S124" s="5" t="inlineStr"/>
+      <c r="T124" s="5" t="inlineStr"/>
+      <c r="U124" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V124" s="4" t="inlineStr"/>
+      <c r="W124" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X124" s="7" t="inlineStr">
@@ -14228,53 +14220,49 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam</t>
+          <t>Ne'matova Sevinch</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr"/>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>289</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Elyor qizi</t>
+          <t>Hikmatullo qizi</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
-      <c r="I125" s="10" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr"/>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>AE4817469</t>
+          <t>AE7082532</t>
         </is>
       </c>
       <c r="K125" s="9" t="inlineStr">
         <is>
-          <t>61809085680096</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>18.09.2008</t>
+          <t>02.12.2008</t>
         </is>
       </c>
       <c r="N125" s="12" t="inlineStr">
@@ -14282,20 +14270,16 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O125" s="11" t="inlineStr">
-        <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
+      <c r="O125" s="11" t="inlineStr"/>
       <c r="P125" s="9" t="inlineStr">
         <is>
-          <t>UM 03728575</t>
+          <t>UM 03727760</t>
         </is>
       </c>
       <c r="Q125" s="11" t="inlineStr"/>
       <c r="R125" s="11" t="inlineStr">
         <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>1-maktab</t>
         </is>
       </c>
       <c r="S125" s="12" t="inlineStr">
@@ -14308,15 +14292,19 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V125" s="11" t="inlineStr"/>
-      <c r="W125" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="U125" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V125" s="11" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Nurmatova Sevinchning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W125" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X125" s="7" t="inlineStr">
@@ -14336,13 +14324,13 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Omonova Charos</t>
+          <t>Normurodova Gulsanam</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -14352,68 +14340,68 @@
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Elyor qizi</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>AE1338424</t>
+          <t>AE4817469</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>40306985590014</t>
+          <t>61809085680096</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>03.06.1998</t>
+          <t>18.09.2008</t>
         </is>
       </c>
       <c r="N126" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>K 5023908</t>
+          <t>UM 03728575</t>
         </is>
       </c>
       <c r="Q126" s="4" t="inlineStr"/>
       <c r="R126" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S126" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T126" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U126" s="7" t="inlineStr">
@@ -14444,83 +14432,95 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Oripova Sevinch</t>
+          <t>Omonova Charos</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr"/>
-      <c r="E127" s="12" t="inlineStr"/>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>G'olib qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Oripova Sevinch G'olib qizi</t>
-        </is>
-      </c>
-      <c r="I127" s="10" t="inlineStr"/>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>AE3333890</t>
+          <t>AE1338424</t>
         </is>
       </c>
       <c r="K127" s="9" t="inlineStr">
         <is>
-          <t>62007085680095</t>
+          <t>40306985590014</t>
         </is>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>09.07.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>20.07.2008</t>
+          <t>03.06.1998</t>
         </is>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O127" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O127" s="11" t="inlineStr">
+        <is>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
       <c r="P127" s="9" t="inlineStr">
         <is>
-          <t>UM 03729323</t>
+          <t>K 5023908</t>
         </is>
       </c>
       <c r="Q127" s="11" t="inlineStr"/>
       <c r="R127" s="11" t="inlineStr">
         <is>
-          <t>45-maktab</t>
+          <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S127" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T127" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U127" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="U127" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V127" s="11" t="inlineStr"/>
-      <c r="W127" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W127" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X127" s="7" t="inlineStr">
@@ -14540,76 +14540,62 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Ozodova Klara</t>
+          <t>Oripova Sevinch</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="F128" s="6" t="n">
-        <v>46272</v>
+      <c r="E128" s="5" t="inlineStr"/>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>Fayzullayevna</t>
+          <t>G'olib qizi</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>Oripova Sevinch G'olib qizi</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr"/>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>AD6663341</t>
+          <t>AE3333890</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>60803075590140</t>
+          <t>62007085680095</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>01.04.2024</t>
+          <t>09.07.2025</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>08.03.2007</t>
+          <t>20.07.2008</t>
         </is>
       </c>
       <c r="N128" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O128" s="4" t="inlineStr">
-        <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O128" s="4" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>UM 03298601</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03729323</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="inlineStr"/>
       <c r="R128" s="4" t="inlineStr">
         <is>
-          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>45-maktab</t>
         </is>
       </c>
       <c r="S128" s="5" t="inlineStr">
@@ -14619,18 +14605,18 @@
       </c>
       <c r="T128" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U128" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U128" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V128" s="4" t="inlineStr"/>
-      <c r="W128" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W128" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X128" s="7" t="inlineStr">
@@ -14650,78 +14636,76 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z</t>
+          <t>Ozodova Klara</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr"/>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F129" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="F129" s="18" t="n">
+        <v>46272</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Ilyos qizi</t>
+          <t>Fayzullayevna</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>AE6043288</t>
+          <t>AD6663341</t>
         </is>
       </c>
       <c r="K129" s="9" t="inlineStr">
         <is>
-          <t>60511085680024</t>
+          <t>60803075590140</t>
         </is>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>01.04.2024</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>05.11.2008</t>
+          <t>08.03.2007</t>
         </is>
       </c>
       <c r="N129" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="P129" s="9" t="inlineStr">
         <is>
-          <t>UM 03730668</t>
+          <t>UM 03298601</t>
         </is>
       </c>
       <c r="Q129" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2957737/2495703/d7955ba2-0dbe-4242-91d5-107b7908e2ed?preview=true</t>
         </is>
       </c>
       <c r="R129" s="11" t="inlineStr">
         <is>
-          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>66-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S129" s="12" t="inlineStr">
@@ -14731,7 +14715,7 @@
       </c>
       <c r="T129" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
@@ -14762,13 +14746,13 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Sharipova Diyora</t>
+          <t>Saidova Dilso'z</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -14778,62 +14762,62 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Ilyos qizi</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AE6043288</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>60511085680024</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>05.11.2008</t>
         </is>
       </c>
       <c r="N130" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>UM 03751494</t>
+          <t>UM 03730668</t>
         </is>
       </c>
       <c r="Q130" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3831062/3537464/f8a74043-7e2a-4905-9acd-fd4e316f3960?preview=true</t>
         </is>
       </c>
       <c r="R130" s="4" t="inlineStr">
         <is>
-          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>85-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S130" s="5" t="inlineStr">
@@ -14874,13 +14858,13 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara</t>
+          <t>Sharipova Diyora</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr"/>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
@@ -14890,37 +14874,37 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Ilxom qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
+          <t>23.07.2009</t>
         </is>
       </c>
       <c r="N131" s="12" t="inlineStr">
@@ -14930,18 +14914,22 @@
       </c>
       <c r="O131" s="11" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="P131" s="9" t="inlineStr">
         <is>
-          <t>UM 1319051</t>
-        </is>
-      </c>
-      <c r="Q131" s="11" t="inlineStr"/>
+          <t>UM 03751494</t>
+        </is>
+      </c>
+      <c r="Q131" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+        </is>
+      </c>
       <c r="R131" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
+          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S131" s="12" t="inlineStr">
@@ -14951,7 +14939,7 @@
       </c>
       <c r="T131" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U131" s="7" t="inlineStr">
@@ -14962,7 +14950,7 @@
       <c r="V131" s="11" t="inlineStr"/>
       <c r="W131" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X131" s="7" t="inlineStr">
@@ -14982,53 +14970,53 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza</t>
+          <t>Toshmurodova Sarvara</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Anvarovna</t>
+          <t>Ilxom qizi</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>28.03.2005</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr">
@@ -15038,22 +15026,18 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>UM 02172465</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1319051</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="inlineStr"/>
       <c r="R132" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
       <c r="S132" s="5" t="inlineStr">
@@ -15063,7 +15047,7 @@
       </c>
       <c r="T132" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U132" s="7" t="inlineStr">
@@ -15094,78 +15078,78 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima</t>
+          <t>Tursunova Aziza</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr"/>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>276</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Qosim qizi</t>
+          <t>Anvarovna</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="K133" s="9" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
       <c r="N133" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O133" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="P133" s="9" t="inlineStr">
         <is>
-          <t>UM 03730083</t>
+          <t>UM 02172465</t>
         </is>
       </c>
       <c r="Q133" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
         </is>
       </c>
       <c r="R133" s="11" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S133" s="12" t="inlineStr">
@@ -15175,7 +15159,7 @@
       </c>
       <c r="T133" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U133" s="7" t="inlineStr">
@@ -15186,7 +15170,7 @@
       <c r="V133" s="11" t="inlineStr"/>
       <c r="W133" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X133" s="7" t="inlineStr">
@@ -15206,13 +15190,13 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra</t>
+          <t>Tursunova Fotima</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -15227,22 +15211,22 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="L134" s="5" t="inlineStr">
@@ -15262,17 +15246,17 @@
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>UM 03730084</t>
+          <t>UM 03730083</t>
         </is>
       </c>
       <c r="Q134" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
         </is>
       </c>
       <c r="R134" s="4" t="inlineStr">
@@ -15318,13 +15302,13 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina</t>
+          <t>Tursunova Zuhra</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr"/>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>219</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
@@ -15334,62 +15318,62 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Qosim qizi</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>27.10.2008</t>
         </is>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="P135" s="9" t="inlineStr">
         <is>
-          <t>UM 03754097</t>
+          <t>UM 03730084</t>
         </is>
       </c>
       <c r="Q135" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
         </is>
       </c>
       <c r="R135" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S135" s="12" t="inlineStr">
@@ -15430,13 +15414,13 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Usmonova Sabrina</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -15446,68 +15430,72 @@
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr"/>
+          <t>UM 03754097</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
+        </is>
+      </c>
       <c r="R136" s="4" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S136" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T136" s="5" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U136" s="7" t="inlineStr">
@@ -15515,14 +15503,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V136" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W136" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V136" s="4" t="inlineStr"/>
+      <c r="W136" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X136" s="7" t="inlineStr">
@@ -15542,13 +15526,13 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr"/>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
@@ -15558,58 +15542,58 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="K137" s="9" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O137" s="11" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P137" s="9" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
+          <t>K 3418837</t>
         </is>
       </c>
       <c r="Q137" s="11" t="inlineStr"/>
       <c r="R137" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son texnikumi</t>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S137" s="12" t="inlineStr">
@@ -15619,7 +15603,7 @@
       </c>
       <c r="T137" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="U137" s="7" t="inlineStr">
@@ -15629,12 +15613,12 @@
       </c>
       <c r="V137" s="11" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
-        </is>
-      </c>
-      <c r="W137" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W137" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
         </is>
       </c>
       <c r="X137" s="7" t="inlineStr">
@@ -15649,88 +15633,84 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira</t>
+          <t>Yuldosheva Ruhshona</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farxod qizi</t>
+          <t>Xabibullo qizi</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>AE4512271</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>62501095720012</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>25.01.2009</t>
+          <t>13.09.2008</t>
         </is>
       </c>
       <c r="N138" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>UM 03718322</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160259/3907782/88616609-4fee-4140-8c92-b0e3d21c7944?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr"/>
       <c r="R138" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
       <c r="S138" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T138" s="5" t="inlineStr">
@@ -15745,12 +15725,12 @@
       </c>
       <c r="V138" s="4" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'ABDIXOLIQOVA ELMIRA' | bazada: 'Abduxoliqova Elmira'; imlo farqi — Shahodatnoma PDF: 'Abdixoliqova Elmira Farxod qizi' | bazada: 'Abduxoliqova Elmira'</t>
-        </is>
-      </c>
-      <c r="W138" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
+        </is>
+      </c>
+      <c r="W138" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X138" s="7" t="inlineStr">
@@ -15770,78 +15750,78 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Bahodirova Asila</t>
+          <t>Abdixoliqova Elmira</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr"/>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>286</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-07 00:00:00</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Olmos qizi</t>
+          <t>Farxod qizi</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>AE1222596</t>
+          <t>AE4512271</t>
         </is>
       </c>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>61711085590032</t>
+          <t>62501095720012</t>
         </is>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>16.01.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>17.11.2008</t>
+          <t>25.01.2009</t>
         </is>
       </c>
       <c r="N139" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O139" s="11" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="P139" s="9" t="inlineStr">
         <is>
-          <t>UM 03753386</t>
+          <t>UM 03718322</t>
         </is>
       </c>
       <c r="Q139" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3364811/3243239/86966b2b-ec7a-4817-bfa2-68cd1aceff78?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160259/3907782/88616609-4fee-4140-8c92-b0e3d21c7944?preview=true</t>
         </is>
       </c>
       <c r="R139" s="11" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S139" s="12" t="inlineStr">
@@ -15859,10 +15839,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V139" s="11" t="inlineStr"/>
-      <c r="W139" s="8" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
+      <c r="V139" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'ABDIXOLIQOVA ELMIRA' | bazada: 'Abduxoliqova Elmira'; imlo farqi — Shahodatnoma PDF: 'Abdixoliqova Elmira Farxod qizi' | bazada: 'Abduxoliqova Elmira'</t>
+        </is>
+      </c>
+      <c r="W139" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X139" s="7" t="inlineStr">
@@ -15882,51 +15866,53 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza</t>
+          <t>Bahodirova Asila</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr"/>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="F140" s="6" t="n">
-        <v>46281</v>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>Husan qizi</t>
+          <t>Olmos qizi</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>AD8208717</t>
+          <t>AE1222596</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>41508955590021</t>
+          <t>61711085590032</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>12.08.2024</t>
+          <t>16.01.2025</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>15.08.1995</t>
+          <t>17.11.2008</t>
         </is>
       </c>
       <c r="N140" s="5" t="inlineStr">
@@ -15936,41 +15922,43 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>K 0216332</t>
-        </is>
-      </c>
-      <c r="Q140" s="4" t="inlineStr"/>
+          <t>UM 03753386</t>
+        </is>
+      </c>
+      <c r="Q140" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3364811/3243239/86966b2b-ec7a-4817-bfa2-68cd1aceff78?preview=true</t>
+        </is>
+      </c>
       <c r="R140" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz Yengil sanoat kasb-hunar kolleji</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S140" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T140" s="5" t="n">
-        <v>2014</v>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T140" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U140" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V140" s="4" t="inlineStr">
-        <is>
-          <t>KARANTIN: ❌ Bir xil PINFL (41508955590021) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06]; ❌ Bir xil Pasport (AD8208717) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06] || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
-        </is>
-      </c>
+      <c r="V140" s="4" t="inlineStr"/>
       <c r="W140" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X140" s="7" t="inlineStr">
@@ -15990,91 +15978,95 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Eshimova Zilola</t>
+          <t>Davlatova Gulnoza</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr"/>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="F141" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="n">
+        <v>46281</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Bekzod qizi</t>
+          <t>Husan qizi</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
+          <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
+          <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>AE2935693</t>
+          <t>AD8208717</t>
         </is>
       </c>
       <c r="K141" s="9" t="inlineStr">
         <is>
-          <t>61506085730076</t>
+          <t>41508955590021</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>09.06.2025</t>
+          <t>12.08.2024</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>15.06.2008</t>
+          <t>15.08.1995</t>
         </is>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
-        </is>
-      </c>
-      <c r="O141" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O141" s="11" t="inlineStr">
+        <is>
+          <t>Davlatova Gulnoza Husan qizi</t>
+        </is>
+      </c>
       <c r="P141" s="9" t="inlineStr">
         <is>
-          <t>UM 03756027</t>
+          <t>K 0216332</t>
         </is>
       </c>
       <c r="Q141" s="11" t="inlineStr"/>
       <c r="R141" s="11" t="inlineStr">
         <is>
-          <t>4-maktab</t>
+          <t>Shahrisabz Yengil sanoat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S141" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T141" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U141" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V141" s="11" t="inlineStr"/>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T141" s="12" t="n">
+        <v>2014</v>
+      </c>
+      <c r="U141" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V141" s="11" t="inlineStr">
+        <is>
+          <t>KARANTIN: ❌ Bir xil PINFL (41508955590021) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06]; ❌ Bir xil Pasport (AD8208717) 2 ta talabada: Maxmudova Musallam [26-04], Davlatova Gulnoza [26-06] || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
+        </is>
+      </c>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X141" s="7" t="inlineStr">
@@ -16094,13 +16086,13 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam</t>
+          <t>Eshimova Zilola</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr"/>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -16110,62 +16102,54 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>Ozodjon qizi</t>
+          <t>Bekzod qizi</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
+          <t>Eshimova Zilola Bekzod qizi</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
+          <t>Eshimova Zilola Bekzod qizi</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>AD9937321</t>
+          <t>AE2935693</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>60603085590037</t>
+          <t>61506085730076</t>
         </is>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>24.12.2024</t>
+          <t>09.06.2025</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
+          <t>15.06.2008</t>
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O142" s="4" t="inlineStr">
-        <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
+          <t>Yakkabog' tumani</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr"/>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>UM 03752997</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03756027</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr"/>
       <c r="R142" s="4" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>4-maktab</t>
         </is>
       </c>
       <c r="S142" s="5" t="inlineStr">
@@ -16178,15 +16162,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U142" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U142" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V142" s="4" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X142" s="7" t="inlineStr">
@@ -16206,13 +16190,13 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida</t>
+          <t>Jalilova Shabnam</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr"/>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
@@ -16222,37 +16206,37 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Shovkat qizi</t>
+          <t>Ozodjon qizi</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>AE6299685</t>
+          <t>AD9937321</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
         <is>
-          <t>60907085590063</t>
+          <t>60603085590037</t>
         </is>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>24.12.2024</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>09.07.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
       <c r="N143" s="12" t="inlineStr">
@@ -16262,17 +16246,17 @@
       </c>
       <c r="O143" s="11" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="P143" s="9" t="inlineStr">
         <is>
-          <t>UM 03752998</t>
+          <t>UM 03752997</t>
         </is>
       </c>
       <c r="Q143" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
         </is>
       </c>
       <c r="R143" s="11" t="inlineStr">
@@ -16296,9 +16280,9 @@
         </is>
       </c>
       <c r="V143" s="11" t="inlineStr"/>
-      <c r="W143" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+      <c r="W143" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X143" s="7" t="inlineStr">
@@ -16318,78 +16302,78 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Karimova Nozliya</t>
+          <t>Jumayeva Husnida</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr"/>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>Rustamovna</t>
+          <t>Shovkat qizi</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>AE4674508</t>
+          <t>AE6299685</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>61502085680047</t>
+          <t>60907085590063</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>15.02.2008</t>
+          <t>09.07.2008</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>UM 03729342</t>
+          <t>UM 03752998</t>
         </is>
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
         </is>
       </c>
       <c r="R144" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S144" s="5" t="inlineStr">
@@ -16408,9 +16392,9 @@
         </is>
       </c>
       <c r="V144" s="4" t="inlineStr"/>
-      <c r="W144" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W144" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
       </c>
       <c r="X144" s="7" t="inlineStr">
@@ -16430,53 +16414,53 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara</t>
+          <t>Karimova Nozliya</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr"/>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Safarali qizi</t>
+          <t>Rustamovna</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>AE2103843</t>
+          <t>AE4674508</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>60705005680087</t>
+          <t>61502085680047</t>
         </is>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>27.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>07.05.2000</t>
+          <t>15.02.2008</t>
         </is>
       </c>
       <c r="N145" s="12" t="inlineStr">
@@ -16486,28 +16470,32 @@
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>Mahmamurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="P145" s="9" t="inlineStr">
         <is>
-          <t>K 5493345</t>
-        </is>
-      </c>
-      <c r="Q145" s="11" t="inlineStr"/>
+          <t>UM 03729342</t>
+        </is>
+      </c>
+      <c r="Q145" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+        </is>
+      </c>
       <c r="R145" s="11" t="inlineStr">
         <is>
-          <t>Kitob agrobiznes kasb-hunar kolleji</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S145" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T145" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U145" s="7" t="inlineStr">
@@ -16515,14 +16503,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V145" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
-        </is>
-      </c>
-      <c r="W145" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: BOSHQA ODAM</t>
+      <c r="V145" s="11" t="inlineStr"/>
+      <c r="W145" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X145" s="7" t="inlineStr">
@@ -16542,85 +16526,101 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Mahmatqulova Nilufar</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Mahmadmurodova Sevara</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="F146" s="5" t="inlineStr"/>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Qayum qizi</t>
+          <t>Safarali qizi</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Mahmatqulova Nilufar Qayum qizi</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="inlineStr"/>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
+        </is>
+      </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>AE6047826</t>
+          <t>AE2103843</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>60806085590115</t>
+          <t>60705005680087</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>08.06.2008</t>
+          <t>07.05.2000</t>
         </is>
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Mahmamurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>UM 03754788</t>
+          <t>K 5493345</t>
         </is>
       </c>
       <c r="Q146" s="4" t="inlineStr"/>
       <c r="R146" s="4" t="inlineStr">
         <is>
-          <t>43-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S146" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T146" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U146" s="5" t="inlineStr"/>
-      <c r="V146" s="4" t="inlineStr"/>
-      <c r="W146" s="15" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U146" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V146" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
+        </is>
+      </c>
+      <c r="W146" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: BOSHQA ODAM</t>
+        </is>
+      </c>
       <c r="X146" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -16638,78 +16638,70 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr"/>
+          <t>Mahmatqulova Nilufar</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F147" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="inlineStr"/>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>To'ra qizi</t>
+          <t>Qayum qizi</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
-      <c r="I147" s="10" t="inlineStr">
-        <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
+          <t>Mahmatqulova Nilufar Qayum qizi</t>
+        </is>
+      </c>
+      <c r="I147" s="10" t="inlineStr"/>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE6047826</t>
         </is>
       </c>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60806085590115</t>
         </is>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>08.06.2008</t>
         </is>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P147" s="9" t="inlineStr">
         <is>
-          <t>UM 03730531</t>
-        </is>
-      </c>
-      <c r="Q147" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03754788</t>
+        </is>
+      </c>
+      <c r="Q147" s="11" t="inlineStr"/>
       <c r="R147" s="11" t="inlineStr">
         <is>
-          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>43-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S147" s="12" t="inlineStr">
@@ -16719,20 +16711,12 @@
       </c>
       <c r="T147" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U147" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U147" s="12" t="inlineStr"/>
       <c r="V147" s="11" t="inlineStr"/>
-      <c r="W147" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W147" s="15" t="inlineStr"/>
       <c r="X147" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -16750,13 +16734,13 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda</t>
+          <t>Mahmudova Maftuna</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -16766,27 +16750,27 @@
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>Nosir qizi</t>
+          <t>To'ra qizi</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr">
@@ -16796,7 +16780,7 @@
       </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
       <c r="N148" s="5" t="inlineStr">
@@ -16806,22 +16790,22 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>UM 03728995</t>
+          <t>UM 03730531</t>
         </is>
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
         </is>
       </c>
       <c r="R148" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S148" s="5" t="inlineStr">
@@ -16862,78 +16846,78 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda</t>
+          <t>Mannonova Shahrizoda</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr"/>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Hasan qizi</t>
+          <t>Nosir qizi</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="K149" s="9" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>07.10.2008</t>
         </is>
       </c>
       <c r="N149" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="P149" s="9" t="inlineStr">
         <is>
-          <t>UM 03718284</t>
+          <t>UM 03728995</t>
         </is>
       </c>
       <c r="Q149" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
         </is>
       </c>
       <c r="R149" s="11" t="inlineStr">
         <is>
-          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S149" s="12" t="inlineStr">
@@ -16974,56 +16958,104 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Muminova Durdona</t>
+          <t>Maxmarajabova Zerda</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr"/>
-      <c r="E150" s="5" t="inlineStr"/>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Anvar qizi</t>
+          <t>Hasan qizi</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Muminova Durdona Anvar qizi</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr"/>
-      <c r="J150" s="5" t="inlineStr"/>
-      <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="5" t="inlineStr"/>
-      <c r="M150" s="5" t="inlineStr"/>
-      <c r="N150" s="5" t="inlineStr"/>
-      <c r="O150" s="4" t="inlineStr"/>
-      <c r="P150" s="2" t="inlineStr"/>
-      <c r="Q150" s="4" t="inlineStr"/>
-      <c r="R150" s="4" t="inlineStr"/>
-      <c r="S150" s="5" t="inlineStr"/>
-      <c r="T150" s="5" t="inlineStr"/>
-      <c r="U150" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V150" s="4" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W150" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X150" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>AE5221552</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>60106075720246</t>
+        </is>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="inlineStr">
+        <is>
+          <t>01.06.2007</t>
+        </is>
+      </c>
+      <c r="N150" s="5" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>UM 03718284</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+        </is>
+      </c>
+      <c r="R150" s="4" t="inlineStr">
+        <is>
+          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S150" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T150" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U150" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V150" s="4" t="inlineStr"/>
+      <c r="W150" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X150" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -17038,104 +17070,56 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Muminova Sevinch</t>
+          <t>Muminova Durdona</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr"/>
-      <c r="E151" s="12" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+      <c r="E151" s="12" t="inlineStr"/>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Anvar qizi</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="J151" s="12" t="inlineStr">
-        <is>
-          <t>AE2259069</t>
-        </is>
-      </c>
-      <c r="K151" s="9" t="inlineStr">
-        <is>
-          <t>63001085590111</t>
-        </is>
-      </c>
-      <c r="L151" s="12" t="inlineStr">
-        <is>
-          <t>09.04.2025</t>
-        </is>
-      </c>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>30.01.2008</t>
-        </is>
-      </c>
-      <c r="N151" s="12" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O151" s="11" t="inlineStr">
-        <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="P151" s="9" t="inlineStr">
-        <is>
-          <t>UM 03752895</t>
-        </is>
-      </c>
-      <c r="Q151" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
-        </is>
-      </c>
-      <c r="R151" s="11" t="inlineStr">
-        <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S151" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T151" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V151" s="11" t="inlineStr"/>
-      <c r="W151" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X151" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Muminova Durdona Anvar qizi</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr"/>
+      <c r="J151" s="12" t="inlineStr"/>
+      <c r="K151" s="9" t="inlineStr"/>
+      <c r="L151" s="12" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr"/>
+      <c r="N151" s="12" t="inlineStr"/>
+      <c r="O151" s="11" t="inlineStr"/>
+      <c r="P151" s="9" t="inlineStr"/>
+      <c r="Q151" s="11" t="inlineStr"/>
+      <c r="R151" s="11" t="inlineStr"/>
+      <c r="S151" s="12" t="inlineStr"/>
+      <c r="T151" s="12" t="inlineStr"/>
+      <c r="U151" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V151" s="11" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W151" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X151" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -17150,13 +17134,13 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha</t>
+          <t>Muminova Sevinch</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -17166,37 +17150,37 @@
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>Zaxriddin qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>30.01.2008</t>
         </is>
       </c>
       <c r="N152" s="5" t="inlineStr">
@@ -17206,22 +17190,22 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>UM 03751925</t>
+          <t>UM 03752895</t>
         </is>
       </c>
       <c r="Q152" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
         </is>
       </c>
       <c r="R152" s="4" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S152" s="5" t="inlineStr">
@@ -17262,56 +17246,104 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Muxtorova Xadicha</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr"/>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="G153" s="12" t="inlineStr"/>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>Zaxriddin qizi</t>
+        </is>
+      </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="I153" s="10" t="inlineStr"/>
-      <c r="J153" s="12" t="inlineStr"/>
-      <c r="K153" s="9" t="inlineStr"/>
-      <c r="L153" s="12" t="inlineStr"/>
-      <c r="M153" s="12" t="inlineStr"/>
-      <c r="N153" s="12" t="inlineStr"/>
-      <c r="O153" s="11" t="inlineStr"/>
-      <c r="P153" s="9" t="inlineStr"/>
-      <c r="Q153" s="11" t="inlineStr"/>
-      <c r="R153" s="11" t="inlineStr"/>
-      <c r="S153" s="12" t="inlineStr"/>
-      <c r="T153" s="12" t="inlineStr"/>
-      <c r="U153" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V153" s="11" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W153" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X153" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="J153" s="12" t="inlineStr">
+        <is>
+          <t>AE2428256</t>
+        </is>
+      </c>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
+          <t>60506085590066</t>
+        </is>
+      </c>
+      <c r="L153" s="12" t="inlineStr">
+        <is>
+          <t>22.04.2025</t>
+        </is>
+      </c>
+      <c r="M153" s="12" t="inlineStr">
+        <is>
+          <t>05.06.2008</t>
+        </is>
+      </c>
+      <c r="N153" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O153" s="11" t="inlineStr">
+        <is>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+        </is>
+      </c>
+      <c r="P153" s="9" t="inlineStr">
+        <is>
+          <t>UM 03751925</t>
+        </is>
+      </c>
+      <c r="Q153" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+        </is>
+      </c>
+      <c r="R153" s="11" t="inlineStr">
+        <is>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S153" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T153" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U153" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V153" s="11" t="inlineStr"/>
+      <c r="W153" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X153" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -17326,104 +17358,56 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
+          <t>Niyozova Sevara</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="inlineStr">
-        <is>
-          <t>Mashrab qizi</t>
-        </is>
-      </c>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr"/>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="J154" s="5" t="inlineStr">
-        <is>
-          <t>AD9494409</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>60504085680019</t>
-        </is>
-      </c>
-      <c r="L154" s="5" t="inlineStr">
-        <is>
-          <t>26.09.2025</t>
-        </is>
-      </c>
-      <c r="M154" s="5" t="inlineStr">
-        <is>
-          <t>05.04.2008</t>
-        </is>
-      </c>
-      <c r="N154" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O154" s="4" t="inlineStr">
-        <is>
-          <t>Mavjud</t>
-        </is>
-      </c>
-      <c r="P154" s="2" t="inlineStr">
-        <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
-      <c r="R154" s="4" t="inlineStr">
-        <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
-        </is>
-      </c>
-      <c r="S154" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T154" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U154" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="inlineStr"/>
-      <c r="W154" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X154" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr"/>
+      <c r="J154" s="5" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="5" t="inlineStr"/>
+      <c r="M154" s="5" t="inlineStr"/>
+      <c r="N154" s="5" t="inlineStr"/>
+      <c r="O154" s="4" t="inlineStr"/>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="4" t="inlineStr"/>
+      <c r="R154" s="4" t="inlineStr"/>
+      <c r="S154" s="5" t="inlineStr"/>
+      <c r="T154" s="5" t="inlineStr"/>
+      <c r="U154" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V154" s="4" t="inlineStr">
+        <is>
+          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W154" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X154" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -17438,13 +17422,13 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza</t>
+          <t>Nurillayeva Sevinch</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr"/>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
@@ -17454,58 +17438,62 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Zokir qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O155" s="11" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P155" s="9" t="inlineStr">
         <is>
-          <t>UM 1313018</t>
-        </is>
-      </c>
-      <c r="Q155" s="11" t="inlineStr"/>
+          <t>UM 03729348</t>
+        </is>
+      </c>
+      <c r="Q155" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
+        </is>
+      </c>
       <c r="R155" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S155" s="12" t="inlineStr">
@@ -17515,7 +17503,7 @@
       </c>
       <c r="T155" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U155" s="7" t="inlineStr">
@@ -17526,7 +17514,7 @@
       <c r="V155" s="11" t="inlineStr"/>
       <c r="W155" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X155" s="7" t="inlineStr">
@@ -17546,13 +17534,13 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo</t>
+          <t>Ortiqova Dilnoza</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
@@ -17562,37 +17550,37 @@
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Talantjon qizi</t>
+          <t>Zokir qizi</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="N156" s="5" t="inlineStr">
@@ -17602,22 +17590,18 @@
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>UM 03753960</t>
-        </is>
-      </c>
-      <c r="Q156" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1313018</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="inlineStr"/>
       <c r="R156" s="4" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S156" s="5" t="inlineStr">
@@ -17627,7 +17611,7 @@
       </c>
       <c r="T156" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U156" s="7" t="inlineStr">
@@ -17638,7 +17622,7 @@
       <c r="V156" s="4" t="inlineStr"/>
       <c r="W156" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X156" s="7" t="inlineStr">
@@ -17658,13 +17642,13 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso</t>
+          <t>Qarshiyeva Shahlo</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr"/>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
@@ -17674,54 +17658,62 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Talantjon qizi</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
-        </is>
-      </c>
-      <c r="O157" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O157" s="11" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+        </is>
+      </c>
       <c r="P157" s="9" t="inlineStr">
         <is>
-          <t>UM 03742130</t>
-        </is>
-      </c>
-      <c r="Q157" s="11" t="inlineStr"/>
+          <t>UM 03753960</t>
+        </is>
+      </c>
+      <c r="Q157" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
+        </is>
+      </c>
       <c r="R157" s="11" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S157" s="12" t="inlineStr">
@@ -17734,19 +17726,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U157" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V157" s="11" t="inlineStr">
-        <is>
-          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
-        </is>
-      </c>
+      <c r="U157" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V157" s="11" t="inlineStr"/>
       <c r="W157" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X157" s="7" t="inlineStr">
@@ -17766,78 +17754,70 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
+          <t>Quchqarova Zebiniso</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O158" s="4" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="O158" s="4" t="inlineStr"/>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03742130</t>
+        </is>
+      </c>
+      <c r="Q158" s="4" t="inlineStr"/>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S158" s="5" t="inlineStr">
@@ -17855,10 +17835,14 @@
           <t>CHALA</t>
         </is>
       </c>
-      <c r="V158" s="4" t="inlineStr"/>
+      <c r="V158" s="4" t="inlineStr">
+        <is>
+          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
+        </is>
+      </c>
       <c r="W158" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X158" s="7" t="inlineStr">
@@ -17878,78 +17862,78 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
+          <t>Samiyeva Sevinchbonu</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr"/>
       <c r="E159" s="12" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="N159" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P159" s="9" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q159" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R159" s="11" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S159" s="12" t="inlineStr">
@@ -17968,9 +17952,9 @@
         </is>
       </c>
       <c r="V159" s="11" t="inlineStr"/>
-      <c r="W159" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W159" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X159" s="7" t="inlineStr">
@@ -17990,53 +17974,53 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
+          <t>Sanaqulova Muxtarama</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N160" s="5" t="inlineStr">
@@ -18046,33 +18030,37 @@
       </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q160" s="4" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q160" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R160" s="4" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S160" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T160" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U160" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U160" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V160" s="4" t="inlineStr"/>
@@ -18098,88 +18086,84 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
+          <t>Sanaqulova Nozliya</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr"/>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="N161" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P161" s="9" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q161" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 5509185</t>
+        </is>
+      </c>
+      <c r="Q161" s="11" t="inlineStr"/>
       <c r="R161" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S161" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T161" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U161" s="7" t="inlineStr">
@@ -18187,14 +18171,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V161" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W161" s="17" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+      <c r="V161" s="11" t="inlineStr"/>
+      <c r="W161" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X161" s="7" t="inlineStr">
@@ -18214,78 +18194,78 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
+          <t>Sayfillayeva Shodiyona</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr"/>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N162" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q162" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R162" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S162" s="5" t="inlineStr">
@@ -18295,7 +18275,7 @@
       </c>
       <c r="T162" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U162" s="7" t="inlineStr">
@@ -18303,10 +18283,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V162" s="4" t="inlineStr"/>
-      <c r="W162" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V162" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W162" s="17" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X162" s="7" t="inlineStr">
@@ -18326,13 +18310,13 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr"/>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
@@ -18342,37 +18326,37 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M163" s="12" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N163" s="12" t="inlineStr">
@@ -18382,18 +18366,22 @@
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P163" s="9" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q163" s="11" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q163" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R163" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S163" s="12" t="inlineStr">
@@ -18403,7 +18391,7 @@
       </c>
       <c r="T163" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
@@ -18414,7 +18402,7 @@
       <c r="V163" s="11" t="inlineStr"/>
       <c r="W163" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X163" s="7" t="inlineStr">
@@ -18434,13 +18422,13 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr"/>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
@@ -18450,62 +18438,58 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N164" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q164" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02172469</t>
+        </is>
+      </c>
+      <c r="Q164" s="4" t="inlineStr"/>
       <c r="R164" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S164" s="5" t="inlineStr">
@@ -18515,7 +18499,7 @@
       </c>
       <c r="T164" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U164" s="7" t="inlineStr">
@@ -18526,7 +18510,7 @@
       <c r="V164" s="4" t="inlineStr"/>
       <c r="W164" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X164" s="7" t="inlineStr">
@@ -18546,13 +18530,13 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yahyomurodova Gulsanam</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr"/>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
@@ -18562,37 +18546,37 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K165" s="9" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N165" s="12" t="inlineStr">
@@ -18602,22 +18586,22 @@
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P165" s="9" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q165" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R165" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S165" s="12" t="inlineStr">
@@ -18653,79 +18637,83 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Zarifova Marjona</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr"/>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="I166" s="3" t="inlineStr"/>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>AC1458884</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>42708915590028</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>04.11.2018</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>27.08.1991</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="N166" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>O'r-Sh 0987579</t>
-        </is>
-      </c>
-      <c r="Q166" s="4" t="inlineStr"/>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q166" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
       <c r="R166" s="4" t="inlineStr">
         <is>
-          <t>Ixtisoslashgan maktab</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S166" s="5" t="inlineStr">
@@ -18733,27 +18721,25 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T166" s="5" t="n">
-        <v>2009</v>
+      <c r="T166" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U166" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V166" s="4" t="inlineStr">
-        <is>
-          <t>Murtazayeva Kamola 25.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
+      <c r="V166" s="4" t="inlineStr"/>
       <c r="W166" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X166" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X166" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -18768,51 +18754,53 @@
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza</t>
-        </is>
-      </c>
-      <c r="D167" s="11" t="inlineStr"/>
+          <t>Murtazayeva Kamola</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="F167" s="18" t="n">
-        <v>46255</v>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F167" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>Ulug‘bek qizi</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
-        </is>
-      </c>
-      <c r="I167" s="10" t="inlineStr">
-        <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
-        </is>
-      </c>
+          <t>Murtazayeva Kamola Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="I167" s="10" t="inlineStr"/>
       <c r="J167" s="12" t="inlineStr">
         <is>
-          <t>AB8521319</t>
+          <t>AC1458884</t>
         </is>
       </c>
       <c r="K167" s="9" t="inlineStr">
         <is>
-          <t>62906005590060</t>
+          <t>42708915590028</t>
         </is>
       </c>
       <c r="L167" s="12" t="inlineStr">
         <is>
-          <t>02.01.2018</t>
+          <t>04.11.2018</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
         <is>
-          <t>29.06.2000</t>
+          <t>27.08.1991</t>
         </is>
       </c>
       <c r="N167" s="12" t="inlineStr">
@@ -18822,27 +18810,27 @@
       </c>
       <c r="O167" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P167" s="9" t="inlineStr">
         <is>
-          <t>K 5487472</t>
+          <t>O'r-Sh 0987579</t>
         </is>
       </c>
       <c r="Q167" s="11" t="inlineStr"/>
       <c r="R167" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
+          <t>Ixtisoslashgan maktab</t>
         </is>
       </c>
       <c r="S167" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T167" s="12" t="n">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="U167" s="7" t="inlineStr">
         <is>
@@ -18851,7 +18839,7 @@
       </c>
       <c r="V167" s="11" t="inlineStr">
         <is>
-          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
+          <t>Murtazayeva Kamola 25.docx faylidan to'liq kiritildi</t>
         </is>
       </c>
       <c r="W167" s="8" t="inlineStr">
@@ -18859,9 +18847,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X167" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X167" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -18876,85 +18864,81 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor</t>
+          <t>Mustafayeva Nargiza</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr"/>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="F168" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="n">
+        <v>46255</v>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>AB5359926</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>40211995680023</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>12.12.2016</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
-          <t>02.11.1999</t>
+          <t>29.06.2000</t>
         </is>
       </c>
       <c r="N168" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>K 5047841</t>
+          <t>K 5487472</t>
         </is>
       </c>
       <c r="Q168" s="4" t="inlineStr"/>
       <c r="R168" s="4" t="inlineStr">
         <is>
-          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S168" s="5" t="inlineStr">
         <is>
-          <t>Kasb-hunar kolleji diplomi</t>
-        </is>
-      </c>
-      <c r="T168" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T168" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="U168" s="7" t="inlineStr">
         <is>
@@ -18963,12 +18947,12 @@
       </c>
       <c r="V168" s="4" t="inlineStr">
         <is>
-          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
         </is>
       </c>
       <c r="W168" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X168" s="7" t="inlineStr">
@@ -18988,13 +18972,13 @@
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
+          <t>Narziyeva Intizor</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr"/>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
@@ -19002,38 +18986,90 @@
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G169" s="12" t="inlineStr"/>
+      <c r="G169" s="12" t="inlineStr">
+        <is>
+          <t>Iskandar qizi</t>
+        </is>
+      </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="I169" s="10" t="inlineStr"/>
-      <c r="J169" s="12" t="inlineStr"/>
-      <c r="K169" s="9" t="inlineStr"/>
-      <c r="L169" s="12" t="inlineStr"/>
-      <c r="M169" s="12" t="inlineStr"/>
-      <c r="N169" s="12" t="inlineStr"/>
-      <c r="O169" s="11" t="inlineStr"/>
-      <c r="P169" s="9" t="inlineStr"/>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="I169" s="10" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="J169" s="12" t="inlineStr">
+        <is>
+          <t>AB5359926</t>
+        </is>
+      </c>
+      <c r="K169" s="9" t="inlineStr">
+        <is>
+          <t>40211995680023</t>
+        </is>
+      </c>
+      <c r="L169" s="12" t="inlineStr">
+        <is>
+          <t>12.12.2016</t>
+        </is>
+      </c>
+      <c r="M169" s="12" t="inlineStr">
+        <is>
+          <t>02.11.1999</t>
+        </is>
+      </c>
+      <c r="N169" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O169" s="11" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="P169" s="9" t="inlineStr">
+        <is>
+          <t>K 5047841</t>
+        </is>
+      </c>
       <c r="Q169" s="11" t="inlineStr"/>
-      <c r="R169" s="11" t="inlineStr"/>
-      <c r="S169" s="12" t="inlineStr"/>
-      <c r="T169" s="12" t="inlineStr"/>
-      <c r="U169" s="14" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V169" s="11" t="inlineStr"/>
-      <c r="W169" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X169" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="R169" s="11" t="inlineStr">
+        <is>
+          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S169" s="12" t="inlineStr">
+        <is>
+          <t>Kasb-hunar kolleji diplomi</t>
+        </is>
+      </c>
+      <c r="T169" s="12" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U169" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V169" s="11" t="inlineStr">
+        <is>
+          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+        </is>
+      </c>
+      <c r="W169" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
+        </is>
+      </c>
+      <c r="X169" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -19048,100 +19084,52 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza</t>
+          <t>Salayeva Dilroz</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr"/>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F170" s="6" t="n">
-        <v>46272</v>
-      </c>
-      <c r="G170" s="5" t="inlineStr">
-        <is>
-          <t>Xamdam qizi</t>
-        </is>
-      </c>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr"/>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="J170" s="5" t="inlineStr">
-        <is>
-          <t>AB5702170</t>
-        </is>
-      </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>42601925680010</t>
-        </is>
-      </c>
-      <c r="L170" s="5" t="inlineStr">
-        <is>
-          <t>19.01.2017</t>
-        </is>
-      </c>
-      <c r="M170" s="5" t="inlineStr">
-        <is>
-          <t>26.01.1992</t>
-        </is>
-      </c>
-      <c r="N170" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O170" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="P170" s="2" t="inlineStr">
-        <is>
-          <t>K 1994177</t>
-        </is>
-      </c>
+          <t>Salayeva Dilroz</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr"/>
+      <c r="J170" s="5" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="5" t="inlineStr"/>
+      <c r="M170" s="5" t="inlineStr"/>
+      <c r="N170" s="5" t="inlineStr"/>
+      <c r="O170" s="4" t="inlineStr"/>
+      <c r="P170" s="2" t="inlineStr"/>
       <c r="Q170" s="4" t="inlineStr"/>
-      <c r="R170" s="4" t="inlineStr">
-        <is>
-          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
-        </is>
-      </c>
-      <c r="S170" s="5" t="inlineStr">
-        <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T170" s="5" t="n">
-        <v>2011</v>
-      </c>
-      <c r="U170" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V170" s="4" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
-        </is>
-      </c>
-      <c r="W170" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X170" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="R170" s="4" t="inlineStr"/>
+      <c r="S170" s="5" t="inlineStr"/>
+      <c r="T170" s="5" t="inlineStr"/>
+      <c r="U170" s="14" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V170" s="4" t="inlineStr"/>
+      <c r="W170" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X170" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -19151,71 +19139,77 @@
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>Talabalar safidan chiqarilganlar</t>
+          <t>26-07</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Axmedova Saodat</t>
+          <t>Usmonova Gulnoza</t>
         </is>
       </c>
       <c r="D171" s="11" t="inlineStr"/>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="F171" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-18 00:00:00</t>
-        </is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F171" s="18" t="n">
+        <v>46272</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Hamro qizi</t>
+          <t>Xamdam qizi</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>Axmedova Saodat Hamro qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr">
         <is>
-          <t>Axmedova Saodat Hamro qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="J171" s="12" t="inlineStr">
         <is>
-          <t>AD8221813</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="K171" s="9" t="inlineStr">
         <is>
-          <t>42504932740019</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="L171" s="12" t="inlineStr">
         <is>
-          <t>13.08.2024</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="M171" s="12" t="inlineStr">
         <is>
-          <t>25.04.1993</t>
-        </is>
-      </c>
-      <c r="N171" s="12" t="inlineStr"/>
-      <c r="O171" s="11" t="inlineStr"/>
+          <t>26.01.1992</t>
+        </is>
+      </c>
+      <c r="N171" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O171" s="11" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
       <c r="P171" s="9" t="inlineStr">
         <is>
-          <t>K 1630107</t>
+          <t>K 1994177</t>
         </is>
       </c>
       <c r="Q171" s="11" t="inlineStr"/>
       <c r="R171" s="11" t="inlineStr">
         <is>
-          <t>Koson maishiy xizmat kasb-hunar kolleji</t>
+          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S171" s="12" t="inlineStr">
@@ -19223,20 +19217,22 @@
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T171" s="12" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="U171" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V171" s="11" t="inlineStr"/>
+      <c r="T171" s="12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="U171" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V171" s="11" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
+        </is>
+      </c>
       <c r="W171" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X171" s="7" t="inlineStr">
@@ -19256,97 +19252,197 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>G'iyosova Shodiyona</t>
+          <t>Axmedova Saodat</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr"/>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>265</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>Abduqahhor qizi</t>
+          <t>Hamro qizi</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>G'iyosova Shodiyona Abduqahhor qizi</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr"/>
+          <t>Axmedova Saodat Hamro qizi</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>Axmedova Saodat Hamro qizi</t>
+        </is>
+      </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>AE 4764561</t>
+          <t>AD8221813</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>60202085590030</t>
+          <t>42504932740019</t>
         </is>
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>13.08.2024</t>
         </is>
       </c>
       <c r="M172" s="5" t="inlineStr">
         <is>
-          <t>02.02.2008</t>
-        </is>
-      </c>
-      <c r="N172" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>25.04.1993</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="inlineStr"/>
       <c r="O172" s="4" t="inlineStr"/>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>UM 03752499</t>
+          <t>K 1630107</t>
         </is>
       </c>
       <c r="Q172" s="4" t="inlineStr"/>
       <c r="R172" s="4" t="inlineStr">
         <is>
+          <t>Koson maishiy xizmat kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S172" s="5" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T172" s="5" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="U172" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V172" s="4" t="inlineStr"/>
+      <c r="W172" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X172" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="9" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>G'iyosova Shodiyona</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr"/>
+      <c r="E173" s="12" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="F173" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t>Abduqahhor qizi</t>
+        </is>
+      </c>
+      <c r="H173" s="11" t="inlineStr">
+        <is>
+          <t>G'iyosova Shodiyona Abduqahhor qizi</t>
+        </is>
+      </c>
+      <c r="I173" s="10" t="inlineStr"/>
+      <c r="J173" s="12" t="inlineStr">
+        <is>
+          <t>AE 4764561</t>
+        </is>
+      </c>
+      <c r="K173" s="9" t="inlineStr">
+        <is>
+          <t>60202085590030</t>
+        </is>
+      </c>
+      <c r="L173" s="12" t="inlineStr">
+        <is>
+          <t>24.10.2025</t>
+        </is>
+      </c>
+      <c r="M173" s="12" t="inlineStr">
+        <is>
+          <t>02.02.2008</t>
+        </is>
+      </c>
+      <c r="N173" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O173" s="11" t="inlineStr"/>
+      <c r="P173" s="9" t="inlineStr">
+        <is>
+          <t>UM 03752499</t>
+        </is>
+      </c>
+      <c r="Q173" s="11" t="inlineStr"/>
+      <c r="R173" s="11" t="inlineStr">
+        <is>
           <t>14-maktab</t>
         </is>
       </c>
-      <c r="S172" s="5" t="inlineStr">
+      <c r="S173" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T172" s="5" t="inlineStr">
+      <c r="T173" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="U172" s="14" t="inlineStr">
+      <c r="U173" s="14" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
         </is>
       </c>
-      <c r="V172" s="4" t="inlineStr"/>
-      <c r="W172" s="15" t="inlineStr">
+      <c r="V173" s="11" t="inlineStr"/>
+      <c r="W173" s="15" t="inlineStr">
         <is>
           <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
-      <c r="X172" s="7" t="inlineStr">
+      <c r="X173" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X172"/>
+  <autoFilter ref="A1:X173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27954,7 +28050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30921,98 +31017,88 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
+          <t>Xujamuratova Durdona</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>46204</v>
-      </c>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Shuhrat qizi</t>
+          <t>Bahrom qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
+          <t>22.04.2008</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 0084478</t>
+          <t>UM 03717652</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Attestat</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr"/>
       <c r="V28" s="4" t="inlineStr"/>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X28" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W28" s="15" t="inlineStr"/>
+      <c r="X28" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -31027,19 +31113,17 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda</t>
+          <t>Xurramova Shahnoza</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr"/>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>46204</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -31048,32 +31132,32 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
@@ -31083,32 +31167,28 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 02149677</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0084478</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr"/>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Attestat</t>
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -31139,13 +31219,13 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza</t>
+          <t>Xurramova Shahrizoda</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -31155,62 +31235,62 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Fazliddin qizi</t>
+          <t>Shuhrat qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>30.04.2007</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03753649</t>
+          <t>UM 02149677</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -31220,7 +31300,7 @@
       </c>
       <c r="T30" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U30" s="7" t="inlineStr">
@@ -31228,14 +31308,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
-        </is>
-      </c>
+      <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X30" s="7" t="inlineStr">
@@ -31255,109 +31331,225 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda</t>
+          <t>Xusanova Aziza</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr"/>
       <c r="E31" s="12" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Fazliddin qizi</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Xusanova Aziza Fazliddin qizi</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Xusanova Aziza Fazliddin qizi</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>AE5015467</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>60110085590092</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>12.11.2025</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>01.10.2008</t>
+        </is>
+      </c>
+      <c r="N31" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>Xusanova Aziza Fazliddin qizi</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="inlineStr">
+        <is>
+          <t>UM 03753649</t>
+        </is>
+      </c>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
+        </is>
+      </c>
+      <c r="R31" s="11" t="inlineStr">
+        <is>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S31" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T31" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X31" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>26-04</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zayidova Shaboda</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>387</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Sodiqovna</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>AE5856503</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>63112085680039</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>14.01.2026</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>31.12.2008</t>
         </is>
       </c>
-      <c r="N31" s="12" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O31" s="11" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
-      <c r="P31" s="9" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>UM 03729571</t>
         </is>
       </c>
-      <c r="Q31" s="11" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
         </is>
       </c>
-      <c r="R31" s="11" t="inlineStr">
+      <c r="R32" s="4" t="inlineStr">
         <is>
           <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
-      <c r="S31" s="12" t="inlineStr">
+      <c r="S32" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T31" s="12" t="inlineStr">
+      <c r="T32" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="U31" s="7" t="inlineStr">
+      <c r="U32" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="11" t="inlineStr"/>
-      <c r="W31" s="8" t="inlineStr">
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS</t>
         </is>
       </c>
-      <c r="X31" s="7" t="inlineStr">
+      <c r="X32" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X31"/>
+  <autoFilter ref="A1:X32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -12072,11 +12072,31 @@
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="J106" s="5" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="5" t="inlineStr"/>
-      <c r="M106" s="5" t="inlineStr"/>
-      <c r="N106" s="5" t="inlineStr"/>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>AC2359638</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>602030 4568 0015</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>03.11.2019</t>
+        </is>
+      </c>
+      <c r="M106" s="5" t="inlineStr">
+        <is>
+          <t>02.03.2004</t>
+        </is>
+      </c>
+      <c r="N106" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
           <t>Qodirova Shabnam O'tkir qizi</t>
@@ -30207,11 +30227,31 @@
           <t>Qodirova Shabnam O'tkir qizi</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="12" t="inlineStr"/>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>AC2359638</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>602030 4568 0015</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>03.11.2019</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>02.03.2004</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
           <t>Qodirova Shabnam O'tkir qizi</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -18117,9 +18117,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X161" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X161" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31232,9 +31232,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X28" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -8432,9 +8432,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X71" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X71" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29847,9 +29847,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X15" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -17779,9 +17779,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X158" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X158" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31118,9 +31118,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X27" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -12130,9 +12130,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X106" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X106" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30285,9 +30285,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X19" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -24,8 +24,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="S86" s="5" t="inlineStr">
         <is>
-          <t>Kasb-hunar kolleji diplomi</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T86" s="5" t="inlineStr">
@@ -35429,7 +35429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X29"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37199,56 +37199,104 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Narziyeva Intizor</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr"/>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr"/>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Iskandar qizi</t>
+        </is>
+      </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="12" t="inlineStr"/>
-      <c r="O17" s="11" t="inlineStr"/>
-      <c r="P17" s="9" t="inlineStr"/>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>AB5359926</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>40211995680023</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>12.12.2016</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>02.11.1999</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t>K 5047841</t>
+        </is>
+      </c>
       <c r="Q17" s="11" t="inlineStr"/>
-      <c r="R17" s="11" t="inlineStr"/>
-      <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="12" t="inlineStr"/>
-      <c r="U17" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+      <c r="R17" s="11" t="inlineStr">
+        <is>
+          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T17" s="12" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V17" s="11" t="inlineStr">
         <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W17" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X17" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37263,104 +37311,56 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
+          <t>Niyozova Sevara</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Mashrab qizi</t>
-        </is>
-      </c>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>AD9494409</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>60504085680019</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>26.09.2025</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>05.04.2008</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>Mavjud</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W18" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X18" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -37375,13 +37375,13 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza</t>
+          <t>Nurillayeva Sevinch</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -37391,58 +37391,62 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Zokir qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM 1313018</t>
-        </is>
-      </c>
-      <c r="Q19" s="11" t="inlineStr"/>
+          <t>UM 03729348</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
+        </is>
+      </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
@@ -37452,7 +37456,7 @@
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
@@ -37463,7 +37467,7 @@
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -37483,13 +37487,13 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo</t>
+          <t>Ortiqova Dilnoza</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -37499,37 +37503,37 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Talantjon qizi</t>
+          <t>Zokir qizi</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -37539,22 +37543,18 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>UM 03753960</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1313018</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -37564,7 +37564,7 @@
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
@@ -37575,7 +37575,7 @@
       <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -37595,13 +37595,13 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso</t>
+          <t>Qarshiyeva Shahlo</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr"/>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -37611,54 +37611,62 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Talantjon qizi</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+        </is>
+      </c>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>UM 03742130</t>
-        </is>
-      </c>
-      <c r="Q21" s="11" t="inlineStr"/>
+          <t>UM 03753960</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
+        </is>
+      </c>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
@@ -37671,19 +37679,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U21" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V21" s="11" t="inlineStr">
-        <is>
-          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
-        </is>
-      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="inlineStr"/>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X21" s="7" t="inlineStr">
@@ -37703,78 +37707,70 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
+          <t>Quchqarova Zebiniso</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03742130</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
@@ -37792,10 +37788,14 @@
           <t>CHALA</t>
         </is>
       </c>
-      <c r="V22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
+        </is>
+      </c>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
@@ -37815,78 +37815,78 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
+          <t>Samiyeva Sevinchbonu</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr"/>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q23" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
@@ -37905,9 +37905,9 @@
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X23" s="7" t="inlineStr">
@@ -37927,53 +37927,53 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
+          <t>Sanaqulova Muxtarama</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -37983,33 +37983,37 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U24" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U24" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V24" s="4" t="inlineStr"/>
@@ -38035,88 +38039,84 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
+          <t>Sanaqulova Nozliya</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 5509185</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -38124,14 +38124,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W25" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+      <c r="V25" s="11" t="inlineStr"/>
+      <c r="W25" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -38151,78 +38147,78 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
+          <t>Sayfillayeva Shodiyona</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -38232,7 +38228,7 @@
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -38240,10 +38236,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W26" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -38263,13 +38263,13 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr"/>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -38279,37 +38279,37 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
@@ -38319,18 +38319,22 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
@@ -38340,7 +38344,7 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -38351,7 +38355,7 @@
       <c r="V27" s="11" t="inlineStr"/>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -38371,13 +38375,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -38387,62 +38391,58 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02172469</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -38452,7 +38452,7 @@
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U28" s="7" t="inlineStr">
@@ -38463,7 +38463,7 @@
       <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X28" s="7" t="inlineStr">
@@ -38483,13 +38483,13 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yahyomurodova Gulsanam</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr"/>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -38499,37 +38499,37 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
@@ -38539,22 +38539,22 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q29" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -38584,8 +38584,120 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Samijon qizi</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>AE4688777</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>63007085680074</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>20.10.2025</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>30.07.2008</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X30" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X29"/>
+  <autoFilter ref="A1:X30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -38596,7 +38708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38976,13 +39088,13 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor</t>
+          <t>Salayeva Dilroz</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -38990,90 +39102,38 @@
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Iskandar qizi</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>AB5359926</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>40211995680023</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>12.12.2016</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>02.11.1999</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>K 5047841</t>
-        </is>
-      </c>
+          <t>Salayeva Dilroz</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>Kitob san'at va xizmat ko'rsatish kasb-hunar kolleji</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>Kasb-hunar kolleji diplomi</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
-        </is>
-      </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
-        </is>
-      </c>
-      <c r="X4" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X4" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -39088,165 +39148,105 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
+          <t>Usmonova Gulnoza</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr"/>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr"/>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>46272</v>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Xamdam qizi</t>
+        </is>
+      </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr"/>
-      <c r="M5" s="12" t="inlineStr"/>
-      <c r="N5" s="12" t="inlineStr"/>
-      <c r="O5" s="11" t="inlineStr"/>
-      <c r="P5" s="9" t="inlineStr"/>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>AB5702170</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>42601925680010</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>19.01.2017</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>26.01.1992</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>K 1994177</t>
+        </is>
+      </c>
       <c r="Q5" s="11" t="inlineStr"/>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="12" t="inlineStr"/>
-      <c r="T5" s="12" t="inlineStr"/>
-      <c r="U5" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V5" s="11" t="inlineStr"/>
-      <c r="W5" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X5" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>26-07</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>46272</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>AB5702170</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42601925680010</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>19.01.2017</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>26.01.1992</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>K 1994177</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T6" s="5" t="n">
+      <c r="T5" s="12" t="n">
         <v>2011</v>
       </c>
-      <c r="U6" s="7" t="inlineStr">
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V5" s="11" t="inlineStr">
         <is>
           <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
         </is>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W5" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X6" s="7" t="inlineStr">
+      <c r="X5" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X6"/>
+  <autoFilter ref="A1:X5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -2665,7 +2665,11 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="inlineStr"/>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -2740,9 +2744,9 @@
       </c>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="14" t="inlineStr"/>
-      <c r="X19" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36163,7 +36167,11 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -36238,9 +36246,9 @@
       </c>
       <c r="V4" s="4" t="inlineStr"/>
       <c r="W4" s="14" t="inlineStr"/>
-      <c r="X4" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X4" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -85,14 +85,14 @@
     </font>
     <font>
       <name val="Segoe UI"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00B45309"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="001E40AF"/>
-      <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -146,14 +146,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-        <bgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1448,9 +1448,9 @@
       </c>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="14" t="inlineStr"/>
-      <c r="X7" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="V9" s="11" t="inlineStr"/>
-      <c r="W9" s="16" t="inlineStr">
+      <c r="W9" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="16" t="inlineStr">
+      <c r="W10" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="14" t="inlineStr"/>
-      <c r="X11" s="15" t="inlineStr">
+      <c r="X11" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="16" t="inlineStr">
+      <c r="W13" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -2405,7 +2405,7 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="U16" s="15" t="inlineStr">
+      <c r="U16" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="16" t="inlineStr">
+      <c r="W18" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -2737,7 +2737,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U19" s="15" t="inlineStr">
+      <c r="U19" s="16" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="16" t="inlineStr">
+      <c r="W23" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -3609,7 +3609,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U27" s="15" t="inlineStr">
+      <c r="U27" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -5025,13 +5025,13 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U40" s="15" t="inlineStr">
+      <c r="U40" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
       </c>
       <c r="V40" s="4" t="inlineStr"/>
-      <c r="W40" s="16" t="inlineStr">
+      <c r="W40" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="V43" s="11" t="inlineStr"/>
-      <c r="W43" s="16" t="inlineStr">
+      <c r="W43" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -6022,7 +6022,7 @@
       <c r="U49" s="12" t="inlineStr"/>
       <c r="V49" s="11" t="inlineStr"/>
       <c r="W49" s="14" t="inlineStr"/>
-      <c r="X49" s="15" t="inlineStr">
+      <c r="X49" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -6118,7 +6118,7 @@
       <c r="U50" s="5" t="inlineStr"/>
       <c r="V50" s="4" t="inlineStr"/>
       <c r="W50" s="14" t="inlineStr"/>
-      <c r="X50" s="15" t="inlineStr">
+      <c r="X50" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="V55" s="11" t="inlineStr"/>
-      <c r="W55" s="16" t="inlineStr">
+      <c r="W55" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="V57" s="11" t="inlineStr"/>
-      <c r="W57" s="16" t="inlineStr">
+      <c r="W57" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -8279,7 +8279,7 @@
       <c r="R70" s="4" t="inlineStr"/>
       <c r="S70" s="5" t="inlineStr"/>
       <c r="T70" s="5" t="inlineStr"/>
-      <c r="U70" s="15" t="inlineStr">
+      <c r="U70" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -9006,7 +9006,7 @@
           <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
-      <c r="X77" s="15" t="inlineStr">
+      <c r="X77" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="V80" s="4" t="inlineStr"/>
-      <c r="W80" s="16" t="inlineStr">
+      <c r="W80" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -9560,7 +9560,7 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X82" s="15" t="inlineStr">
+      <c r="X82" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -10297,7 +10297,7 @@
       <c r="R89" s="11" t="inlineStr"/>
       <c r="S89" s="12" t="inlineStr"/>
       <c r="T89" s="12" t="inlineStr"/>
-      <c r="U89" s="15" t="inlineStr">
+      <c r="U89" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -10516,7 +10516,7 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X91" s="15" t="inlineStr">
+      <c r="X91" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -10580,7 +10580,7 @@
           <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
-      <c r="X92" s="15" t="inlineStr">
+      <c r="X92" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -12423,7 +12423,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U109" s="15" t="inlineStr">
+      <c r="U109" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -12549,7 +12549,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
         </is>
       </c>
-      <c r="W110" s="16" t="inlineStr">
+      <c r="W110" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -12777,7 +12777,7 @@
           <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60204095590028).</t>
         </is>
       </c>
-      <c r="W112" s="16" t="inlineStr">
+      <c r="W112" s="15" t="inlineStr">
         <is>
           <t>Shahodatnoma: TRANSLIT</t>
         </is>
@@ -13284,7 +13284,7 @@
           <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
-      <c r="X117" s="15" t="inlineStr">
+      <c r="X117" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -13493,7 +13493,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U119" s="15" t="inlineStr">
+      <c r="U119" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -13605,7 +13605,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U120" s="15" t="inlineStr">
+      <c r="U120" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -14013,14 +14013,14 @@
         </is>
       </c>
       <c r="T124" s="5" t="inlineStr"/>
-      <c r="U124" s="15" t="inlineStr">
+      <c r="U124" s="16" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
       </c>
       <c r="V124" s="4" t="inlineStr"/>
       <c r="W124" s="14" t="inlineStr"/>
-      <c r="X124" s="15" t="inlineStr">
+      <c r="X124" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -15757,7 +15757,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U140" s="15" t="inlineStr">
+      <c r="U140" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -16089,7 +16089,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U143" s="15" t="inlineStr">
+      <c r="U143" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -16750,7 +16750,7 @@
       <c r="U149" s="12" t="inlineStr"/>
       <c r="V149" s="11" t="inlineStr"/>
       <c r="W149" s="14" t="inlineStr"/>
-      <c r="X149" s="15" t="inlineStr">
+      <c r="X149" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -16953,7 +16953,7 @@
           <t>Noma'lum</t>
         </is>
       </c>
-      <c r="U151" s="15" t="inlineStr">
+      <c r="U151" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -17075,7 +17075,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'UROQOVA JASMINA' | bazada: 'O'roqova Jasmina'; imlo farqi — Shahodatnoma PDF: 'Uroqova Jasmina Jasur qizi' | bazada: 'O'roqova Jasmina'</t>
         </is>
       </c>
-      <c r="W152" s="16" t="inlineStr">
+      <c r="W152" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -17173,7 +17173,7 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="U153" s="15" t="inlineStr">
+      <c r="U153" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -17573,14 +17573,14 @@
         </is>
       </c>
       <c r="T157" s="12" t="inlineStr"/>
-      <c r="U157" s="15" t="inlineStr">
+      <c r="U157" s="16" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
       </c>
       <c r="V157" s="11" t="inlineStr"/>
       <c r="W157" s="14" t="inlineStr"/>
-      <c r="X157" s="15" t="inlineStr">
+      <c r="X157" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -17766,13 +17766,13 @@
       <c r="R159" s="11" t="inlineStr"/>
       <c r="S159" s="12" t="inlineStr"/>
       <c r="T159" s="12" t="inlineStr"/>
-      <c r="U159" s="15" t="inlineStr">
+      <c r="U159" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
       </c>
       <c r="V159" s="11" t="inlineStr"/>
-      <c r="W159" s="16" t="inlineStr">
+      <c r="W159" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -18649,7 +18649,7 @@
       <c r="U167" s="12" t="inlineStr"/>
       <c r="V167" s="11" t="inlineStr"/>
       <c r="W167" s="14" t="inlineStr"/>
-      <c r="X167" s="15" t="inlineStr">
+      <c r="X167" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -19538,7 +19538,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
         </is>
       </c>
-      <c r="W175" s="16" t="inlineStr">
+      <c r="W175" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="16" t="inlineStr">
+      <c r="W4" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -21257,7 +21257,7 @@
           <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60204095590028).</t>
         </is>
       </c>
-      <c r="W12" s="16" t="inlineStr">
+      <c r="W12" s="15" t="inlineStr">
         <is>
           <t>Shahodatnoma: TRANSLIT</t>
         </is>
@@ -21471,7 +21471,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U14" s="15" t="inlineStr">
+      <c r="U14" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -21849,7 +21849,7 @@
       </c>
       <c r="V2" s="4" t="inlineStr"/>
       <c r="W2" s="14" t="inlineStr"/>
-      <c r="X2" s="15" t="inlineStr">
+      <c r="X2" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -22386,13 +22386,13 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U7" s="15" t="inlineStr">
+      <c r="U7" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
       </c>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="16" t="inlineStr">
+      <c r="W7" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -22840,7 +22840,7 @@
         </is>
       </c>
       <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="16" t="inlineStr">
+      <c r="W11" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -23512,7 +23512,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
         </is>
       </c>
-      <c r="W17" s="16" t="inlineStr">
+      <c r="W17" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -24390,7 +24390,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U25" s="15" t="inlineStr">
+      <c r="U25" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -24736,7 +24736,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'UROQOVA JASMINA' | bazada: 'O'roqova Jasmina'; imlo farqi — Shahodatnoma PDF: 'Uroqova Jasmina Jasur qizi' | bazada: 'O'roqova Jasmina'</t>
         </is>
       </c>
-      <c r="W28" s="16" t="inlineStr">
+      <c r="W28" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -24834,7 +24834,7 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="U29" s="15" t="inlineStr">
+      <c r="U29" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -25771,7 +25771,7 @@
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="16" t="inlineStr">
+      <c r="W6" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -25982,7 +25982,7 @@
       <c r="U8" s="5" t="inlineStr"/>
       <c r="V8" s="4" t="inlineStr"/>
       <c r="W8" s="14" t="inlineStr"/>
-      <c r="X8" s="15" t="inlineStr">
+      <c r="X8" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -26169,7 +26169,7 @@
       <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="5" t="inlineStr"/>
       <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="15" t="inlineStr">
+      <c r="U10" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -26392,7 +26392,7 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X12" s="15" t="inlineStr">
+      <c r="X12" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -27909,7 +27909,7 @@
           <t>Noma'lum</t>
         </is>
       </c>
-      <c r="U26" s="15" t="inlineStr">
+      <c r="U26" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -28974,7 +28974,7 @@
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="16" t="inlineStr">
+      <c r="W4" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -29086,7 +29086,7 @@
         </is>
       </c>
       <c r="V5" s="11" t="inlineStr"/>
-      <c r="W5" s="16" t="inlineStr">
+      <c r="W5" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -30282,7 +30282,7 @@
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="16" t="inlineStr">
+      <c r="W16" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -31139,7 +31139,7 @@
       <c r="U24" s="5" t="inlineStr"/>
       <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="14" t="inlineStr"/>
-      <c r="X24" s="15" t="inlineStr">
+      <c r="X24" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -31325,13 +31325,13 @@
       <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="5" t="inlineStr"/>
       <c r="T26" s="5" t="inlineStr"/>
-      <c r="U26" s="15" t="inlineStr">
+      <c r="U26" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="16" t="inlineStr">
+      <c r="W26" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -31656,7 +31656,7 @@
       <c r="U29" s="12" t="inlineStr"/>
       <c r="V29" s="11" t="inlineStr"/>
       <c r="W29" s="14" t="inlineStr"/>
-      <c r="X29" s="15" t="inlineStr">
+      <c r="X29" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -32484,7 +32484,7 @@
         </is>
       </c>
       <c r="V3" s="11" t="inlineStr"/>
-      <c r="W3" s="16" t="inlineStr">
+      <c r="W3" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="16" t="inlineStr">
+      <c r="W6" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -33253,7 +33253,7 @@
       <c r="U10" s="5" t="inlineStr"/>
       <c r="V10" s="4" t="inlineStr"/>
       <c r="W10" s="14" t="inlineStr"/>
-      <c r="X10" s="15" t="inlineStr">
+      <c r="X10" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -34214,7 +34214,7 @@
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
       <c r="T19" s="12" t="inlineStr"/>
-      <c r="U19" s="15" t="inlineStr">
+      <c r="U19" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -35750,7 +35750,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
         </is>
       </c>
-      <c r="W33" s="16" t="inlineStr">
+      <c r="W33" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -36142,9 +36142,9 @@
       </c>
       <c r="V3" s="11" t="inlineStr"/>
       <c r="W3" s="14" t="inlineStr"/>
-      <c r="X3" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X3" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36239,7 +36239,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U4" s="15" t="inlineStr">
+      <c r="U4" s="16" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
@@ -36559,7 +36559,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U7" s="15" t="inlineStr">
+      <c r="U7" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -36789,7 +36789,7 @@
         </is>
       </c>
       <c r="V9" s="11" t="inlineStr"/>
-      <c r="W9" s="16" t="inlineStr">
+      <c r="W9" s="15" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -37514,7 +37514,7 @@
           <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
-      <c r="X16" s="15" t="inlineStr">
+      <c r="X16" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -37918,7 +37918,7 @@
           <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
-      <c r="X20" s="15" t="inlineStr">
+      <c r="X20" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -38343,7 +38343,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U24" s="15" t="inlineStr">
+      <c r="U24" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -38459,7 +38459,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U25" s="15" t="inlineStr">
+      <c r="U25" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -38571,7 +38571,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U26" s="15" t="inlineStr">
+      <c r="U26" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -38863,14 +38863,14 @@
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr"/>
-      <c r="U29" s="15" t="inlineStr">
+      <c r="U29" s="16" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr"/>
       <c r="W29" s="14" t="inlineStr"/>
-      <c r="X29" s="15" t="inlineStr">
+      <c r="X29" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -39039,14 +39039,14 @@
         </is>
       </c>
       <c r="T31" s="12" t="inlineStr"/>
-      <c r="U31" s="15" t="inlineStr">
+      <c r="U31" s="16" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
       </c>
       <c r="V31" s="11" t="inlineStr"/>
       <c r="W31" s="14" t="inlineStr"/>
-      <c r="X31" s="15" t="inlineStr">
+      <c r="X31" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -39651,7 +39651,7 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X2" s="15" t="inlineStr">
+      <c r="X2" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -39819,7 +39819,7 @@
           <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
-      <c r="X4" s="15" t="inlineStr">
+      <c r="X4" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -40179,7 +40179,7 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="U2" s="15" t="inlineStr">
+      <c r="U2" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -13998,12 +13998,32 @@
           <t>Sayfiyeva Sarvinoz Zafar qizi</t>
         </is>
       </c>
-      <c r="J124" s="5" t="inlineStr"/>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="5" t="inlineStr"/>
-      <c r="M124" s="5" t="inlineStr"/>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>AB6304158</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>28071542703279</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>28.03.2017</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
+          <t>15.07.1998</t>
+        </is>
+      </c>
       <c r="N124" s="5" t="inlineStr"/>
-      <c r="O124" s="4" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
       <c r="P124" s="2" t="inlineStr"/>
       <c r="Q124" s="4" t="inlineStr"/>
       <c r="R124" s="4" t="inlineStr"/>
@@ -38848,12 +38868,32 @@
           <t>Sayfiyeva Sarvinoz Zafar qizi</t>
         </is>
       </c>
-      <c r="J29" s="12" t="inlineStr"/>
-      <c r="K29" s="9" t="inlineStr"/>
-      <c r="L29" s="12" t="inlineStr"/>
-      <c r="M29" s="12" t="inlineStr"/>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>AB6304158</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>28071542703279</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>28.03.2017</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>15.07.1998</t>
+        </is>
+      </c>
       <c r="N29" s="12" t="inlineStr"/>
-      <c r="O29" s="11" t="inlineStr"/>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
       <c r="P29" s="9" t="inlineStr"/>
       <c r="Q29" s="11" t="inlineStr"/>
       <c r="R29" s="11" t="inlineStr"/>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -14005,7 +14005,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>28071542703279</t>
+          <t>41507985590024</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
@@ -14018,7 +14018,11 @@
           <t>15.07.1998</t>
         </is>
       </c>
-      <c r="N124" s="5" t="inlineStr"/>
+      <c r="N124" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
           <t>Mavjud</t>
@@ -38875,7 +38879,7 @@
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>28071542703279</t>
+          <t>41507985590024</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
@@ -38888,7 +38892,11 @@
           <t>15.07.1998</t>
         </is>
       </c>
-      <c r="N29" s="12" t="inlineStr"/>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
           <t>Mavjud</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -14005,7 +14005,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>41507985590024</t>
+          <t>41507985590074</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
@@ -14028,15 +14028,27 @@
           <t>Mavjud</t>
         </is>
       </c>
-      <c r="P124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>K № 4587984</t>
+        </is>
+      </c>
       <c r="Q124" s="4" t="inlineStr"/>
-      <c r="R124" s="4" t="inlineStr"/>
+      <c r="R124" s="4" t="inlineStr">
+        <is>
+          <t>KASBIY KOLLEJ</t>
+        </is>
+      </c>
       <c r="S124" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T124" s="5" t="inlineStr"/>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T124" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
       <c r="U124" s="16" t="inlineStr">
         <is>
           <t>Chala</t>
@@ -38879,7 +38891,7 @@
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>41507985590024</t>
+          <t>41507985590074</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
@@ -38902,15 +38914,27 @@
           <t>Mavjud</t>
         </is>
       </c>
-      <c r="P29" s="9" t="inlineStr"/>
+      <c r="P29" s="9" t="inlineStr">
+        <is>
+          <t>K № 4587984</t>
+        </is>
+      </c>
       <c r="Q29" s="11" t="inlineStr"/>
-      <c r="R29" s="11" t="inlineStr"/>
+      <c r="R29" s="11" t="inlineStr">
+        <is>
+          <t>KASBIY KOLLEJ</t>
+        </is>
+      </c>
       <c r="S29" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T29" s="12" t="inlineStr"/>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T29" s="12" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
       <c r="U29" s="16" t="inlineStr">
         <is>
           <t>Chala</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -13857,108 +13857,92 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
-        </is>
-      </c>
-      <c r="D123" s="11" t="inlineStr"/>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-19 00:00:00</t>
-        </is>
-      </c>
+          <t>Sayfieva Sarvinoz</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr"/>
+      <c r="F123" s="12" t="inlineStr"/>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>Zafar qizi</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="K123" s="9" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>15.07.1998</t>
         </is>
       </c>
       <c r="N123" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O123" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P123" s="9" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q123" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 4587984</t>
+        </is>
+      </c>
+      <c r="Q123" s="11" t="inlineStr"/>
       <c r="R123" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S123" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T123" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U123" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V123" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W123" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
-        </is>
-      </c>
-      <c r="X123" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U123" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V123" s="11" t="inlineStr"/>
+      <c r="W123" s="14" t="inlineStr"/>
+      <c r="X123" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -13973,92 +13957,108 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr"/>
-      <c r="F124" s="5" t="inlineStr"/>
+          <t>Sayfillayeva Shodiyona</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>Zafar qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>41507985590074</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N124" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>K № 4587984</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr"/>
+          <t>UM 03757340</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
+        </is>
+      </c>
       <c r="R124" s="4" t="inlineStr">
         <is>
-          <t>KASBIY KOLLEJ</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S124" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T124" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U124" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="inlineStr"/>
-      <c r="W124" s="14" t="inlineStr"/>
-      <c r="X124" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U124" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V124" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W124" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+        </is>
+      </c>
+      <c r="X124" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38743,108 +38743,92 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-19 00:00:00</t>
-        </is>
-      </c>
+          <t>Sayfieva Sarvinoz</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>Zafar qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>15.07.1998</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 4587984</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W28" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
-        </is>
-      </c>
-      <c r="X28" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U28" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="14" t="inlineStr"/>
+      <c r="X28" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -38859,92 +38843,108 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr"/>
-      <c r="F29" s="12" t="inlineStr"/>
+          <t>Sayfillayeva Shodiyona</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr"/>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Zafar qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>41507985590074</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>K № 4587984</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="inlineStr"/>
+          <t>UM 03757340</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
+        </is>
+      </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>KASBIY KOLLEJ</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U29" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V29" s="11" t="inlineStr"/>
-      <c r="W29" s="14" t="inlineStr"/>
-      <c r="X29" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V29" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W29" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+        </is>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -24,9 +24,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -8989,7 +8989,11 @@
       <c r="P77" s="9" t="inlineStr"/>
       <c r="Q77" s="11" t="inlineStr"/>
       <c r="R77" s="11" t="inlineStr"/>
-      <c r="S77" s="12" t="inlineStr"/>
+      <c r="S77" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
       <c r="T77" s="12" t="inlineStr"/>
       <c r="U77" s="17" t="inlineStr">
         <is>
@@ -35809,7 +35813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37503,56 +37507,104 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Muminova Durdona</t>
+          <t>Muminova Sevinch</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Anvar qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Muminova Durdona Anvar qizi</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr"/>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
-        </is>
-      </c>
-      <c r="W16" s="14" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X16" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Muminova Sevinch Uchqun qizi</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>AE2259069</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>63001085590111</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>09.04.2025</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>30.01.2008</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>Muminova Sevinch Uchqun qizi</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>UM 03752895</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37567,13 +37619,13 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Muminova Sevinch</t>
+          <t>Muxtorova Xadicha</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr"/>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -37583,37 +37635,37 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Zaxriddin qizi</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>AE2259069</t>
+          <t>AE2428256</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>63001085590111</t>
+          <t>60506085590066</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>09.04.2025</t>
+          <t>22.04.2025</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>30.01.2008</t>
+          <t>05.06.2008</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
@@ -37623,22 +37675,22 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>UM 03752895</t>
+          <t>UM 03751925</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
         </is>
       </c>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
@@ -37679,99 +37731,103 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
+          <t>Narziyeva Intizor</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Zaxriddin qizi</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AB5359926</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>40211995680023</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>12.12.2016</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>02.11.1999</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>UM 03751925</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
-        </is>
-      </c>
+          <t>K 5047841</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr"/>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>To'liq</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+        </is>
+      </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X18" s="7" t="inlineStr">
@@ -37791,108 +37847,56 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>Iskandar qizi</t>
-        </is>
-      </c>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr"/>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>AB5359926</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>40211995680023</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>12.12.2016</t>
-        </is>
-      </c>
-      <c r="M19" s="12" t="inlineStr">
-        <is>
-          <t>02.11.1999</t>
-        </is>
-      </c>
-      <c r="N19" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="inlineStr">
-        <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
-        </is>
-      </c>
-      <c r="P19" s="9" t="inlineStr">
-        <is>
-          <t>K 5047841</t>
-        </is>
-      </c>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="12" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr"/>
+      <c r="L19" s="12" t="inlineStr"/>
+      <c r="M19" s="12" t="inlineStr"/>
+      <c r="N19" s="12" t="inlineStr"/>
+      <c r="O19" s="11" t="inlineStr"/>
+      <c r="P19" s="9" t="inlineStr"/>
       <c r="Q19" s="11" t="inlineStr"/>
-      <c r="R19" s="11" t="inlineStr">
-        <is>
-          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
-        </is>
-      </c>
-      <c r="S19" s="12" t="inlineStr">
-        <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T19" s="12" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U19" s="12" t="inlineStr">
-        <is>
-          <t>To'liq</t>
+      <c r="R19" s="11" t="inlineStr"/>
+      <c r="S19" s="12" t="inlineStr"/>
+      <c r="T19" s="12" t="inlineStr"/>
+      <c r="U19" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V19" s="11" t="inlineStr">
         <is>
-          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W19" s="14" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X19" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -37907,56 +37911,104 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Nurillayeva Sevinch</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Mashrab qizi</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="5" t="inlineStr"/>
-      <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W20" s="14" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X20" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>AD9494409</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>60504085680019</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>26.09.2025</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>05.04.2008</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>UM 03729348</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37971,13 +38023,13 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
+          <t>Ortiqova Dilnoza</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr"/>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -37987,62 +38039,58 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Mashrab qizi</t>
+          <t>Zokir qizi</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Nuraliyeva Sevinch Mirsharaf qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AD9494409</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>60504085680019</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>26.09.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>05.04.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q21" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1313018</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
@@ -38052,7 +38100,7 @@
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -38063,7 +38111,7 @@
       <c r="V21" s="11" t="inlineStr"/>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X21" s="7" t="inlineStr">
@@ -38083,13 +38131,13 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza</t>
+          <t>Qarshiyeva Shahlo</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -38099,37 +38147,37 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Zokir qizi</t>
+          <t>Talantjon qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -38139,18 +38187,22 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 1313018</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr"/>
+          <t>UM 03753960</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
+        </is>
+      </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
@@ -38160,7 +38212,7 @@
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
@@ -38171,7 +38223,7 @@
       <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
@@ -38191,13 +38243,13 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo</t>
+          <t>Quchqarova Zebiniso</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr"/>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -38207,62 +38259,54 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Talantjon qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
-        </is>
-      </c>
+          <t>Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr"/>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03753960</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03742130</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
@@ -38275,15 +38319,19 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V23" s="11" t="inlineStr"/>
+      <c r="U23" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
+        </is>
+      </c>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X23" s="7" t="inlineStr">
@@ -38303,70 +38351,78 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso</t>
+          <t>Samiyeva Sevinchbonu</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03742130</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+          <t>UM 03729118</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
+        </is>
+      </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
@@ -38384,14 +38440,10 @@
           <t>CHALA</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
-        </is>
-      </c>
+      <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -38411,78 +38463,78 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
+          <t>Sanaqulova Muxtarama</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
+          <t>UM 03751785</t>
         </is>
       </c>
       <c r="Q25" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
         </is>
       </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
@@ -38501,9 +38553,9 @@
         </is>
       </c>
       <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
+      <c r="W25" s="14" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -38523,53 +38575,53 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
+          <t>Sanaqulova Nozliya</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -38579,37 +38631,33 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
-        </is>
-      </c>
+          <t>K 5509185</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U26" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
@@ -38635,53 +38683,49 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr"/>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Sayfieva Sarvinoz</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr"/>
+      <c r="F27" s="12" t="inlineStr"/>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Zafar qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>15.07.1998</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
@@ -38691,18 +38735,18 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>K 5509185</t>
+          <t>K 4587984</t>
         </is>
       </c>
       <c r="Q27" s="11" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
@@ -38712,23 +38756,19 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U27" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr"/>
-      <c r="W27" s="14" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X27" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W27" s="14" t="inlineStr"/>
+      <c r="X27" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -38743,92 +38783,108 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
+          <t>Sayfillayeva Shodiyona</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Zafar qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>415079 8559 0074</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>K 4587984</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr"/>
+          <t>UM 03757340</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
+        </is>
+      </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U28" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr"/>
-      <c r="W28" s="14" t="inlineStr"/>
-      <c r="X28" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W28" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+        </is>
+      </c>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38843,78 +38899,78 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr"/>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
+          <t>UM 01922678</t>
         </is>
       </c>
       <c r="Q29" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
         </is>
       </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -38924,7 +38980,7 @@
       </c>
       <c r="T29" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -38932,14 +38988,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V29" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W29" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
+      <c r="V29" s="11" t="inlineStr"/>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X29" s="7" t="inlineStr">
@@ -38959,104 +39011,56 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Uzoqova Fazilat</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>AD2624840</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>62408065590018</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>18.02.2023</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>24.08.2006</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O30" s="4" t="inlineStr">
-        <is>
-          <t>Turayeva Gulasal Jura qizi</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>UM 01922678</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
-        </is>
-      </c>
-      <c r="R30" s="4" t="inlineStr">
-        <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="4" t="inlineStr"/>
+      <c r="R30" s="4" t="inlineStr"/>
       <c r="S30" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="T30" s="5" t="inlineStr"/>
+      <c r="U30" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
         </is>
       </c>
       <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X30" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W30" s="14" t="inlineStr"/>
+      <c r="X30" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -39071,56 +39075,100 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr"/>
-      <c r="F31" s="12" t="inlineStr"/>
+          <t>Xolmurodova Sabina</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr"/>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="inlineStr"/>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr"/>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="12" t="inlineStr"/>
-      <c r="O31" s="11" t="inlineStr"/>
-      <c r="P31" s="9" t="inlineStr"/>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>AD2922676</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>61604065590015</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>01.04.2023</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>16.04.2006</t>
+        </is>
+      </c>
+      <c r="N31" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="inlineStr">
+        <is>
+          <t>UM 02172469</t>
+        </is>
+      </c>
       <c r="Q31" s="11" t="inlineStr"/>
-      <c r="R31" s="11" t="inlineStr"/>
+      <c r="R31" s="11" t="inlineStr">
+        <is>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+        </is>
+      </c>
       <c r="S31" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T31" s="12" t="inlineStr"/>
-      <c r="U31" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
+      <c r="T31" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V31" s="11" t="inlineStr"/>
-      <c r="W31" s="14" t="inlineStr"/>
-      <c r="X31" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X31" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39135,13 +39183,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Yahyomurodova Gulsanam</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -39151,58 +39199,62 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr"/>
+          <t>UM 03729356</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
+        </is>
+      </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
@@ -39212,7 +39264,7 @@
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U32" s="7" t="inlineStr">
@@ -39223,7 +39275,7 @@
       <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -39243,13 +39295,13 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr"/>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -39259,37 +39311,37 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="N33" s="12" t="inlineStr">
@@ -39299,22 +39351,22 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
+          <t>UM 03729007</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
         </is>
       </c>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S33" s="12" t="inlineStr">
@@ -39344,120 +39396,8 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Samijon qizi</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>AE4688777</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>63007085680074</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>20.10.2025</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>30.07.2008</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>UM 03729007</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
-        </is>
-      </c>
-      <c r="R34" s="4" t="inlineStr">
-        <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U34" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X34" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X34"/>
+  <autoFilter ref="A1:X33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40017,7 +39957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -40368,8 +40308,76 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Muminova Durdona</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Anvar qizi</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Muminova Durdona Anvar qizi</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Fayl yuklanmagan (Raxmonova Durdonaning adashib birikkan begona ma'lumotlari olib tashlandi).</t>
+        </is>
+      </c>
+      <c r="W4" s="14" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X4" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X3"/>
+  <autoFilter ref="A1:X4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -1016,7 +1016,11 @@
           <t>Abdixalilova Shohzoda</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>274</t>
@@ -1248,7 +1252,11 @@
           <t>Abdiyeva Sabina</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>140</t>
@@ -1468,7 +1476,11 @@
           <t>Abdurahmonova Parvinabonu</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>203</t>
@@ -1580,7 +1592,11 @@
           <t>Abduraxmonova Zahrobonu</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
           <t>204</t>
@@ -1692,7 +1708,11 @@
           <t>Ahmadova Munisa</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>33</t>
@@ -2000,7 +2020,11 @@
           <t>Arzikulova Amina</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr"/>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
           <t>182</t>
@@ -2224,7 +2248,11 @@
           <t>Ashirova Gulsanam</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
           <t>224</t>
@@ -2336,10 +2364,14 @@
           <t>Axmedova Saodat</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>258</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2436,7 +2468,11 @@
           <t>Azamatova Charos</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
           <t>229</t>
@@ -2548,7 +2584,11 @@
           <t>A'zamov Shohjaxon</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
           <t>86</t>
@@ -2764,7 +2804,11 @@
           <t>Bahodirova Asila</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
           <t>44</t>
@@ -2992,7 +3036,11 @@
           <t>Berdiqulova Gulshan</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>239</t>
@@ -3208,7 +3256,11 @@
           <t>Davlatova Gulnoza</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
           <t>310</t>
@@ -3428,7 +3480,11 @@
           <t>Eshboboyeva Fotima</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>45</t>
@@ -3536,7 +3592,11 @@
           <t>Eshimova Zilola</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
           <t>174</t>
@@ -3640,7 +3700,11 @@
           <t>Eshmurotova Charos</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>110</t>
@@ -3856,10 +3920,14 @@
           <t>Eshpulatova Shahnoza</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -4290,7 +4358,11 @@
           <t>G'aybullayeva Ruxsora</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
           <t>236</t>
@@ -4402,7 +4474,11 @@
           <t>G'ayratova Jasmina</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr"/>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
           <t>97</t>
@@ -4614,7 +4690,11 @@
           <t>Halimova Sevinch</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr"/>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
           <t>26</t>
@@ -4836,7 +4916,11 @@
           <t>Hamroqulova Marjona</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr"/>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
           <t>275</t>
@@ -4952,7 +5036,11 @@
           <t>Hasanova Dilnura</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
           <t>166</t>
@@ -5172,7 +5260,11 @@
           <t>Hazratova Farzona</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
           <t>167</t>
@@ -5396,10 +5488,14 @@
           <t>Ibodullayeva Asilzoda</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>292</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -5614,7 +5710,11 @@
           <t>Ilhomova Zuhra</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>294</t>
@@ -5722,7 +5822,11 @@
           <t>Islomova Nilufar</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr"/>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
           <t>94</t>
@@ -5834,7 +5938,11 @@
           <t>Isomiddinova Ruhshona</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
           <t>65</t>
@@ -6138,7 +6246,11 @@
           <t>Jabborova Bahoroy</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr"/>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
           <t>202</t>
@@ -6250,7 +6362,11 @@
           <t>Jalilova Jasmina</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>95</t>
@@ -6362,7 +6478,11 @@
           <t>Jalilova Shabnam</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr"/>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
           <t>17</t>
@@ -6474,7 +6594,11 @@
           <t>Jalolov Javlonbek</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
           <t>211</t>
@@ -6574,7 +6698,11 @@
           <t>Jalolova Rayxona</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr"/>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
           <t>262</t>
@@ -6686,7 +6814,11 @@
           <t>Javliyeva Nargiza</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
           <t>173</t>
@@ -6798,7 +6930,11 @@
           <t>Jumayeva Husnida</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr"/>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
           <t>18</t>
@@ -6910,10 +7046,14 @@
           <t>Jumayeva Muxlisa</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -7130,7 +7270,11 @@
           <t>Jurayeva Madina</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
           <t>215</t>
@@ -7246,7 +7390,11 @@
           <t>Karimova Nozliya</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr"/>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
           <t>250</t>
@@ -7458,7 +7606,11 @@
           <t>Luxmonova Nozima</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr"/>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
           <t>139</t>
@@ -7570,7 +7722,11 @@
           <t>Mahmadmurodova Sevara</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
           <t>390</t>
@@ -7778,7 +7934,11 @@
           <t>Mahmudova Gulsanam</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
           <t>277</t>
@@ -7888,7 +8048,11 @@
           <t>Mahmudova Maftuna</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr"/>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
           <t>120</t>
@@ -8108,7 +8272,11 @@
           <t>Mannonova Shahrizoda</t>
         </is>
       </c>
-      <c r="D69" s="11" t="inlineStr"/>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
           <t>199</t>
@@ -8220,7 +8388,11 @@
           <t>Mansurova Gulasal</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
           <t>301</t>
@@ -8422,7 +8594,11 @@
           <t>Maxmashoxova Feruza</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
           <t>101</t>
@@ -8534,10 +8710,14 @@
           <t>Maxmudova Musallam</t>
         </is>
       </c>
-      <c r="D73" s="11" t="inlineStr"/>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -8648,7 +8828,11 @@
           <t>Meyliqulova Hilola</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
           <t>60</t>
@@ -8752,10 +8936,14 @@
           <t>Miliyeva Umida</t>
         </is>
       </c>
-      <c r="D75" s="11" t="inlineStr"/>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -9030,7 +9218,11 @@
           <t>Muminova Sevinch</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr"/>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
           <t>163</t>
@@ -9142,10 +9334,14 @@
           <t>Murodova Munisa</t>
         </is>
       </c>
-      <c r="D79" s="11" t="inlineStr"/>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -9250,7 +9446,11 @@
           <t>Murodova Ruhshona</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
           <t>72</t>
@@ -9800,7 +10000,11 @@
           <t>Muxtorova Xadicha</t>
         </is>
       </c>
-      <c r="D85" s="11" t="inlineStr"/>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
           <t>176</t>
@@ -10540,7 +10744,11 @@
           <t>Niyozova Sevara</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr"/>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
           <t>304</t>
@@ -10604,7 +10812,11 @@
           <t>Norboboyeva Farangiz</t>
         </is>
       </c>
-      <c r="D93" s="11" t="inlineStr"/>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
           <t>231</t>
@@ -10824,7 +11036,11 @@
           <t>Numonova Jasmina</t>
         </is>
       </c>
-      <c r="D95" s="11" t="inlineStr"/>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
           <t>106</t>
@@ -10936,7 +11152,11 @@
           <t>Nu'monova Saidabonu</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
           <t>38</t>
@@ -11160,7 +11380,11 @@
           <t>Ochildiyeva Dinora</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr"/>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
           <t>87</t>
@@ -11480,7 +11704,11 @@
           <t>Ortiqova Dilnoza</t>
         </is>
       </c>
-      <c r="D101" s="11" t="inlineStr"/>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
           <t>47</t>
@@ -11698,7 +11926,11 @@
           <t>Pardaqulova Farzona</t>
         </is>
       </c>
-      <c r="D103" s="11" t="inlineStr"/>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
           <t>90</t>
@@ -11810,7 +12042,11 @@
           <t>Pardayeva Farangiz</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
           <t>105</t>
@@ -12034,7 +12270,11 @@
           <t>Primova Husnora</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
           <t>251</t>
@@ -12138,10 +12378,14 @@
           <t>Qarshiyeva Shahlo</t>
         </is>
       </c>
-      <c r="D107" s="11" t="inlineStr"/>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -12250,10 +12494,14 @@
           <t>Qodirova Sabina</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr"/>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>295</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -12462,7 +12710,11 @@
           <t>Quysinova Rohshona</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr"/>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
           <t>242</t>
@@ -12578,7 +12830,11 @@
           <t>Rasulova Husnobod</t>
         </is>
       </c>
-      <c r="D111" s="11" t="inlineStr"/>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
           <t>392</t>
@@ -12806,7 +13062,11 @@
           <t>Rayimova Nozliya</t>
         </is>
       </c>
-      <c r="D113" s="11" t="inlineStr"/>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
           <t>291</t>
@@ -13308,10 +13568,14 @@
           <t>Samadova Nigora</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr"/>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -13528,7 +13792,11 @@
           <t>Sanaqulova Muxtarama</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr"/>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
           <t>254</t>
@@ -13748,7 +14016,11 @@
           <t>Saydalimova Ruxshona</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr"/>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
           <t>74</t>
@@ -13964,10 +14236,14 @@
           <t>Sayfillayeva Shodiyona</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr"/>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -14304,7 +14580,11 @@
           <t>Shamsiyeva Fotima</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr"/>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
           <t>107</t>
@@ -14416,7 +14696,11 @@
           <t>Sharipova Diyora</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr"/>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
           <t>57</t>
@@ -14528,7 +14812,11 @@
           <t>Shukriyeva Nariye</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr"/>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
           <t>162</t>
@@ -14640,7 +14928,11 @@
           <t>Shukurova Zilola</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr"/>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
           <t>172</t>
@@ -14748,7 +15040,11 @@
           <t>Soyipova Dinora</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr"/>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
           <t>288</t>
@@ -15072,7 +15368,11 @@
           <t>Temirboyeva Iroda</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr"/>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
           <t>20</t>
@@ -15184,7 +15484,11 @@
           <t>Temirova Rushana</t>
         </is>
       </c>
-      <c r="D135" s="11" t="inlineStr"/>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
           <t>299</t>
@@ -15288,7 +15592,11 @@
           <t>To'raboyeva Sabrina</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr"/>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
           <t>6</t>
@@ -15400,7 +15708,11 @@
           <t>Tosheva Aziza</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr"/>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
           <t>11</t>
@@ -15504,7 +15816,11 @@
           <t>Toshmurodova Sarvara</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr"/>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
           <t>388</t>
@@ -15612,7 +15928,11 @@
           <t>Toshpo'latova Asila</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr"/>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
           <t>112</t>
@@ -15724,7 +16044,11 @@
           <t>To'xtayeva Durdona</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr"/>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
           <t>161</t>
@@ -15940,7 +16264,11 @@
           <t>Turayeva Gulasal</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr"/>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
           <t>21</t>
@@ -16052,10 +16380,14 @@
           <t>Turg'unova Jasmina</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr"/>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
@@ -16272,7 +16604,11 @@
           <t>Tursunova Aziza</t>
         </is>
       </c>
-      <c r="D145" s="11" t="inlineStr"/>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
           <t>276</t>
@@ -16810,10 +17146,14 @@
           <t>Umarova Iroda</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr"/>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -17024,7 +17364,11 @@
           <t>Uraqova Jasmina</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr"/>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
           <t>148</t>
@@ -17140,7 +17484,11 @@
           <t>Usmanova Iroda</t>
         </is>
       </c>
-      <c r="D153" s="11" t="inlineStr"/>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E153" s="12" t="inlineStr">
         <is>
           <t>279</t>
@@ -17352,7 +17700,11 @@
           <t>Usmonova Sabrina</t>
         </is>
       </c>
-      <c r="D155" s="11" t="inlineStr"/>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
           <t>188</t>
@@ -17640,7 +17992,11 @@
           <t>Xamdamova Madina</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr"/>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
           <t>14</t>
@@ -17837,7 +18193,11 @@
           <t>Xaydarova Iroda</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr"/>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
           <t>113</t>
@@ -17949,7 +18309,11 @@
           <t>Xayrullayeva Umida</t>
         </is>
       </c>
-      <c r="D161" s="11" t="inlineStr"/>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
           <t>116</t>
@@ -18057,7 +18421,11 @@
           <t>Xo'jaqulova Navbahor</t>
         </is>
       </c>
-      <c r="D162" s="4" t="inlineStr"/>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
           <t>302</t>
@@ -18167,7 +18535,11 @@
           <t>Xolmaxmatova Sevinch</t>
         </is>
       </c>
-      <c r="D163" s="11" t="inlineStr"/>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
           <t>108</t>
@@ -18279,7 +18651,11 @@
           <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr"/>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
           <t>183</t>
@@ -18391,7 +18767,11 @@
           <t>Xolmurodova Dilnura</t>
         </is>
       </c>
-      <c r="D165" s="11" t="inlineStr"/>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
           <t>307</t>
@@ -18505,7 +18885,11 @@
           <t>Xolmurodova Sabina</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr"/>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
           <t>138</t>
@@ -18709,7 +19093,11 @@
           <t>Xurramova Lobar</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr"/>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
           <t>234</t>
@@ -18821,7 +19209,11 @@
           <t>Xurramova Shahnoza</t>
         </is>
       </c>
-      <c r="D169" s="11" t="inlineStr"/>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
           <t>29</t>
@@ -18927,7 +19319,11 @@
           <t>Xurramova Shahrizoda</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr"/>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
           <t>96</t>
@@ -19039,7 +19435,11 @@
           <t>Xurramova Shodiya</t>
         </is>
       </c>
-      <c r="D171" s="11" t="inlineStr"/>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
           <t>2</t>
@@ -19151,7 +19551,11 @@
           <t>Xusanova Aziza</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr"/>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
           <t>196</t>
@@ -19379,7 +19783,11 @@
           <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
-      <c r="D174" s="4" t="inlineStr"/>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
           <t>75</t>
@@ -19491,7 +19899,11 @@
           <t>Yuldosheva Ruhshona</t>
         </is>
       </c>
-      <c r="D175" s="11" t="inlineStr"/>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
           <t>118</t>
@@ -19603,7 +20015,11 @@
           <t>Zarifova Marjona</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr"/>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
           <t>93</t>
@@ -19715,7 +20131,11 @@
           <t>Zayidova Shaboda</t>
         </is>
       </c>
-      <c r="D177" s="11" t="inlineStr"/>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
           <t>387</t>
@@ -20214,7 +20634,11 @@
           <t>Abdurahmonova Parvinabonu</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
           <t>203</t>
@@ -20326,7 +20750,11 @@
           <t>Arzikulova Amina</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>182</t>
@@ -20438,7 +20866,11 @@
           <t>Azamatova Charos</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr"/>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
           <t>229</t>
@@ -20550,7 +20982,11 @@
           <t>Hazratova Farzona</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>167</t>
@@ -20662,10 +21098,14 @@
           <t>Ibodullayeva Asilzoda</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr"/>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>292</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -20878,10 +21318,14 @@
           <t>Miliyeva Umida</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -21094,7 +21538,11 @@
           <t>Numonova Jasmina</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
           <t>106</t>
@@ -21434,10 +21882,14 @@
           <t>Turg'unova Jasmina</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -21909,7 +22361,11 @@
           <t>Berdiqulova Gulshan</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
           <t>239</t>
@@ -22017,7 +22473,11 @@
           <t>Eshmurotova Charos</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>110</t>
@@ -22129,7 +22589,11 @@
           <t>G'aybullayeva Ruxsora</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr"/>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
           <t>236</t>
@@ -22353,7 +22817,11 @@
           <t>Hasanova Dilnura</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr"/>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
           <t>166</t>
@@ -22573,7 +23041,11 @@
           <t>Ilhomova Zuhra</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
           <t>294</t>
@@ -22681,7 +23153,11 @@
           <t>Islomova Nilufar</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>94</t>
@@ -22793,7 +23269,11 @@
           <t>Jalolova Rayxona</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
           <t>262</t>
@@ -22905,7 +23385,11 @@
           <t>Javliyeva Nargiza</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>173</t>
@@ -23017,7 +23501,11 @@
           <t>Maxmashoxova Feruza</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr"/>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
           <t>101</t>
@@ -23129,7 +23617,11 @@
           <t>Meyliqulova Hilola</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>60</t>
@@ -23233,7 +23725,11 @@
           <t>Nu'monova Saidabonu</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
           <t>38</t>
@@ -23345,7 +23841,11 @@
           <t>Ochildiyeva Dinora</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>87</t>
@@ -23461,7 +23961,11 @@
           <t>Quysinova Rohshona</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
           <t>242</t>
@@ -23693,10 +24197,14 @@
           <t>Samadova Nigora</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr"/>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -23801,7 +24309,11 @@
           <t>Saydalimova Ruxshona</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
           <t>74</t>
@@ -23917,7 +24429,11 @@
           <t>Shukriyeva Nariye</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr"/>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
           <t>162</t>
@@ -24141,7 +24657,11 @@
           <t>To'raboyeva Sabrina</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr"/>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
           <t>6</t>
@@ -24253,7 +24773,11 @@
           <t>Tosheva Aziza</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
           <t>11</t>
@@ -24357,7 +24881,11 @@
           <t>To'xtayeva Durdona</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr"/>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
           <t>161</t>
@@ -24573,10 +25101,14 @@
           <t>Umarova Iroda</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -24685,7 +25217,11 @@
           <t>Uraqova Jasmina</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>148</t>
@@ -24801,7 +25337,11 @@
           <t>Usmanova Iroda</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr"/>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
           <t>279</t>
@@ -24905,7 +25445,11 @@
           <t>Xurramova Shodiya</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
           <t>2</t>
@@ -25017,7 +25561,11 @@
           <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
           <t>75</t>
@@ -26150,7 +26698,11 @@
           <t>Mansurova Gulasal</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>301</t>
@@ -26452,7 +27004,11 @@
           <t>Norboboyeva Farangiz</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr"/>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
           <t>231</t>
@@ -26564,7 +27120,11 @@
           <t>Pardaqulova Farzona</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>90</t>
@@ -26676,7 +27236,11 @@
           <t>Pardayeva Farangiz</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
           <t>105</t>
@@ -26788,7 +27352,11 @@
           <t>Primova Husnora</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>251</t>
@@ -26892,7 +27460,11 @@
           <t>Rasulova Husnobod</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
           <t>392</t>
@@ -27004,7 +27576,11 @@
           <t>Rayimova Nozliya</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
           <t>291</t>
@@ -27442,7 +28018,11 @@
           <t>Shamsiyeva Fotima</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>107</t>
@@ -27554,7 +28134,11 @@
           <t>Shukurova Zilola</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr"/>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
           <t>172</t>
@@ -27662,7 +28246,11 @@
           <t>Temirova Rushana</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
           <t>299</t>
@@ -27766,7 +28354,11 @@
           <t>Toshpo'latova Asila</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr"/>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
           <t>112</t>
@@ -28092,7 +28684,11 @@
           <t>Xaydarova Iroda</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>113</t>
@@ -28204,7 +28800,11 @@
           <t>Xayrullayeva Umida</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr"/>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
           <t>116</t>
@@ -28312,7 +28912,11 @@
           <t>Xolmaxmatova Sevinch</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
           <t>108</t>
@@ -28424,7 +29028,11 @@
           <t>Xurramova Lobar</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
           <t>234</t>
@@ -28699,7 +29307,11 @@
           <t>Abdixalilova Shohzoda</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>274</t>
@@ -28815,7 +29427,11 @@
           <t>Abdiyeva Sabina</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
           <t>140</t>
@@ -28927,7 +29543,11 @@
           <t>Abduraxmonova Zahrobonu</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>204</t>
@@ -29039,7 +29659,11 @@
           <t>A'zamov Shohjaxon</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr"/>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
           <t>86</t>
@@ -29151,10 +29775,14 @@
           <t>Eshpulatova Shahnoza</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -29473,7 +30101,11 @@
           <t>Halimova Sevinch</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
           <t>26</t>
@@ -29583,7 +30215,11 @@
           <t>Hamroqulova Marjona</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>275</t>
@@ -29699,7 +30335,11 @@
           <t>Isomiddinova Ruhshona</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
           <t>65</t>
@@ -29811,7 +30451,11 @@
           <t>Jalolov Javlonbek</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>211</t>
@@ -30011,7 +30655,11 @@
           <t>Mahmudova Gulsanam</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>277</t>
@@ -30121,10 +30769,14 @@
           <t>Maxmudova Musallam</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -30235,7 +30887,11 @@
           <t>Murodova Ruhshona</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>72</t>
@@ -30569,10 +31225,14 @@
           <t>Qodirova Sabina</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr"/>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>295</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -30673,7 +31333,11 @@
           <t>Soyipova Dinora</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
           <t>288</t>
@@ -30885,7 +31549,11 @@
           <t>Temirboyeva Iroda</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>20</t>
@@ -31199,7 +31867,11 @@
           <t>Xamdamova Madina</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr"/>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
           <t>14</t>
@@ -31396,7 +32068,11 @@
           <t>Xo'jaqulova Navbahor</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
           <t>302</t>
@@ -31506,7 +32182,11 @@
           <t>Xolmurodova Dilnura</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>307</t>
@@ -31716,7 +32396,11 @@
           <t>Xurramova Shahnoza</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
           <t>29</t>
@@ -31822,7 +32506,11 @@
           <t>Xurramova Shahrizoda</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
           <t>96</t>
@@ -31934,7 +32622,11 @@
           <t>Xusanova Aziza</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
           <t>196</t>
@@ -32050,7 +32742,11 @@
           <t>Zayidova Shaboda</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr"/>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
           <t>387</t>
@@ -32437,7 +33133,11 @@
           <t>Ahmadova Munisa</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
           <t>33</t>
@@ -32549,7 +33249,11 @@
           <t>Ashirova Gulsanam</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>224</t>
@@ -32997,7 +33701,11 @@
           <t>Eshboboyeva Fotima</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>45</t>
@@ -33105,7 +33813,11 @@
           <t>G'ayratova Jasmina</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
           <t>97</t>
@@ -33313,7 +34025,11 @@
           <t>Jabborova Bahoroy</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
           <t>202</t>
@@ -33425,7 +34141,11 @@
           <t>Jalilova Jasmina</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>95</t>
@@ -33537,10 +34257,14 @@
           <t>Jumayeva Muxlisa</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr"/>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -33649,7 +34373,11 @@
           <t>Jurayeva Madina</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>215</t>
@@ -33765,7 +34493,11 @@
           <t>Luxmonova Nozima</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
           <t>139</t>
@@ -33983,10 +34715,14 @@
           <t>Murodova Munisa</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -34923,7 +35659,11 @@
           <t>Sharipova Diyora</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>57</t>
@@ -35035,7 +35775,11 @@
           <t>Toshmurodova Sarvara</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
           <t>388</t>
@@ -35143,7 +35887,11 @@
           <t>Tursunova Aziza</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>276</t>
@@ -35479,7 +36227,11 @@
           <t>Usmonova Sabrina</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
           <t>188</t>
@@ -35591,7 +36343,11 @@
           <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
           <t>183</t>
@@ -35703,7 +36459,11 @@
           <t>Yuldosheva Ruhshona</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr"/>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
           <t>118</t>
@@ -36306,7 +37066,11 @@
           <t>Bahodirova Asila</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr"/>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
           <t>44</t>
@@ -36418,7 +37182,11 @@
           <t>Davlatova Gulnoza</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>310</t>
@@ -36526,7 +37294,11 @@
           <t>Eshimova Zilola</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr"/>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
           <t>174</t>
@@ -36630,7 +37402,11 @@
           <t>Jalilova Shabnam</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>17</t>
@@ -36742,7 +37518,11 @@
           <t>Jumayeva Husnida</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
           <t>18</t>
@@ -36854,7 +37634,11 @@
           <t>Karimova Nozliya</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>250</t>
@@ -36966,7 +37750,11 @@
           <t>Mahmadmurodova Sevara</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
           <t>390</t>
@@ -37174,7 +37962,11 @@
           <t>Mahmudova Maftuna</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr"/>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
           <t>120</t>
@@ -37286,7 +38078,11 @@
           <t>Mannonova Shahrizoda</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>199</t>
@@ -37510,7 +38306,11 @@
           <t>Muminova Sevinch</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>163</t>
@@ -37622,7 +38422,11 @@
           <t>Muxtorova Xadicha</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
           <t>176</t>
@@ -37850,7 +38654,11 @@
           <t>Niyozova Sevara</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr"/>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
           <t>304</t>
@@ -38026,7 +38834,11 @@
           <t>Ortiqova Dilnoza</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr"/>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
           <t>47</t>
@@ -38134,10 +38946,14 @@
           <t>Qarshiyeva Shahlo</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -38466,7 +39282,11 @@
           <t>Sanaqulova Muxtarama</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr"/>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
           <t>254</t>
@@ -38786,10 +39606,14 @@
           <t>Sayfillayeva Shodiyona</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -38902,7 +39726,11 @@
           <t>Turayeva Gulasal</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr"/>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
           <t>21</t>
@@ -39078,7 +39906,11 @@
           <t>Xolmurodova Sabina</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
           <t>138</t>
@@ -39298,7 +40130,11 @@
           <t>Zarifova Marjona</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr"/>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
           <t>93</t>
@@ -40122,10 +40958,14 @@
           <t>Axmedova Saodat</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>258</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -15405,12 +15405,12 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Sarvarovna qizi</t>
+          <t>Sarvarovna</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna qizi</t>
+          <t>Temirova Rushana Sarvarovna</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr"/>
@@ -28195,12 +28195,12 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Sarvarovna qizi</t>
+          <t>Sarvarovna</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna qizi</t>
+          <t>Temirova Rushana Sarvarovna</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr"/>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -18,14 +18,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$179</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X178"/>
+  <dimension ref="A1:X179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>Ulug‘bek qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -9910,8 +9910,10 @@
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T83" s="12" t="n">
-        <v>2019</v>
+      <c r="T83" s="12" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
       </c>
       <c r="U83" s="7" t="inlineStr">
         <is>
@@ -19213,12 +19215,12 @@
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza</t>
+          <t>Xurramova Sabina</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
@@ -19228,92 +19230,74 @@
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F169" s="18" t="n">
-        <v>46204</v>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F169" s="12" t="inlineStr"/>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Shuhrat qizi</t>
+          <t>Yuldosh qizi</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
-      <c r="I169" s="10" t="inlineStr">
-        <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
+          <t>Xurramova Sabina Yuldosh qizi</t>
+        </is>
+      </c>
+      <c r="I169" s="10" t="inlineStr"/>
       <c r="J169" s="12" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AC3081523</t>
         </is>
       </c>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>60803048230011</t>
         </is>
       </c>
       <c r="L169" s="12" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>16.10.2020</t>
         </is>
       </c>
       <c r="M169" s="12" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
-        </is>
-      </c>
-      <c r="N169" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
+          <t>08.03.2004</t>
+        </is>
+      </c>
+      <c r="N169" s="12" t="inlineStr"/>
       <c r="O169" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P169" s="9" t="inlineStr">
         <is>
-          <t>UM 0084478</t>
+          <t>UM 1315230</t>
         </is>
       </c>
       <c r="Q169" s="11" t="inlineStr"/>
       <c r="R169" s="11" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S169" s="12" t="inlineStr">
         <is>
-          <t>Attestat</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T169" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U169" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U169" s="12" t="inlineStr"/>
       <c r="V169" s="11" t="inlineStr"/>
-      <c r="W169" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X169" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W169" s="15" t="inlineStr"/>
+      <c r="X169" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -19328,7 +19312,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda</t>
+          <t>Xurramova Shahnoza</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -19338,13 +19322,11 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="n">
+        <v>46204</v>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
@@ -19353,32 +19335,32 @@
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="M170" s="5" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
       <c r="N170" s="5" t="inlineStr">
@@ -19388,32 +19370,28 @@
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>UM 02149677</t>
-        </is>
-      </c>
-      <c r="Q170" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0084478</t>
+        </is>
+      </c>
+      <c r="Q170" s="4" t="inlineStr"/>
       <c r="R170" s="4" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S170" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Attestat</t>
         </is>
       </c>
       <c r="T170" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U170" s="7" t="inlineStr">
@@ -19439,12 +19417,12 @@
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Xurramova Shahrizoda</t>
         </is>
       </c>
       <c r="D171" s="11" t="inlineStr">
@@ -19454,7 +19432,7 @@
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
@@ -19464,58 +19442,62 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Shuhrat qizi</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="J171" s="12" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="K171" s="9" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="L171" s="12" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="M171" s="12" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>30.04.2007</t>
         </is>
       </c>
       <c r="N171" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="P171" s="9" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q171" s="11" t="inlineStr"/>
+          <t>UM 02149677</t>
+        </is>
+      </c>
+      <c r="Q171" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
+        </is>
+      </c>
       <c r="R171" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S171" s="12" t="inlineStr">
@@ -19525,7 +19507,7 @@
       </c>
       <c r="T171" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U171" s="7" t="inlineStr">
@@ -19533,11 +19515,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V171" s="11" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V171" s="11" t="inlineStr"/>
       <c r="W171" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -19555,12 +19533,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza</t>
+          <t>Xurramova Shodiya</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -19570,7 +19548,7 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -19580,37 +19558,37 @@
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>Fazliddin qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M172" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>27.04.2002</t>
         </is>
       </c>
       <c r="N172" s="5" t="inlineStr">
@@ -19620,22 +19598,18 @@
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>UM 03753649</t>
-        </is>
-      </c>
-      <c r="Q172" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0438281</t>
+        </is>
+      </c>
+      <c r="Q172" s="4" t="inlineStr"/>
       <c r="R172" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S172" s="5" t="inlineStr">
@@ -19645,7 +19619,7 @@
       </c>
       <c r="T172" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="U172" s="7" t="inlineStr">
@@ -19655,12 +19629,12 @@
       </c>
       <c r="V172" s="4" t="inlineStr">
         <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
         </is>
       </c>
       <c r="W172" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X172" s="7" t="inlineStr">
@@ -19675,18 +19649,22 @@
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
-        </is>
-      </c>
-      <c r="D173" s="11" t="inlineStr"/>
+          <t>Xusanova Aziza</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
@@ -19696,62 +19674,62 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Fazliddin qizi</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="J173" s="12" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="L173" s="12" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="M173" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N173" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="P173" s="9" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
+          <t>UM 03753649</t>
         </is>
       </c>
       <c r="Q173" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
         </is>
       </c>
       <c r="R173" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S173" s="12" t="inlineStr">
@@ -19769,10 +19747,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V173" s="11" t="inlineStr"/>
+      <c r="V173" s="11" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+        </is>
+      </c>
       <c r="W173" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X173" s="7" t="inlineStr">
@@ -19787,22 +19769,18 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Yahyomurodova Gulsanam</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr"/>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -19812,37 +19790,37 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Xusan qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>AB9239333</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>42207935680042</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>09.04.2018</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
-          <t>22.07.1993</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N174" s="5" t="inlineStr">
@@ -19852,22 +19830,22 @@
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>UM 03524597</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q174" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R174" s="4" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S174" s="5" t="inlineStr">
@@ -19877,7 +19855,7 @@
       </c>
       <c r="T174" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U174" s="7" t="inlineStr">
@@ -19888,7 +19866,7 @@
       <c r="V174" s="4" t="inlineStr"/>
       <c r="W174" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X174" s="7" t="inlineStr">
@@ -19903,12 +19881,12 @@
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
       <c r="D175" s="11" t="inlineStr">
@@ -19918,7 +19896,7 @@
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
@@ -19928,68 +19906,72 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L175" s="12" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M175" s="12" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N175" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="P175" s="9" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
-        </is>
-      </c>
-      <c r="Q175" s="11" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q175" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R175" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son texnikumi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S175" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T175" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
@@ -19997,14 +19979,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V175" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
-        </is>
-      </c>
-      <c r="W175" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+      <c r="V175" s="11" t="inlineStr"/>
+      <c r="W175" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X175" s="7" t="inlineStr">
@@ -20019,12 +19997,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yuldosheva Ruhshona</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -20034,7 +20012,7 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -20044,67 +20022,63 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Xabibullo qizi</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>13.09.2008</t>
         </is>
       </c>
       <c r="N176" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
-        </is>
-      </c>
-      <c r="Q176" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q176" s="4" t="inlineStr"/>
       <c r="R176" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
       <c r="S176" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T176" s="5" t="inlineStr">
@@ -20117,10 +20091,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V176" s="4" t="inlineStr"/>
-      <c r="W176" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V176" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
+        </is>
+      </c>
+      <c r="W176" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X176" s="7" t="inlineStr">
@@ -20135,12 +20113,12 @@
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D177" s="11" t="inlineStr">
@@ -20150,7 +20128,7 @@
       </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
@@ -20160,37 +20138,37 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Sodiqovna</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="K177" s="9" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="L177" s="12" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="M177" s="12" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="N177" s="12" t="inlineStr">
@@ -20200,22 +20178,22 @@
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P177" s="9" t="inlineStr">
         <is>
-          <t>UM 03729571</t>
+          <t>UM 03729007</t>
         </is>
       </c>
       <c r="Q177" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
         </is>
       </c>
       <c r="R177" s="11" t="inlineStr">
         <is>
-          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S177" s="12" t="inlineStr">
@@ -20236,7 +20214,7 @@
       <c r="V177" s="11" t="inlineStr"/>
       <c r="W177" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X177" s="7" t="inlineStr">
@@ -20251,18 +20229,22 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr"/>
+          <t>Zayidova Shaboda</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -20272,62 +20254,62 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Alisher qizi</t>
+          <t>Sodiqovna</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>12.06.2007</t>
+          <t>31.12.2008</t>
         </is>
       </c>
       <c r="N178" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>UM 03296188</t>
+          <t>UM 03729571</t>
         </is>
       </c>
       <c r="Q178" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
         </is>
       </c>
       <c r="R178" s="4" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S178" s="5" t="inlineStr">
@@ -20337,7 +20319,7 @@
       </c>
       <c r="T178" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U178" s="7" t="inlineStr">
@@ -20348,17 +20330,129 @@
       <c r="V178" s="4" t="inlineStr"/>
       <c r="W178" s="8" t="inlineStr">
         <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X178" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="22" customHeight="1">
+      <c r="A179" s="9" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina</t>
+        </is>
+      </c>
+      <c r="D179" s="11" t="inlineStr"/>
+      <c r="E179" s="12" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="F179" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>Alisher qizi</t>
+        </is>
+      </c>
+      <c r="H179" s="11" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="I179" s="10" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="J179" s="12" t="inlineStr">
+        <is>
+          <t>AD9812146</t>
+        </is>
+      </c>
+      <c r="K179" s="9" t="inlineStr">
+        <is>
+          <t>61206075590076</t>
+        </is>
+      </c>
+      <c r="L179" s="12" t="inlineStr">
+        <is>
+          <t>13.12.2024</t>
+        </is>
+      </c>
+      <c r="M179" s="12" t="inlineStr">
+        <is>
+          <t>12.06.2007</t>
+        </is>
+      </c>
+      <c r="N179" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O179" s="11" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="P179" s="9" t="inlineStr">
+        <is>
+          <t>UM 03296188</t>
+        </is>
+      </c>
+      <c r="Q179" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+        </is>
+      </c>
+      <c r="R179" s="11" t="inlineStr">
+        <is>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S179" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T179" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U179" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V179" s="11" t="inlineStr"/>
+      <c r="W179" s="8" t="inlineStr">
+        <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X178" s="7" t="inlineStr">
+      <c r="X179" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X178"/>
+  <autoFilter ref="A1:X179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25707,7 +25801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -29170,8 +29264,100 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Xurramova Sabina</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Yuldosh qizi</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Xurramova Sabina Yuldosh qizi</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>AC3081523</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>60803048230011</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>16.10.2020</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>08.03.2004</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>UM 1315230</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="15" t="inlineStr"/>
+      <c r="X32" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X31"/>
+  <autoFilter ref="A1:X32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36581,7 +36767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38435,57 +38621,51 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Mustafayeva Nargiza</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr"/>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>46255</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Zaxriddin qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>29.06.2000</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
@@ -38495,32 +38675,28 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>UM 03751925</t>
-        </is>
-      </c>
-      <c r="Q17" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
-        </is>
-      </c>
+          <t>K 5487472</t>
+        </is>
+      </c>
+      <c r="Q17" s="11" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T17" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
@@ -38528,7 +38704,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V17" s="11" t="inlineStr"/>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
+        </is>
+      </c>
       <c r="W17" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -38551,7 +38731,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor</t>
+          <t>Muxtorova Xadicha</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -38561,93 +38741,93 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Zaxriddin qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AB5359926</t>
+          <t>AE2428256</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40211995680023</t>
+          <t>60506085590066</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>12.12.2016</t>
+          <t>22.04.2025</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>02.11.1999</t>
+          <t>05.06.2008</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>K 5047841</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr"/>
+          <t>UM 03751925</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+        </is>
+      </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="inlineStr">
-        <is>
-          <t>To'liq</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X18" s="7" t="inlineStr">
@@ -38667,7 +38847,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Narziyeva Intizor</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -38677,50 +38857,98 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr"/>
+          <t>22.08.2026</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Iskandar qizi</t>
+        </is>
+      </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="12" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="12" t="inlineStr"/>
-      <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="9" t="inlineStr"/>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>AB5359926</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>40211995680023</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>12.12.2016</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>02.11.1999</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>K 5047841</t>
+        </is>
+      </c>
       <c r="Q19" s="11" t="inlineStr"/>
-      <c r="R19" s="11" t="inlineStr"/>
-      <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="12" t="inlineStr"/>
-      <c r="U19" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+      <c r="R19" s="11" t="inlineStr">
+        <is>
+          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T19" s="12" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U19" s="12" t="inlineStr">
+        <is>
+          <t>To'liq</t>
         </is>
       </c>
       <c r="V19" s="11" t="inlineStr">
         <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W19" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X19" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38735,108 +38963,60 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Mashrab qizi</t>
-        </is>
-      </c>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>AD9494409</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>60504085680019</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>26.09.2025</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>05.04.2008</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
-      <c r="R20" s="4" t="inlineStr">
-        <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi (#246) ma'lumotlari tasdiqlandi</t>
-        </is>
-      </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W20" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X20" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -38851,78 +39031,78 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Nurillayeva Sevinch</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr"/>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Zokir qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>UM 1313018</t>
-        </is>
-      </c>
-      <c r="Q21" s="11" t="inlineStr"/>
+          <t>UM 03729348</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
+        </is>
+      </c>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
@@ -38932,7 +39112,7 @@
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -38940,10 +39120,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V21" s="11" t="inlineStr"/>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>Nurillayeva Sevinch Mashrab qizi (#246) ma'lumotlari tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X21" s="7" t="inlineStr">
@@ -38963,7 +39147,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo</t>
+          <t>Ortiqova Dilnoza</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -38973,7 +39157,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -38983,37 +39167,37 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Talantjon qizi</t>
+          <t>Zokir qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -39023,22 +39207,18 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 03753960</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1313018</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
@@ -39048,7 +39228,7 @@
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
@@ -39059,7 +39239,7 @@
       <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
@@ -39079,13 +39259,17 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr"/>
+          <t>Qarshiyeva Shahlo</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -39095,54 +39279,62 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Talantjon qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+        </is>
+      </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03742130</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr"/>
+          <t>UM 03753960</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
+        </is>
+      </c>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
@@ -39155,19 +39347,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U23" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V23" s="11" t="inlineStr">
-        <is>
-          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
-        </is>
-      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr"/>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X23" s="7" t="inlineStr">
@@ -39187,78 +39375,70 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
+          <t>Quchqarova Zebiniso</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03742130</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
@@ -39276,10 +39456,14 @@
           <t>CHALA</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
+        </is>
+      </c>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -39299,82 +39483,78 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Samiyeva Sevinchbonu</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q25" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
@@ -39393,9 +39573,9 @@
         </is>
       </c>
       <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -39415,53 +39595,57 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>Sanaqulova Muxtarama</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -39471,33 +39655,37 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U26" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
@@ -39523,49 +39711,53 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr"/>
-      <c r="F27" s="12" t="inlineStr"/>
+          <t>Sanaqulova Nozliya</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr"/>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Zafar qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>415079 8559 0074</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
@@ -39575,18 +39767,18 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>K 4587984</t>
+          <t>K 5509185</t>
         </is>
       </c>
       <c r="Q27" s="11" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
@@ -39596,19 +39788,23 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U27" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr"/>
-      <c r="W27" s="15" t="inlineStr"/>
-      <c r="X27" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="W27" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39623,7 +39819,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
+          <t>Sayfieva Sarvinoz</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -39631,104 +39827,84 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-19 00:00:00</t>
-        </is>
-      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>Zafar qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>15.07.1998</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 4587984</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W28" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
-        </is>
-      </c>
-      <c r="X28" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U28" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="15" t="inlineStr"/>
+      <c r="X28" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -39743,7 +39919,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
+          <t>Sayfillayeva Shodiyona</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -39753,72 +39929,72 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q29" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -39828,7 +40004,7 @@
       </c>
       <c r="T29" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -39836,10 +40012,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V29" s="11" t="inlineStr"/>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V29" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W29" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X29" s="7" t="inlineStr">
@@ -39859,7 +40039,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -39867,48 +40047,100 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="4" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="4" t="inlineStr"/>
-      <c r="R30" s="4" t="inlineStr"/>
+          <t>Turayeva Gulasal Jura qizi</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>AD2624840</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>62408065590018</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>18.02.2023</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>24.08.2006</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>Turayeva Gulasal Jura qizi</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="15" t="inlineStr"/>
-      <c r="X30" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="W30" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X30" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39923,7 +40155,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Uzoqova Fazilat</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -39931,96 +40163,48 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E31" s="12" t="inlineStr"/>
+      <c r="F31" s="12" t="inlineStr"/>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="inlineStr">
-        <is>
-          <t>AD2922676</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>61604065590015</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>01.04.2023</t>
-        </is>
-      </c>
-      <c r="M31" s="12" t="inlineStr">
-        <is>
-          <t>16.04.2006</t>
-        </is>
-      </c>
-      <c r="N31" s="12" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O31" s="11" t="inlineStr">
-        <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
-        </is>
-      </c>
-      <c r="P31" s="9" t="inlineStr">
-        <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr"/>
+      <c r="K31" s="9" t="inlineStr"/>
+      <c r="L31" s="12" t="inlineStr"/>
+      <c r="M31" s="12" t="inlineStr"/>
+      <c r="N31" s="12" t="inlineStr"/>
+      <c r="O31" s="11" t="inlineStr"/>
+      <c r="P31" s="9" t="inlineStr"/>
       <c r="Q31" s="11" t="inlineStr"/>
-      <c r="R31" s="11" t="inlineStr">
-        <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
-        </is>
-      </c>
+      <c r="R31" s="11" t="inlineStr"/>
       <c r="S31" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T31" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="T31" s="12" t="inlineStr"/>
+      <c r="U31" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
         </is>
       </c>
       <c r="V31" s="11" t="inlineStr"/>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X31" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W31" s="15" t="inlineStr"/>
+      <c r="X31" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -40035,13 +40219,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
+          <t>Xolmurodova Sabina</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -40051,62 +40239,58 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02172469</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
@@ -40116,7 +40300,7 @@
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U32" s="7" t="inlineStr">
@@ -40127,7 +40311,7 @@
       <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -40147,17 +40331,13 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Yahyomurodova Gulsanam</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr"/>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -40167,37 +40347,37 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N33" s="12" t="inlineStr">
@@ -40207,22 +40387,22 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S33" s="12" t="inlineStr">
@@ -40252,8 +40432,124 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Samijon qizi</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>AE4688777</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>63007085680074</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>20.10.2025</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>30.07.2008</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U34" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X34" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X33"/>
+  <autoFilter ref="A1:X34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40264,7 +40560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -40540,100 +40836,52 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza</t>
+          <t>Salayeva Dilroz</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr"/>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="n">
-        <v>46255</v>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Ulug‘bek qizi</t>
-        </is>
-      </c>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr"/>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>AB8521319</t>
-        </is>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>62906005590060</t>
-        </is>
-      </c>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>02.01.2018</t>
-        </is>
-      </c>
-      <c r="M3" s="12" t="inlineStr">
-        <is>
-          <t>29.06.2000</t>
-        </is>
-      </c>
-      <c r="N3" s="12" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O3" s="11" t="inlineStr">
-        <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
-        </is>
-      </c>
-      <c r="P3" s="9" t="inlineStr">
-        <is>
-          <t>K 5487472</t>
-        </is>
-      </c>
+          <t>Salayeva Dilroz</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="12" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr"/>
+      <c r="M3" s="12" t="inlineStr"/>
+      <c r="N3" s="12" t="inlineStr"/>
+      <c r="O3" s="11" t="inlineStr"/>
+      <c r="P3" s="9" t="inlineStr"/>
       <c r="Q3" s="11" t="inlineStr"/>
-      <c r="R3" s="11" t="inlineStr">
-        <is>
-          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
-        </is>
-      </c>
-      <c r="S3" s="12" t="inlineStr">
-        <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T3" s="12" t="n">
-        <v>2019</v>
-      </c>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V3" s="11" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
-        </is>
-      </c>
-      <c r="W3" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X3" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="R3" s="11" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr"/>
+      <c r="T3" s="12" t="inlineStr"/>
+      <c r="U3" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V3" s="11" t="inlineStr"/>
+      <c r="W3" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X3" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -40648,165 +40896,105 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
+          <t>Usmonova Gulnoza</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>46272</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Xamdam qizi</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>AB5702170</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>42601925680010</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>19.01.2017</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>26.01.1992</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>K 1994177</t>
+        </is>
+      </c>
       <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X4" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>26-07</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr"/>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>46272</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>AB5702170</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>42601925680010</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>19.01.2017</t>
-        </is>
-      </c>
-      <c r="M5" s="12" t="inlineStr">
-        <is>
-          <t>26.01.1992</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>K 1994177</t>
-        </is>
-      </c>
-      <c r="Q5" s="11" t="inlineStr"/>
-      <c r="R5" s="11" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="S5" s="12" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T5" s="12" t="n">
+      <c r="T4" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="U5" s="7" t="inlineStr">
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V5" s="11" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
         </is>
       </c>
-      <c r="W5" s="8" t="inlineStr">
+      <c r="W4" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X5" s="7" t="inlineStr">
+      <c r="X4" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X5"/>
+  <autoFilter ref="A1:X4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -24,8 +24,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17482,7 +17482,7 @@
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
@@ -17560,8 +17560,10 @@
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T153" s="12" t="n">
-        <v>2011</v>
+      <c r="T153" s="12" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
       </c>
       <c r="U153" s="7" t="inlineStr">
         <is>
@@ -36767,7 +36769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -40155,56 +40157,102 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr"/>
-      <c r="F31" s="12" t="inlineStr"/>
+          <t>Usmonova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr"/>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>46272</v>
+      </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Xamdam qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="inlineStr"/>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr"/>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="12" t="inlineStr"/>
-      <c r="O31" s="11" t="inlineStr"/>
-      <c r="P31" s="9" t="inlineStr"/>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>AB5702170</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>42601925680010</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>19.01.2017</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>26.01.1992</t>
+        </is>
+      </c>
+      <c r="N31" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="inlineStr">
+        <is>
+          <t>K 1994177</t>
+        </is>
+      </c>
       <c r="Q31" s="11" t="inlineStr"/>
-      <c r="R31" s="11" t="inlineStr"/>
+      <c r="R31" s="11" t="inlineStr">
+        <is>
+          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
+        </is>
+      </c>
       <c r="S31" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T31" s="12" t="inlineStr"/>
-      <c r="U31" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V31" s="11" t="inlineStr"/>
-      <c r="W31" s="15" t="inlineStr"/>
-      <c r="X31" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T31" s="12" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X31" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40219,7 +40267,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Uzoqova Fazilat</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -40227,96 +40275,48 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>AD2922676</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>61604065590015</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>01.04.2023</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>16.04.2006</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="4" t="inlineStr"/>
-      <c r="R32" s="4" t="inlineStr">
-        <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
-        </is>
-      </c>
+      <c r="R32" s="4" t="inlineStr"/>
       <c r="S32" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="T32" s="5" t="inlineStr"/>
+      <c r="U32" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
         </is>
       </c>
       <c r="V32" s="4" t="inlineStr"/>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X32" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W32" s="15" t="inlineStr"/>
+      <c r="X32" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -40331,13 +40331,17 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr"/>
+          <t>Xolmurodova Sabina</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -40347,62 +40351,58 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q33" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02172469</t>
+        </is>
+      </c>
+      <c r="Q33" s="11" t="inlineStr"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S33" s="12" t="inlineStr">
@@ -40412,7 +40412,7 @@
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -40423,7 +40423,7 @@
       <c r="V33" s="11" t="inlineStr"/>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X33" s="7" t="inlineStr">
@@ -40443,17 +40443,13 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Yahyomurodova Gulsanam</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -40463,37 +40459,37 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -40503,22 +40499,22 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr">
@@ -40548,8 +40544,124 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Samijon qizi</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>AE4688777</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>63007085680074</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>20.10.2025</t>
+        </is>
+      </c>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>30.07.2008</t>
+        </is>
+      </c>
+      <c r="N35" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O35" s="11" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="P35" s="9" t="inlineStr">
+        <is>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q35" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
+      <c r="R35" s="11" t="inlineStr">
+        <is>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S35" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T35" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U35" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V35" s="11" t="inlineStr"/>
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X35" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X34"/>
+  <autoFilter ref="A1:X35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40560,7 +40672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -40885,116 +40997,8 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>26-07</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>46272</v>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>AB5702170</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42601925680010</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>19.01.2017</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>26.01.1992</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>K 1994177</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>2011</v>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
-        </is>
-      </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X4" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X4"/>
+  <autoFilter ref="A1:X3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10665,24 +10665,64 @@
           <t>2026-09-14 00:00:00</t>
         </is>
       </c>
-      <c r="G91" s="12" t="inlineStr"/>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>Turoqulovna</t>
+        </is>
+      </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr"/>
-      <c r="J91" s="12" t="inlineStr"/>
-      <c r="K91" s="9" t="inlineStr"/>
-      <c r="L91" s="12" t="inlineStr"/>
-      <c r="M91" s="12" t="inlineStr"/>
-      <c r="N91" s="12" t="inlineStr"/>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>AD9706738</t>
+        </is>
+      </c>
+      <c r="K91" s="9" t="inlineStr">
+        <is>
+          <t>412068 9256 0120</t>
+        </is>
+      </c>
+      <c r="L91" s="12" t="inlineStr">
+        <is>
+          <t>12.06.1989</t>
+        </is>
+      </c>
+      <c r="M91" s="12" t="inlineStr">
+        <is>
+          <t>12.06.1989</t>
+        </is>
+      </c>
+      <c r="N91" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O91" s="11" t="inlineStr"/>
-      <c r="P91" s="9" t="inlineStr"/>
+      <c r="P91" s="9" t="inlineStr">
+        <is>
+          <t>K 0998119</t>
+        </is>
+      </c>
       <c r="Q91" s="11" t="inlineStr"/>
-      <c r="R91" s="11" t="inlineStr"/>
-      <c r="S91" s="12" t="inlineStr"/>
-      <c r="T91" s="12" t="inlineStr"/>
+      <c r="R91" s="11" t="inlineStr">
+        <is>
+          <t>Shahrisabz qishloq xo'jaligi kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S91" s="12" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T91" s="12" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
       <c r="U91" s="17" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -38983,24 +39023,64 @@
           <t>2026-09-14 00:00:00</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Turoqulovna</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>AD9706738</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>412068 9256 0120</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>12.06.1989</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>12.06.1989</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>K 0998119</t>
+        </is>
+      </c>
       <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="5" t="inlineStr"/>
-      <c r="T20" s="5" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>Shahrisabz qishloq xo'jaligi kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
       <c r="U20" s="17" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10500,17 +10500,53 @@
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr"/>
-      <c r="J89" s="12" t="inlineStr"/>
-      <c r="K89" s="9" t="inlineStr"/>
-      <c r="L89" s="12" t="inlineStr"/>
-      <c r="M89" s="12" t="inlineStr"/>
-      <c r="N89" s="12" t="inlineStr"/>
+      <c r="J89" s="12" t="inlineStr">
+        <is>
+          <t>AE7082532</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>602121 8568 0048</t>
+        </is>
+      </c>
+      <c r="L89" s="12" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="M89" s="12" t="inlineStr">
+        <is>
+          <t>02.12.2018</t>
+        </is>
+      </c>
+      <c r="N89" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O89" s="11" t="inlineStr"/>
-      <c r="P89" s="9" t="inlineStr"/>
+      <c r="P89" s="9" t="inlineStr">
+        <is>
+          <t>UM03727760</t>
+        </is>
+      </c>
       <c r="Q89" s="11" t="inlineStr"/>
-      <c r="R89" s="11" t="inlineStr"/>
-      <c r="S89" s="12" t="inlineStr"/>
-      <c r="T89" s="12" t="inlineStr"/>
+      <c r="R89" s="11" t="inlineStr">
+        <is>
+          <t>1-maktab</t>
+        </is>
+      </c>
+      <c r="S89" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T89" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="U89" s="17" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -35315,17 +35351,53 @@
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>AE7082532</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>602121 8568 0048</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>02.12.2018</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>UM03727760</t>
+        </is>
+      </c>
       <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="5" t="inlineStr"/>
-      <c r="T20" s="5" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>1-maktab</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="U20" s="17" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -17926,21 +17926,53 @@
           <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
-      <c r="J156" s="5" t="inlineStr"/>
-      <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="5" t="inlineStr"/>
-      <c r="M156" s="5" t="inlineStr"/>
-      <c r="N156" s="5" t="inlineStr"/>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>AE 4385291</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>407129 0256 0079</t>
+        </is>
+      </c>
+      <c r="L156" s="5" t="inlineStr">
+        <is>
+          <t>29.09.2025</t>
+        </is>
+      </c>
+      <c r="M156" s="5" t="inlineStr">
+        <is>
+          <t>07.12.1990</t>
+        </is>
+      </c>
+      <c r="N156" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O156" s="4" t="inlineStr"/>
-      <c r="P156" s="2" t="inlineStr"/>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>O'R-A 5263487</t>
+        </is>
+      </c>
       <c r="Q156" s="4" t="inlineStr"/>
-      <c r="R156" s="4" t="inlineStr"/>
+      <c r="R156" s="4" t="inlineStr">
+        <is>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
       <c r="S156" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T156" s="5" t="inlineStr"/>
+      <c r="T156" s="5" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
       <c r="U156" s="16" t="inlineStr">
         <is>
           <t>Chala</t>
@@ -40444,21 +40476,53 @@
           <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>AE 4385291</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>407129 0256 0079</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>29.09.2025</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>07.12.1990</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O32" s="4" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>O'R-A 5263487</t>
+        </is>
+      </c>
       <c r="Q32" s="4" t="inlineStr"/>
-      <c r="R32" s="4" t="inlineStr"/>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T32" s="5" t="inlineStr"/>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
       <c r="U32" s="16" t="inlineStr">
         <is>
           <t>Chala</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -21,11 +21,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$179</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -13501,24 +13501,60 @@
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Muroulla+qizi</t>
+        </is>
+      </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
+          <t>Salayeva Dilroz Muroulla+qizi</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr"/>
-      <c r="J116" s="5" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="5" t="inlineStr"/>
-      <c r="M116" s="5" t="inlineStr"/>
-      <c r="N116" s="5" t="inlineStr"/>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>AE3039330</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>60408085730030</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>16.06.2025</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>04.08.2008</t>
+        </is>
+      </c>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="O116" s="4" t="inlineStr"/>
-      <c r="P116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>UM+03758292</t>
+        </is>
+      </c>
       <c r="Q116" s="4" t="inlineStr"/>
-      <c r="R116" s="4" t="inlineStr"/>
+      <c r="R116" s="4" t="inlineStr">
+        <is>
+          <t>81-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+        </is>
+      </c>
       <c r="S116" s="5" t="inlineStr"/>
-      <c r="T116" s="5" t="inlineStr"/>
+      <c r="T116" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="U116" s="17" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -25911,7 +25947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -27927,13 +27963,13 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina</t>
+          <t>Salayeva Dilroz</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -27943,88 +27979,72 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Axmad qizi</t>
+          <t>Muroulla+qizi</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
-        </is>
-      </c>
+          <t>Salayeva Dilroz Muroulla+qizi</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr"/>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>AD7984192</t>
+          <t>AE3039330</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>61007085590081</t>
+          <t>60408085730030</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>23.07.2024</t>
+          <t>16.06.2025</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>10.07.2008</t>
+          <t>04.08.2008</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="inlineStr">
-        <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
-        </is>
-      </c>
+          <t>Yakkabog' tumani</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr"/>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM 03751932</t>
-        </is>
-      </c>
-      <c r="Q19" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832608/3447191/76c097af-86b5-43c8-a92d-2811565e56f3?preview=true</t>
-        </is>
-      </c>
+          <t>UM+03758292</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S19" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
+          <t>81-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr"/>
       <c r="T19" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U19" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W19" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X19" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -28039,78 +28059,78 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z</t>
+          <t>Sayfiyeva Zarina</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Qahramon qizi</t>
+          <t>Axmad qizi</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AE6071273</t>
+          <t>AD7984192</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>62708095680047</t>
+          <t>61007085590081</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>27.01.2026</t>
+          <t>23.07.2024</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>27.08.2009</t>
+          <t>10.07.2008</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>UM 03729168</t>
+          <t>UM 03751932</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3743118/3827061/8d968761-cded-44aa-a481-f5732e7b775c?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832608/3447191/76c097af-86b5-43c8-a92d-2811565e56f3?preview=true</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>38-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -28151,82 +28171,78 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Sayidova Dilafro'z</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr"/>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>263</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Qahramon qizi</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AE2370999</t>
+          <t>AE6071273</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>60307085730074</t>
+          <t>62708095680047</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>27.01.2026</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>03.07.2008</t>
+          <t>27.08.2009</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>UM 03758004</t>
+          <t>UM 03729168</t>
         </is>
       </c>
       <c r="Q21" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845467/3883533/77671008-6a79-4442-bbd3-dc2cfb091ca8?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3743118/3827061/8d968761-cded-44aa-a481-f5732e7b775c?preview=true</t>
         </is>
       </c>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>38-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
@@ -28267,7 +28283,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Shukurova Zilola</t>
+          <t>Shamsiyeva Fotima</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -28277,7 +28293,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -28287,63 +28303,67 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Farxod qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AE1059205</t>
+          <t>AE2370999</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60610085590150</t>
+          <t>60307085730074</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>06.10.2008</t>
+          <t>03.07.2008</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farhod qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>PT 0339050</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr"/>
+          <t>UM 03758004</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845467/3883533/77671008-6a79-4442-bbd3-dc2cfb091ca8?preview=true</t>
+        </is>
+      </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
@@ -28359,7 +28379,7 @@
       <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
@@ -28379,7 +28399,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Temirova Rushana</t>
+          <t>Shukurova Zilola</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -28389,43 +28409,47 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Sarvarovna</t>
+          <t>Farxod qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr"/>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AD9123776</t>
+          <t>AE1059205</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>60709085590113</t>
+          <t>60610085590150</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>07.09.2008</t>
+          <t>06.10.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
@@ -28435,23 +28459,23 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Shukurova Zilola Farhod qizi</t>
         </is>
       </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03755349</t>
+          <t>PT 0339050</t>
         </is>
       </c>
       <c r="Q23" s="11" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -28459,15 +28483,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U23" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X23" s="7" t="inlineStr">
@@ -28487,7 +28511,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila</t>
+          <t>Temirova Rushana</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -28497,47 +28521,43 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>299</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-10 00:00:00</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Sarvarovna</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
-        </is>
-      </c>
+          <t>Temirova Rushana Sarvarovna</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AE3444231</t>
+          <t>AD9123776</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61709085590015</t>
+          <t>60709085590113</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>18.07.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>17.09.2008</t>
+          <t>07.09.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -28547,22 +28567,18 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03754061</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03755349</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
@@ -28575,15 +28591,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U24" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U24" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W24" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -28603,86 +28619,108 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Umirova Sevinch</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr"/>
+          <t>Toshpo'latova Asila</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>46275</v>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Avlayor qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AD1671106</t>
-        </is>
-      </c>
-      <c r="K25" s="9" t="inlineStr"/>
+          <t>AE3444231</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>61709085590015</t>
+        </is>
+      </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>18.08.2022</t>
+          <t>18.07.2025</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>09.06.2005</t>
-        </is>
-      </c>
-      <c r="N25" s="12" t="inlineStr"/>
-      <c r="O25" s="11" t="inlineStr"/>
-      <c r="P25" s="9" t="inlineStr"/>
-      <c r="Q25" s="11" t="inlineStr"/>
+          <t>17.09.2008</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr">
+        <is>
+          <t>Toshpo'latova Asila Akmal qizi</t>
+        </is>
+      </c>
+      <c r="P25" s="9" t="inlineStr">
+        <is>
+          <t>UM 03754061</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
+        </is>
+      </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>Noma'lum</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>ID-karta</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>Noma'lum</t>
-        </is>
-      </c>
-      <c r="U25" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V25" s="11" t="inlineStr">
-        <is>
-          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V25" s="11" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X25" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28697,104 +28735,86 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz</t>
+          <t>Umirova Sevinch</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>46275</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Nu'mon qizi</t>
+          <t>Avlayor qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AD9589389</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>62112075680077</t>
-        </is>
-      </c>
+          <t>AD1671106</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>18.08.2022</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>21.12.2007</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>UM 03273678</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
-        </is>
-      </c>
+          <t>09.06.2005</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Noma'lum</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>ID-karta</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="inlineStr"/>
+          <t>Noma'lum</t>
+        </is>
+      </c>
+      <c r="U26" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
+        </is>
+      </c>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X26" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X26" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -28809,17 +28829,13 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Yulduz</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr"/>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>209</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -28829,62 +28845,62 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Zarif qizi</t>
+          <t>Nu'mon qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AE4240266</t>
+          <t>AD9589389</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>62112075680077</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>21.12.2007</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 03754068</t>
+          <t>UM 03273678</t>
         </is>
       </c>
       <c r="Q27" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
         </is>
       </c>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
@@ -28894,7 +28910,7 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -28925,7 +28941,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida</t>
+          <t>Xaydarova Iroda</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -28935,7 +28951,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -28945,37 +28961,37 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Safar qizi</t>
+          <t>Zarif qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AE4240266</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>61906085590032</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -28985,23 +29001,27 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>PT 0025701</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr"/>
+          <t>UM 03754068</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
+        </is>
+      </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
@@ -29015,9 +29035,9 @@
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
-      <c r="W28" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X28" s="7" t="inlineStr">
@@ -29037,13 +29057,17 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr"/>
+          <t>Xayrullayeva Umida</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -29053,67 +29077,63 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Sobir qizi</t>
+          <t>Safar qizi</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>19.11.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03718337</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0025701</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr"/>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr">
@@ -29126,14 +29146,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V29" s="11" t="inlineStr">
-        <is>
-          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
-        </is>
-      </c>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V29" s="11" t="inlineStr"/>
+      <c r="W29" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X29" s="7" t="inlineStr">
@@ -29153,17 +29169,13 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xolmamatova Shoxista</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -29173,62 +29185,62 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Isomiddin qizi</t>
+          <t>Sobir qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03758009</t>
+          <t>UM 03718337</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -29246,7 +29258,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+        </is>
+      </c>
       <c r="W30" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -29269,7 +29285,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Lobar</t>
+          <t>Xolmaxmatova Sevinch</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -29279,7 +29295,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -29289,62 +29305,62 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Ural qizi</t>
+          <t>Isomiddin qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>25.11.2008</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>UM 03728374</t>
+          <t>UM 03758009</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
         </is>
       </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
@@ -29385,89 +29401,205 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
+          <t>Xurramova Lobar</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Ural qizi</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>AE2656510</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>62508085680062</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>13.05.2025</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>25.08.2008</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>UM 03728374</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X32" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
           <t>Xurramova Sabina</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr"/>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Yuldosh qizi</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>AC3081523</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>60803048230011</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="L33" s="12" t="inlineStr">
         <is>
           <t>16.10.2020</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="M33" s="12" t="inlineStr">
         <is>
           <t>08.03.2004</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="N33" s="12" t="inlineStr"/>
+      <c r="O33" s="11" t="inlineStr">
         <is>
           <t>Mavjud</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P33" s="9" t="inlineStr">
         <is>
           <t>UM 1315230</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="inlineStr"/>
-      <c r="R32" s="4" t="inlineStr">
+      <c r="Q33" s="11" t="inlineStr"/>
+      <c r="R33" s="11" t="inlineStr">
         <is>
           <t>4-sonli umumiy o’rta ta’lim maktabi</t>
         </is>
       </c>
-      <c r="S32" s="5" t="inlineStr">
+      <c r="S33" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T32" s="5" t="inlineStr">
+      <c r="T33" s="12" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" s="4" t="inlineStr"/>
-      <c r="W32" s="15" t="inlineStr"/>
-      <c r="X32" s="16" t="inlineStr">
+      <c r="U33" s="12" t="inlineStr"/>
+      <c r="V33" s="11" t="inlineStr"/>
+      <c r="W33" s="15" t="inlineStr"/>
+      <c r="X33" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X32"/>
+  <autoFilter ref="A1:X33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40888,7 +41020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -41153,68 +41285,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>26-07</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr"/>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr"/>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>Salayeva Dilroz</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr"/>
-      <c r="J3" s="12" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr"/>
-      <c r="M3" s="12" t="inlineStr"/>
-      <c r="N3" s="12" t="inlineStr"/>
-      <c r="O3" s="11" t="inlineStr"/>
-      <c r="P3" s="9" t="inlineStr"/>
-      <c r="Q3" s="11" t="inlineStr"/>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="12" t="inlineStr"/>
-      <c r="T3" s="12" t="inlineStr"/>
-      <c r="U3" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V3" s="11" t="inlineStr"/>
-      <c r="W3" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X3" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X3"/>
+  <autoFilter ref="A1:X2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -16991,7 +16991,11 @@
           <t>AE4114421</t>
         </is>
       </c>
-      <c r="K147" s="9" t="inlineStr"/>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>60508095680049</t>
+        </is>
+      </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
           <t>09.09.2025</t>
@@ -17002,7 +17006,11 @@
           <t>05.08.2009</t>
         </is>
       </c>
-      <c r="N147" s="12" t="inlineStr"/>
+      <c r="N147" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
           <t>Tuychiyeva Farzona Dalerovna</t>
@@ -32158,7 +32166,11 @@
           <t>AE4114421</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>60508095680049</t>
+        </is>
+      </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
           <t>09.09.2025</t>
@@ -32169,7 +32181,11 @@
           <t>05.08.2009</t>
         </is>
       </c>
-      <c r="N23" s="12" t="inlineStr"/>
+      <c r="N23" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
           <t>Tuychiyeva Farzona Dalerovna</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -17317,7 +17317,11 @@
           <t>AD1671106</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>60906055720101</t>
+        </is>
+      </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
           <t>18.08.2022</t>
@@ -17328,7 +17332,11 @@
           <t>09.06.2005</t>
         </is>
       </c>
-      <c r="N150" s="5" t="inlineStr"/>
+      <c r="N150" s="5" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
       <c r="O150" s="4" t="inlineStr"/>
       <c r="P150" s="2" t="inlineStr"/>
       <c r="Q150" s="4" t="inlineStr"/>
@@ -28775,7 +28783,11 @@
           <t>AD1671106</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>60906055720101</t>
+        </is>
+      </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
           <t>18.08.2022</t>
@@ -28786,7 +28798,11 @@
           <t>09.06.2005</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="4" t="inlineStr"/>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -8370,11 +8370,23 @@
           <t>Mavjud</t>
         </is>
       </c>
-      <c r="P69" s="9" t="inlineStr"/>
+      <c r="P69" s="9" t="inlineStr">
+        <is>
+          <t>UM+03728547</t>
+        </is>
+      </c>
       <c r="Q69" s="11" t="inlineStr"/>
-      <c r="R69" s="11" t="inlineStr"/>
+      <c r="R69" s="11" t="inlineStr">
+        <is>
+          <t>20-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+        </is>
+      </c>
       <c r="S69" s="12" t="inlineStr"/>
-      <c r="T69" s="12" t="inlineStr"/>
+      <c r="T69" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="U69" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
@@ -26940,11 +26952,23 @@
           <t>Mavjud</t>
         </is>
       </c>
-      <c r="P9" s="9" t="inlineStr"/>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>UM+03728547</t>
+        </is>
+      </c>
       <c r="Q9" s="11" t="inlineStr"/>
-      <c r="R9" s="11" t="inlineStr"/>
+      <c r="R9" s="11" t="inlineStr">
+        <is>
+          <t>20-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+        </is>
+      </c>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="12" t="inlineStr"/>
+      <c r="T9" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="U9" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -17350,11 +17350,15 @@
         </is>
       </c>
       <c r="O150" s="4" t="inlineStr"/>
-      <c r="P150" s="2" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>UM+01891594</t>
+        </is>
+      </c>
       <c r="Q150" s="4" t="inlineStr"/>
       <c r="R150" s="4" t="inlineStr">
         <is>
-          <t>Noma'lum</t>
+          <t>42-sonli+umumiy+o'rta+ta'lim+maktabi</t>
         </is>
       </c>
       <c r="S150" s="5" t="inlineStr">
@@ -17364,7 +17368,7 @@
       </c>
       <c r="T150" s="5" t="inlineStr">
         <is>
-          <t>Noma'lum</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U150" s="16" t="inlineStr">
@@ -28828,11 +28832,15 @@
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>UM+01891594</t>
+        </is>
+      </c>
       <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Noma'lum</t>
+          <t>42-sonli+umumiy+o'rta+ta'lim+maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -28842,7 +28850,7 @@
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>Noma'lum</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U26" s="16" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -17386,9 +17386,9 @@
           <t>Pasport: MOS</t>
         </is>
       </c>
-      <c r="X150" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X150" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28868,9 +28868,9 @@
           <t>Pasport: MOS</t>
         </is>
       </c>
-      <c r="X26" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -12548,19 +12548,31 @@
         </is>
       </c>
       <c r="O107" s="11" t="inlineStr"/>
-      <c r="P107" s="9" t="inlineStr"/>
+      <c r="P107" s="9" t="inlineStr">
+        <is>
+          <t>DB+00173015</t>
+        </is>
+      </c>
       <c r="Q107" s="11" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R107" s="11" t="inlineStr"/>
+      <c r="R107" s="11" t="inlineStr">
+        <is>
+          <t>18-sonli+umumiy+o'rta+ta'lim+maktab</t>
+        </is>
+      </c>
       <c r="S107" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T107" s="12" t="inlineStr"/>
+      <c r="T107" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U107" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
@@ -31805,19 +31817,31 @@
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="9" t="inlineStr"/>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>DB+00173015</t>
+        </is>
+      </c>
       <c r="Q19" s="11" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3934766/3452539/98763bcf-ef33-4ddb-b3e1-ddf8c7990688?preview=true</t>
         </is>
       </c>
-      <c r="R19" s="11" t="inlineStr"/>
+      <c r="R19" s="11" t="inlineStr">
+        <is>
+          <t>18-sonli+umumiy+o'rta+ta'lim+maktab</t>
+        </is>
+      </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T19" s="12" t="inlineStr"/>
+      <c r="T19" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U19" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -18245,11 +18245,23 @@
         </is>
       </c>
       <c r="O158" s="4" t="inlineStr"/>
-      <c r="P158" s="2" t="inlineStr"/>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>UM+0862565</t>
+        </is>
+      </c>
       <c r="Q158" s="4" t="inlineStr"/>
-      <c r="R158" s="4" t="inlineStr"/>
+      <c r="R158" s="4" t="inlineStr">
+        <is>
+          <t>1-sonli+ayrim+fanlar+chuqur+o'rganiladigan+ixtisoslashtirilgan+maktab</t>
+        </is>
+      </c>
       <c r="S158" s="5" t="inlineStr"/>
-      <c r="T158" s="5" t="inlineStr"/>
+      <c r="T158" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U158" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
@@ -32584,11 +32596,23 @@
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>UM+0862565</t>
+        </is>
+      </c>
       <c r="Q26" s="4" t="inlineStr"/>
-      <c r="R26" s="4" t="inlineStr"/>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>1-sonli+ayrim+fanlar+chuqur+o'rganiladigan+ixtisoslashtirilgan+maktab</t>
+        </is>
+      </c>
       <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr"/>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U26" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -1884,17 +1884,25 @@
           <t>Mavjud</t>
         </is>
       </c>
-      <c r="P11" s="9" t="inlineStr"/>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>K+5486730</t>
+        </is>
+      </c>
       <c r="Q11" s="11" t="inlineStr"/>
-      <c r="R11" s="11" t="inlineStr"/>
+      <c r="R11" s="11" t="inlineStr">
+        <is>
+          <t>Qarshi+pedagogika+kolleji</t>
+        </is>
+      </c>
       <c r="S11" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T11" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
@@ -22637,17 +22645,25 @@
           <t>Mavjud</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>K+5486730</t>
+        </is>
+      </c>
       <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>Qarshi+pedagogika+kolleji</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U2" s="7" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10527,7 +10527,7 @@
       </c>
       <c r="K89" s="9" t="inlineStr">
         <is>
-          <t>602121 8568 0048</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="L89" s="12" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>02.12.2018</t>
+          <t>02.12.2008</t>
         </is>
       </c>
       <c r="N89" s="12" t="inlineStr">
@@ -35650,7 +35650,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>602121 8568 0048</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -35660,7 +35660,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>02.12.2018</t>
+          <t>02.12.2008</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -1886,13 +1886,13 @@
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>K+5486730</t>
+          <t>K 5486730</t>
         </is>
       </c>
       <c r="Q11" s="11" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>Qarshi+pedagogika+kolleji</t>
+          <t>Qarshi pedagogika kolleji</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="S47" s="12" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T47" s="12" t="inlineStr">
@@ -8380,13 +8380,13 @@
       </c>
       <c r="P69" s="9" t="inlineStr">
         <is>
-          <t>UM+03728547</t>
+          <t>UM 03728547</t>
         </is>
       </c>
       <c r="Q69" s="11" t="inlineStr"/>
       <c r="R69" s="11" t="inlineStr">
         <is>
-          <t>20-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S69" s="12" t="inlineStr"/>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>12.06.1989</t>
+          <t>05.12.2024</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
@@ -12558,7 +12558,7 @@
       <c r="O107" s="11" t="inlineStr"/>
       <c r="P107" s="9" t="inlineStr">
         <is>
-          <t>DB+00173015</t>
+          <t>DB 00173015</t>
         </is>
       </c>
       <c r="Q107" s="11" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="R107" s="11" t="inlineStr">
         <is>
-          <t>18-sonli+umumiy+o'rta+ta'lim+maktab</t>
+          <t>18-sonli umumiy o'rta ta'lim maktab</t>
         </is>
       </c>
       <c r="S107" s="12" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>Muroulla+qizi</t>
+          <t>Muroulla qizi</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz Muroulla+qizi</t>
+          <t>Salayeva Dilroz Muroulla qizi</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr"/>
@@ -13572,13 +13572,13 @@
       <c r="O116" s="4" t="inlineStr"/>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>UM+03758292</t>
+          <t>UM 03758292</t>
         </is>
       </c>
       <c r="Q116" s="4" t="inlineStr"/>
       <c r="R116" s="4" t="inlineStr">
         <is>
-          <t>81-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S116" s="5" t="inlineStr"/>
@@ -17372,13 +17372,13 @@
       <c r="O150" s="4" t="inlineStr"/>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>UM+01891594</t>
+          <t>UM 01891594</t>
         </is>
       </c>
       <c r="Q150" s="4" t="inlineStr"/>
       <c r="R150" s="4" t="inlineStr">
         <is>
-          <t>42-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S150" s="5" t="inlineStr">
@@ -18255,13 +18255,13 @@
       <c r="O158" s="4" t="inlineStr"/>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>UM+0862565</t>
+          <t>UM 0862565</t>
         </is>
       </c>
       <c r="Q158" s="4" t="inlineStr"/>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>1-sonli+ayrim+fanlar+chuqur+o'rganiladigan+ixtisoslashtirilgan+maktab</t>
+          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
         </is>
       </c>
       <c r="S158" s="5" t="inlineStr"/>
@@ -22647,13 +22647,13 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>K+5486730</t>
+          <t>K 5486730</t>
         </is>
       </c>
       <c r="Q2" s="4" t="inlineStr"/>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>Qarshi+pedagogika+kolleji</t>
+          <t>Qarshi pedagogika kolleji</t>
         </is>
       </c>
       <c r="S2" s="5" t="inlineStr">
@@ -26998,13 +26998,13 @@
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>UM+03728547</t>
+          <t>UM 03728547</t>
         </is>
       </c>
       <c r="Q9" s="11" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>20-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S9" s="12" t="inlineStr"/>
@@ -28063,12 +28063,12 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Muroulla+qizi</t>
+          <t>Muroulla qizi</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz Muroulla+qizi</t>
+          <t>Salayeva Dilroz Muroulla qizi</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr"/>
@@ -28100,13 +28100,13 @@
       <c r="O19" s="11" t="inlineStr"/>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM+03758292</t>
+          <t>UM 03758292</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>81-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr"/>
@@ -28874,13 +28874,13 @@
       <c r="O26" s="4" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM+01891594</t>
+          <t>UM 01891594</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>42-sonli+umumiy+o'rta+ta'lim+maktabi</t>
+          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -30972,7 +30972,7 @@
       </c>
       <c r="S11" s="12" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T11" s="12" t="inlineStr">
@@ -31847,7 +31847,7 @@
       <c r="O19" s="11" t="inlineStr"/>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>DB+00173015</t>
+          <t>DB 00173015</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr">
@@ -31857,7 +31857,7 @@
       </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>18-sonli+umumiy+o'rta+ta'lim+maktab</t>
+          <t>18-sonli umumiy o'rta ta'lim maktab</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
@@ -32614,13 +32614,13 @@
       <c r="O26" s="4" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM+0862565</t>
+          <t>UM 0862565</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>1-sonli+ayrim+fanlar+chuqur+o'rganiladigan+ixtisoslashtirilgan+maktab</t>
+          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr"/>
@@ -39410,7 +39410,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>12.06.1989</t>
+          <t>05.12.2024</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -7051,7 +7051,7 @@
       </c>
       <c r="S57" s="12" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T57" s="12" t="inlineStr">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="S13" s="12" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T13" s="12" t="inlineStr">

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -14,19 +14,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26-04 (Hamdamova.M)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26-05 (Rayimova.X)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26-06 (Yuldashev.O)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26-07 (Asraliyev.A)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$179</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'26-07 (Asraliyev.A)'!$A$1:$X$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9626,7 +9624,7 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -26019,7 +26017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -27041,74 +27039,78 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Mustafayeva Madina</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
+          <t>Murtazayeva Kamola</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:00</t>
+          <t>2026-06-29 00:00:00</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Ortiq qizi</t>
+          <t>Jamoliddin qizi</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Mustafayeva Madina Ortiq qizi</t>
+          <t>Murtazayeva Kamola Jamoliddin qizi</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Mustafayeva Madina Ortiq qizi</t>
+          <t>Murtazayeva Kamola Jamoliddin qizi</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>AE4846447</t>
+          <t>AC1458884</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63110085680103</t>
+          <t>42708915590028</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>31.10.2025</t>
+          <t>04.11.2018</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>31.10.2008</t>
+          <t>27.08.1991</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Mustafayeva Madina Ortiq qizi</t>
+          <t>Murtazayeva Kamola Jamoliddin qizi</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>UM 03729407</t>
+          <t>O'r-Sh 0987579</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr"/>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>49-maktab</t>
+          <t>Ixtisoslashgan maktab</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
@@ -27116,10 +27118,8 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="T10" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="U10" s="7" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>Mustafayeva Madina Ortiq qizi (#282) ma'lumotlari tasdiqlandi</t>
+          <t>Otasining ismi 'Jamoliddin qizi' deb to'g'rilandi (#25)</t>
         </is>
       </c>
       <c r="W10" s="8" t="inlineStr">
@@ -27153,66 +27153,74 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Niyozova Komila</t>
+          <t>Mustafayeva Madina</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr"/>
-      <c r="E11" s="12" t="inlineStr"/>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-07 00:00:00</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Toshpulatovna</t>
+          <t>Ortiq qizi</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Niyozova Komila Toshpulatovna</t>
+          <t>Mustafayeva Madina Ortiq qizi</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Niyozova Komila Toshpulatovna</t>
+          <t>Mustafayeva Madina Ortiq qizi</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>AB9205278</t>
+          <t>AE4846447</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>42405832640057</t>
+          <t>63110085680103</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>07.04.2018</t>
+          <t>31.10.2025</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>24.05.1983</t>
-        </is>
-      </c>
-      <c r="N11" s="12" t="inlineStr"/>
+          <t>31.10.2008</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>Niyozova Komila Toshpulatovna</t>
+          <t>Mustafayeva Madina Ortiq qizi</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>DB 00222382</t>
+          <t>UM 03729407</t>
         </is>
       </c>
       <c r="Q11" s="11" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>49-maktab</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
@@ -27222,7 +27230,7 @@
       </c>
       <c r="T11" s="12" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
@@ -27232,7 +27240,7 @@
       </c>
       <c r="V11" s="11" t="inlineStr">
         <is>
-          <t>Telegram (tg) orqali yuborilgan pasport va shahodatnoma dublikatidan to'liq kiritildi</t>
+          <t>Mustafayeva Madina Ortiq qizi (#282) ma'lumotlari tasdiqlandi</t>
         </is>
       </c>
       <c r="W11" s="8" t="inlineStr">
@@ -27240,9 +27248,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X11" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X11" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27257,82 +27265,66 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Norboboyeva Farangiz</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
+          <t>Niyozova Komila</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Nuriddin qizi</t>
+          <t>Toshpulatovna</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Norboboyeva Farangiz Nuriddin qizi</t>
+          <t>Niyozova Komila Toshpulatovna</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Norboboyeva Farangiz Nuriddin qizi</t>
+          <t>Niyozova Komila Toshpulatovna</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>AE5898909</t>
+          <t>AB9205278</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62808085590100</t>
+          <t>42405832640057</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>16.01.2026</t>
+          <t>07.04.2018</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>28.08.2008</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>24.05.1983</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr"/>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Norboboyeva Farangiz Nuriddin qizi</t>
+          <t>Niyozova Komila Toshpulatovna</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>UM 03753862</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3372975/3160794/4c79322b-c376-4475-b3c0-ade80431cd1f?preview=true</t>
-        </is>
-      </c>
+          <t>DB 00222382</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr"/>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
@@ -27342,7 +27334,7 @@
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="U12" s="7" t="inlineStr">
@@ -27350,15 +27342,19 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>Telegram (tg) orqali yuborilgan pasport va shahodatnoma dublikatidan to'liq kiritildi</t>
+        </is>
+      </c>
       <c r="W12" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X12" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -27373,7 +27369,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Pardaqulova Farzona</t>
+          <t>Norboboyeva Farangiz</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -27383,7 +27379,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>231</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -27393,37 +27389,37 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Shovkatovna</t>
+          <t>Nuriddin qizi</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Pardaqulova Farzona Shovkatovna</t>
+          <t>Norboboyeva Farangiz Nuriddin qizi</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>Pardaqulova Farzona Shovkatovna</t>
+          <t>Norboboyeva Farangiz Nuriddin qizi</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>AE1336538</t>
+          <t>AE5898909</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>60312085590052</t>
+          <t>62808085590100</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>16.01.2026</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>03.12.2008</t>
+          <t>28.08.2008</t>
         </is>
       </c>
       <c r="N13" s="12" t="inlineStr">
@@ -27433,22 +27429,22 @@
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>Pardaqulova Farzona Shovkatovna</t>
+          <t>Norboboyeva Farangiz Nuriddin qizi</t>
         </is>
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>UM 03755343</t>
+          <t>UM 03753862</t>
         </is>
       </c>
       <c r="Q13" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4019179/3526276/61dfdf8f-87f2-4595-8ec2-b9d8efc6be60?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3372975/3160794/4c79322b-c376-4475-b3c0-ade80431cd1f?preview=true</t>
         </is>
       </c>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>61-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S13" s="12" t="inlineStr">
@@ -27469,7 +27465,7 @@
       <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X13" s="7" t="inlineStr">
@@ -27489,7 +27485,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Pardayeva Farangiz</t>
+          <t>Pardaqulova Farzona</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -27499,7 +27495,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -27509,37 +27505,37 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Norali qizi</t>
+          <t>Shovkatovna</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Pardayeva Farangiz Norali qizi</t>
+          <t>Pardaqulova Farzona Shovkatovna</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Pardayeva Farangiz Norali qizi</t>
+          <t>Pardaqulova Farzona Shovkatovna</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>AE5643897</t>
+          <t>AE1336538</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60102085590053</t>
+          <t>60312085590052</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>29.12.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>01.02.2008</t>
+          <t>03.12.2008</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -27549,22 +27545,22 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Pardayeva Farangiz Norali qizi</t>
+          <t>Pardaqulova Farzona Shovkatovna</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>UM 03755453</t>
+          <t>UM 03755343</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4199408/3752037/081f6da6-bd38-4be6-8cb8-5e771f5a7a10?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4019179/3526276/61dfdf8f-87f2-4595-8ec2-b9d8efc6be60?preview=true</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>68-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
@@ -27585,7 +27581,7 @@
       <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X14" s="7" t="inlineStr">
@@ -27605,7 +27601,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Primova Husnora</t>
+          <t>Pardayeva Farangiz</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -27615,7 +27611,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -27625,37 +27621,37 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Shovkat qizi</t>
+          <t>Norali qizi</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Primova Husnora Shovkat qizi</t>
+          <t>Pardayeva Farangiz Norali qizi</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Primova Husnora Shovkat qizi</t>
+          <t>Pardayeva Farangiz Norali qizi</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>AC 0443770</t>
+          <t>AE5643897</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>61310015590029</t>
+          <t>60102085590053</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>10.12.2018</t>
+          <t>29.12.2025</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>13.10.2001</t>
+          <t>01.02.2008</t>
         </is>
       </c>
       <c r="N15" s="12" t="inlineStr">
@@ -27663,37 +27659,45 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr"/>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>Pardayeva Farangiz Norali qizi</t>
+        </is>
+      </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>D 0095067</t>
-        </is>
-      </c>
-      <c r="Q15" s="11" t="inlineStr"/>
+          <t>UM 03755453</t>
+        </is>
+      </c>
+      <c r="Q15" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4199408/3752037/081f6da6-bd38-4be6-8cb8-5e771f5a7a10?preview=true</t>
+        </is>
+      </c>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz texnalogiya kasb-hunar kolleji</t>
+          <t>68-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U15" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X15" s="7" t="inlineStr">
@@ -27713,7 +27717,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Rasulova Husnobod</t>
+          <t>Primova Husnora</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -27723,7 +27727,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>251</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -27733,83 +27737,75 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Bekmurod qizi</t>
+          <t>Shovkat qizi</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Rasulova Husnobod Bekmurod qizi</t>
+          <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Rasulova Husnobod Bekmurod qizi</t>
+          <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>AD1615363</t>
+          <t>AC 0443770</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62705055720049</t>
+          <t>61310015590029</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>03.08.2022</t>
+          <t>10.12.2018</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>27.05.2005</t>
+          <t>13.10.2001</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>Rasulova Husnobod Bekmurod qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>UM 01891815</t>
+          <t>D 0095067</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr"/>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>49-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz texnalogiya kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>KARANTIN: ❌ Bir xil Shahodatnoma (UM 01891815) 2 ta talabada: Suyunova Maftuna [26-02], Rasulova Husnobod [26-03]; ❌ Bir xil QR havola (https://e-shahodatnoma.uz/api/public/getcertpdf/921114/889651/0cca6b2c-74dd-4711-d168-08db6f99367e?preview=true) 2 ta talaba</t>
-        </is>
-      </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U16" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X16" s="7" t="inlineStr">
@@ -27829,7 +27825,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Rayimova Nozliya</t>
+          <t>Rasulova Husnobod</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -27839,60 +27835,68 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>392</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Laziz qizi</t>
+          <t>Bekmurod qizi</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Rayimova Nozliya Laziz qizi</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr"/>
+          <t>Rasulova Husnobod Bekmurod qizi</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Rasulova Husnobod Bekmurod qizi</t>
+        </is>
+      </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>AE4759683</t>
+          <t>AD1615363</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>62606085590056</t>
+          <t>62705055720049</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>03.08.2022</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>26.06.2008</t>
+          <t>27.05.2005</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="inlineStr"/>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>Rasulova Husnobod Bekmurod qizi</t>
+        </is>
+      </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>UM 03755475</t>
+          <t>UM 01891815</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>68-maktab</t>
+          <t>49-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
@@ -27902,18 +27906,22 @@
       </c>
       <c r="T17" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U17" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>KARANTIN: ❌ Bir xil Shahodatnoma (UM 01891815) 2 ta talabada: Suyunova Maftuna [26-02], Rasulova Husnobod [26-03]; ❌ Bir xil QR havola (https://e-shahodatnoma.uz/api/public/getcertpdf/921114/889651/0cca6b2c-74dd-4711-d168-08db6f99367e?preview=true) 2 ta talaba</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X17" s="7" t="inlineStr">
@@ -27933,78 +27941,70 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Rustamova Charos</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
+          <t>Rayimova Nozliya</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>291</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>O'ktam qizi</t>
+          <t>Laziz qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Rustamova Charos O'ktam qizi</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>Rustamova Charos O'ktam qizi</t>
-        </is>
-      </c>
+          <t>Rayimova Nozliya Laziz qizi</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AE4730990</t>
+          <t>AE4759683</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60810085680017</t>
+          <t>62606085590056</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>08.10.2008</t>
+          <t>26.06.2008</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>Rustamova Charos O'ktam qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>UM 03728038</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4065248/3579915/251a81e0-79f2-4882-bc82-231a0a1ab956?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03755475</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>4-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>68-maktab</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
@@ -28012,22 +28012,20 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T18" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>Telegram (tg) orqali yuborilgan haqiqiy ID-karta va Shahodatnoma rasmlari biriktirildi</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U18" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X18" s="7" t="inlineStr">
@@ -28047,88 +28045,106 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz</t>
+          <t>Rustamova Charos</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>309</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-15 00:00:00</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Muroulla qizi</t>
+          <t>O'ktam qizi</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz Muroulla qizi</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr"/>
+          <t>Rustamova Charos O'ktam qizi</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Rustamova Charos O'ktam qizi</t>
+        </is>
+      </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>AE3039330</t>
+          <t>AE4730990</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>60408085730030</t>
+          <t>60810085680017</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>16.06.2025</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>04.08.2008</t>
+          <t>08.10.2008</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>Rustamova Charos O'ktam qizi</t>
+        </is>
+      </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM 03758292</t>
-        </is>
-      </c>
-      <c r="Q19" s="11" t="inlineStr"/>
+          <t>UM 03728038</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4065248/3579915/251a81e0-79f2-4882-bc82-231a0a1ab956?preview=true</t>
+        </is>
+      </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U19" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
-      <c r="X19" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>4-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T19" s="12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>Telegram (tg) orqali yuborilgan haqiqiy ID-karta va Shahodatnoma rasmlari biriktirildi</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28143,13 +28159,13 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina</t>
+          <t>Salayeva Dilroz</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -28159,88 +28175,72 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Axmad qizi</t>
+          <t>Muroulla qizi</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
-        </is>
-      </c>
+          <t>Salayeva Dilroz Muroulla qizi</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AD7984192</t>
+          <t>AE3039330</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61007085590081</t>
+          <t>60408085730030</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>23.07.2024</t>
+          <t>16.06.2025</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>10.07.2008</t>
+          <t>04.08.2008</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
-        </is>
-      </c>
+          <t>Yakkabog' tumani</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>UM 03751932</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832608/3447191/76c097af-86b5-43c8-a92d-2811565e56f3?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03758292</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr"/>
       <c r="T20" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U20" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="W20" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
+      <c r="X20" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -28255,78 +28255,78 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z</t>
+          <t>Sayfiyeva Zarina</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr"/>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Qahramon qizi</t>
+          <t>Axmad qizi</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AE6071273</t>
+          <t>AD7984192</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>62708095680047</t>
+          <t>61007085590081</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>27.01.2026</t>
+          <t>23.07.2024</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>27.08.2009</t>
+          <t>10.07.2008</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>UM 03729168</t>
+          <t>UM 03751932</t>
         </is>
       </c>
       <c r="Q21" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3743118/3827061/8d968761-cded-44aa-a481-f5732e7b775c?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832608/3447191/76c097af-86b5-43c8-a92d-2811565e56f3?preview=true</t>
         </is>
       </c>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>38-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
@@ -28367,82 +28367,78 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Sayidova Dilafro'z</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>263</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Qahramon qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AE2370999</t>
+          <t>AE6071273</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60307085730074</t>
+          <t>62708095680047</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>27.01.2026</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>03.07.2008</t>
+          <t>27.08.2009</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 03758004</t>
+          <t>UM 03729168</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845467/3883533/77671008-6a79-4442-bbd3-dc2cfb091ca8?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3743118/3827061/8d968761-cded-44aa-a481-f5732e7b775c?preview=true</t>
         </is>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>38-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
@@ -28483,7 +28479,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Shukurova Zilola</t>
+          <t>Shamsiyeva Fotima</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -28493,7 +28489,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -28503,63 +28499,67 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Farxod qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AE1059205</t>
+          <t>AE2370999</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>60610085590150</t>
+          <t>60307085730074</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>06.10.2008</t>
+          <t>03.07.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farhod qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>PT 0339050</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr"/>
+          <t>UM 03758004</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845467/3883533/77671008-6a79-4442-bbd3-dc2cfb091ca8?preview=true</t>
+        </is>
+      </c>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -28575,7 +28575,7 @@
       <c r="V23" s="11" t="inlineStr"/>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X23" s="7" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Temirova Rushana</t>
+          <t>Shukurova Zilola</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -28605,43 +28605,47 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-09-10 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Sarvarovna</t>
+          <t>Farxod qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AD9123776</t>
+          <t>AE1059205</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>60709085590113</t>
+          <t>60610085590150</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>07.09.2008</t>
+          <t>06.10.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -28651,23 +28655,23 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Shukurova Zilola Farhod qizi</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03755349</t>
+          <t>PT 0339050</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
@@ -28675,15 +28679,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U24" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -28703,7 +28707,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila</t>
+          <t>Temirova Rushana</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -28713,47 +28717,43 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>299</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-10 00:00:00</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Sarvarovna</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
-        </is>
-      </c>
+          <t>Temirova Rushana Sarvarovna</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr"/>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AE3444231</t>
+          <t>AD9123776</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>61709085590015</t>
+          <t>60709085590113</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>18.07.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>17.09.2008</t>
+          <t>07.09.2008</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
@@ -28763,22 +28763,18 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03754061</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03755349</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
@@ -28791,15 +28787,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U25" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W25" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -28819,93 +28815,103 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Umirova Sevinch</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>Toshpo'latova Asila</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>46275</v>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Avlayor qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AD1671106</t>
+          <t>AE3444231</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>60906055720101</t>
+          <t>61709085590015</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>18.08.2022</t>
+          <t>18.07.2025</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>09.06.2005</t>
+          <t>17.09.2008</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>Toshpo'latova Asila Akmal qizi</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 01891594</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+          <t>UM 03754061</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>ID-karta</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U26" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -28925,99 +28931,93 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz</t>
+          <t>Umirova Sevinch</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr"/>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>46275</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Nu'mon qizi</t>
+          <t>Avlayor qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AD9589389</t>
+          <t>AD1671106</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>62112075680077</t>
+          <t>60906055720101</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>18.08.2022</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>21.12.2007</t>
+          <t>09.06.2005</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O27" s="11" t="inlineStr">
-        <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="inlineStr"/>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 03273678</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
-        </is>
-      </c>
+          <t>UM 01891594</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>ID-karta</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V27" s="11" t="inlineStr"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U27" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V27" s="11" t="inlineStr">
+        <is>
+          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
+        </is>
+      </c>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -29037,17 +29037,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Yulduz</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>209</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -29057,62 +29053,62 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Zarif qizi</t>
+          <t>Nu'mon qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE4240266</t>
+          <t>AD9589389</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>62112075680077</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>21.12.2007</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03754068</t>
+          <t>UM 03273678</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
         </is>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -29122,7 +29118,7 @@
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U28" s="7" t="inlineStr">
@@ -29153,7 +29149,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida</t>
+          <t>Xaydarova Iroda</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -29163,7 +29159,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -29173,37 +29169,37 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Safar qizi</t>
+          <t>Zarif qizi</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AE4240266</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>61906085590032</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
@@ -29213,23 +29209,27 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>PT 0025701</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="inlineStr"/>
+          <t>UM 03754068</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
+        </is>
+      </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr">
@@ -29243,9 +29243,9 @@
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr"/>
-      <c r="W29" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X29" s="7" t="inlineStr">
@@ -29265,13 +29265,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
+          <t>Xayrullayeva Umida</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -29281,67 +29285,63 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Sobir qizi</t>
+          <t>Safar qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>19.11.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03718337</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0025701</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr"/>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T30" s="5" t="inlineStr">
@@ -29354,14 +29354,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
-        </is>
-      </c>
-      <c r="W30" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X30" s="7" t="inlineStr">
@@ -29381,17 +29377,13 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xolmamatova Shoxista</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr"/>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -29401,62 +29393,62 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Isomiddin qizi</t>
+          <t>Sobir qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>UM 03758009</t>
+          <t>UM 03718337</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
         </is>
       </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
@@ -29474,7 +29466,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="11" t="inlineStr"/>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+        </is>
+      </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -29497,7 +29493,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Lobar</t>
+          <t>Xolmaxmatova Sevinch</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -29507,7 +29503,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -29517,62 +29513,62 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Ural qizi</t>
+          <t>Isomiddin qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>25.11.2008</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 03728374</t>
+          <t>UM 03758009</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
         </is>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
@@ -29613,89 +29609,205 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
+          <t>Xurramova Lobar</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Ural qizi</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>AE2656510</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>62508085680062</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>13.05.2025</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>25.08.2008</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>UM 03728374</t>
+        </is>
+      </c>
+      <c r="Q33" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
+        </is>
+      </c>
+      <c r="R33" s="11" t="inlineStr">
+        <is>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S33" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T33" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr"/>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X33" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
           <t>Xurramova Sabina</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Yuldosh qizi</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>AC3081523</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>60803048230011</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>16.10.2020</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>08.03.2004</t>
         </is>
       </c>
-      <c r="N33" s="12" t="inlineStr"/>
-      <c r="O33" s="11" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Mavjud</t>
         </is>
       </c>
-      <c r="P33" s="9" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>UM 1315230</t>
         </is>
       </c>
-      <c r="Q33" s="11" t="inlineStr"/>
-      <c r="R33" s="11" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr"/>
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>4-sonli umumiy o’rta ta’lim maktabi</t>
         </is>
       </c>
-      <c r="S33" s="12" t="inlineStr">
+      <c r="S34" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T33" s="12" t="inlineStr">
+      <c r="T34" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U33" s="12" t="inlineStr"/>
-      <c r="V33" s="11" t="inlineStr"/>
-      <c r="W33" s="15" t="inlineStr"/>
-      <c r="X33" s="16" t="inlineStr">
+      <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="15" t="inlineStr"/>
+      <c r="X34" s="16" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X33"/>
+  <autoFilter ref="A1:X34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41148,283 +41260,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="35" customWidth="1" min="17" max="17"/>
-    <col width="35" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>T/R</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Guruh</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>I.F.O</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>To'lov statusi</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Sanasi</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Otasining ismi (Sharifi)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>To'liq F.I.SH</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Passport bo'yicha F.I.SH</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Passport / ID-karta (Seriya va raqam)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>JSHSHIR (PINFL)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Berilgan sanasi</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Tug'ilgan sanasi</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Tug'ilgan tumani</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Shahodatnoma bo'yicha F.I.SH</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Shahodatnoma / Diplom Seriyasi</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Shahodatnoma QR Havolasi (e-shahodatnoma.uz)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Tugatgan o'qish joyi</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Ta'lim muassasasi turi</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Bitirgan yili</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Qidiruv holati (Status)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Izoh va Eslatmalar (Notes)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Ism mosligi (Pasport / Shahodatnoma)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Operator Tasdig'i</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>26-07</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Murtazayeva Kamola</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Jamoliddin qizi</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Murtazayeva Kamola Jamoliddin qizi</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Murtazayeva Kamola Jamoliddin qizi</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>AC1458884</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>42708915590028</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>04.11.2018</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>27.08.1991</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>Murtazayeva Kamola Jamoliddin qizi</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>O'r-Sh 0987579</t>
-        </is>
-      </c>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr">
-        <is>
-          <t>Ixtisoslashgan maktab</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>2009</v>
-      </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>Otasining ismi 'Jamoliddin qizi' deb to'g'rilandi (#25)</t>
-        </is>
-      </c>
-      <c r="W2" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X2" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:X2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10468,11 +10468,23 @@
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>UM+1174926</t>
+        </is>
+      </c>
       <c r="Q88" s="4" t="inlineStr"/>
-      <c r="R88" s="4" t="inlineStr"/>
+      <c r="R88" s="4" t="inlineStr">
+        <is>
+          <t>29-maktab</t>
+        </is>
+      </c>
       <c r="S88" s="5" t="inlineStr"/>
-      <c r="T88" s="5" t="inlineStr"/>
+      <c r="T88" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U88" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
@@ -35705,11 +35717,23 @@
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="9" t="inlineStr"/>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>UM+1174926</t>
+        </is>
+      </c>
       <c r="Q19" s="11" t="inlineStr"/>
-      <c r="R19" s="11" t="inlineStr"/>
+      <c r="R19" s="11" t="inlineStr">
+        <is>
+          <t>29-maktab</t>
+        </is>
+      </c>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="12" t="inlineStr"/>
+      <c r="T19" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U19" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -12745,26 +12745,58 @@
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G109" s="12" t="inlineStr"/>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>Azamat+qizi</t>
+        </is>
+      </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona</t>
+          <t>Qulmatova Shabbona Azamat+qizi</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr"/>
-      <c r="J109" s="12" t="inlineStr"/>
-      <c r="K109" s="9" t="inlineStr"/>
-      <c r="L109" s="12" t="inlineStr"/>
-      <c r="M109" s="12" t="inlineStr"/>
-      <c r="N109" s="12" t="inlineStr"/>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>AE+4905104</t>
+        </is>
+      </c>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>61008085680019</t>
+        </is>
+      </c>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>05.11.2025</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>10.08.2008</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O109" s="11" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>
       </c>
-      <c r="P109" s="9" t="inlineStr"/>
+      <c r="P109" s="9" t="inlineStr">
+        <is>
+          <t>UM+03730102</t>
+        </is>
+      </c>
       <c r="Q109" s="11" t="inlineStr"/>
-      <c r="R109" s="11" t="inlineStr"/>
+      <c r="R109" s="11" t="inlineStr">
+        <is>
+          <t>70-maktab</t>
+        </is>
+      </c>
       <c r="S109" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -24394,26 +24426,58 @@
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr"/>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Azamat+qizi</t>
+        </is>
+      </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona</t>
+          <t>Qulmatova Shabbona Azamat+qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="12" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>AE+4905104</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>61008085680019</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>05.11.2025</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>10.08.2008</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>
       </c>
-      <c r="P17" s="9" t="inlineStr"/>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t>UM+03730102</t>
+        </is>
+      </c>
       <c r="Q17" s="11" t="inlineStr"/>
-      <c r="R17" s="11" t="inlineStr"/>
+      <c r="R17" s="11" t="inlineStr">
+        <is>
+          <t>70-maktab</t>
+        </is>
+      </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -10470,7 +10470,7 @@
       <c r="O88" s="4" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>UM+1174926</t>
+          <t>UM 1174926</t>
         </is>
       </c>
       <c r="Q88" s="4" t="inlineStr"/>
@@ -12747,18 +12747,18 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>Azamat+qizi</t>
+          <t>Azamat qizi</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat+qizi</t>
+          <t>Qulmatova Shabbona Azamat qizi</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr"/>
       <c r="J109" s="12" t="inlineStr">
         <is>
-          <t>AE+4905104</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="P109" s="9" t="inlineStr">
         <is>
-          <t>UM+03730102</t>
+          <t>UM 03730102</t>
         </is>
       </c>
       <c r="Q109" s="11" t="inlineStr"/>
@@ -24428,18 +24428,18 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Azamat+qizi</t>
+          <t>Azamat qizi</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat+qizi</t>
+          <t>Qulmatova Shabbona Azamat qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>AE+4905104</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>UM+03730102</t>
+          <t>UM 03730102</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr"/>
@@ -35919,7 +35919,7 @@
       <c r="O19" s="11" t="inlineStr"/>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM+1174926</t>
+          <t>UM 1174926</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr"/>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X181"/>
+  <dimension ref="A1:X182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -15069,79 +15069,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E130" s="5" t="inlineStr"/>
+      <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr"/>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N130" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O130" s="4" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="inlineStr"/>
       <c r="R130" s="4" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S130" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T130" s="5" t="inlineStr">
@@ -15154,15 +15134,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V130" s="4" t="inlineStr"/>
-      <c r="W130" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X130" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V130" s="4" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W130" s="15" t="inlineStr"/>
+      <c r="X130" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -15172,12 +15152,12 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Shukurova Zilola</t>
+          <t>Shukriyeva Nariye</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
@@ -15187,7 +15167,7 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
@@ -15197,37 +15177,37 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Farxod qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>AE1059205</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>60610085590150</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>06.10.2008</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N131" s="12" t="inlineStr">
@@ -15237,23 +15217,27 @@
       </c>
       <c r="O131" s="11" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farhod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="P131" s="9" t="inlineStr">
         <is>
-          <t>PT 0339050</t>
-        </is>
-      </c>
-      <c r="Q131" s="11" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q131" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R131" s="11" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S131" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T131" s="12" t="inlineStr">
@@ -15284,12 +15268,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Soyipova Dinora</t>
+          <t>Shukurova Zilola</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -15299,43 +15283,47 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Sanjar qizi</t>
+          <t>Farxod qizi</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Soyipova Dinora Sanjar qizi</t>
-        </is>
-      </c>
-      <c r="I132" s="3" t="inlineStr"/>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>AD9484395</t>
+          <t>AE1059205</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>62208085590065</t>
+          <t>60610085590150</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>22.08.2008</t>
+          <t>06.10.2008</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr">
@@ -15343,41 +15331,41 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O132" s="4" t="inlineStr"/>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farhod qizi</t>
+        </is>
+      </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>UM03297405</t>
+          <t>PT 0339050</t>
         </is>
       </c>
       <c r="Q132" s="4" t="inlineStr"/>
       <c r="R132" s="4" t="inlineStr">
         <is>
-          <t>22-maktab</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S132" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T132" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U132" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V132" s="4" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 125) dan shartnoma №288 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W132" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U132" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V132" s="4" t="inlineStr"/>
+      <c r="W132" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X132" s="7" t="inlineStr">
@@ -15397,51 +15385,53 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Suyarova Dinora</t>
-        </is>
-      </c>
-      <c r="D133" s="11" t="inlineStr"/>
+          <t>Soyipova Dinora</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="F133" s="18" t="n">
-        <v>46280</v>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Sodiq qizi</t>
+          <t>Sanjar qizi</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
+          <t>Soyipova Dinora Sanjar qizi</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>AD9863476</t>
+          <t>AD9484395</t>
         </is>
       </c>
       <c r="K133" s="9" t="inlineStr">
         <is>
-          <t>60108085590037</t>
+          <t>62208085590065</t>
         </is>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>18.12.2024</t>
+          <t>20.11.2024</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>22.08.2008</t>
         </is>
       </c>
       <c r="N133" s="12" t="inlineStr">
@@ -15449,20 +15439,16 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O133" s="11" t="inlineStr">
-        <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
+      <c r="O133" s="11" t="inlineStr"/>
       <c r="P133" s="9" t="inlineStr">
         <is>
-          <t>UM 03755218</t>
+          <t>UM03297405</t>
         </is>
       </c>
       <c r="Q133" s="11" t="inlineStr"/>
       <c r="R133" s="11" t="inlineStr">
         <is>
-          <t>56-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>22-maktab</t>
         </is>
       </c>
       <c r="S133" s="12" t="inlineStr">
@@ -15470,22 +15456,24 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T133" s="12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U133" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="T133" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U133" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V133" s="11" t="inlineStr">
         <is>
-          <t>KARANTIN: ❌ Bir xil PINFL (60108085590037) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Pasport (AD9863476) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Shahodatnoma (UM 03755218) 2 ta talabada: Rus | Operator: begona xujjat ma'lumotlari kerak emas || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
-        </is>
-      </c>
-      <c r="W133" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>1-kurs kontrakt biriktirish (bank qatori 125) dan shartnoma №288 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W133" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X133" s="7" t="inlineStr">
@@ -15500,90 +15488,86 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
+          <t>Suyarova Dinora</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>46280</v>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Sodiq qizi</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD9863476</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>60108085590037</t>
         </is>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>18.12.2024</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>01.08.2008</t>
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>K 5491697</t>
+          <t>UM 03755218</t>
         </is>
       </c>
       <c r="Q134" s="4" t="inlineStr"/>
       <c r="R134" s="4" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>56-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S134" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T134" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T134" s="5" t="n">
+        <v>2026</v>
       </c>
       <c r="U134" s="7" t="inlineStr">
         <is>
@@ -15592,12 +15576,12 @@
       </c>
       <c r="V134" s="4" t="inlineStr">
         <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+          <t>KARANTIN: ❌ Bir xil PINFL (60108085590037) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Pasport (AD9863476) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Shahodatnoma (UM 03755218) 2 ta talabada: Rus | Operator: begona xujjat ma'lumotlari kerak emas || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
         </is>
       </c>
       <c r="W134" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X134" s="7" t="inlineStr">
@@ -15612,22 +15596,18 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda</t>
-        </is>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr"/>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
@@ -15637,72 +15617,68 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>AD6024952</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr">
         <is>
-          <t>60112075590084</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>05.02.2024</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>01.12.2007</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P135" s="9" t="inlineStr">
         <is>
-          <t>UM 03296212</t>
-        </is>
-      </c>
-      <c r="Q135" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973552/2554812/7f935a7a-8206-4976-970f-b2b0bfec833a?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q135" s="11" t="inlineStr"/>
       <c r="R135" s="11" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S135" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T135" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U135" s="7" t="inlineStr">
@@ -15710,10 +15686,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V135" s="11" t="inlineStr"/>
+      <c r="V135" s="11" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X135" s="7" t="inlineStr">
@@ -15728,12 +15708,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Temirova Rushana</t>
+          <t>Temirboyeva Iroda</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -15743,43 +15723,47 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>2026-09-10 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>Sarvarovna</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr"/>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+        </is>
+      </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>AD9123776</t>
+          <t>AD6024952</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>60709085590113</t>
+          <t>60112075590084</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>05.02.2024</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>07.09.2008</t>
+          <t>01.12.2007</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr">
@@ -15789,18 +15773,22 @@
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>UM 03755349</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr"/>
+          <t>UM 03296212</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973552/2554812/7f935a7a-8206-4976-970f-b2b0bfec833a?preview=true</t>
+        </is>
+      </c>
       <c r="R136" s="4" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S136" s="5" t="inlineStr">
@@ -15810,18 +15798,18 @@
       </c>
       <c r="T136" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U136" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U136" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V136" s="4" t="inlineStr"/>
-      <c r="W136" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W136" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X136" s="7" t="inlineStr">
@@ -15836,12 +15824,12 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
+          <t>Temirova Rushana</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
@@ -15851,47 +15839,43 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>299</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-10 00:00:00</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Sarvarovna</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
-        </is>
-      </c>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
-        </is>
-      </c>
+          <t>Temirova Rushana Sarvarovna</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr"/>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AD9123776</t>
         </is>
       </c>
       <c r="K137" s="9" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>60709085590113</t>
         </is>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>07.09.2008</t>
         </is>
       </c>
       <c r="N137" s="12" t="inlineStr">
@@ -15901,22 +15885,18 @@
       </c>
       <c r="O137" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P137" s="9" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q137" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03755349</t>
+        </is>
+      </c>
+      <c r="Q137" s="11" t="inlineStr"/>
       <c r="R137" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S137" s="12" t="inlineStr">
@@ -15929,15 +15909,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U137" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U137" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V137" s="11" t="inlineStr"/>
-      <c r="W137" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="W137" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X137" s="7" t="inlineStr">
@@ -15957,7 +15937,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'raboyeva Sabrina</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -15967,74 +15947,82 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N138" s="5" t="inlineStr"/>
+          <t>27.09.2008</t>
+        </is>
+      </c>
+      <c r="N138" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>K 3736287</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R138" s="4" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S138" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T138" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U138" s="7" t="inlineStr">
@@ -16043,9 +16031,9 @@
         </is>
       </c>
       <c r="V138" s="4" t="inlineStr"/>
-      <c r="W138" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W138" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X138" s="7" t="inlineStr">
@@ -16060,12 +16048,12 @@
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
@@ -16075,7 +16063,7 @@
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
@@ -16085,68 +16073,64 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Ilxom qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
-        </is>
-      </c>
-      <c r="N139" s="12" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N139" s="12" t="inlineStr"/>
       <c r="O139" s="11" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="P139" s="9" t="inlineStr">
         <is>
-          <t>UM 1319051</t>
+          <t>K 3736287</t>
         </is>
       </c>
       <c r="Q139" s="11" t="inlineStr"/>
       <c r="R139" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S139" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T139" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
@@ -16172,12 +16156,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila</t>
+          <t>Toshmurodova Sarvara</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -16187,7 +16171,7 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -16197,37 +16181,37 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Ilxom qizi</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>AE3444231</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>61709085590015</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>18.07.2025</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>17.09.2008</t>
+          <t>28.03.2005</t>
         </is>
       </c>
       <c r="N140" s="5" t="inlineStr">
@@ -16237,22 +16221,18 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>UM 03754061</t>
-        </is>
-      </c>
-      <c r="Q140" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1319051</t>
+        </is>
+      </c>
+      <c r="Q140" s="4" t="inlineStr"/>
       <c r="R140" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
       <c r="S140" s="5" t="inlineStr">
@@ -16262,7 +16242,7 @@
       </c>
       <c r="T140" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U140" s="7" t="inlineStr">
@@ -16273,7 +16253,7 @@
       <c r="V140" s="4" t="inlineStr"/>
       <c r="W140" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X140" s="7" t="inlineStr">
@@ -16288,12 +16268,12 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
+          <t>Toshpo'latova Asila</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
@@ -16303,7 +16283,7 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
@@ -16313,54 +16293,62 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE3444231</t>
         </is>
       </c>
       <c r="K141" s="9" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>61709085590015</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>18.07.2025</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>17.09.2008</t>
         </is>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O141" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O141" s="11" t="inlineStr">
+        <is>
+          <t>Toshpo'latova Asila Akmal qizi</t>
+        </is>
+      </c>
       <c r="P141" s="9" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
-        </is>
-      </c>
-      <c r="Q141" s="11" t="inlineStr"/>
+          <t>UM 03754061</t>
+        </is>
+      </c>
+      <c r="Q141" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
+        </is>
+      </c>
       <c r="R141" s="11" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S141" s="12" t="inlineStr">
@@ -16373,15 +16361,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U141" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="U141" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V141" s="11" t="inlineStr"/>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X141" s="7" t="inlineStr">
@@ -16396,83 +16384,79 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr"/>
+          <t>To'xtayeva Durdona</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>2026-09-18 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>Oybek qizi</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O142" s="4" t="inlineStr">
-        <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr"/>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>UM 03751635</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4361470/3974374/48b26608-a18d-46a4-ac19-cba528a20b3b?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728346</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr"/>
       <c r="R142" s="4" t="inlineStr">
         <is>
-          <t>2-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S142" s="5" t="inlineStr">
@@ -16485,15 +16469,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U142" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U142" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V142" s="4" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X142" s="7" t="inlineStr">
@@ -16508,62 +16492,58 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
-        </is>
-      </c>
-      <c r="D143" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Turayeva Dilsuz</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr"/>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Oybek qizi</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>12.05.2009</t>
         </is>
       </c>
       <c r="N143" s="12" t="inlineStr">
@@ -16573,22 +16553,22 @@
       </c>
       <c r="O143" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="P143" s="9" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03751635</t>
         </is>
       </c>
       <c r="Q143" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4361470/3974374/48b26608-a18d-46a4-ac19-cba528a20b3b?preview=true</t>
         </is>
       </c>
       <c r="R143" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>2-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S143" s="12" t="inlineStr">
@@ -16598,7 +16578,7 @@
       </c>
       <c r="T143" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U143" s="7" t="inlineStr">
@@ -16624,12 +16604,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -16639,7 +16619,7 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -16649,37 +16629,37 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>Turg'un qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
@@ -16689,39 +16669,43 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>PT 0339231</t>
-        </is>
-      </c>
-      <c r="Q144" s="4" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R144" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-sonli politexnikum</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S144" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T144" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U144" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U144" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V144" s="4" t="inlineStr"/>
       <c r="W144" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X144" s="7" t="inlineStr">
@@ -16736,18 +16720,22 @@
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D145" s="11" t="inlineStr"/>
+          <t>Turg'unova Jasmina</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
@@ -16757,67 +16745,63 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Turg'un qizi</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE6171425</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>62802085590087</t>
         </is>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N145" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="P145" s="9" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
-        </is>
-      </c>
-      <c r="Q145" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339231</t>
+        </is>
+      </c>
+      <c r="Q145" s="11" t="inlineStr"/>
       <c r="R145" s="11" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-sonli politexnikum</t>
         </is>
       </c>
       <c r="S145" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T145" s="12" t="inlineStr">
@@ -16825,15 +16809,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U145" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U145" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V145" s="11" t="inlineStr"/>
       <c r="W145" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X145" s="7" t="inlineStr">
@@ -16848,87 +16832,83 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Anvarovna</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>UM 02172465</t>
+          <t>UM 03730110</t>
         </is>
       </c>
       <c r="Q146" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
         </is>
       </c>
       <c r="R146" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S146" s="5" t="inlineStr">
@@ -16938,7 +16918,7 @@
       </c>
       <c r="T146" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U146" s="7" t="inlineStr">
@@ -16949,7 +16929,7 @@
       <c r="V146" s="4" t="inlineStr"/>
       <c r="W146" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X146" s="7" t="inlineStr">
@@ -16969,78 +16949,82 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr"/>
+          <t>Tursunova Aziza</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>276</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Qosim qizi</t>
+          <t>Anvarovna</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="P147" s="9" t="inlineStr">
         <is>
-          <t>UM 03730083</t>
+          <t>UM 02172465</t>
         </is>
       </c>
       <c r="Q147" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
         </is>
       </c>
       <c r="R147" s="11" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S147" s="12" t="inlineStr">
@@ -17050,7 +17034,7 @@
       </c>
       <c r="T147" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
@@ -17061,7 +17045,7 @@
       <c r="V147" s="11" t="inlineStr"/>
       <c r="W147" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X147" s="7" t="inlineStr">
@@ -17081,13 +17065,13 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra</t>
+          <t>Tursunova Fotima</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -17102,22 +17086,22 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr">
@@ -17137,17 +17121,17 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>UM 03730084</t>
+          <t>UM 03730083</t>
         </is>
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
         </is>
       </c>
       <c r="R148" s="4" t="inlineStr">
@@ -17188,56 +17172,58 @@
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona</t>
+          <t>Tursunova Zuhra</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr"/>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="F149" s="18" t="n">
-        <v>46272</v>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Dalerovna</t>
+          <t>Qosim qizi</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>AE4114421</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="K149" s="9" t="inlineStr">
         <is>
-          <t>60508095680049</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>05.08.2009</t>
+          <t>27.10.2008</t>
         </is>
       </c>
       <c r="N149" s="12" t="inlineStr">
@@ -17247,22 +17233,22 @@
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="P149" s="9" t="inlineStr">
         <is>
-          <t>UM-O 00064269</t>
+          <t>UM 03730084</t>
         </is>
       </c>
       <c r="Q149" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
         </is>
       </c>
       <c r="R149" s="11" t="inlineStr">
         <is>
-          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S149" s="12" t="inlineStr">
@@ -17280,11 +17266,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V149" s="11" t="inlineStr">
-        <is>
-          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
-        </is>
-      </c>
+      <c r="V149" s="11" t="inlineStr"/>
       <c r="W149" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -17307,70 +17289,76 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tuychiyeva Farzona</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="F150" s="5" t="inlineStr"/>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Ulug'bek qizi</t>
+          <t>Dalerovna</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr"/>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>AE4760779</t>
+          <t>AE4114421</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>61109085590127</t>
+          <t>60508095680049</t>
         </is>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="M150" s="5" t="inlineStr">
         <is>
-          <t>11.09.2008</t>
+          <t>05.08.2009</t>
         </is>
       </c>
       <c r="N150" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Tuychiyeva Farzona Dalerovna</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>UM 03728161</t>
-        </is>
-      </c>
-      <c r="Q150" s="4" t="inlineStr"/>
+          <t>UM-O 00064269</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
+        </is>
+      </c>
       <c r="R150" s="4" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S150" s="5" t="inlineStr">
@@ -17380,12 +17368,24 @@
       </c>
       <c r="T150" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U150" s="5" t="inlineStr"/>
-      <c r="V150" s="4" t="inlineStr"/>
-      <c r="W150" s="15" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U150" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V150" s="4" t="inlineStr">
+        <is>
+          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
+        </is>
+      </c>
+      <c r="W150" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X150" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
+          <t>Ulugbekova Zara</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
@@ -17413,47 +17413,39 @@
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F151" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="inlineStr"/>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
-        </is>
-      </c>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
-        </is>
-      </c>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr"/>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4760779</t>
         </is>
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>61109085590127</t>
         </is>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.09.2008</t>
         </is>
       </c>
       <c r="N151" s="12" t="inlineStr">
@@ -17463,22 +17455,18 @@
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P151" s="9" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
-        </is>
-      </c>
-      <c r="Q151" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728161</t>
+        </is>
+      </c>
+      <c r="Q151" s="11" t="inlineStr"/>
       <c r="R151" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S151" s="12" t="inlineStr">
@@ -17488,20 +17476,12 @@
       </c>
       <c r="T151" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U151" s="12" t="inlineStr"/>
       <c r="V151" s="11" t="inlineStr"/>
-      <c r="W151" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W151" s="15" t="inlineStr"/>
       <c r="X151" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -17514,98 +17494,108 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Umirova Sevinch</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr"/>
+          <t>Umarova Iroda</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="F152" s="6" t="n">
-        <v>46275</v>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>Avlayor qizi</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>AD1671106</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>60906055720101</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>18.08.2022</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>09.06.2005</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N152" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O152" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>Umarova Iroda Muzaffar qizi</t>
+        </is>
+      </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>UM 01891594</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr"/>
+          <t>UM 03754201</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+        </is>
+      </c>
       <c r="R152" s="4" t="inlineStr">
         <is>
-          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S152" s="5" t="inlineStr">
         <is>
-          <t>ID-karta</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T152" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U152" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V152" s="4" t="inlineStr">
-        <is>
-          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U152" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V152" s="4" t="inlineStr"/>
       <c r="W152" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X152" s="7" t="inlineStr">
@@ -17620,112 +17610,98 @@
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Umirova Sevinch</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr"/>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="F153" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="n">
+        <v>46275</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Avlayor qizi</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AD1671106</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60906055720101</t>
         </is>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>18.08.2022</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>09.06.2005</t>
         </is>
       </c>
       <c r="N153" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O153" s="11" t="inlineStr">
-        <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O153" s="11" t="inlineStr"/>
       <c r="P153" s="9" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
-        </is>
-      </c>
-      <c r="Q153" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 01891594</t>
+        </is>
+      </c>
+      <c r="Q153" s="11" t="inlineStr"/>
       <c r="R153" s="11" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S153" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>ID-karta</t>
         </is>
       </c>
       <c r="T153" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U153" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U153" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V153" s="11" t="inlineStr">
         <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
         </is>
       </c>
       <c r="W153" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X153" s="7" t="inlineStr">
@@ -17745,7 +17721,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -17755,85 +17731,97 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N154" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O154" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>Uroqova Jasmina Jasur qizi</t>
+        </is>
+      </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>K 4590366</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr"/>
+          <t>UM 03752857</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+        </is>
+      </c>
       <c r="R154" s="4" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S154" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T154" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U154" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U154" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V154" s="4" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W154" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X154" s="7" t="inlineStr">
@@ -17848,56 +17836,62 @@
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D155" s="11" t="inlineStr"/>
+          <t>Usmanova Iroda</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F155" s="18" t="n">
-        <v>46272</v>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-12 00:00:00</t>
+        </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Xamdam qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>AB5702170</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>42601925680010</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>19.01.2017</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>26.01.1992</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N155" s="12" t="inlineStr">
@@ -17905,20 +17899,16 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O155" s="11" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
+      <c r="O155" s="11" t="inlineStr"/>
       <c r="P155" s="9" t="inlineStr">
         <is>
-          <t>K 1994177</t>
+          <t>K 4590366</t>
         </is>
       </c>
       <c r="Q155" s="11" t="inlineStr"/>
       <c r="R155" s="11" t="inlineStr">
         <is>
-          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S155" s="12" t="inlineStr">
@@ -17928,22 +17918,18 @@
       </c>
       <c r="T155" s="12" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="U155" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V155" s="11" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U155" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V155" s="11" t="inlineStr"/>
       <c r="W155" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X155" s="7" t="inlineStr">
@@ -17958,97 +17944,87 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Xamdam qizi</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>26.01.1992</t>
         </is>
       </c>
       <c r="N156" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>UM 03754097</t>
-        </is>
-      </c>
-      <c r="Q156" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
-        </is>
-      </c>
+          <t>K 1994177</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="inlineStr"/>
       <c r="R156" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S156" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T156" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="U156" s="7" t="inlineStr">
@@ -18056,7 +18032,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V156" s="4" t="inlineStr"/>
+      <c r="V156" s="4" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
+        </is>
+      </c>
       <c r="W156" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -18074,18 +18054,22 @@
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr"/>
+          <t>Usmonova Sabrina</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
@@ -18095,62 +18079,62 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Nu'mon qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>AD9589389</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>62112075680077</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>21.12.2007</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P157" s="9" t="inlineStr">
         <is>
-          <t>UM 03273678</t>
+          <t>UM 03754097</t>
         </is>
       </c>
       <c r="Q157" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
         </is>
       </c>
       <c r="R157" s="11" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S157" s="12" t="inlineStr">
@@ -18160,7 +18144,7 @@
       </c>
       <c r="T157" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
@@ -18186,71 +18170,83 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr"/>
-      <c r="F158" s="5" t="inlineStr"/>
+          <t>Usmonova Yulduz</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr"/>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Nu'mon qizi</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AD9589389</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>62112075680077</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>21.12.2007</t>
         </is>
       </c>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O158" s="4" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
+        </is>
+      </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr"/>
+          <t>UM 03273678</t>
+        </is>
+      </c>
+      <c r="Q158" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
+        </is>
+      </c>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S158" s="5" t="inlineStr">
@@ -18260,16 +18256,20 @@
       </c>
       <c r="T158" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U158" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U158" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V158" s="4" t="inlineStr"/>
-      <c r="W158" s="15" t="inlineStr"/>
+      <c r="W158" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X158" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -18282,12 +18282,12 @@
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Xamdamova Madina</t>
+          <t>Uzoqova Fazilat</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
@@ -18295,96 +18295,77 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E159" s="12" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F159" s="18" t="n">
-        <v>46197</v>
-      </c>
+      <c r="E159" s="12" t="inlineStr"/>
+      <c r="F159" s="12" t="inlineStr"/>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Abdiqodir qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>AB8517012</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>62701015680026</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>07.01.2018</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>27.01.2001</t>
+          <t>07.12.1990</t>
         </is>
       </c>
       <c r="N159" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O159" s="11" t="inlineStr">
-        <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O159" s="11" t="inlineStr"/>
       <c r="P159" s="9" t="inlineStr">
         <is>
-          <t>K 5487959</t>
+          <t>O'R-A 5263487</t>
         </is>
       </c>
       <c r="Q159" s="11" t="inlineStr"/>
       <c r="R159" s="11" t="inlineStr">
         <is>
-          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S159" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T159" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U159" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V159" s="11" t="inlineStr">
-        <is>
-          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
-to'g'risi: 62701015680026</t>
-        </is>
-      </c>
-      <c r="W159" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U159" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V159" s="11" t="inlineStr"/>
+      <c r="W159" s="15" t="inlineStr"/>
       <c r="X159" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -18402,51 +18383,55 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr"/>
+          <t>Xamdamova Madina</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F160" s="6" t="n">
-        <v>46247</v>
+        <v>46197</v>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Abdiqodir qizi</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>AD0284895</t>
+          <t>AB8517012</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>60206045680052</t>
+          <t>62701015680026</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>01.04.2021</t>
+          <t>07.01.2018</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>02.06.2004</t>
+          <t>27.01.2001</t>
         </is>
       </c>
       <c r="N160" s="5" t="inlineStr">
@@ -18454,33 +18439,46 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O160" s="4" t="inlineStr"/>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
+        </is>
+      </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>UM 0862565</t>
+          <t>K 5487959</t>
         </is>
       </c>
       <c r="Q160" s="4" t="inlineStr"/>
       <c r="R160" s="4" t="inlineStr">
         <is>
-          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
-        </is>
-      </c>
-      <c r="S160" s="5" t="inlineStr"/>
+          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S160" s="5" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
       <c r="T160" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U160" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="inlineStr"/>
-      <c r="W160" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U160" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V160" s="4" t="inlineStr">
+        <is>
+          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
+to'g'risi: 62701015680026</t>
+        </is>
+      </c>
+      <c r="W160" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X160" s="7" t="inlineStr">
@@ -18495,108 +18493,90 @@
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda</t>
-        </is>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xannonova Shohsanam</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr"/>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="F161" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="F161" s="18" t="n">
+        <v>46247</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Zarif qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>AE4240266</t>
+          <t>AD0284895</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>60206045680052</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>01.04.2021</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>02.06.2004</t>
         </is>
       </c>
       <c r="N161" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O161" s="11" t="inlineStr">
-        <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O161" s="11" t="inlineStr"/>
       <c r="P161" s="9" t="inlineStr">
         <is>
-          <t>UM 03754068</t>
-        </is>
-      </c>
-      <c r="Q161" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0862565</t>
+        </is>
+      </c>
+      <c r="Q161" s="11" t="inlineStr"/>
       <c r="R161" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S161" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
+          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
+        </is>
+      </c>
+      <c r="S161" s="12" t="inlineStr"/>
       <c r="T161" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U161" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U161" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V161" s="11" t="inlineStr"/>
-      <c r="W161" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W161" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X161" s="7" t="inlineStr">
@@ -18616,7 +18596,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida</t>
+          <t>Xaydarova Iroda</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -18626,7 +18606,7 @@
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
@@ -18636,37 +18616,37 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Safar qizi</t>
+          <t>Zarif qizi</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AE4240266</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>61906085590032</t>
         </is>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N162" s="5" t="inlineStr">
@@ -18676,23 +18656,27 @@
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>PT 0025701</t>
-        </is>
-      </c>
-      <c r="Q162" s="4" t="inlineStr"/>
+          <t>UM 03754068</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
+        </is>
+      </c>
       <c r="R162" s="4" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S162" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T162" s="5" t="inlineStr">
@@ -18706,9 +18690,9 @@
         </is>
       </c>
       <c r="V162" s="4" t="inlineStr"/>
-      <c r="W162" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W162" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X162" s="7" t="inlineStr">
@@ -18723,12 +18707,12 @@
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor</t>
+          <t>Xayrullayeva Umida</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
@@ -18738,91 +18722,89 @@
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Azim qizi</t>
+          <t>Safar qizi</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>AD4186543</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>62104025680040</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="M163" s="12" t="inlineStr">
         <is>
-          <t>21.04.2002</t>
+          <t>19.11.2008</t>
         </is>
       </c>
       <c r="N163" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="P163" s="9" t="inlineStr">
         <is>
-          <t>UM 0086260</t>
+          <t>PT 0025701</t>
         </is>
       </c>
       <c r="Q163" s="11" t="inlineStr"/>
       <c r="R163" s="11" t="inlineStr">
         <is>
-          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S163" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T163" s="12" t="n">
-        <v>2019</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T163" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V163" s="11" t="inlineStr">
-        <is>
-          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W163" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V163" s="11" t="inlineStr"/>
+      <c r="W163" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X163" s="7" t="inlineStr">
@@ -18837,83 +18819,83 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr"/>
+          <t>Xo'jaqulova Navbahor</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>302</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-14 00:00:00</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Sobir qizi</t>
+          <t>Azim qizi</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AD4186543</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>62104025680040</t>
         </is>
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>21.04.2002</t>
         </is>
       </c>
       <c r="N164" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>UM 03718337</t>
-        </is>
-      </c>
-      <c r="Q164" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0086260</t>
+        </is>
+      </c>
+      <c r="Q164" s="4" t="inlineStr"/>
       <c r="R164" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S164" s="5" t="inlineStr">
@@ -18921,10 +18903,8 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T164" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="T164" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="U164" s="7" t="inlineStr">
         <is>
@@ -18933,7 +18913,7 @@
       </c>
       <c r="V164" s="4" t="inlineStr">
         <is>
-          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
         </is>
       </c>
       <c r="W164" s="8" t="inlineStr">
@@ -18958,17 +18938,13 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch</t>
-        </is>
-      </c>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xolmamatova Shoxista</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr"/>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
@@ -18978,62 +18954,62 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Isomiddin qizi</t>
+          <t>Sobir qizi</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="K165" s="9" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
       <c r="N165" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="P165" s="9" t="inlineStr">
         <is>
-          <t>UM 03758009</t>
+          <t>UM 03718337</t>
         </is>
       </c>
       <c r="Q165" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
         </is>
       </c>
       <c r="R165" s="11" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S165" s="12" t="inlineStr">
@@ -19051,7 +19027,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V165" s="11" t="inlineStr"/>
+      <c r="V165" s="11" t="inlineStr">
+        <is>
+          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+        </is>
+      </c>
       <c r="W165" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -19069,12 +19049,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Xolmaxmatova Sevinch</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -19084,7 +19064,7 @@
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
@@ -19094,37 +19074,37 @@
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Isomiddin qizi</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>25.11.2008</t>
         </is>
       </c>
       <c r="N166" s="5" t="inlineStr">
@@ -19134,28 +19114,32 @@
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q166" s="4" t="inlineStr"/>
+          <t>UM 03758009</t>
+        </is>
+      </c>
+      <c r="Q166" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+        </is>
+      </c>
       <c r="R166" s="4" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S166" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T166" s="5" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U166" s="7" t="inlineStr">
@@ -19163,14 +19147,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V166" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W166" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V166" s="4" t="inlineStr"/>
+      <c r="W166" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X166" s="7" t="inlineStr">
@@ -19185,12 +19165,12 @@
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
@@ -19200,81 +19180,79 @@
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>Dilmurod qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J167" s="12" t="inlineStr">
         <is>
-          <t>AE1516812</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="K167" s="9" t="inlineStr">
         <is>
-          <t>60110085590193</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="L167" s="12" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="N167" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O167" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P167" s="9" t="inlineStr">
         <is>
-          <t>UM 03755333</t>
-        </is>
-      </c>
-      <c r="Q167" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
-        </is>
-      </c>
+          <t>K 3418837</t>
+        </is>
+      </c>
+      <c r="Q167" s="11" t="inlineStr"/>
       <c r="R167" s="11" t="inlineStr">
         <is>
-          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S167" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T167" s="12" t="n">
-        <v>2026</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T167" s="12" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
         <is>
@@ -19283,12 +19261,12 @@
       </c>
       <c r="V167" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W167" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W167" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
         </is>
       </c>
       <c r="X167" s="7" t="inlineStr">
@@ -19303,12 +19281,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Xolmurodova Dilnura</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -19318,47 +19296,47 @@
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-15 00:00:00</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Dilmurod qizi</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE1516812</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>60110085590193</t>
         </is>
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N168" s="5" t="inlineStr">
@@ -19368,18 +19346,22 @@
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q168" s="4" t="inlineStr"/>
+          <t>UM 03755333</t>
+        </is>
+      </c>
+      <c r="Q168" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
+        </is>
+      </c>
       <c r="R168" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S168" s="5" t="inlineStr">
@@ -19387,20 +19369,22 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T168" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="T168" s="5" t="n">
+        <v>2026</v>
       </c>
       <c r="U168" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V168" s="4" t="inlineStr"/>
+      <c r="V168" s="4" t="inlineStr">
+        <is>
+          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
+        </is>
+      </c>
       <c r="W168" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X168" s="7" t="inlineStr">
@@ -19415,12 +19399,12 @@
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
@@ -19430,60 +19414,68 @@
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="F169" s="12" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F169" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Bahrom qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
-        </is>
-      </c>
-      <c r="I169" s="10" t="inlineStr"/>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
+      <c r="I169" s="10" t="inlineStr">
+        <is>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
       <c r="J169" s="12" t="inlineStr">
         <is>
-          <t>AE5954513</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>62204085720105</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L169" s="12" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M169" s="12" t="inlineStr">
         <is>
-          <t>22.04.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N169" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O169" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P169" s="9" t="inlineStr">
         <is>
-          <t>UM 03717652</t>
+          <t>UM 02172469</t>
         </is>
       </c>
       <c r="Q169" s="11" t="inlineStr"/>
       <c r="R169" s="11" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S169" s="12" t="inlineStr">
@@ -19496,9 +19488,17 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U169" s="12" t="inlineStr"/>
+      <c r="U169" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V169" s="11" t="inlineStr"/>
-      <c r="W169" s="15" t="inlineStr"/>
+      <c r="W169" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
       <c r="X169" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Lobar</t>
+          <t>Xujamuratova Durdona</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -19526,72 +19526,60 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr"/>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Ural qizi</t>
+          <t>Bahrom qizi</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr"/>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M170" s="5" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>22.04.2008</t>
         </is>
       </c>
       <c r="N170" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>UM 03728374</t>
-        </is>
-      </c>
-      <c r="Q170" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03717652</t>
+        </is>
+      </c>
+      <c r="Q170" s="4" t="inlineStr"/>
       <c r="R170" s="4" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S170" s="5" t="inlineStr">
@@ -19601,20 +19589,12 @@
       </c>
       <c r="T170" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U170" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U170" s="5" t="inlineStr"/>
       <c r="V170" s="4" t="inlineStr"/>
-      <c r="W170" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W170" s="15" t="inlineStr"/>
       <c r="X170" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19632,7 +19612,7 @@
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Sabina</t>
+          <t>Xurramova Lobar</t>
         </is>
       </c>
       <c r="D171" s="11" t="inlineStr">
@@ -19642,56 +19622,72 @@
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F171" s="12" t="inlineStr"/>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Yuldosh qizi</t>
+          <t>Ural qizi</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
-        </is>
-      </c>
-      <c r="I171" s="10" t="inlineStr"/>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="I171" s="10" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
       <c r="J171" s="12" t="inlineStr">
         <is>
-          <t>AC3081523</t>
+          <t>AE2656510</t>
         </is>
       </c>
       <c r="K171" s="9" t="inlineStr">
         <is>
-          <t>60803048230011</t>
+          <t>62508085680062</t>
         </is>
       </c>
       <c r="L171" s="12" t="inlineStr">
         <is>
-          <t>16.10.2020</t>
+          <t>13.05.2025</t>
         </is>
       </c>
       <c r="M171" s="12" t="inlineStr">
         <is>
-          <t>08.03.2004</t>
-        </is>
-      </c>
-      <c r="N171" s="12" t="inlineStr"/>
+          <t>25.08.2008</t>
+        </is>
+      </c>
+      <c r="N171" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xurramova Lobar Ural qizi</t>
         </is>
       </c>
       <c r="P171" s="9" t="inlineStr">
         <is>
-          <t>UM 1315230</t>
-        </is>
-      </c>
-      <c r="Q171" s="11" t="inlineStr"/>
+          <t>UM 03728374</t>
+        </is>
+      </c>
+      <c r="Q171" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
+        </is>
+      </c>
       <c r="R171" s="11" t="inlineStr">
         <is>
-          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S171" s="12" t="inlineStr">
@@ -19701,12 +19697,20 @@
       </c>
       <c r="T171" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U171" s="12" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U171" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V171" s="11" t="inlineStr"/>
-      <c r="W171" s="15" t="inlineStr"/>
+      <c r="W171" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X171" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19719,12 +19723,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza</t>
+          <t>Xurramova Sabina</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -19734,89 +19738,71 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F172" s="6" t="n">
-        <v>46204</v>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr"/>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>Shuhrat qizi</t>
+          <t>Yuldosh qizi</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
+          <t>Xurramova Sabina Yuldosh qizi</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr"/>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AC3081523</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>60803048230011</t>
         </is>
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>16.10.2020</t>
         </is>
       </c>
       <c r="M172" s="5" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
-        </is>
-      </c>
-      <c r="N172" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
+          <t>08.03.2004</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="inlineStr"/>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>UM 0084478</t>
+          <t>UM 1315230</t>
         </is>
       </c>
       <c r="Q172" s="4" t="inlineStr"/>
       <c r="R172" s="4" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S172" s="5" t="inlineStr">
         <is>
-          <t>Attestat</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T172" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U172" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U172" s="5" t="inlineStr"/>
       <c r="V172" s="4" t="inlineStr"/>
-      <c r="W172" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W172" s="15" t="inlineStr"/>
       <c r="X172" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19834,7 +19820,7 @@
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda</t>
+          <t>Xurramova Shahnoza</t>
         </is>
       </c>
       <c r="D173" s="11" t="inlineStr">
@@ -19844,13 +19830,11 @@
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="F173" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="n">
+        <v>46204</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -19859,32 +19843,32 @@
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="J173" s="12" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="L173" s="12" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="M173" s="12" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
       <c r="N173" s="12" t="inlineStr">
@@ -19894,32 +19878,28 @@
       </c>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="P173" s="9" t="inlineStr">
         <is>
-          <t>UM 02149677</t>
-        </is>
-      </c>
-      <c r="Q173" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0084478</t>
+        </is>
+      </c>
+      <c r="Q173" s="11" t="inlineStr"/>
       <c r="R173" s="11" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S173" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Attestat</t>
         </is>
       </c>
       <c r="T173" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U173" s="7" t="inlineStr">
@@ -19945,12 +19925,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Xurramova Shahrizoda</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -19960,7 +19940,7 @@
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -19970,58 +19950,62 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Shuhrat qizi</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>30.04.2007</t>
         </is>
       </c>
       <c r="N174" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q174" s="4" t="inlineStr"/>
+          <t>UM 02149677</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
+        </is>
+      </c>
       <c r="R174" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S174" s="5" t="inlineStr">
@@ -20031,7 +20015,7 @@
       </c>
       <c r="T174" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U174" s="7" t="inlineStr">
@@ -20039,11 +20023,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V174" s="4" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V174" s="4" t="inlineStr"/>
       <c r="W174" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -20061,12 +20041,12 @@
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>Xusanova Aziza</t>
+          <t>Xurramova Shodiya</t>
         </is>
       </c>
       <c r="D175" s="11" t="inlineStr">
@@ -20076,7 +20056,7 @@
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
@@ -20086,37 +20066,37 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Fazliddin qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L175" s="12" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M175" s="12" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>27.04.2002</t>
         </is>
       </c>
       <c r="N175" s="12" t="inlineStr">
@@ -20126,22 +20106,18 @@
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="P175" s="9" t="inlineStr">
         <is>
-          <t>UM 03753649</t>
-        </is>
-      </c>
-      <c r="Q175" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0438281</t>
+        </is>
+      </c>
+      <c r="Q175" s="11" t="inlineStr"/>
       <c r="R175" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S175" s="12" t="inlineStr">
@@ -20151,7 +20127,7 @@
       </c>
       <c r="T175" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
@@ -20161,12 +20137,12 @@
       </c>
       <c r="V175" s="11" t="inlineStr">
         <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
         </is>
       </c>
       <c r="W175" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X175" s="7" t="inlineStr">
@@ -20181,18 +20157,22 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
-        </is>
-      </c>
-      <c r="D176" s="4" t="inlineStr"/>
+          <t>Xusanova Aziza</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -20202,62 +20182,62 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Fazliddin qizi</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N176" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
+          <t>UM 03753649</t>
         </is>
       </c>
       <c r="Q176" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
         </is>
       </c>
       <c r="R176" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S176" s="5" t="inlineStr">
@@ -20275,10 +20255,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V176" s="4" t="inlineStr"/>
+      <c r="V176" s="4" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+        </is>
+      </c>
       <c r="W176" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X176" s="7" t="inlineStr">
@@ -20293,22 +20277,18 @@
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Yahyomurodova Gulsanam</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr"/>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
@@ -20318,37 +20298,37 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Xusan qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
         <is>
-          <t>AB9239333</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K177" s="9" t="inlineStr">
         <is>
-          <t>42207935680042</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L177" s="12" t="inlineStr">
         <is>
-          <t>09.04.2018</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M177" s="12" t="inlineStr">
         <is>
-          <t>22.07.1993</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N177" s="12" t="inlineStr">
@@ -20358,22 +20338,22 @@
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P177" s="9" t="inlineStr">
         <is>
-          <t>UM 03524597</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q177" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R177" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S177" s="12" t="inlineStr">
@@ -20383,7 +20363,7 @@
       </c>
       <c r="T177" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U177" s="7" t="inlineStr">
@@ -20394,7 +20374,7 @@
       <c r="V177" s="11" t="inlineStr"/>
       <c r="W177" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X177" s="7" t="inlineStr">
@@ -20409,12 +20389,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -20424,7 +20404,7 @@
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -20434,68 +20414,72 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N178" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
-        </is>
-      </c>
-      <c r="Q178" s="4" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q178" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R178" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son texnikumi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S178" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T178" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U178" s="7" t="inlineStr">
@@ -20503,14 +20487,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V178" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
-        </is>
-      </c>
-      <c r="W178" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+      <c r="V178" s="4" t="inlineStr"/>
+      <c r="W178" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X178" s="7" t="inlineStr">
@@ -20525,12 +20505,12 @@
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yuldosheva Ruhshona</t>
         </is>
       </c>
       <c r="D179" s="11" t="inlineStr">
@@ -20540,7 +20520,7 @@
       </c>
       <c r="E179" s="12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
@@ -20550,67 +20530,63 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Xabibullo qizi</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="K179" s="9" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="L179" s="12" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="M179" s="12" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>13.09.2008</t>
         </is>
       </c>
       <c r="N179" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O179" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="P179" s="9" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
-        </is>
-      </c>
-      <c r="Q179" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q179" s="11" t="inlineStr"/>
       <c r="R179" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
       <c r="S179" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T179" s="12" t="inlineStr">
@@ -20623,10 +20599,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V179" s="11" t="inlineStr"/>
-      <c r="W179" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V179" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
+        </is>
+      </c>
+      <c r="W179" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X179" s="7" t="inlineStr">
@@ -20641,12 +20621,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -20656,7 +20636,7 @@
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -20666,37 +20646,37 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Sodiqovna</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="M180" s="5" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="N180" s="5" t="inlineStr">
@@ -20706,22 +20686,22 @@
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>UM 03729571</t>
+          <t>UM 03729007</t>
         </is>
       </c>
       <c r="Q180" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
         </is>
       </c>
       <c r="R180" s="4" t="inlineStr">
         <is>
-          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S180" s="5" t="inlineStr">
@@ -20742,7 +20722,7 @@
       <c r="V180" s="4" t="inlineStr"/>
       <c r="W180" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X180" s="7" t="inlineStr">
@@ -20757,18 +20737,22 @@
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina</t>
-        </is>
-      </c>
-      <c r="D181" s="11" t="inlineStr"/>
+          <t>Zayidova Shaboda</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E181" s="12" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
@@ -20778,62 +20762,62 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>Alisher qizi</t>
+          <t>Sodiqovna</t>
         </is>
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="K181" s="9" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="L181" s="12" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="M181" s="12" t="inlineStr">
         <is>
-          <t>12.06.2007</t>
+          <t>31.12.2008</t>
         </is>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O181" s="11" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="P181" s="9" t="inlineStr">
         <is>
-          <t>UM 03296188</t>
+          <t>UM 03729571</t>
         </is>
       </c>
       <c r="Q181" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
         </is>
       </c>
       <c r="R181" s="11" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S181" s="12" t="inlineStr">
@@ -20843,7 +20827,7 @@
       </c>
       <c r="T181" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U181" s="7" t="inlineStr">
@@ -20854,17 +20838,129 @@
       <c r="V181" s="11" t="inlineStr"/>
       <c r="W181" s="8" t="inlineStr">
         <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X181" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>Alisher qizi</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>AD9812146</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>61206075590076</t>
+        </is>
+      </c>
+      <c r="L182" s="5" t="inlineStr">
+        <is>
+          <t>13.12.2024</t>
+        </is>
+      </c>
+      <c r="M182" s="5" t="inlineStr">
+        <is>
+          <t>12.06.2007</t>
+        </is>
+      </c>
+      <c r="N182" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O182" s="4" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>UM 03296188</t>
+        </is>
+      </c>
+      <c r="Q182" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+        </is>
+      </c>
+      <c r="R182" s="4" t="inlineStr">
+        <is>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S182" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T182" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U182" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V182" s="4" t="inlineStr"/>
+      <c r="W182" s="8" t="inlineStr">
+        <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X181" s="7" t="inlineStr">
+      <c r="X182" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X181"/>
+  <autoFilter ref="A1:X182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22630,7 +22726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25164,7 +25260,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -25172,79 +25268,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr"/>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr"/>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -25257,15 +25333,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W23" s="15" t="inlineStr"/>
+      <c r="X23" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25280,13 +25356,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
+          <t>Shukriyeva Nariye</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -25296,68 +25376,72 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>K 5491697</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U24" s="7" t="inlineStr">
@@ -25365,14 +25449,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
-        </is>
-      </c>
+      <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -25392,92 +25472,84 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -25485,10 +25557,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -25508,7 +25584,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'raboyeva Sabrina</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -25518,74 +25594,82 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr"/>
+          <t>27.09.2008</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>K 3736287</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -25594,9 +25678,9 @@
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W26" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -25616,7 +25700,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -25626,7 +25710,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -25636,69 +25720,69 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O27" s="11" t="inlineStr"/>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr"/>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>Tosheva Aziza Sherzod qizi</t>
+        </is>
+      </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
+          <t>K 3736287</t>
         </is>
       </c>
       <c r="Q27" s="11" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U27" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr"/>
@@ -25724,13 +25808,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
+          <t>To'xtayeva Durdona</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -25740,37 +25828,37 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -25778,24 +25866,16 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
-        </is>
-      </c>
+      <c r="O28" s="4" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728346</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -25808,15 +25888,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U28" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X28" s="7" t="inlineStr">
@@ -25836,17 +25916,13 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr"/>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -25856,62 +25932,62 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
+          <t>UM 03730110</t>
         </is>
       </c>
       <c r="Q29" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
         </is>
       </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -25952,7 +26028,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
+          <t>Umarova Iroda</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -25962,7 +26038,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -25972,37 +26048,37 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -26012,22 +26088,22 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
+          <t>UM 03754201</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -26045,11 +26121,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
-        </is>
-      </c>
+      <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -26072,7 +26144,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -26082,85 +26154,97 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O31" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>Uroqova Jasmina Jasur qizi</t>
+        </is>
+      </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>K 4590366</t>
-        </is>
-      </c>
-      <c r="Q31" s="11" t="inlineStr"/>
+          <t>UM 03752857</t>
+        </is>
+      </c>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+        </is>
+      </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T31" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U31" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V31" s="11" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X31" s="7" t="inlineStr">
@@ -26180,7 +26264,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Usmanova Iroda</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -26190,93 +26274,85 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>Xurramova Shodiya Arol qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
+          <t>K 4590366</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U32" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -26296,113 +26372,229 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
+          <t>Xurramova Shodiya</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Arol qizi</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>AC1967100</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>62704025590042</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>12.06.2019</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>27.04.2002</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>UM 0438281</t>
+        </is>
+      </c>
+      <c r="Q33" s="11" t="inlineStr"/>
+      <c r="R33" s="11" t="inlineStr">
+        <is>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S33" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T33" s="12" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X33" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
           <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Xusan qizi</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>AB9239333</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>42207935680042</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>09.04.2018</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>22.07.1993</t>
         </is>
       </c>
-      <c r="N33" s="12" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O33" s="11" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="P33" s="9" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>UM 03524597</t>
         </is>
       </c>
-      <c r="Q33" s="11" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
         </is>
       </c>
-      <c r="R33" s="11" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="S33" s="12" t="inlineStr">
+      <c r="S34" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T33" s="12" t="inlineStr">
+      <c r="T34" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="U33" s="7" t="inlineStr">
+      <c r="U34" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V33" s="11" t="inlineStr"/>
-      <c r="W33" s="8" t="inlineStr">
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t>Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X33" s="7" t="inlineStr">
+      <c r="X34" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X33"/>
+  <autoFilter ref="A1:X34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -5786,7 +5786,11 @@
         </is>
       </c>
       <c r="Q46" s="4" t="inlineStr"/>
-      <c r="R46" s="4" t="inlineStr"/>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>14-maktab</t>
+        </is>
+      </c>
       <c r="S46" s="5" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>
@@ -23837,7 +23841,11 @@
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>14-maktab</t>
+        </is>
+      </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$183</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X182"/>
+  <dimension ref="A1:X183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13928,109 +13928,97 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr"/>
+          <t>Samatova Oydin</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr"/>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Sulaymon qizi</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Samatova Oydin Sulaymon qizi</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr"/>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.10.1990</t>
         </is>
       </c>
       <c r="N120" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O120" s="4" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr"/>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>OR-SH 0346677</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="inlineStr"/>
       <c r="R120" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
         </is>
       </c>
       <c r="S120" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T120" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U120" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V120" s="4" t="inlineStr"/>
-      <c r="W120" s="8" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X120" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U120" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V120" s="4" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W120" s="15" t="inlineStr"/>
+      <c r="X120" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -14045,82 +14033,78 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Samiyeva Sevinchbonu</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr"/>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="K121" s="9" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O121" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P121" s="9" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q121" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R121" s="11" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S121" s="12" t="inlineStr">
@@ -14139,9 +14123,9 @@
         </is>
       </c>
       <c r="V121" s="11" t="inlineStr"/>
-      <c r="W121" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W121" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X121" s="7" t="inlineStr">
@@ -14161,53 +14145,57 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="inlineStr"/>
+          <t>Sanaqulova Muxtarama</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N122" s="5" t="inlineStr">
@@ -14217,33 +14205,37 @@
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R122" s="4" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S122" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T122" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U122" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U122" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V122" s="4" t="inlineStr"/>
@@ -14264,62 +14256,58 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona</t>
-        </is>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Sanaqulova Nozliya</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr"/>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="K123" s="9" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="N123" s="12" t="inlineStr">
@@ -14329,32 +14317,28 @@
       </c>
       <c r="O123" s="11" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P123" s="9" t="inlineStr">
         <is>
-          <t>UM 03754198</t>
-        </is>
-      </c>
-      <c r="Q123" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
-        </is>
-      </c>
+          <t>K 5509185</t>
+        </is>
+      </c>
+      <c r="Q123" s="11" t="inlineStr"/>
       <c r="R123" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S123" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T123" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
@@ -14362,14 +14346,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V123" s="11" t="inlineStr">
-        <is>
-          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
-        </is>
-      </c>
-      <c r="W123" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V123" s="11" t="inlineStr"/>
+      <c r="W123" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X123" s="7" t="inlineStr">
@@ -14384,12 +14364,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz</t>
+          <t>Saydalimova Ruxshona</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -14397,41 +14377,49 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E124" s="5" t="inlineStr"/>
-      <c r="F124" s="5" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00:00</t>
+        </is>
+      </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>Zafar qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>415079 8559 0074</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>18.07.2008</t>
         </is>
       </c>
       <c r="N124" s="5" t="inlineStr">
@@ -14441,37 +14429,49 @@
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>K 4587984</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr"/>
+          <t>UM 03754198</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
+        </is>
+      </c>
       <c r="R124" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S124" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T124" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U124" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="inlineStr"/>
-      <c r="W124" s="15" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U124" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V124" s="4" t="inlineStr">
+        <is>
+          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
+        </is>
+      </c>
+      <c r="W124" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X124" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -14489,7 +14489,7 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
+          <t>Sayfieva Sarvinoz</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
@@ -14497,101 +14497,81 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E125" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F125" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-19 00:00:00</t>
-        </is>
-      </c>
+      <c r="E125" s="12" t="inlineStr"/>
+      <c r="F125" s="12" t="inlineStr"/>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>Zafar qizi</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="K125" s="9" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>15.07.1998</t>
         </is>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O125" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P125" s="9" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q125" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 4587984</t>
+        </is>
+      </c>
+      <c r="Q125" s="11" t="inlineStr"/>
       <c r="R125" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S125" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T125" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V125" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W125" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
-        </is>
-      </c>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U125" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V125" s="11" t="inlineStr"/>
+      <c r="W125" s="15" t="inlineStr"/>
       <c r="X125" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -14604,83 +14584,87 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr"/>
+          <t>Sayfillayeva Shodiyona</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>Axmad qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>AD7984192</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>61007085590081</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>23.07.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>10.07.2008</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N126" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>UM 03751932</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q126" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832608/3447191/76c097af-86b5-43c8-a92d-2811565e56f3?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R126" s="4" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S126" s="5" t="inlineStr">
@@ -14698,10 +14682,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V126" s="4" t="inlineStr"/>
-      <c r="W126" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V126" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W126" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X126" s="7" t="inlineStr">
@@ -14721,78 +14709,78 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z</t>
+          <t>Sayfiyeva Zarina</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr"/>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>Qahramon qizi</t>
+          <t>Axmad qizi</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>AE6071273</t>
+          <t>AD7984192</t>
         </is>
       </c>
       <c r="K127" s="9" t="inlineStr">
         <is>
-          <t>62708095680047</t>
+          <t>61007085590081</t>
         </is>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>27.01.2026</t>
+          <t>23.07.2024</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>27.08.2009</t>
+          <t>10.07.2008</t>
         </is>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="P127" s="9" t="inlineStr">
         <is>
-          <t>UM 03729168</t>
+          <t>UM 03751932</t>
         </is>
       </c>
       <c r="Q127" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3743118/3827061/8d968761-cded-44aa-a481-f5732e7b775c?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832608/3447191/76c097af-86b5-43c8-a92d-2811565e56f3?preview=true</t>
         </is>
       </c>
       <c r="R127" s="11" t="inlineStr">
         <is>
-          <t>38-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S127" s="12" t="inlineStr">
@@ -14833,82 +14821,78 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Sayidova Dilafro'z</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>263</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Qahramon qizi</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>AE2370999</t>
+          <t>AE6071273</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>60307085730074</t>
+          <t>62708095680047</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>27.01.2026</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>03.07.2008</t>
+          <t>27.08.2009</t>
         </is>
       </c>
       <c r="N128" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>UM 03758004</t>
+          <t>UM 03729168</t>
         </is>
       </c>
       <c r="Q128" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845467/3883533/77671008-6a79-4442-bbd3-dc2cfb091ca8?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3743118/3827061/8d968761-cded-44aa-a481-f5732e7b775c?preview=true</t>
         </is>
       </c>
       <c r="R128" s="4" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>38-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S128" s="5" t="inlineStr">
@@ -14944,12 +14928,12 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Sharipova Diyora</t>
+          <t>Shamsiyeva Fotima</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
@@ -14959,7 +14943,7 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
@@ -14969,62 +14953,62 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AE2370999</t>
         </is>
       </c>
       <c r="K129" s="9" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>60307085730074</t>
         </is>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>03.07.2008</t>
         </is>
       </c>
       <c r="N129" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="P129" s="9" t="inlineStr">
         <is>
-          <t>UM 03751494</t>
+          <t>UM 03758004</t>
         </is>
       </c>
       <c r="Q129" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845467/3883533/77671008-6a79-4442-bbd3-dc2cfb091ca8?preview=true</t>
         </is>
       </c>
       <c r="R129" s="11" t="inlineStr">
         <is>
-          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S129" s="12" t="inlineStr">
@@ -15060,12 +15044,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira</t>
+          <t>Sharipova Diyora</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -15073,59 +15057,79 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="5" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr"/>
+          <t>Sharipova Diyora Jasur qizi</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>Sharipova Diyora Jasur qizi</t>
+        </is>
+      </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>23.07.2009</t>
         </is>
       </c>
       <c r="N130" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O130" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr">
+        <is>
+          <t>Sharipova Diyora Jasur qizi</t>
+        </is>
+      </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>UM 03730412</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr"/>
+          <t>UM 03751494</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+        </is>
+      </c>
       <c r="R130" s="4" t="inlineStr">
         <is>
-          <t>78-maktab</t>
+          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S130" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T130" s="5" t="inlineStr">
@@ -15138,15 +15142,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V130" s="4" t="inlineStr">
-        <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W130" s="15" t="inlineStr"/>
-      <c r="X130" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V130" s="4" t="inlineStr"/>
+      <c r="W130" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X130" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -15161,7 +15165,7 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
@@ -15169,79 +15173,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="F131" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E131" s="12" t="inlineStr"/>
+      <c r="F131" s="12" t="inlineStr"/>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="I131" s="10" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N131" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O131" s="11" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O131" s="11" t="inlineStr"/>
       <c r="P131" s="9" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q131" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q131" s="11" t="inlineStr"/>
       <c r="R131" s="11" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S131" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T131" s="12" t="inlineStr">
@@ -15254,15 +15238,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V131" s="11" t="inlineStr"/>
-      <c r="W131" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X131" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V131" s="11" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W131" s="15" t="inlineStr"/>
+      <c r="X131" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -15272,12 +15256,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Shukurova Zilola</t>
+          <t>Shukriyeva Nariye</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -15287,7 +15271,7 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -15297,37 +15281,37 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Farxod qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>AE1059205</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>60610085590150</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>06.10.2008</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr">
@@ -15337,23 +15321,27 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farhod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>PT 0339050</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R132" s="4" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S132" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T132" s="5" t="inlineStr">
@@ -15384,12 +15372,12 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Soyipova Dinora</t>
+          <t>Shukurova Zilola</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
@@ -15399,43 +15387,47 @@
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Sanjar qizi</t>
+          <t>Farxod qizi</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Soyipova Dinora Sanjar qizi</t>
-        </is>
-      </c>
-      <c r="I133" s="10" t="inlineStr"/>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>AD9484395</t>
+          <t>AE1059205</t>
         </is>
       </c>
       <c r="K133" s="9" t="inlineStr">
         <is>
-          <t>62208085590065</t>
+          <t>60610085590150</t>
         </is>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>22.08.2008</t>
+          <t>06.10.2008</t>
         </is>
       </c>
       <c r="N133" s="12" t="inlineStr">
@@ -15443,41 +15435,41 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O133" s="11" t="inlineStr"/>
+      <c r="O133" s="11" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farhod qizi</t>
+        </is>
+      </c>
       <c r="P133" s="9" t="inlineStr">
         <is>
-          <t>UM03297405</t>
+          <t>PT 0339050</t>
         </is>
       </c>
       <c r="Q133" s="11" t="inlineStr"/>
       <c r="R133" s="11" t="inlineStr">
         <is>
-          <t>22-maktab</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S133" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T133" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U133" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V133" s="11" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 125) dan shartnoma №288 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W133" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U133" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V133" s="11" t="inlineStr"/>
+      <c r="W133" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X133" s="7" t="inlineStr">
@@ -15497,51 +15489,53 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Suyarova Dinora</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="inlineStr"/>
+          <t>Soyipova Dinora</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="F134" s="6" t="n">
-        <v>46280</v>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Sodiq qizi</t>
+          <t>Sanjar qizi</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
+          <t>Soyipova Dinora Sanjar qizi</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr"/>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>AD9863476</t>
+          <t>AD9484395</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>60108085590037</t>
+          <t>62208085590065</t>
         </is>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>18.12.2024</t>
+          <t>20.11.2024</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>22.08.2008</t>
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr">
@@ -15549,20 +15543,16 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O134" s="4" t="inlineStr">
-        <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
+      <c r="O134" s="4" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>UM 03755218</t>
+          <t>UM03297405</t>
         </is>
       </c>
       <c r="Q134" s="4" t="inlineStr"/>
       <c r="R134" s="4" t="inlineStr">
         <is>
-          <t>56-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>22-maktab</t>
         </is>
       </c>
       <c r="S134" s="5" t="inlineStr">
@@ -15570,22 +15560,24 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T134" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U134" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="T134" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U134" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V134" s="4" t="inlineStr">
         <is>
-          <t>KARANTIN: ❌ Bir xil PINFL (60108085590037) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Pasport (AD9863476) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Shahodatnoma (UM 03755218) 2 ta talabada: Rus | Operator: begona xujjat ma'lumotlari kerak emas || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
-        </is>
-      </c>
-      <c r="W134" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>1-kurs kontrakt biriktirish (bank qatori 125) dan shartnoma №288 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W134" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X134" s="7" t="inlineStr">
@@ -15600,90 +15592,86 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
+          <t>Suyarova Dinora</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr"/>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="F135" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="n">
+        <v>46280</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Sodiq qizi</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD9863476</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>60108085590037</t>
         </is>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>18.12.2024</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>01.08.2008</t>
         </is>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="P135" s="9" t="inlineStr">
         <is>
-          <t>K 5491697</t>
+          <t>UM 03755218</t>
         </is>
       </c>
       <c r="Q135" s="11" t="inlineStr"/>
       <c r="R135" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>56-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S135" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T135" s="12" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T135" s="12" t="n">
+        <v>2026</v>
       </c>
       <c r="U135" s="7" t="inlineStr">
         <is>
@@ -15692,12 +15680,12 @@
       </c>
       <c r="V135" s="11" t="inlineStr">
         <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+          <t>KARANTIN: ❌ Bir xil PINFL (60108085590037) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Pasport (AD9863476) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Shahodatnoma (UM 03755218) 2 ta talabada: Rus | Operator: begona xujjat ma'lumotlari kerak emas || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
         </is>
       </c>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X135" s="7" t="inlineStr">
@@ -15712,22 +15700,18 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -15737,72 +15721,68 @@
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>AD6024952</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>60112075590084</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>05.02.2024</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>01.12.2007</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>UM 03296212</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973552/2554812/7f935a7a-8206-4976-970f-b2b0bfec833a?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="inlineStr"/>
       <c r="R136" s="4" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S136" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T136" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U136" s="7" t="inlineStr">
@@ -15810,10 +15790,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V136" s="4" t="inlineStr"/>
+      <c r="V136" s="4" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X136" s="7" t="inlineStr">
@@ -15828,12 +15812,12 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Temirova Rushana</t>
+          <t>Temirboyeva Iroda</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
@@ -15843,43 +15827,47 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Sarvarovna</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna</t>
-        </is>
-      </c>
-      <c r="I137" s="10" t="inlineStr"/>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr">
+        <is>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+        </is>
+      </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>AD9123776</t>
+          <t>AD6024952</t>
         </is>
       </c>
       <c r="K137" s="9" t="inlineStr">
         <is>
-          <t>60709085590113</t>
+          <t>60112075590084</t>
         </is>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>05.02.2024</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>07.09.2008</t>
+          <t>01.12.2007</t>
         </is>
       </c>
       <c r="N137" s="12" t="inlineStr">
@@ -15889,18 +15877,22 @@
       </c>
       <c r="O137" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P137" s="9" t="inlineStr">
         <is>
-          <t>UM 03755349</t>
-        </is>
-      </c>
-      <c r="Q137" s="11" t="inlineStr"/>
+          <t>UM 03296212</t>
+        </is>
+      </c>
+      <c r="Q137" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973552/2554812/7f935a7a-8206-4976-970f-b2b0bfec833a?preview=true</t>
+        </is>
+      </c>
       <c r="R137" s="11" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S137" s="12" t="inlineStr">
@@ -15910,18 +15902,18 @@
       </c>
       <c r="T137" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U137" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U137" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V137" s="11" t="inlineStr"/>
-      <c r="W137" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W137" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X137" s="7" t="inlineStr">
@@ -15936,12 +15928,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
+          <t>Temirova Rushana</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -15951,47 +15943,43 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>299</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-10 00:00:00</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Sarvarovna</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
-        </is>
-      </c>
+          <t>Temirova Rushana Sarvarovna</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr"/>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AD9123776</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>60709085590113</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>07.09.2008</t>
         </is>
       </c>
       <c r="N138" s="5" t="inlineStr">
@@ -16001,22 +15989,18 @@
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03755349</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr"/>
       <c r="R138" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S138" s="5" t="inlineStr">
@@ -16029,15 +16013,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U138" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U138" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V138" s="4" t="inlineStr"/>
-      <c r="W138" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="W138" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X138" s="7" t="inlineStr">
@@ -16057,7 +16041,7 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'raboyeva Sabrina</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
@@ -16067,74 +16051,82 @@
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N139" s="12" t="inlineStr"/>
+          <t>27.09.2008</t>
+        </is>
+      </c>
+      <c r="N139" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O139" s="11" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P139" s="9" t="inlineStr">
         <is>
-          <t>K 3736287</t>
-        </is>
-      </c>
-      <c r="Q139" s="11" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q139" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R139" s="11" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S139" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T139" s="12" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
@@ -16143,9 +16135,9 @@
         </is>
       </c>
       <c r="V139" s="11" t="inlineStr"/>
-      <c r="W139" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W139" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X139" s="7" t="inlineStr">
@@ -16160,12 +16152,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -16175,7 +16167,7 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -16185,68 +16177,64 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>Ilxom qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
-        </is>
-      </c>
-      <c r="N140" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N140" s="5" t="inlineStr"/>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>UM 1319051</t>
+          <t>K 3736287</t>
         </is>
       </c>
       <c r="Q140" s="4" t="inlineStr"/>
       <c r="R140" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S140" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T140" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U140" s="7" t="inlineStr">
@@ -16272,12 +16260,12 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila</t>
+          <t>Toshmurodova Sarvara</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
@@ -16287,7 +16275,7 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
@@ -16297,37 +16285,37 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Ilxom qizi</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>AE3444231</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="K141" s="9" t="inlineStr">
         <is>
-          <t>61709085590015</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>18.07.2025</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>17.09.2008</t>
+          <t>28.03.2005</t>
         </is>
       </c>
       <c r="N141" s="12" t="inlineStr">
@@ -16337,22 +16325,18 @@
       </c>
       <c r="O141" s="11" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="P141" s="9" t="inlineStr">
         <is>
-          <t>UM 03754061</t>
-        </is>
-      </c>
-      <c r="Q141" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1319051</t>
+        </is>
+      </c>
+      <c r="Q141" s="11" t="inlineStr"/>
       <c r="R141" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
       <c r="S141" s="12" t="inlineStr">
@@ -16362,7 +16346,7 @@
       </c>
       <c r="T141" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
@@ -16373,7 +16357,7 @@
       <c r="V141" s="11" t="inlineStr"/>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X141" s="7" t="inlineStr">
@@ -16388,12 +16372,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
+          <t>Toshpo'latova Asila</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -16403,7 +16387,7 @@
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -16413,54 +16397,62 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE3444231</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>61709085590015</t>
         </is>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>18.07.2025</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>17.09.2008</t>
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O142" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>Toshpo'latova Asila Akmal qizi</t>
+        </is>
+      </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr"/>
+          <t>UM 03754061</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
+        </is>
+      </c>
       <c r="R142" s="4" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S142" s="5" t="inlineStr">
@@ -16473,15 +16465,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U142" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="U142" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V142" s="4" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X142" s="7" t="inlineStr">
@@ -16496,83 +16488,79 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz</t>
-        </is>
-      </c>
-      <c r="D143" s="11" t="inlineStr"/>
+          <t>To'xtayeva Durdona</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>2026-09-18 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Oybek qizi</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N143" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O143" s="11" t="inlineStr">
-        <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O143" s="11" t="inlineStr"/>
       <c r="P143" s="9" t="inlineStr">
         <is>
-          <t>UM 03751635</t>
-        </is>
-      </c>
-      <c r="Q143" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4361470/3974374/48b26608-a18d-46a4-ac19-cba528a20b3b?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728346</t>
+        </is>
+      </c>
+      <c r="Q143" s="11" t="inlineStr"/>
       <c r="R143" s="11" t="inlineStr">
         <is>
-          <t>2-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S143" s="12" t="inlineStr">
@@ -16585,15 +16573,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U143" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U143" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V143" s="11" t="inlineStr"/>
       <c r="W143" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X143" s="7" t="inlineStr">
@@ -16608,62 +16596,58 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Turayeva Dilsuz</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr"/>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Oybek qizi</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>12.05.2009</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
@@ -16673,22 +16657,22 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03751635</t>
         </is>
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4361470/3974374/48b26608-a18d-46a4-ac19-cba528a20b3b?preview=true</t>
         </is>
       </c>
       <c r="R144" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>2-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S144" s="5" t="inlineStr">
@@ -16698,7 +16682,7 @@
       </c>
       <c r="T144" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U144" s="7" t="inlineStr">
@@ -16724,12 +16708,12 @@
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
@@ -16739,7 +16723,7 @@
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
@@ -16749,37 +16733,37 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Turg'un qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N145" s="12" t="inlineStr">
@@ -16789,39 +16773,43 @@
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P145" s="9" t="inlineStr">
         <is>
-          <t>PT 0339231</t>
-        </is>
-      </c>
-      <c r="Q145" s="11" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q145" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R145" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-sonli politexnikum</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S145" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T145" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U145" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U145" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V145" s="11" t="inlineStr"/>
       <c r="W145" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X145" s="7" t="inlineStr">
@@ -16836,18 +16824,22 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr"/>
+          <t>Turg'unova Jasmina</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -16857,67 +16849,63 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Turg'un qizi</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE6171425</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>62802085590087</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
-        </is>
-      </c>
-      <c r="Q146" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339231</t>
+        </is>
+      </c>
+      <c r="Q146" s="4" t="inlineStr"/>
       <c r="R146" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-sonli politexnikum</t>
         </is>
       </c>
       <c r="S146" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T146" s="5" t="inlineStr">
@@ -16925,15 +16913,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U146" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U146" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V146" s="4" t="inlineStr"/>
       <c r="W146" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X146" s="7" t="inlineStr">
@@ -16948,87 +16936,83 @@
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Aziza</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr"/>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Anvarovna</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="P147" s="9" t="inlineStr">
         <is>
-          <t>UM 02172465</t>
+          <t>UM 03730110</t>
         </is>
       </c>
       <c r="Q147" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
         </is>
       </c>
       <c r="R147" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S147" s="12" t="inlineStr">
@@ -17038,7 +17022,7 @@
       </c>
       <c r="T147" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
@@ -17049,7 +17033,7 @@
       <c r="V147" s="11" t="inlineStr"/>
       <c r="W147" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X147" s="7" t="inlineStr">
@@ -17069,78 +17053,82 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Fotima</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr"/>
+          <t>Tursunova Aziza</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>276</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>Qosim qizi</t>
+          <t>Anvarovna</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
       <c r="N148" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>UM 03730083</t>
+          <t>UM 02172465</t>
         </is>
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
         </is>
       </c>
       <c r="R148" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S148" s="5" t="inlineStr">
@@ -17150,7 +17138,7 @@
       </c>
       <c r="T148" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U148" s="7" t="inlineStr">
@@ -17161,7 +17149,7 @@
       <c r="V148" s="4" t="inlineStr"/>
       <c r="W148" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X148" s="7" t="inlineStr">
@@ -17181,13 +17169,13 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra</t>
+          <t>Tursunova Fotima</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr"/>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
@@ -17202,22 +17190,22 @@
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="K149" s="9" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="L149" s="12" t="inlineStr">
@@ -17237,17 +17225,17 @@
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="P149" s="9" t="inlineStr">
         <is>
-          <t>UM 03730084</t>
+          <t>UM 03730083</t>
         </is>
       </c>
       <c r="Q149" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
         </is>
       </c>
       <c r="R149" s="11" t="inlineStr">
@@ -17288,56 +17276,58 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona</t>
+          <t>Tursunova Zuhra</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="F150" s="6" t="n">
-        <v>46272</v>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Dalerovna</t>
+          <t>Qosim qizi</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>AE4114421</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>60508095680049</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M150" s="5" t="inlineStr">
         <is>
-          <t>05.08.2009</t>
+          <t>27.10.2008</t>
         </is>
       </c>
       <c r="N150" s="5" t="inlineStr">
@@ -17347,22 +17337,22 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>UM-O 00064269</t>
+          <t>UM 03730084</t>
         </is>
       </c>
       <c r="Q150" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
         </is>
       </c>
       <c r="R150" s="4" t="inlineStr">
         <is>
-          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S150" s="5" t="inlineStr">
@@ -17380,11 +17370,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V150" s="4" t="inlineStr">
-        <is>
-          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
-        </is>
-      </c>
+      <c r="V150" s="4" t="inlineStr"/>
       <c r="W150" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -17407,70 +17393,76 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara</t>
-        </is>
-      </c>
-      <c r="D151" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tuychiyeva Farzona</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr"/>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="F151" s="12" t="inlineStr"/>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="n">
+        <v>46272</v>
+      </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Ulug'bek qizi</t>
+          <t>Dalerovna</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
-        </is>
-      </c>
-      <c r="I151" s="10" t="inlineStr"/>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>AE4760779</t>
+          <t>AE4114421</t>
         </is>
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>61109085590127</t>
+          <t>60508095680049</t>
         </is>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>11.09.2008</t>
+          <t>05.08.2009</t>
         </is>
       </c>
       <c r="N151" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Tuychiyeva Farzona Dalerovna</t>
         </is>
       </c>
       <c r="P151" s="9" t="inlineStr">
         <is>
-          <t>UM 03728161</t>
-        </is>
-      </c>
-      <c r="Q151" s="11" t="inlineStr"/>
+          <t>UM-O 00064269</t>
+        </is>
+      </c>
+      <c r="Q151" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
+        </is>
+      </c>
       <c r="R151" s="11" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S151" s="12" t="inlineStr">
@@ -17480,12 +17472,24 @@
       </c>
       <c r="T151" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U151" s="12" t="inlineStr"/>
-      <c r="V151" s="11" t="inlineStr"/>
-      <c r="W151" s="15" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U151" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V151" s="11" t="inlineStr">
+        <is>
+          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
+        </is>
+      </c>
+      <c r="W151" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X151" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -17498,12 +17502,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
+          <t>Ulugbekova Zara</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -17513,47 +17517,39 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr"/>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
-        </is>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
-        </is>
-      </c>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr"/>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4760779</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>61109085590127</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.09.2008</t>
         </is>
       </c>
       <c r="N152" s="5" t="inlineStr">
@@ -17563,22 +17559,18 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728161</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="inlineStr"/>
       <c r="R152" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S152" s="5" t="inlineStr">
@@ -17588,20 +17580,12 @@
       </c>
       <c r="T152" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U152" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U152" s="5" t="inlineStr"/>
       <c r="V152" s="4" t="inlineStr"/>
-      <c r="W152" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W152" s="15" t="inlineStr"/>
       <c r="X152" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -17614,98 +17598,108 @@
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Umirova Sevinch</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr"/>
+          <t>Umarova Iroda</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="F153" s="18" t="n">
-        <v>46275</v>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Avlayor qizi</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>AD1671106</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
         <is>
-          <t>60906055720101</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>18.08.2022</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>09.06.2005</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N153" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O153" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O153" s="11" t="inlineStr">
+        <is>
+          <t>Umarova Iroda Muzaffar qizi</t>
+        </is>
+      </c>
       <c r="P153" s="9" t="inlineStr">
         <is>
-          <t>UM 01891594</t>
-        </is>
-      </c>
-      <c r="Q153" s="11" t="inlineStr"/>
+          <t>UM 03754201</t>
+        </is>
+      </c>
+      <c r="Q153" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+        </is>
+      </c>
       <c r="R153" s="11" t="inlineStr">
         <is>
-          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S153" s="12" t="inlineStr">
         <is>
-          <t>ID-karta</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T153" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U153" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V153" s="11" t="inlineStr">
-        <is>
-          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U153" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V153" s="11" t="inlineStr"/>
       <c r="W153" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X153" s="7" t="inlineStr">
@@ -17720,112 +17714,98 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Umirova Sevinch</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="n">
+        <v>46275</v>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Avlayor qizi</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AD1671106</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60906055720101</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>18.08.2022</t>
         </is>
       </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>09.06.2005</t>
         </is>
       </c>
       <c r="N154" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O154" s="4" t="inlineStr">
-        <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr"/>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 01891594</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="inlineStr"/>
       <c r="R154" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S154" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>ID-karta</t>
         </is>
       </c>
       <c r="T154" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U154" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U154" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V154" s="4" t="inlineStr">
         <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
         </is>
       </c>
       <c r="W154" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X154" s="7" t="inlineStr">
@@ -17845,7 +17825,7 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
@@ -17855,85 +17835,97 @@
       </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O155" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O155" s="11" t="inlineStr">
+        <is>
+          <t>Uroqova Jasmina Jasur qizi</t>
+        </is>
+      </c>
       <c r="P155" s="9" t="inlineStr">
         <is>
-          <t>K 4590366</t>
-        </is>
-      </c>
-      <c r="Q155" s="11" t="inlineStr"/>
+          <t>UM 03752857</t>
+        </is>
+      </c>
+      <c r="Q155" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+        </is>
+      </c>
       <c r="R155" s="11" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S155" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T155" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U155" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V155" s="11" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U155" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V155" s="11" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W155" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X155" s="7" t="inlineStr">
@@ -17948,56 +17940,62 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr"/>
+          <t>Usmanova Iroda</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F156" s="6" t="n">
-        <v>46272</v>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-12 00:00:00</t>
+        </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Xamdam qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>AB5702170</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>42601925680010</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>19.01.2017</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>26.01.1992</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N156" s="5" t="inlineStr">
@@ -18005,20 +18003,16 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O156" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
+      <c r="O156" s="4" t="inlineStr"/>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>K 1994177</t>
+          <t>K 4590366</t>
         </is>
       </c>
       <c r="Q156" s="4" t="inlineStr"/>
       <c r="R156" s="4" t="inlineStr">
         <is>
-          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S156" s="5" t="inlineStr">
@@ -18028,22 +18022,18 @@
       </c>
       <c r="T156" s="5" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="U156" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V156" s="4" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U156" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V156" s="4" t="inlineStr"/>
       <c r="W156" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X156" s="7" t="inlineStr">
@@ -18058,97 +18048,87 @@
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr"/>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="F157" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="n">
+        <v>46272</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Xamdam qizi</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>26.01.1992</t>
         </is>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="P157" s="9" t="inlineStr">
         <is>
-          <t>UM 03754097</t>
-        </is>
-      </c>
-      <c r="Q157" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
-        </is>
-      </c>
+          <t>K 1994177</t>
+        </is>
+      </c>
+      <c r="Q157" s="11" t="inlineStr"/>
       <c r="R157" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S157" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T157" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
@@ -18156,7 +18136,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V157" s="11" t="inlineStr"/>
+      <c r="V157" s="11" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
+        </is>
+      </c>
       <c r="W157" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -18174,18 +18158,22 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr"/>
+          <t>Usmonova Sabrina</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
@@ -18195,62 +18183,62 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>Nu'mon qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>AD9589389</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>62112075680077</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>21.12.2007</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>UM 03273678</t>
+          <t>UM 03754097</t>
         </is>
       </c>
       <c r="Q158" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
         </is>
       </c>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S158" s="5" t="inlineStr">
@@ -18260,7 +18248,7 @@
       </c>
       <c r="T158" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U158" s="7" t="inlineStr">
@@ -18286,71 +18274,83 @@
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D159" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E159" s="12" t="inlineStr"/>
-      <c r="F159" s="12" t="inlineStr"/>
+          <t>Usmonova Yulduz</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr"/>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Nu'mon qizi</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AD9589389</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>62112075680077</t>
         </is>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>21.12.2007</t>
         </is>
       </c>
       <c r="N159" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O159" s="11" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O159" s="11" t="inlineStr">
+        <is>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
+        </is>
+      </c>
       <c r="P159" s="9" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
-        </is>
-      </c>
-      <c r="Q159" s="11" t="inlineStr"/>
+          <t>UM 03273678</t>
+        </is>
+      </c>
+      <c r="Q159" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
+        </is>
+      </c>
       <c r="R159" s="11" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S159" s="12" t="inlineStr">
@@ -18360,16 +18360,20 @@
       </c>
       <c r="T159" s="12" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U159" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U159" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V159" s="11" t="inlineStr"/>
-      <c r="W159" s="15" t="inlineStr"/>
+      <c r="W159" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X159" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -18382,12 +18386,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Xamdamova Madina</t>
+          <t>Uzoqova Fazilat</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -18395,96 +18399,77 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F160" s="6" t="n">
-        <v>46197</v>
-      </c>
+      <c r="E160" s="5" t="inlineStr"/>
+      <c r="F160" s="5" t="inlineStr"/>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>Abdiqodir qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>AB8517012</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>62701015680026</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>07.01.2018</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>27.01.2001</t>
+          <t>07.12.1990</t>
         </is>
       </c>
       <c r="N160" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O160" s="4" t="inlineStr">
-        <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O160" s="4" t="inlineStr"/>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>K 5487959</t>
+          <t>O'R-A 5263487</t>
         </is>
       </c>
       <c r="Q160" s="4" t="inlineStr"/>
       <c r="R160" s="4" t="inlineStr">
         <is>
-          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S160" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T160" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U160" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="inlineStr">
-        <is>
-          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
-to'g'risi: 62701015680026</t>
-        </is>
-      </c>
-      <c r="W160" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U160" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V160" s="4" t="inlineStr"/>
+      <c r="W160" s="15" t="inlineStr"/>
       <c r="X160" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -18502,51 +18487,55 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam</t>
-        </is>
-      </c>
-      <c r="D161" s="11" t="inlineStr"/>
+          <t>Xamdamova Madina</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F161" s="18" t="n">
-        <v>46247</v>
+        <v>46197</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Abdiqodir qizi</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>AD0284895</t>
+          <t>AB8517012</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
         <is>
-          <t>60206045680052</t>
+          <t>62701015680026</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>01.04.2021</t>
+          <t>07.01.2018</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>02.06.2004</t>
+          <t>27.01.2001</t>
         </is>
       </c>
       <c r="N161" s="12" t="inlineStr">
@@ -18554,33 +18543,46 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O161" s="11" t="inlineStr"/>
+      <c r="O161" s="11" t="inlineStr">
+        <is>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
+        </is>
+      </c>
       <c r="P161" s="9" t="inlineStr">
         <is>
-          <t>UM 0862565</t>
+          <t>K 5487959</t>
         </is>
       </c>
       <c r="Q161" s="11" t="inlineStr"/>
       <c r="R161" s="11" t="inlineStr">
         <is>
-          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
-        </is>
-      </c>
-      <c r="S161" s="12" t="inlineStr"/>
+          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S161" s="12" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
       <c r="T161" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U161" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V161" s="11" t="inlineStr"/>
-      <c r="W161" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U161" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V161" s="11" t="inlineStr">
+        <is>
+          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
+to'g'risi: 62701015680026</t>
+        </is>
+      </c>
+      <c r="W161" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X161" s="7" t="inlineStr">
@@ -18595,108 +18597,90 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xannonova Shohsanam</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr"/>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="n">
+        <v>46247</v>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Zarif qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>AE4240266</t>
+          <t>AD0284895</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>60206045680052</t>
         </is>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>01.04.2021</t>
         </is>
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>02.06.2004</t>
         </is>
       </c>
       <c r="N162" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O162" s="4" t="inlineStr">
-        <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O162" s="4" t="inlineStr"/>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>UM 03754068</t>
-        </is>
-      </c>
-      <c r="Q162" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0862565</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="inlineStr"/>
       <c r="R162" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S162" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
+          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
+        </is>
+      </c>
+      <c r="S162" s="5" t="inlineStr"/>
       <c r="T162" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U162" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U162" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V162" s="4" t="inlineStr"/>
-      <c r="W162" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W162" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X162" s="7" t="inlineStr">
@@ -18716,7 +18700,7 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida</t>
+          <t>Xaydarova Iroda</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
@@ -18726,7 +18710,7 @@
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
@@ -18736,37 +18720,37 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Safar qizi</t>
+          <t>Zarif qizi</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AE4240266</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>61906085590032</t>
         </is>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M163" s="12" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N163" s="12" t="inlineStr">
@@ -18776,23 +18760,27 @@
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="P163" s="9" t="inlineStr">
         <is>
-          <t>PT 0025701</t>
-        </is>
-      </c>
-      <c r="Q163" s="11" t="inlineStr"/>
+          <t>UM 03754068</t>
+        </is>
+      </c>
+      <c r="Q163" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
+        </is>
+      </c>
       <c r="R163" s="11" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S163" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T163" s="12" t="inlineStr">
@@ -18806,9 +18794,9 @@
         </is>
       </c>
       <c r="V163" s="11" t="inlineStr"/>
-      <c r="W163" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W163" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X163" s="7" t="inlineStr">
@@ -18823,12 +18811,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor</t>
+          <t>Xayrullayeva Umida</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -18838,91 +18826,89 @@
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Azim qizi</t>
+          <t>Safar qizi</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>AD4186543</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>62104025680040</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>21.04.2002</t>
+          <t>19.11.2008</t>
         </is>
       </c>
       <c r="N164" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>UM 0086260</t>
+          <t>PT 0025701</t>
         </is>
       </c>
       <c r="Q164" s="4" t="inlineStr"/>
       <c r="R164" s="4" t="inlineStr">
         <is>
-          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S164" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T164" s="5" t="n">
-        <v>2019</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T164" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U164" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V164" s="4" t="inlineStr">
-        <is>
-          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W164" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V164" s="4" t="inlineStr"/>
+      <c r="W164" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X164" s="7" t="inlineStr">
@@ -18937,83 +18923,83 @@
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista</t>
-        </is>
-      </c>
-      <c r="D165" s="11" t="inlineStr"/>
+          <t>Xo'jaqulova Navbahor</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>302</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-14 00:00:00</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Sobir qizi</t>
+          <t>Azim qizi</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AD4186543</t>
         </is>
       </c>
       <c r="K165" s="9" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>62104025680040</t>
         </is>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>21.04.2002</t>
         </is>
       </c>
       <c r="N165" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="P165" s="9" t="inlineStr">
         <is>
-          <t>UM 03718337</t>
-        </is>
-      </c>
-      <c r="Q165" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0086260</t>
+        </is>
+      </c>
+      <c r="Q165" s="11" t="inlineStr"/>
       <c r="R165" s="11" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S165" s="12" t="inlineStr">
@@ -19021,10 +19007,8 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T165" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="T165" s="12" t="n">
+        <v>2019</v>
       </c>
       <c r="U165" s="7" t="inlineStr">
         <is>
@@ -19033,7 +19017,7 @@
       </c>
       <c r="V165" s="11" t="inlineStr">
         <is>
-          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
         </is>
       </c>
       <c r="W165" s="8" t="inlineStr">
@@ -19058,17 +19042,13 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xolmamatova Shoxista</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr"/>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
@@ -19078,62 +19058,62 @@
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>Isomiddin qizi</t>
+          <t>Sobir qizi</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
       <c r="N166" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>UM 03758009</t>
+          <t>UM 03718337</t>
         </is>
       </c>
       <c r="Q166" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
         </is>
       </c>
       <c r="R166" s="4" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S166" s="5" t="inlineStr">
@@ -19151,7 +19131,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V166" s="4" t="inlineStr"/>
+      <c r="V166" s="4" t="inlineStr">
+        <is>
+          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+        </is>
+      </c>
       <c r="W166" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -19169,12 +19153,12 @@
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Xolmaxmatova Sevinch</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
@@ -19184,7 +19168,7 @@
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
@@ -19194,37 +19178,37 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Isomiddin qizi</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="J167" s="12" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="K167" s="9" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="L167" s="12" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>25.11.2008</t>
         </is>
       </c>
       <c r="N167" s="12" t="inlineStr">
@@ -19234,28 +19218,32 @@
       </c>
       <c r="O167" s="11" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="P167" s="9" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q167" s="11" t="inlineStr"/>
+          <t>UM 03758009</t>
+        </is>
+      </c>
+      <c r="Q167" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+        </is>
+      </c>
       <c r="R167" s="11" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S167" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T167" s="12" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
@@ -19263,14 +19251,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V167" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W167" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V167" s="11" t="inlineStr"/>
+      <c r="W167" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X167" s="7" t="inlineStr">
@@ -19285,12 +19269,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -19300,81 +19284,79 @@
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>Dilmurod qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>AE1516812</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>60110085590193</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="N168" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>UM 03755333</t>
-        </is>
-      </c>
-      <c r="Q168" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
-        </is>
-      </c>
+          <t>K 3418837</t>
+        </is>
+      </c>
+      <c r="Q168" s="4" t="inlineStr"/>
       <c r="R168" s="4" t="inlineStr">
         <is>
-          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S168" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T168" s="5" t="n">
-        <v>2026</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T168" s="5" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
       </c>
       <c r="U168" s="7" t="inlineStr">
         <is>
@@ -19383,12 +19365,12 @@
       </c>
       <c r="V168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W168" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W168" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
         </is>
       </c>
       <c r="X168" s="7" t="inlineStr">
@@ -19403,12 +19385,12 @@
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Xolmurodova Dilnura</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
@@ -19418,47 +19400,47 @@
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-15 00:00:00</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Dilmurod qizi</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="J169" s="12" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE1516812</t>
         </is>
       </c>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>60110085590193</t>
         </is>
       </c>
       <c r="L169" s="12" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="M169" s="12" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N169" s="12" t="inlineStr">
@@ -19468,18 +19450,22 @@
       </c>
       <c r="O169" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="P169" s="9" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q169" s="11" t="inlineStr"/>
+          <t>UM 03755333</t>
+        </is>
+      </c>
+      <c r="Q169" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
+        </is>
+      </c>
       <c r="R169" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S169" s="12" t="inlineStr">
@@ -19487,20 +19473,22 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T169" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="T169" s="12" t="n">
+        <v>2026</v>
       </c>
       <c r="U169" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V169" s="11" t="inlineStr"/>
+      <c r="V169" s="11" t="inlineStr">
+        <is>
+          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
+        </is>
+      </c>
       <c r="W169" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X169" s="7" t="inlineStr">
@@ -19515,12 +19503,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -19530,60 +19518,68 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="F170" s="5" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Bahrom qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr"/>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>AE5954513</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>62204085720105</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M170" s="5" t="inlineStr">
         <is>
-          <t>22.04.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N170" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>UM 03717652</t>
+          <t>UM 02172469</t>
         </is>
       </c>
       <c r="Q170" s="4" t="inlineStr"/>
       <c r="R170" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S170" s="5" t="inlineStr">
@@ -19596,9 +19592,17 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U170" s="5" t="inlineStr"/>
+      <c r="U170" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V170" s="4" t="inlineStr"/>
-      <c r="W170" s="15" t="inlineStr"/>
+      <c r="W170" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
       <c r="X170" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19611,12 +19615,12 @@
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Lobar</t>
+          <t>Xujamuratova Durdona</t>
         </is>
       </c>
       <c r="D171" s="11" t="inlineStr">
@@ -19626,72 +19630,60 @@
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="F171" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr"/>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Ural qizi</t>
+          <t>Bahrom qizi</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
-      <c r="I171" s="10" t="inlineStr">
-        <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
+        </is>
+      </c>
+      <c r="I171" s="10" t="inlineStr"/>
       <c r="J171" s="12" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="K171" s="9" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="L171" s="12" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M171" s="12" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>22.04.2008</t>
         </is>
       </c>
       <c r="N171" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P171" s="9" t="inlineStr">
         <is>
-          <t>UM 03728374</t>
-        </is>
-      </c>
-      <c r="Q171" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03717652</t>
+        </is>
+      </c>
+      <c r="Q171" s="11" t="inlineStr"/>
       <c r="R171" s="11" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S171" s="12" t="inlineStr">
@@ -19701,20 +19693,12 @@
       </c>
       <c r="T171" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U171" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U171" s="12" t="inlineStr"/>
       <c r="V171" s="11" t="inlineStr"/>
-      <c r="W171" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W171" s="15" t="inlineStr"/>
       <c r="X171" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19732,7 +19716,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Sabina</t>
+          <t>Xurramova Lobar</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -19742,56 +19726,72 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F172" s="5" t="inlineStr"/>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>Yuldosh qizi</t>
+          <t>Ural qizi</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr"/>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>AC3081523</t>
+          <t>AE2656510</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>60803048230011</t>
+          <t>62508085680062</t>
         </is>
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>16.10.2020</t>
+          <t>13.05.2025</t>
         </is>
       </c>
       <c r="M172" s="5" t="inlineStr">
         <is>
-          <t>08.03.2004</t>
-        </is>
-      </c>
-      <c r="N172" s="5" t="inlineStr"/>
+          <t>25.08.2008</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xurramova Lobar Ural qizi</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>UM 1315230</t>
-        </is>
-      </c>
-      <c r="Q172" s="4" t="inlineStr"/>
+          <t>UM 03728374</t>
+        </is>
+      </c>
+      <c r="Q172" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
+        </is>
+      </c>
       <c r="R172" s="4" t="inlineStr">
         <is>
-          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S172" s="5" t="inlineStr">
@@ -19801,12 +19801,20 @@
       </c>
       <c r="T172" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U172" s="5" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U172" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V172" s="4" t="inlineStr"/>
-      <c r="W172" s="15" t="inlineStr"/>
+      <c r="W172" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X172" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19819,12 +19827,12 @@
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza</t>
+          <t>Xurramova Sabina</t>
         </is>
       </c>
       <c r="D173" s="11" t="inlineStr">
@@ -19834,89 +19842,71 @@
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F173" s="18" t="n">
-        <v>46204</v>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F173" s="12" t="inlineStr"/>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>Shuhrat qizi</t>
+          <t>Yuldosh qizi</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
-      <c r="I173" s="10" t="inlineStr">
-        <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
+          <t>Xurramova Sabina Yuldosh qizi</t>
+        </is>
+      </c>
+      <c r="I173" s="10" t="inlineStr"/>
       <c r="J173" s="12" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AC3081523</t>
         </is>
       </c>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>60803048230011</t>
         </is>
       </c>
       <c r="L173" s="12" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>16.10.2020</t>
         </is>
       </c>
       <c r="M173" s="12" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
-        </is>
-      </c>
-      <c r="N173" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
+          <t>08.03.2004</t>
+        </is>
+      </c>
+      <c r="N173" s="12" t="inlineStr"/>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P173" s="9" t="inlineStr">
         <is>
-          <t>UM 0084478</t>
+          <t>UM 1315230</t>
         </is>
       </c>
       <c r="Q173" s="11" t="inlineStr"/>
       <c r="R173" s="11" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S173" s="12" t="inlineStr">
         <is>
-          <t>Attestat</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T173" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U173" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U173" s="12" t="inlineStr"/>
       <c r="V173" s="11" t="inlineStr"/>
-      <c r="W173" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W173" s="15" t="inlineStr"/>
       <c r="X173" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19934,7 +19924,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda</t>
+          <t>Xurramova Shahnoza</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -19944,13 +19934,11 @@
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="F174" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="n">
+        <v>46204</v>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
@@ -19959,32 +19947,32 @@
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
       <c r="N174" s="5" t="inlineStr">
@@ -19994,32 +19982,28 @@
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>UM 02149677</t>
-        </is>
-      </c>
-      <c r="Q174" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0084478</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="inlineStr"/>
       <c r="R174" s="4" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S174" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Attestat</t>
         </is>
       </c>
       <c r="T174" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U174" s="7" t="inlineStr">
@@ -20045,12 +20029,12 @@
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Xurramova Shahrizoda</t>
         </is>
       </c>
       <c r="D175" s="11" t="inlineStr">
@@ -20060,7 +20044,7 @@
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
@@ -20070,58 +20054,62 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Shuhrat qizi</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="L175" s="12" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="M175" s="12" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>30.04.2007</t>
         </is>
       </c>
       <c r="N175" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="P175" s="9" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q175" s="11" t="inlineStr"/>
+          <t>UM 02149677</t>
+        </is>
+      </c>
+      <c r="Q175" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
+        </is>
+      </c>
       <c r="R175" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S175" s="12" t="inlineStr">
@@ -20131,7 +20119,7 @@
       </c>
       <c r="T175" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
@@ -20139,11 +20127,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V175" s="11" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V175" s="11" t="inlineStr"/>
       <c r="W175" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -20161,12 +20145,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza</t>
+          <t>Xurramova Shodiya</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -20176,7 +20160,7 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -20186,37 +20170,37 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Fazliddin qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>27.04.2002</t>
         </is>
       </c>
       <c r="N176" s="5" t="inlineStr">
@@ -20226,22 +20210,18 @@
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>UM 03753649</t>
-        </is>
-      </c>
-      <c r="Q176" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0438281</t>
+        </is>
+      </c>
+      <c r="Q176" s="4" t="inlineStr"/>
       <c r="R176" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S176" s="5" t="inlineStr">
@@ -20251,7 +20231,7 @@
       </c>
       <c r="T176" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="U176" s="7" t="inlineStr">
@@ -20261,12 +20241,12 @@
       </c>
       <c r="V176" s="4" t="inlineStr">
         <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
         </is>
       </c>
       <c r="W176" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X176" s="7" t="inlineStr">
@@ -20281,18 +20261,22 @@
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
-        </is>
-      </c>
-      <c r="D177" s="11" t="inlineStr"/>
+          <t>Xusanova Aziza</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
@@ -20302,62 +20286,62 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Fazliddin qizi</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="K177" s="9" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="L177" s="12" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="M177" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N177" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="P177" s="9" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
+          <t>UM 03753649</t>
         </is>
       </c>
       <c r="Q177" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
         </is>
       </c>
       <c r="R177" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S177" s="12" t="inlineStr">
@@ -20375,10 +20359,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V177" s="11" t="inlineStr"/>
+      <c r="V177" s="11" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+        </is>
+      </c>
       <c r="W177" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X177" s="7" t="inlineStr">
@@ -20393,22 +20381,18 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Yahyomurodova Gulsanam</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr"/>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -20418,37 +20402,37 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Xusan qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>AB9239333</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>42207935680042</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>09.04.2018</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>22.07.1993</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N178" s="5" t="inlineStr">
@@ -20458,22 +20442,22 @@
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>UM 03524597</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q178" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R178" s="4" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S178" s="5" t="inlineStr">
@@ -20483,7 +20467,7 @@
       </c>
       <c r="T178" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U178" s="7" t="inlineStr">
@@ -20494,7 +20478,7 @@
       <c r="V178" s="4" t="inlineStr"/>
       <c r="W178" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X178" s="7" t="inlineStr">
@@ -20509,12 +20493,12 @@
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
       <c r="D179" s="11" t="inlineStr">
@@ -20524,7 +20508,7 @@
       </c>
       <c r="E179" s="12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
@@ -20534,68 +20518,72 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K179" s="9" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L179" s="12" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M179" s="12" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N179" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O179" s="11" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="P179" s="9" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
-        </is>
-      </c>
-      <c r="Q179" s="11" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q179" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R179" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son texnikumi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S179" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T179" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U179" s="7" t="inlineStr">
@@ -20603,14 +20591,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V179" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
-        </is>
-      </c>
-      <c r="W179" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+      <c r="V179" s="11" t="inlineStr"/>
+      <c r="W179" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X179" s="7" t="inlineStr">
@@ -20625,12 +20609,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yuldosheva Ruhshona</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -20640,7 +20624,7 @@
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -20650,67 +20634,63 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Xabibullo qizi</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="M180" s="5" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>13.09.2008</t>
         </is>
       </c>
       <c r="N180" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
-        </is>
-      </c>
-      <c r="Q180" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q180" s="4" t="inlineStr"/>
       <c r="R180" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
       <c r="S180" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T180" s="5" t="inlineStr">
@@ -20723,10 +20703,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V180" s="4" t="inlineStr"/>
-      <c r="W180" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V180" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
+        </is>
+      </c>
+      <c r="W180" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X180" s="7" t="inlineStr">
@@ -20741,12 +20725,12 @@
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D181" s="11" t="inlineStr">
@@ -20756,7 +20740,7 @@
       </c>
       <c r="E181" s="12" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
@@ -20766,37 +20750,37 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>Sodiqovna</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="K181" s="9" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="L181" s="12" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="M181" s="12" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="N181" s="12" t="inlineStr">
@@ -20806,22 +20790,22 @@
       </c>
       <c r="O181" s="11" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P181" s="9" t="inlineStr">
         <is>
-          <t>UM 03729571</t>
+          <t>UM 03729007</t>
         </is>
       </c>
       <c r="Q181" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
         </is>
       </c>
       <c r="R181" s="11" t="inlineStr">
         <is>
-          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S181" s="12" t="inlineStr">
@@ -20842,7 +20826,7 @@
       <c r="V181" s="11" t="inlineStr"/>
       <c r="W181" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X181" s="7" t="inlineStr">
@@ -20857,18 +20841,22 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr"/>
+          <t>Zayidova Shaboda</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
@@ -20878,62 +20866,62 @@
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>Alisher qizi</t>
+          <t>Sodiqovna</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="M182" s="5" t="inlineStr">
         <is>
-          <t>12.06.2007</t>
+          <t>31.12.2008</t>
         </is>
       </c>
       <c r="N182" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>UM 03296188</t>
+          <t>UM 03729571</t>
         </is>
       </c>
       <c r="Q182" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
         </is>
       </c>
       <c r="R182" s="4" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S182" s="5" t="inlineStr">
@@ -20943,7 +20931,7 @@
       </c>
       <c r="T182" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U182" s="7" t="inlineStr">
@@ -20954,17 +20942,129 @@
       <c r="V182" s="4" t="inlineStr"/>
       <c r="W182" s="8" t="inlineStr">
         <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X182" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
+        <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina</t>
+        </is>
+      </c>
+      <c r="D183" s="11" t="inlineStr"/>
+      <c r="E183" s="12" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="F183" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G183" s="12" t="inlineStr">
+        <is>
+          <t>Alisher qizi</t>
+        </is>
+      </c>
+      <c r="H183" s="11" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="I183" s="10" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="J183" s="12" t="inlineStr">
+        <is>
+          <t>AD9812146</t>
+        </is>
+      </c>
+      <c r="K183" s="9" t="inlineStr">
+        <is>
+          <t>61206075590076</t>
+        </is>
+      </c>
+      <c r="L183" s="12" t="inlineStr">
+        <is>
+          <t>13.12.2024</t>
+        </is>
+      </c>
+      <c r="M183" s="12" t="inlineStr">
+        <is>
+          <t>12.06.2007</t>
+        </is>
+      </c>
+      <c r="N183" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O183" s="11" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="P183" s="9" t="inlineStr">
+        <is>
+          <t>UM 03296188</t>
+        </is>
+      </c>
+      <c r="Q183" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+        </is>
+      </c>
+      <c r="R183" s="11" t="inlineStr">
+        <is>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S183" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T183" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U183" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V183" s="11" t="inlineStr"/>
+      <c r="W183" s="8" t="inlineStr">
+        <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X182" s="7" t="inlineStr">
+      <c r="X183" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X182"/>
+  <autoFilter ref="A1:X183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22730,7 +22830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25148,7 +25248,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona</t>
+          <t>Samatova Oydin</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -25158,82 +25258,66 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:00:00</t>
-        </is>
-      </c>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Sulaymon qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Samatova Oydin Sulaymon qizi</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>29.10.1990</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 03754198</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
-        </is>
-      </c>
+          <t>OR-SH 0346677</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
@@ -25243,17 +25327,13 @@
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W22" s="15" t="inlineStr"/>
+      <c r="X22" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25268,7 +25348,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira</t>
+          <t>Saydalimova Ruxshona</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -25276,59 +25356,79 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr"/>
-      <c r="F23" s="12" t="inlineStr"/>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00:00</t>
+        </is>
+      </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr"/>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>18.07.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03730412</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr"/>
+          <t>UM 03754198</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
+        </is>
+      </c>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>78-maktab</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -25343,13 +25443,17 @@
       </c>
       <c r="V23" s="11" t="inlineStr">
         <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W23" s="15" t="inlineStr"/>
-      <c r="X23" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25364,7 +25468,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -25372,79 +25476,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
@@ -25457,15 +25541,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X24" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W24" s="15" t="inlineStr"/>
+      <c r="X24" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25480,13 +25564,17 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr"/>
+          <t>Shukriyeva Nariye</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -25496,68 +25584,72 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>K 5491697</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -25565,14 +25657,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="11" t="inlineStr">
-        <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
-        </is>
-      </c>
+      <c r="V25" s="11" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -25592,92 +25680,84 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -25685,10 +25765,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -25708,7 +25792,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'raboyeva Sabrina</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -25718,74 +25802,82 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr"/>
+          <t>27.09.2008</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>K 3736287</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -25794,9 +25886,9 @@
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr"/>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -25816,7 +25908,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -25826,7 +25918,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -25836,69 +25928,69 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="inlineStr"/>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>Tosheva Aziza Sherzod qizi</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
+          <t>K 3736287</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U28" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
@@ -25924,13 +26016,17 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr"/>
+          <t>To'xtayeva Durdona</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -25940,37 +26036,37 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
@@ -25978,24 +26074,16 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O29" s="11" t="inlineStr">
-        <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
-        </is>
-      </c>
+      <c r="O29" s="11" t="inlineStr"/>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728346</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr"/>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -26008,15 +26096,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U29" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr"/>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X29" s="7" t="inlineStr">
@@ -26036,17 +26124,13 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -26056,62 +26140,62 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
+          <t>UM 03730110</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -26152,7 +26236,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
+          <t>Umarova Iroda</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -26162,7 +26246,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -26172,37 +26256,37 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
@@ -26212,22 +26296,22 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
+          <t>UM 03754201</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
         </is>
       </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
@@ -26245,11 +26329,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="11" t="inlineStr">
-        <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
-        </is>
-      </c>
+      <c r="V31" s="11" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -26272,7 +26352,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -26282,85 +26362,97 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Uroqova Jasmina Jasur qizi</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>K 4590366</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr"/>
+          <t>UM 03752857</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+        </is>
+      </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U32" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -26380,7 +26472,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Usmanova Iroda</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -26390,93 +26482,85 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O33" s="11" t="inlineStr">
-        <is>
-          <t>Xurramova Shodiya Arol qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr"/>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
+          <t>K 4590366</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S33" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V33" s="11" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U33" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr"/>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X33" s="7" t="inlineStr">
@@ -26496,113 +26580,229 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
+          <t>Xurramova Shodiya</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Arol qizi</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>AC1967100</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>62704025590042</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>12.06.2019</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>27.04.2002</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>UM 0438281</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr"/>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U34" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
+        </is>
+      </c>
+      <c r="W34" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X34" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
           <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Xusan qizi</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>AB9239333</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>42207935680042</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L35" s="12" t="inlineStr">
         <is>
           <t>09.04.2018</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M35" s="12" t="inlineStr">
         <is>
           <t>22.07.1993</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="N35" s="12" t="inlineStr">
         <is>
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="O35" s="11" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P35" s="9" t="inlineStr">
         <is>
           <t>UM 03524597</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="Q35" s="11" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr">
+      <c r="R35" s="11" t="inlineStr">
         <is>
           <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="S34" s="5" t="inlineStr">
+      <c r="S35" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T34" s="5" t="inlineStr">
+      <c r="T35" s="12" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="U34" s="7" t="inlineStr">
+      <c r="U35" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="8" t="inlineStr">
+      <c r="V35" s="11" t="inlineStr"/>
+      <c r="W35" s="8" t="inlineStr">
         <is>
           <t>Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X34" s="7" t="inlineStr">
+      <c r="X35" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X34"/>
+  <autoFilter ref="A1:X35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
+++ b/qayta_tekshiruv/Talabalar_Yangilangan_Royxat.xlsx
@@ -19,11 +19,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$183</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -22830,7 +22830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -23888,7 +23888,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Irgasheva Dinora</t>
+          <t>Islomova Nilufar</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -23896,37 +23896,49 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Shodmon qizi</t>
+          <t>Abdulxafiz qizi</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Irgasheva Dinora Shodmon qizi</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+          <t>Islomova Nilufar Abdulxafiz qizi</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Islomova Nilufar Abdulxafiz qizi</t>
+        </is>
+      </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>AC 2430931</t>
+          <t>AD9664280</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60106035590029</t>
+          <t>61911085590104</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>15.11.2019</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>01.06.2003</t>
+          <t>19.11.2008</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -23934,21 +23946,29 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Islomova Nilufar Abdulxafiz qizi</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>UM 0441030</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr"/>
+          <t>UM 03752502</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3580119/3231058/665e452b-f84e-49a9-8c0a-114015a02ee9?preview=true</t>
+        </is>
+      </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>14-maktab</t>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
@@ -23961,15 +23981,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W10" s="15" t="inlineStr"/>
-      <c r="X10" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -23984,7 +24004,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Islomova Nilufar</t>
+          <t>Jalolova Rayxona</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -23994,72 +24014,72 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>262</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Abdulxafiz qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Islomova Nilufar Abdulxafiz qizi</t>
+          <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Islomova Nilufar Abdulxafiz qizi</t>
+          <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>AD9664280</t>
+          <t>AE3492384</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>61911085590104</t>
+          <t>62207085680059</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>22.07.2008</t>
         </is>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>Islomova Nilufar Abdulxafiz qizi</t>
+          <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>UM 03752502</t>
+          <t>UM 03729365</t>
         </is>
       </c>
       <c r="Q11" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3580119/3231058/665e452b-f84e-49a9-8c0a-114015a02ee9?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4054768/3621740/e249f0ee-bae2-4fd1-b709-560d5089a083?preview=true</t>
         </is>
       </c>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>47-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
@@ -24078,9 +24098,9 @@
         </is>
       </c>
       <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W11" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
       </c>
       <c r="X11" s="7" t="inlineStr">
@@ -24100,7 +24120,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona</t>
+          <t>Javliyeva Nargiza</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -24110,47 +24130,47 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Ortiq qizi</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona Akmal qizi</t>
+          <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona Akmal qizi</t>
+          <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>AE3492384</t>
+          <t>AE5222372</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62207085680059</t>
+          <t>62401095680012</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>23.07.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>22.07.2008</t>
+          <t>24.01.2009</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -24160,22 +24180,22 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona Akmal qizi</t>
+          <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>UM 03729365</t>
+          <t>UM 03729316</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4054768/3621740/e249f0ee-bae2-4fd1-b709-560d5089a083?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4089340/3633473/dd6bd3e0-37a5-444d-8a53-a22ed29c5347?preview=true</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>47-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
@@ -24194,9 +24214,9 @@
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X12" s="7" t="inlineStr">
@@ -24216,7 +24236,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza</t>
+          <t>Maxmashoxova Feruza</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -24226,7 +24246,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -24236,62 +24256,62 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Ortiq qizi</t>
+          <t>Bekmurod qizi</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza Ortiq qizi</t>
+          <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza Ortiq qizi</t>
+          <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>AE5222372</t>
+          <t>AE5088010</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>62401095680012</t>
+          <t>60201085630050</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>18.11.2025</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>02.01.2008</t>
         </is>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Qamashi tumani</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza Ortiq qizi</t>
+          <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>UM 03729316</t>
+          <t>UM 03742126</t>
         </is>
       </c>
       <c r="Q13" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4089340/3633473/dd6bd3e0-37a5-444d-8a53-a22ed29c5347?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801846/3533937/132e5ac9-15d4-4739-bdb7-4e20c5ce7245?preview=true</t>
         </is>
       </c>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S13" s="12" t="inlineStr">
@@ -24312,7 +24332,7 @@
       <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X13" s="7" t="inlineStr">
@@ -24332,7 +24352,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza</t>
+          <t>Meyliqulova Hilola</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -24342,7 +24362,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -24352,72 +24372,68 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Bekmurod qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza Bekmurod qizi</t>
+          <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza Bekmurod qizi</t>
+          <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>AE5088010</t>
+          <t>AB7137876</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60201085630050</t>
+          <t>61202005680055</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>18.11.2025</t>
+          <t>07.07.2017</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>12.02.2000</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza Bekmurod qizi</t>
+          <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>UM 03742126</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801846/3533937/132e5ac9-15d4-4739-bdb7-4e20c5ce7245?preview=true</t>
-        </is>
-      </c>
+          <t>K 5470992</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr"/>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U14" s="7" t="inlineStr">
@@ -24425,10 +24441,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>Qo'lda tasdiqlandi: Meyliqulova Hilola Farhod qizi</t>
+        </is>
+      </c>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X14" s="7" t="inlineStr">
@@ -24448,7 +24468,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola</t>
+          <t>Nu'monova Saidabonu</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -24458,7 +24478,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -24468,68 +24488,72 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola Farhod qizi</t>
+          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola Farhod qizi</t>
+          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>AB7137876</t>
+          <t>AE1067914</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>61202005680055</t>
+          <t>62410085590084</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>07.07.2017</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>12.02.2000</t>
+          <t>24.10.2008</t>
         </is>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola Farhod qizi</t>
+          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>K 5470992</t>
-        </is>
-      </c>
-      <c r="Q15" s="11" t="inlineStr"/>
+          <t>UM 03752610</t>
+        </is>
+      </c>
+      <c r="Q15" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3982307/4146791/0ce0ca2c-2594-48a0-b1c4-8773beb807f7?preview=true</t>
+        </is>
+      </c>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>Kitob agrobiznes kasb-hunar kolleji</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
@@ -24537,14 +24561,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V15" s="11" t="inlineStr">
-        <is>
-          <t>Qo'lda tasdiqlandi: Meyliqulova Hilola Farhod qizi</t>
-        </is>
-      </c>
+      <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: TUTUQ BELGISI</t>
         </is>
       </c>
       <c r="X15" s="7" t="inlineStr">
@@ -24564,7 +24584,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu</t>
+          <t>Ochildiyeva Dinora</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -24574,7 +24594,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -24584,37 +24604,37 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Ulug'bek qizi</t>
+          <t>Otabek qizi</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
+          <t>Ochildiyeva Dinora Otabek qizi</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
+          <t>Ochildiyeva Dinora Otabek qizi</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>AE1067914</t>
+          <t>AE4084333</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62410085590084</t>
+          <t>62012085590055</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>08.09.2025</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>24.10.2008</t>
+          <t>20.12.2008</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -24624,22 +24644,22 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
+          <t>Ochildiyeva Dinora Otabek qizi</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>UM 03752610</t>
+          <t>UM 03754418</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3982307/4146791/0ce0ca2c-2594-48a0-b1c4-8773beb807f7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3714426/3303458/d7200d74-420a-43ca-a745-51967def2eee?preview=true</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>34-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
@@ -24657,10 +24677,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: TUTUQ BELGISI</t>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'OCHILDIYEVA DINORA' | bazada: 'Ochildiyeva Dinara'; imlo farqi — Shahodatnoma PDF: 'Ochildiyeva Dinora Otabek qizi' | bazada: 'Ochildiyeva Dinara'</t>
+        </is>
+      </c>
+      <c r="W16" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X16" s="7" t="inlineStr">
@@ -24680,7 +24704,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Ochildiyeva Dinora</t>
+          <t>Qulmatova Shabbona</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -24688,74 +24712,62 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
+      <c r="E17" s="12" t="inlineStr"/>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Otabek qizi</t>
+          <t>Azamat qizi</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Ochildiyeva Dinora Otabek qizi</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Ochildiyeva Dinora Otabek qizi</t>
-        </is>
-      </c>
+          <t>Qulmatova Shabbona Azamat qizi</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>AE4084333</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>62012085590055</t>
+          <t>61008085680019</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>08.09.2025</t>
+          <t>05.11.2025</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>20.12.2008</t>
+          <t>10.08.2008</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Ochildiyeva Dinora Otabek qizi</t>
+          <t>Yo'q</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>UM 03754418</t>
-        </is>
-      </c>
-      <c r="Q17" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3714426/3303458/d7200d74-420a-43ca-a745-51967def2eee?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730102</t>
+        </is>
+      </c>
+      <c r="Q17" s="11" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>34-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
@@ -24773,19 +24785,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V17" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'OCHILDIYEVA DINORA' | bazada: 'Ochildiyeva Dinara'; imlo farqi — Shahodatnoma PDF: 'Ochildiyeva Dinora Otabek qizi' | bazada: 'Ochildiyeva Dinara'</t>
-        </is>
-      </c>
-      <c r="W17" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V17" s="11" t="inlineStr"/>
+      <c r="W17" s="15" t="inlineStr"/>
+      <c r="X17" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -24800,7 +24804,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona</t>
+          <t>Quysinova Rohshona</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -24808,62 +24812,74 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Azamat qizi</t>
+          <t>To'lqin qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat qizi</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
+          <t>Quysinova Rohshona To'lqin qizi</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Quysinova Rohshona To'lqin qizi</t>
+        </is>
+      </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AE4905104</t>
+          <t>AE7231113</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61008085680019</t>
+          <t>60406055720067</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>05.11.2025</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>10.08.2008</t>
+          <t>04.06.2005</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Yo'q</t>
+          <t>Quysinova Rohshona To'lqin qizi</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>UM 03730102</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr"/>
+          <t>UM 02138929</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2162723/1195039/000613cf-4d65-4df9-dae0-08dc8cc4bb61?preview=true</t>
+        </is>
+      </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>Ixtisoslashtirilgan maktabni</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
@@ -24873,7 +24889,7 @@
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
@@ -24881,11 +24897,19 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="15" t="inlineStr"/>
-      <c r="X18" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
+        </is>
+      </c>
+      <c r="W18" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -24900,17 +24924,13 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Ro'zimurodova Larisa</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -24920,62 +24940,62 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>To'lqin qizi</t>
+          <t>Ma'matali qizi</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>AE7231113</t>
+          <t>AE5324961</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>60406055720067</t>
+          <t>61608085630072</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>05.12.2025</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>04.06.2005</t>
+          <t>16.08.2008</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Qamashi tumani</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Maxmatali qizi</t>
         </is>
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM 02138929</t>
+          <t>UM 03742132</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2162723/1195039/000613cf-4d65-4df9-dae0-08dc8cc4bb61?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801844/3535807/0b280dc6-72ff-4cdc-b46b-4de552e5425e?preview=true</t>
         </is>
       </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>Ixtisoslashtirilgan maktabni</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
@@ -24985,7 +25005,7 @@
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
@@ -24995,12 +25015,12 @@
       </c>
       <c r="V19" s="11" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
-        </is>
-      </c>
-      <c r="W19" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+          <t>TEKSHIRILSIN: imlo farqi — Shahodatnoma PDF: 'Ro'zimurodova Larisa Maxmatali qizi' | bazada: 'Ruzimurodova Larisa'</t>
+        </is>
+      </c>
+      <c r="W19" s="13" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -25020,13 +25040,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
+          <t>Samadova Nigora</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -25036,62 +25060,58 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Ma'matali qizi</t>
+          <t>Abdisamiyevna</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AE5324961</t>
+          <t>AE1836076</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61608085630072</t>
+          <t>40710895590044</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>05.12.2025</t>
+          <t>05.03.2025</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>16.08.2008</t>
+          <t>07.10.1989</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Maxmatali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>UM 03742132</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801844/3535807/0b280dc6-72ff-4cdc-b46b-4de552e5425e?preview=true</t>
-        </is>
-      </c>
+          <t>O'R-SH 0658073</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati shahrisabz tumanidagi 26-umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -25101,7 +25121,7 @@
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
@@ -25109,14 +25129,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — Shahodatnoma PDF: 'Ro'zimurodova Larisa Maxmatali qizi' | bazada: 'Ruzimurodova Larisa'</t>
-        </is>
-      </c>
-      <c r="W20" s="13" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: FARQ</t>
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -25136,7 +25152,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Samadova Nigora</t>
+          <t>Samatova Oydin</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -25146,78 +25162,66 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr"/>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Abdisamiyevna</t>
+          <t>Sulaymon qizi</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
-        </is>
-      </c>
+          <t>Samatova Oydin Sulaymon qizi</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AE1836076</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>40710895590044</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>05.03.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>07.10.1989</t>
+          <t>29.10.1990</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr"/>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>O'R-SH 0658073</t>
+          <t>OR-SH 0346677</t>
         </is>
       </c>
       <c r="Q21" s="11" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati shahrisabz tumanidagi 26-umumiy o'rta ta'lim maktabi</t>
+          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -25225,15 +25229,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V21" s="11" t="inlineStr"/>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W21" s="15" t="inlineStr"/>
+      <c r="X21" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25248,7 +25252,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Samatova Oydin</t>
+          <t>Saydalimova Ruxshona</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -25258,66 +25262,82 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr"/>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00:00</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Sulaymon qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Samatova Oydin Sulaymon qizi</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AD8980430</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42910905720012</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>11.10.2024</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>29.10.1990</t>
+          <t>18.07.2008</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>OR-SH 0346677</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr"/>
+          <t>UM 03754198</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
+        </is>
+      </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
@@ -25327,13 +25347,17 @@
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W22" s="15" t="inlineStr"/>
-      <c r="X22" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25348,7 +25372,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -25356,79 +25380,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:00:00</t>
-        </is>
-      </c>
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr"/>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr"/>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03754198</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -25443,17 +25447,13 @@
       </c>
       <c r="V23" s="11" t="inlineStr">
         <is>
-          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
-        </is>
-      </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W23" s="15" t="inlineStr"/>
+      <c r="X23" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25468,7 +25468,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira</t>
+          <t>Shukriyeva Nariye</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -25476,59 +25476,79 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03730412</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>78-maktab</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
@@ -25541,15 +25561,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W24" s="15" t="inlineStr"/>
-      <c r="X24" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25564,17 +25584,13 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -25584,72 +25600,68 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -25657,10 +25669,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="11" t="inlineStr"/>
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -25680,84 +25696,92 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>To'raboyeva Sabrina</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>27.09.2008</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>K 5491697</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -25765,14 +25789,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -25792,7 +25812,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -25802,82 +25822,74 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr"/>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>K 3736287</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -25886,9 +25898,9 @@
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr"/>
-      <c r="W27" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -25908,7 +25920,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'xtayeva Durdona</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -25918,7 +25930,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -25928,69 +25940,69 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
-        </is>
-      </c>
+          <t>19.06.2008</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>K 3736287</t>
+          <t>UM 03728346</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U28" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
@@ -26016,17 +26028,13 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr"/>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -26036,37 +26044,37 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
@@ -26074,16 +26082,24 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O29" s="11" t="inlineStr"/>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
+        </is>
+      </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="inlineStr"/>
+          <t>UM 03730110</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
+        </is>
+      </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -26096,15 +26112,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U29" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr"/>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X29" s="7" t="inlineStr">
@@ -26124,13 +26140,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
+          <t>Umarova Iroda</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -26140,62 +26160,62 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
+          <t>UM 03754201</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -26236,7 +26256,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -26246,7 +26266,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -26256,37 +26276,37 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
@@ -26296,22 +26316,22 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
+          <t>UM 03752857</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
         </is>
       </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
@@ -26329,7 +26349,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="11" t="inlineStr"/>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -26352,7 +26376,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
+          <t>Usmanova Iroda</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -26362,97 +26386,85 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
-        </is>
-      </c>
+          <t>K 4590366</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U32" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -26472,7 +26484,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Xurramova Shodiya</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -26482,85 +26494,93 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>27.04.2002</t>
         </is>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O33" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>K 4590366</t>
+          <t>UM 0438281</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S33" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U33" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V33" s="11" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
+        </is>
+      </c>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X33" s="7" t="inlineStr">
@@ -26580,7 +26600,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -26590,7 +26610,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -26600,58 +26620,62 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr">
@@ -26661,7 +26685,7 @@
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U34" s="7" t="inlineStr">
@@ -26669,140 +26693,20 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V34" s="4" t="inlineStr"/>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X34" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>26-02</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>Xusan qizi</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="J35" s="12" t="inlineStr">
-        <is>
-          <t>AB9239333</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>42207935680042</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>09.04.2018</t>
-        </is>
-      </c>
-      <c r="M35" s="12" t="inlineStr">
-        <is>
-          <t>22.07.1993</t>
-        </is>
-      </c>
-      <c r="N35" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O35" s="11" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="P35" s="9" t="inlineStr">
-        <is>
-          <t>UM 03524597</t>
-        </is>
-      </c>
-      <c r="Q35" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
-        </is>
-      </c>
-      <c r="R35" s="11" t="inlineStr">
-        <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S35" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T35" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V35" s="11" t="inlineStr"/>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X35" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X35"/>
+  <autoFilter ref="A1:X34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -38093,7 +37997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38927,7 +38831,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam</t>
+          <t>Irgasheva Dinora</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -38935,49 +38839,37 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Ozodjon qizi</t>
+          <t>Shodmon qizi</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
+          <t>Irgasheva Dinora Shodmon qizi</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>AD9937321</t>
+          <t>AC 2430931</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>60603085590037</t>
+          <t>60106035590029</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>24.12.2024</t>
+          <t>15.11.2019</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
+          <t>01.06.2003</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -38985,29 +38877,21 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
+      <c r="O8" s="4" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>UM 03752997</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0441030</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr"/>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>14-maktab</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
@@ -39020,15 +38904,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X8" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W8" s="15" t="inlineStr"/>
+      <c r="X8" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -39043,7 +38927,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida</t>
+          <t>Jalilova Shabnam</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -39053,7 +38937,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -39063,37 +38947,37 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Shovkat qizi</t>
+          <t>Ozodjon qizi</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>AE6299685</t>
+          <t>AD9937321</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>60907085590063</t>
+          <t>60603085590037</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>24.12.2024</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>09.07.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
       <c r="N9" s="12" t="inlineStr">
@@ -39103,17 +38987,17 @@
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>UM 03752998</t>
+          <t>UM 03752997</t>
         </is>
       </c>
       <c r="Q9" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
         </is>
       </c>
       <c r="R9" s="11" t="inlineStr">
@@ -39137,9 +39021,9 @@
         </is>
       </c>
       <c r="V9" s="11" t="inlineStr"/>
-      <c r="W9" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+      <c r="W9" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X9" s="7" t="inlineStr">
@@ -39159,7 +39043,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Karimova Nozliya</t>
+          <t>Jumayeva Husnida</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -39169,72 +39053,72 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Rustamovna</t>
+          <t>Shovkat qizi</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>AE4674508</t>
+          <t>AE6299685</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61502085680047</t>
+          <t>60907085590063</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>15.02.2008</t>
+          <t>09.07.2008</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>UM 03729342</t>
+          <t>UM 03752998</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
@@ -39253,9 +39137,9 @@
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W10" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
       </c>
       <c r="X10" s="7" t="inlineStr">
@@ -39275,7 +39159,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara</t>
+          <t>Karimova Nozliya</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -39285,47 +39169,47 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Safarali qizi</t>
+          <t>Rustamovna</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>AE2103843</t>
+          <t>AE4674508</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>60705005680087</t>
+          <t>61502085680047</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>27.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>07.05.2000</t>
+          <t>15.02.2008</t>
         </is>
       </c>
       <c r="N11" s="12" t="inlineStr">
@@ -39335,28 +39219,32 @@
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>Mahmamurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>K 5493345</t>
-        </is>
-      </c>
-      <c r="Q11" s="11" t="inlineStr"/>
+          <t>UM 03729342</t>
+        </is>
+      </c>
+      <c r="Q11" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+        </is>
+      </c>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>Kitob agrobiznes kasb-hunar kolleji</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T11" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
@@ -39364,14 +39252,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
-        </is>
-      </c>
-      <c r="W11" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: BOSHQA ODAM</t>
+      <c r="V11" s="11" t="inlineStr"/>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X11" s="7" t="inlineStr">
@@ -39391,7 +39275,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Mahmatqulova Nilufar</t>
+          <t>Mahmadmurodova Sevara</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -39401,75 +39285,95 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Qayum qizi</t>
+          <t>Safarali qizi</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Mahmatqulova Nilufar Qayum qizi</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
+        </is>
+      </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>AE6047826</t>
+          <t>AE2103843</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60806085590115</t>
+          <t>60705005680087</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>08.06.2008</t>
+          <t>07.05.2000</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Mahmamurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>UM 03754788</t>
+          <t>K 5493345</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr"/>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>43-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="15" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
+        </is>
+      </c>
+      <c r="W12" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: BOSHQA ODAM</t>
+        </is>
+      </c>
       <c r="X12" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -39487,7 +39391,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna</t>
+          <t>Mahmatqulova Nilufar</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -39497,72 +39401,60 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr"/>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>To'ra qizi</t>
+          <t>Qayum qizi</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
+          <t>Mahmatqulova Nilufar Qayum qizi</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr"/>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE6047826</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60806085590115</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>08.06.2008</t>
         </is>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>UM 03730531</t>
-        </is>
-      </c>
-      <c r="Q13" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03754788</t>
+        </is>
+      </c>
+      <c r="Q13" s="11" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>43-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S13" s="12" t="inlineStr">
@@ -39572,20 +39464,12 @@
       </c>
       <c r="T13" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="inlineStr"/>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W13" s="15" t="inlineStr"/>
       <c r="X13" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -39603,7 +39487,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda</t>
+          <t>Mahmudova Maftuna</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -39613,7 +39497,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -39623,27 +39507,27 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Nosir qizi</t>
+          <t>To'ra qizi</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -39653,7 +39537,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -39663,22 +39547,22 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>UM 03728995</t>
+          <t>UM 03730531</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
@@ -39719,78 +39603,82 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr"/>
+          <t>Mannonova Shahrizoda</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Hasan qizi</t>
+          <t>Nosir qizi</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>07.10.2008</t>
         </is>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>UM 03718284</t>
+          <t>UM 03728995</t>
         </is>
       </c>
       <c r="Q15" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
         </is>
       </c>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
@@ -39831,82 +39719,78 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Muminova Sevinch</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Maxmarajabova Zerda</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>253</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Hasan qizi</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>AE2259069</t>
+          <t>AE5221552</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>63001085590111</t>
+          <t>60106075720246</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>09.04.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>30.01.2008</t>
+          <t>01.06.2007</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>UM 03752895</t>
+          <t>UM 03718284</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
@@ -39947,51 +39831,57 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr"/>
+          <t>Muminova Sevinch</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>46255</v>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Ulug'bek qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>AB8521319</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>62906005590060</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>02.01.2018</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>29.06.2000</t>
+          <t>30.01.2008</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
@@ -40001,28 +39891,32 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>K 5487472</t>
-        </is>
-      </c>
-      <c r="Q17" s="11" t="inlineStr"/>
+          <t>UM 03752895</t>
+        </is>
+      </c>
+      <c r="Q17" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
+        </is>
+      </c>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T17" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
@@ -40030,11 +39924,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V17" s="11" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
-        </is>
-      </c>
+      <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -40057,57 +39947,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Mustafayeva Nargiza</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>46255</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Zaxriddin qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>29.06.2000</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -40117,32 +40001,28 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>UM 03751925</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
-        </is>
-      </c>
+          <t>K 5487472</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
@@ -40150,7 +40030,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
+        </is>
+      </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -40173,7 +40057,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor</t>
+          <t>Muxtorova Xadicha</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -40183,93 +40067,93 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Zaxriddin qizi</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>AB5359926</t>
+          <t>AE2428256</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>40211995680023</t>
+          <t>60506085590066</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>12.12.2016</t>
+          <t>22.04.2025</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>02.11.1999</t>
+          <t>05.06.2008</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>K 5047841</t>
-        </is>
-      </c>
-      <c r="Q19" s="11" t="inlineStr"/>
+          <t>UM 03751925</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+        </is>
+      </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U19" s="12" t="inlineStr">
-        <is>
-          <t>To'liq</t>
-        </is>
-      </c>
-      <c r="V19" s="11" t="inlineStr">
-        <is>
-          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -40289,7 +40173,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Narziyeva Intizor</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -40299,60 +40183,68 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Turoqulovna</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Niyozova Sevara Turoqulovna</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AD9706738</t>
+          <t>AB5359926</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>412068 9256 0120</t>
+          <t>40211995680023</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>05.12.2024</t>
+          <t>12.12.2016</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>12.06.1989</t>
+          <t>02.11.1999</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>K 0998119</t>
+          <t>K 5047841</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz qishloq xo'jaligi kasb-hunar kolleji</t>
+          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -40362,22 +40254,22 @@
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U20" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>To'liq</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W20" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -40397,103 +40289,95 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr"/>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-14 00:00:00</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Mashrab qizi</t>
+          <t>Turoqulovna</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
+          <t>Niyozova Sevara Turoqulovna</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AD9494409</t>
+          <t>AD9706738</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>60504085680019</t>
+          <t>412068 9256 0120</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>26.09.2025</t>
+          <t>05.12.2024</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>05.04.2008</t>
+          <t>12.06.1989</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr"/>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q21" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
+          <t>K 0998119</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="inlineStr"/>
       <c r="R21" s="11" t="inlin